--- a/financial_models/templates/Valuation_v2.0.xlsx
+++ b/financial_models/templates/Valuation_v2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCCCF1C3-025B-4CA0-AB4C-69872314C68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43BD4BA1-65E2-4CF1-9AF6-8D236ED45627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="395">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -183,10 +183,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Contingent Liabilities</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>HKD</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -240,10 +236,6 @@
   </si>
   <si>
     <t>CAPX</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Other Data</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -952,14 +944,6 @@
   </si>
   <si>
     <t>Implied Growth Scenario Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 1: Calculate FCFE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FCFE represents the cash available to equity holders after accounting for operating expenses, reinvestments, taxes, and interest obligations.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1254,14 +1238,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 3: Calculate Equity Value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>The Equity Value adjusts the stable income value for debt and incorporates non-operating resources available to equity holders. The formula is:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -1325,58 +1301,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Purpose:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> This step ensures the equity value reflects all resources available to shareholders by deducting debt and adding excess cash and non-operating assets, avoiding double-counting of income-generating assets.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">Purpose: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>This step ensures a comprehensive measure of cash flow by incorporating both operating and stable non-operating sources while accounting for taxes and reinvestment needs.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Expected Equity Value =</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -1401,18 +1325,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Assume the Equity Value will be realized over the holding period.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Expected Holding period = </t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
   <si>
-    <t>Step 4: Scenario Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Total Cash =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1445,32 +1361,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">Guidance Note: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>This valuation method estimates the equity value of a company through a five-step process. Each step is designed to systematically derive cash flows available to equity holders, discount them appropriately, and adjust for debt and non-operating assets.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Asset Value Stress Test</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1519,23 +1409,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Calculate Target Buy Price</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>No Growth Equity Value per share =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>No Growth SIV Per Share =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 2: Calculate Stable Income Value (SIV) Using FCFE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>The Stable Income Value (SIV) represents the present value of FCFE, assuming it grows at a constant rate indefinitely. This is calculated using the Gordon Growth Model:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1663,10 +1541,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Market Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>assuming a holding period of</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1771,22 +1645,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Based on fundamental research, the following scenarios have been developed, considering driving factors of high growth periods (HGP) and high growth rates (HGR), along with their associated probabilities.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Note that this model prioritizes fundamental analysis when combined with supplementary market signal analysis. While market signal analysis predicts future trends, fundamental analysis interprets these trends and identifies relevant factors and possibilities.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SINO LAND</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>0083.HK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>WCInv is by default excluded</t>
   </si>
   <si>
@@ -1806,9 +1664,6 @@
   </si>
   <si>
     <t>Assume 0</t>
-  </si>
-  <si>
-    <t>Historical Average or D&amp;A</t>
   </si>
   <si>
     <r>
@@ -1902,58 +1757,6 @@
         <family val="2"/>
         <scheme val="major"/>
       </rPr>
-      <t>Note on Cost of Equity:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> Cost of Equity reflects the company’s risk profile, while target annual return is the investor’s hurdle rate.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Note on Terminal Growth Rate:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> Setting g=0 can be a conservative assumption to avoid overestimating the stock’s value, especially if future growth is uncertain or unreliable.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
       <t xml:space="preserve">Note on debt: </t>
     </r>
     <r>
@@ -2006,7 +1809,369 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>RES_01</t>
+    <t>六福珠宝</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0590.HK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNS_05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 2: The No-Growth Baseline (Calculating Stable Income Value)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 3: Adjusting for Financial Structure (Calculating No Growth Equity Value)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 4: Incorporating Future Potential &amp; Risk (Scenario Analysis)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision (Calculating Target Buy Price)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Implied Market Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Guidance Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>This model determines a target buy price consistent with defined investment criteria. It follows a logical progression: establishing current sustainable earnings, adjusting for financial structure, incorporating growth scenarios, and finally applying the investor’s required return.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates for its equity owners, stripping away temporary fluctuations or accounting choices.The FCFE/Market Cap yield gives a direct measure of this cash generation relative to the current market price.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Insight: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>This step ensures a comprehensive measure of cash flow by incorporating both operating and stable non-operating sources while accounting for taxes and reinvestment needs.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To determine the intrinsic value of the company’s equity if the Normalized FCFE (calculated in Step 1) were to remain constant perpetually, with zero future growth. This establishes a baseline value derived solely from the current sustainable earnings power.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Cost of Equity reflects the company’s risk profile and represents the minimum return the investor requires for taking on the general risk of owning this type of business, while the target annual return serves as the investor’s hurdle rate.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Terminal Growth Rate:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Setting g=0% is a conservative assumption, valuing the company based only on its current demonstrated earning power without relying on potentially optimistic future growth projections.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To refine the Stable Income Value (SIV) by incorporating the company’s balance sheet structure. </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Insight:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> The No Growth Equity Value per share represents an estimate of the company’s intrinsic worth based on its current sustainable operations and net financial position, before factoring in any future growth potential. It serves as a fundamentally anchored valuation baseline.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To estimate the company’s intrinsic value by considering plausible future scenarios beyond the static no-growth assumption. Based on fundamental research, each scenario defines high growth periods (HGP), high growth rates (HGR), and its probability.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>To translate our estimate of the company’s intrinsic value (from Step 4) into a concrete buy price that meets the specific investment requirements.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Calculation Logic:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Insight:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFF</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFI</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2674,7 +2839,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="349">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3377,23 +3542,24 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3683,7 +3849,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -3696,22 +3862,22 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C1" s="44">
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="337" t="s">
-        <v>390</v>
+        <v>368</v>
       </c>
       <c r="F1" s="290" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="253" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -3726,7 +3892,7 @@
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B4" s="45" t="str">
         <f>D5&amp;" Stock Information"</f>
-        <v>0083.HK Stock Information</v>
+        <v>0590.HK Stock Information</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -3735,24 +3901,24 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>7.9</v>
+        <v>15.4</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -3761,14 +3927,14 @@
         <v>0</v>
       </c>
       <c r="C7" s="51">
-        <v>8171879936</v>
+        <v>587107850</v>
       </c>
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="C8" s="285">
         <v>6</v>
@@ -3778,7 +3944,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -3794,7 +3960,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>64557.851494399998</v>
+        <v>9041.4608900000003</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -3804,37 +3970,37 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
-        <v>285</v>
-      </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="B12" s="341" t="s">
+        <v>380</v>
+      </c>
+      <c r="C12" s="341"/>
+      <c r="D12" s="341"/>
+      <c r="E12" s="341"/>
+      <c r="F12" s="341"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>385</v>
+        <v>363</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
-        <v>Negative Growth Asset Play</v>
+        <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>384</v>
+        <v>362</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -3854,16 +4020,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="C19" s="255">
         <v>0.2</v>
@@ -3876,11 +4042,11 @@
         <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="258">
-        <f>C127</f>
-        <v>6.4883606756817951</v>
+        <f>C129</f>
+        <v>16.361242554197645</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="E20" s="336">
         <v>3</v>
@@ -3888,11 +4054,11 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1185224959199922</v>
+        <v>0.22622690546409729</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3903,7 +4069,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="253" t="s">
-        <v>234</v>
+        <v>373</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -3911,49 +4077,49 @@
       <c r="E23" s="36"/>
       <c r="F23" s="36"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
-        <v>235</v>
-      </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+    <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="341" t="s">
+        <v>381</v>
+      </c>
+      <c r="C25" s="341"/>
+      <c r="D25" s="341"/>
+      <c r="E25" s="341"/>
+      <c r="F25" s="341"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="340" t="s">
-        <v>374</v>
-      </c>
-      <c r="C26" s="340"/>
-      <c r="D26" s="340"/>
-      <c r="E26" s="340"/>
-      <c r="F26" s="340"/>
+      <c r="B26" s="339" t="s">
+        <v>354</v>
+      </c>
+      <c r="C26" s="339"/>
+      <c r="D26" s="339"/>
+      <c r="E26" s="339"/>
+      <c r="F26" s="339"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C28" s="111">
         <f>Data!C3</f>
-        <v>1000000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="338" t="s">
-        <v>237</v>
-      </c>
-      <c r="C29" s="338"/>
-      <c r="D29" s="338"/>
-      <c r="E29" s="338"/>
-      <c r="F29" s="338"/>
+      <c r="B29" s="340" t="s">
+        <v>233</v>
+      </c>
+      <c r="C29" s="340"/>
+      <c r="D29" s="340"/>
+      <c r="E29" s="340"/>
+      <c r="F29" s="340"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C30" s="191">
         <f>Normalized_FCF!C8</f>
-        <v>2591.8202592374382</v>
+        <v>1876773</v>
       </c>
       <c r="D30" s="1" t="str">
         <f>Reporting_currency</f>
@@ -3965,21 +4131,21 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="338" t="s">
-        <v>239</v>
-      </c>
-      <c r="C32" s="338"/>
-      <c r="D32" s="338"/>
-      <c r="E32" s="338"/>
-      <c r="F32" s="338"/>
+      <c r="B32" s="340" t="s">
+        <v>235</v>
+      </c>
+      <c r="C32" s="340"/>
+      <c r="D32" s="340"/>
+      <c r="E32" s="340"/>
+      <c r="F32" s="340"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C33" s="191">
         <f>Normalized_FCF!C9</f>
-        <v>159.99999999999997</v>
+        <v>463424</v>
       </c>
       <c r="D33" s="1" t="str">
         <f>Reporting_currency</f>
@@ -3988,11 +4154,11 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="52" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C34" s="191">
         <f>Normalized_FCF!C10</f>
-        <v>-159.99999999999997</v>
+        <v>-676387</v>
       </c>
       <c r="D34" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4000,21 +4166,21 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="338" t="s">
-        <v>242</v>
-      </c>
-      <c r="C36" s="338"/>
-      <c r="D36" s="338"/>
-      <c r="E36" s="338"/>
-      <c r="F36" s="338"/>
+      <c r="B36" s="340" t="s">
+        <v>238</v>
+      </c>
+      <c r="C36" s="340"/>
+      <c r="D36" s="340"/>
+      <c r="E36" s="340"/>
+      <c r="F36" s="340"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C37" s="191">
         <f>Normalized_FCF!C11</f>
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="D37" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4022,21 +4188,21 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="338" t="s">
-        <v>246</v>
-      </c>
-      <c r="C39" s="338"/>
-      <c r="D39" s="338"/>
-      <c r="E39" s="338"/>
-      <c r="F39" s="338"/>
+      <c r="B39" s="340" t="s">
+        <v>242</v>
+      </c>
+      <c r="C39" s="340"/>
+      <c r="D39" s="340"/>
+      <c r="E39" s="340"/>
+      <c r="F39" s="340"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
-        <v>163.69305155463843</v>
+        <v>17217.595540639435</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4047,11 +4213,11 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
-        <v>-43</v>
+        <v>-59596</v>
       </c>
       <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4062,11 +4228,11 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="47" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
-        <v>120.69305155463843</v>
+        <v>-42378.404459360565</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4075,16 +4241,16 @@
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B44" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="C45" s="191">
         <f>Normalized_FCF!C15</f>
-        <v>-22.869707937042335</v>
+        <v>0</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4092,21 +4258,21 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="338" t="s">
-        <v>247</v>
-      </c>
-      <c r="C47" s="338"/>
-      <c r="D47" s="338"/>
-      <c r="E47" s="338"/>
-      <c r="F47" s="338"/>
+      <c r="B47" s="340" t="s">
+        <v>243</v>
+      </c>
+      <c r="C47" s="340"/>
+      <c r="D47" s="340"/>
+      <c r="E47" s="340"/>
+      <c r="F47" s="340"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
-        <v>-804.36319459009837</v>
+        <v>-458598.64888515987</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4114,17 +4280,17 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="338" t="s">
-        <v>373</v>
-      </c>
-      <c r="C50" s="342"/>
-      <c r="D50" s="342"/>
-      <c r="E50" s="342"/>
-      <c r="F50" s="342"/>
+      <c r="B50" s="340" t="s">
+        <v>353</v>
+      </c>
+      <c r="C50" s="344"/>
+      <c r="D50" s="344"/>
+      <c r="E50" s="344"/>
+      <c r="F50" s="344"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C51" s="1">
         <f>Normalized_FCF!C17</f>
@@ -4136,30 +4302,30 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
-        <v>378</v>
-      </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="B53" s="341" t="s">
+        <v>358</v>
+      </c>
+      <c r="C53" s="341"/>
+      <c r="D53" s="341"/>
+      <c r="E53" s="341"/>
+      <c r="F53" s="341"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
-        <v>267</v>
-      </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="B54" s="341" t="s">
+        <v>382</v>
+      </c>
+      <c r="C54" s="341"/>
+      <c r="D54" s="341"/>
+      <c r="E54" s="341"/>
+      <c r="F54" s="341"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
-        <v>2772.792068232593</v>
+        <v>1294904.5955406395</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4168,11 +4334,11 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B57" s="47" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
-        <v>2524.2804082649359</v>
+        <v>1162832.9466554797</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4181,25 +4347,25 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="260" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
-        <v>3.9101059744590508E-2</v>
+        <v>0.12861117918914977</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="260" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>7.3417721518987331E-2</v>
+        <v>8.8311688311688313E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="253" t="s">
-        <v>301</v>
+        <v>374</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4212,31 +4378,31 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
-        <v>302</v>
-      </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="B63" s="341" t="s">
+        <v>383</v>
+      </c>
+      <c r="C63" s="341"/>
+      <c r="D63" s="341"/>
+      <c r="E63" s="341"/>
+      <c r="F63" s="341"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="340" t="s">
-        <v>258</v>
-      </c>
-      <c r="C64" s="340"/>
-      <c r="D64" s="340"/>
-      <c r="E64" s="340"/>
-      <c r="F64" s="340"/>
+      <c r="B64" s="339" t="s">
+        <v>254</v>
+      </c>
+      <c r="C64" s="339"/>
+      <c r="D64" s="339"/>
+      <c r="E64" s="339"/>
+      <c r="F64" s="339"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="C67" s="317">
         <v>0.08</v>
@@ -4244,171 +4410,164 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="C68" s="269">
         <f>IF(D68="Y",1%,0)</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D68" s="292" t="s">
-        <v>306</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="C69" s="269">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="292" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C70" s="269">
         <f>SUM(C67:C69)</f>
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="339" t="s">
-        <v>379</v>
-      </c>
-      <c r="C72" s="339"/>
-      <c r="D72" s="339"/>
-      <c r="E72" s="339"/>
-      <c r="F72" s="339"/>
+      <c r="B72" s="338" t="s">
+        <v>375</v>
+      </c>
+      <c r="C72" s="125"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
-        <v>380</v>
-      </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B75" s="47" t="s">
-        <v>257</v>
-      </c>
-      <c r="C75" s="269">
-        <v>0</v>
-      </c>
+      <c r="B73" s="341" t="s">
+        <v>384</v>
+      </c>
+      <c r="C73" s="341"/>
+      <c r="D73" s="341"/>
+      <c r="E73" s="341"/>
+      <c r="F73" s="341"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="341" t="s">
+        <v>385</v>
+      </c>
+      <c r="C74" s="341"/>
+      <c r="D74" s="341"/>
+      <c r="E74" s="341"/>
+      <c r="F74" s="341"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
-        <v>300</v>
-      </c>
-      <c r="C76" s="254">
+        <v>253</v>
+      </c>
+      <c r="C76" s="269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B77" s="47" t="s">
+        <v>288</v>
+      </c>
+      <c r="C77" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>3.432204133136278</v>
-      </c>
-      <c r="D76" s="1" t="str">
+        <v>24.757651993911335</v>
+      </c>
+      <c r="D77" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A78" s="253" t="s">
-        <v>259</v>
-      </c>
-      <c r="B78" s="36"/>
-      <c r="C78" s="36"/>
-      <c r="D78" s="36"/>
-      <c r="E78" s="36"/>
-      <c r="F78" s="36"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" s="239"/>
-    </row>
-    <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="339" t="s">
-        <v>260</v>
-      </c>
-      <c r="C80" s="339"/>
-      <c r="D80" s="339"/>
-      <c r="E80" s="339"/>
-      <c r="F80" s="339"/>
+    <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A79" s="253" t="s">
+        <v>376</v>
+      </c>
+      <c r="B79" s="36"/>
+      <c r="C79" s="36"/>
+      <c r="D79" s="36"/>
+      <c r="E79" s="36"/>
+      <c r="F79" s="36"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="239"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B83" s="240" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="339" t="s">
-        <v>381</v>
-      </c>
-      <c r="C84" s="339"/>
-      <c r="D84" s="339"/>
-      <c r="E84" s="339"/>
-      <c r="F84" s="339"/>
-    </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B85" s="47" t="s">
-        <v>263</v>
-      </c>
-      <c r="C85" s="191">
+      <c r="B81" s="341" t="s">
+        <v>386</v>
+      </c>
+      <c r="C81" s="341"/>
+      <c r="D81" s="341"/>
+      <c r="E81" s="341"/>
+      <c r="F81" s="341"/>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B82" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B84" s="240" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B85" s="341" t="s">
+        <v>359</v>
+      </c>
+      <c r="C85" s="341"/>
+      <c r="D85" s="341"/>
+      <c r="E85" s="341"/>
+      <c r="F85" s="341"/>
+    </row>
+    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B86" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="C86" s="191">
         <f>Valuation_Model!C7</f>
-        <v>3093</v>
-      </c>
-      <c r="D85" s="1" t="str">
+        <v>2034922</v>
+      </c>
+      <c r="D86" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B86" s="47" t="s">
-        <v>303</v>
-      </c>
-      <c r="C86" s="254">
-        <f>C85*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.37849307922088393</v>
-      </c>
-      <c r="D86" s="1" t="str">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B87" s="47" t="s">
+        <v>289</v>
+      </c>
+      <c r="C87" s="254">
+        <f>C86*C28*Exchange_Rate/Common_Shares</f>
+        <v>3.4660105464438944</v>
+      </c>
+      <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B88" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B89" s="47" t="s">
-        <v>277</v>
-      </c>
-      <c r="C89" s="191">
-        <f>BS!C66</f>
-        <v>47679</v>
-      </c>
-      <c r="D89" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
+      <c r="B89" s="1" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="C90" s="191">
-        <f>Valuation_Model!C8</f>
-        <v>42222.564948178719</v>
+        <f>BS!C66</f>
+        <v>1998219</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4417,363 +4576,386 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>304</v>
-      </c>
-      <c r="C91" s="254">
-        <f>C90*C28*Exchange_Rate/Common_Shares</f>
-        <v>5.1668117102618574</v>
+        <v>269</v>
+      </c>
+      <c r="C91" s="191">
+        <f>Valuation_Model!C8</f>
+        <v>810914.36033333349</v>
       </c>
       <c r="D91" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B92" s="47" t="s">
+        <v>290</v>
+      </c>
+      <c r="C92" s="254">
+        <f>C91*C28*Exchange_Rate/Common_Shares</f>
+        <v>1.3812016997104255</v>
+      </c>
+      <c r="D92" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B93" s="1" t="s">
-        <v>264</v>
-      </c>
-    </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B94" s="47" t="s">
-        <v>265</v>
-      </c>
-      <c r="C94" s="191">
+      <c r="B94" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B95" s="47" t="s">
+        <v>259</v>
+      </c>
+      <c r="C95" s="191">
         <f>Valuation_Model!C9</f>
-        <v>7814.4</v>
-      </c>
-      <c r="D94" s="1" t="str">
+        <v>92572.6</v>
+      </c>
+      <c r="D95" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B95" s="47" t="s">
-        <v>305</v>
-      </c>
-      <c r="C95" s="254">
-        <f>C94*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.95625487173090062</v>
-      </c>
-      <c r="D95" s="1" t="str">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B96" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="C96" s="254">
+        <f>C95*C28*Exchange_Rate/Common_Shares</f>
+        <v>0.15767562978420405</v>
+      </c>
+      <c r="D96" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="339" t="s">
-        <v>266</v>
-      </c>
-      <c r="C97" s="339"/>
-      <c r="D97" s="339"/>
-      <c r="E97" s="339"/>
-      <c r="F97" s="339"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B99" s="47" t="s">
-        <v>299</v>
-      </c>
-      <c r="C99" s="254">
+    <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B98" s="341" t="s">
+        <v>387</v>
+      </c>
+      <c r="C98" s="341"/>
+      <c r="D98" s="341"/>
+      <c r="E98" s="341"/>
+      <c r="F98" s="341"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B100" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="C100" s="254">
         <f>Valuation_Model!C12</f>
-        <v>9.1767776359081505</v>
-      </c>
-      <c r="D99" s="1" t="str">
+        <v>22.830518776962066</v>
+      </c>
+      <c r="D100" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A101" s="253" t="s">
-        <v>276</v>
-      </c>
-      <c r="B101" s="36"/>
-      <c r="C101" s="36"/>
-      <c r="D101" s="36"/>
-      <c r="E101" s="36"/>
-      <c r="F101" s="36"/>
-    </row>
-    <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="338" t="s">
-        <v>361</v>
-      </c>
-      <c r="C103" s="338"/>
-      <c r="D103" s="338"/>
-      <c r="E103" s="338"/>
-      <c r="F103" s="338"/>
-    </row>
-    <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
-      <c r="B105" s="266" t="s">
-        <v>121</v>
-      </c>
-      <c r="C105" s="266" t="s">
-        <v>136</v>
-      </c>
-      <c r="D105" s="266" t="s">
-        <v>116</v>
-      </c>
-      <c r="E105" s="266" t="s">
-        <v>269</v>
-      </c>
-      <c r="F105" s="266" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B106" s="261" t="str">
+    <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A102" s="253" t="s">
+        <v>377</v>
+      </c>
+      <c r="B102" s="36"/>
+      <c r="C102" s="36"/>
+      <c r="D102" s="36"/>
+      <c r="E102" s="36"/>
+      <c r="F102" s="36"/>
+    </row>
+    <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B104" s="340" t="s">
+        <v>388</v>
+      </c>
+      <c r="C104" s="340"/>
+      <c r="D104" s="340"/>
+      <c r="E104" s="340"/>
+      <c r="F104" s="340"/>
+    </row>
+    <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+      <c r="B106" s="266" t="s">
+        <v>119</v>
+      </c>
+      <c r="C106" s="266" t="s">
+        <v>134</v>
+      </c>
+      <c r="D106" s="266" t="s">
+        <v>114</v>
+      </c>
+      <c r="E106" s="266" t="s">
+        <v>261</v>
+      </c>
+      <c r="F106" s="266" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B107" s="261" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C106" s="262">
+      <c r="C107" s="262">
         <f>Valuation_Model!C74</f>
-        <v>0.05</v>
-      </c>
-      <c r="D106" s="263">
+        <v>0.06</v>
+      </c>
+      <c r="D107" s="263">
         <f>Valuation_Model!D74</f>
-        <v>15</v>
-      </c>
-      <c r="E106" s="264" t="str">
+        <v>10</v>
+      </c>
+      <c r="E107" s="264" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>10.21 HKD</v>
-      </c>
-      <c r="F106" s="265">
+        <v>28.13 HKD</v>
+      </c>
+      <c r="F107" s="265">
         <f>Valuation_Model!F74</f>
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B107" s="248" t="str">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B108" s="248" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C107" s="249">
+      <c r="C108" s="249">
         <f>Valuation_Model!C75</f>
-        <v>0.02</v>
-      </c>
-      <c r="D107" s="250">
+        <v>0.05</v>
+      </c>
+      <c r="D108" s="250">
         <f>Valuation_Model!D75</f>
-        <v>10</v>
-      </c>
-      <c r="E107" s="251" t="str">
+        <v>5</v>
+      </c>
+      <c r="E108" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>9.41 HKD</v>
-      </c>
-      <c r="F107" s="252">
+        <v>24.87 HKD</v>
+      </c>
+      <c r="F108" s="252">
         <f>Valuation_Model!F75</f>
-        <v>0.22499999999999992</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B108" s="248" t="str">
+        <v>0.192</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B109" s="248" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C108" s="249">
+      <c r="C109" s="249">
         <f>Valuation_Model!C76</f>
-        <v>0</v>
-      </c>
-      <c r="D108" s="250">
+        <v>0.02</v>
+      </c>
+      <c r="D109" s="250">
         <f>Valuation_Model!D76</f>
-        <v>10</v>
-      </c>
-      <c r="E108" s="251" t="str">
+        <v>5</v>
+      </c>
+      <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>9.18 HKD</v>
-      </c>
-      <c r="F108" s="252">
+        <v>23.63 HKD</v>
+      </c>
+      <c r="F109" s="252">
         <f>Valuation_Model!F76</f>
-        <v>0.495</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B109" s="248" t="str">
+        <v>0.57599999999999996</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B110" s="248" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C109" s="249">
+      <c r="C110" s="249">
         <f>Valuation_Model!C77</f>
         <v>-0.05</v>
       </c>
-      <c r="D109" s="250">
+      <c r="D110" s="250">
         <f>Valuation_Model!D77</f>
-        <v>10</v>
-      </c>
-      <c r="E109" s="251" t="str">
+        <v>5</v>
+      </c>
+      <c r="E110" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>8.69 HKD</v>
-      </c>
-      <c r="F109" s="252">
+        <v>20.93 HKD</v>
+      </c>
+      <c r="F110" s="252">
         <f>Valuation_Model!F77</f>
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B110" s="248" t="str">
+        <v>0.192</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B111" s="248" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C110" s="249">
+      <c r="C111" s="249">
         <f>Valuation_Model!C78</f>
-        <v>-0.2</v>
-      </c>
-      <c r="D110" s="250">
+        <v>-0.08</v>
+      </c>
+      <c r="D111" s="250">
         <f>Valuation_Model!D78</f>
-        <v>15</v>
-      </c>
-      <c r="E110" s="251" t="str">
+        <v>10</v>
+      </c>
+      <c r="E111" s="251" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>7.34 HKD</v>
-      </c>
-      <c r="F110" s="252">
+        <v>17.72 HKD</v>
+      </c>
+      <c r="F111" s="252">
         <f>Valuation_Model!F78</f>
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B112" s="241" t="s">
-        <v>268</v>
-      </c>
-      <c r="C112" s="247">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B113" s="241" t="s">
+        <v>260</v>
+      </c>
+      <c r="C113" s="247">
         <f>Scenarios!C60</f>
-        <v>9.1006872475781417</v>
-      </c>
-      <c r="D112" s="242" t="str">
+        <v>23.321827133653532</v>
+      </c>
+      <c r="D113" s="242" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B114" s="343" t="s">
-        <v>362</v>
-      </c>
-      <c r="C114" s="343"/>
-      <c r="D114" s="343"/>
-      <c r="E114" s="343"/>
-      <c r="F114" s="343"/>
-    </row>
-    <row r="116" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A116" s="253" t="s">
-        <v>298</v>
-      </c>
-      <c r="B116" s="36"/>
-      <c r="C116" s="36"/>
-      <c r="D116" s="36"/>
-      <c r="E116" s="36"/>
-      <c r="F116" s="36"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="341" t="s">
-        <v>274</v>
-      </c>
-      <c r="C118" s="341"/>
-      <c r="D118" s="341"/>
-      <c r="E118" s="341"/>
-      <c r="F118" s="341"/>
+    <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B115" s="342" t="s">
+        <v>391</v>
+      </c>
+      <c r="C115" s="342"/>
+      <c r="D115" s="342"/>
+      <c r="E115" s="342"/>
+      <c r="F115" s="342"/>
+    </row>
+    <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A117" s="253" t="s">
+        <v>378</v>
+      </c>
+      <c r="B117" s="36"/>
+      <c r="C117" s="36"/>
+      <c r="D117" s="36"/>
+      <c r="E117" s="36"/>
+      <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="240" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B120" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C120" s="257">
+      <c r="B119" s="343" t="s">
+        <v>389</v>
+      </c>
+      <c r="C119" s="343"/>
+      <c r="D119" s="343"/>
+      <c r="E119" s="343"/>
+      <c r="F119" s="343"/>
+    </row>
+    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B120" s="341" t="s">
+        <v>390</v>
+      </c>
+      <c r="C120" s="341"/>
+      <c r="D120" s="341"/>
+      <c r="E120" s="341"/>
+      <c r="F120" s="341"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B121" s="240" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B122" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C122" s="257">
         <f>E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B121" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="C121" s="256">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B123" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C123" s="256">
         <f>C19</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B122" s="242" t="s">
-        <v>271</v>
-      </c>
-      <c r="C122" s="243">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B124" s="242" t="s">
+        <v>263</v>
+      </c>
+      <c r="C124" s="243">
         <f>Scenarios!C77</f>
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="D122" s="242" t="str">
+        <v>1.36</v>
+      </c>
+      <c r="D124" s="242" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B124" s="240" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B125" s="242" t="str">
-        <f>"PV("&amp;C120&amp;" yrs of Dividends)"</f>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B126" s="240" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B127" s="242" t="str">
+        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C125" s="246">
+      <c r="C127" s="246">
         <f>Scenarios!C81</f>
-        <v>1.2217592592592592</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B126" s="242" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C120&amp;")"</f>
+        <v>2.8648148148148147</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B128" s="242" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C126" s="246">
+      <c r="C128" s="246">
         <f>Scenarios!C82</f>
-        <v>5.2666014164225361</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B127" s="82" t="s">
-        <v>270</v>
-      </c>
-      <c r="C127" s="245">
+        <v>13.496427739382831</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B129" s="82" t="s">
+        <v>262</v>
+      </c>
+      <c r="C129" s="245">
         <f>Scenarios!C83</f>
-        <v>6.4883606756817951</v>
-      </c>
-      <c r="D127" s="47" t="str">
+        <v>16.361242554197645</v>
+      </c>
+      <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B128" s="244" t="s">
-        <v>272</v>
-      </c>
-      <c r="C128" s="94">
+    <row r="130" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B130" s="244" t="s">
+        <v>264</v>
+      </c>
+      <c r="C130" s="94">
         <f>Scenarios!F83</f>
-        <v>0.28704717576043881</v>
+        <v>0.29845794412101279</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B118:F118"/>
+  <mergeCells count="22">
+    <mergeCell ref="B120:F120"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B98:F98"/>
+    <mergeCell ref="B119:F119"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B103:F103"/>
-    <mergeCell ref="B72:F72"/>
-    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
     <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B84:F84"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B85:F85"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -4812,52 +4994,52 @@
         <v>HKD</v>
       </c>
       <c r="C1" s="107">
-        <v>45473</v>
+        <v>45382</v>
       </c>
       <c r="D1" s="38">
         <f>EOMONTH(EDATE(C1,-12),0)</f>
-        <v>45107</v>
+        <v>45016</v>
       </c>
       <c r="E1" s="38">
         <f t="shared" ref="E1:M1" si="0">EOMONTH(EDATE(D1,-12),0)</f>
-        <v>44742</v>
+        <v>44651</v>
       </c>
       <c r="F1" s="38">
         <f t="shared" si="0"/>
-        <v>44377</v>
+        <v>44286</v>
       </c>
       <c r="G1" s="38">
         <f t="shared" si="0"/>
-        <v>44012</v>
+        <v>43921</v>
       </c>
       <c r="H1" s="38">
         <f t="shared" si="0"/>
-        <v>43646</v>
+        <v>43555</v>
       </c>
       <c r="I1" s="38">
         <f t="shared" si="0"/>
-        <v>43281</v>
+        <v>43190</v>
       </c>
       <c r="J1" s="38">
         <f t="shared" si="0"/>
-        <v>42916</v>
+        <v>42825</v>
       </c>
       <c r="K1" s="38">
         <f t="shared" si="0"/>
-        <v>42551</v>
+        <v>42460</v>
       </c>
       <c r="L1" s="38">
         <f t="shared" si="0"/>
-        <v>42185</v>
+        <v>42094</v>
       </c>
       <c r="M1" s="38">
         <f t="shared" si="0"/>
-        <v>41820</v>
+        <v>41729</v>
       </c>
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -4876,7 +5058,7 @@
         <v>27</v>
       </c>
       <c r="C3" s="109">
-        <v>1000000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.35">
@@ -4884,11 +5066,9 @@
         <v>2</v>
       </c>
       <c r="C4" s="193">
-        <v>8765</v>
-      </c>
-      <c r="D4" s="184">
-        <v>11881</v>
-      </c>
+        <v>15325962</v>
+      </c>
+      <c r="D4" s="184"/>
       <c r="E4" s="184"/>
       <c r="F4" s="184"/>
       <c r="G4" s="184"/>
@@ -4901,14 +5081,12 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" s="193">
-        <v>5344</v>
-      </c>
-      <c r="D5" s="184">
-        <v>6492</v>
-      </c>
+        <v>11151623</v>
+      </c>
+      <c r="D5" s="184"/>
       <c r="E5" s="184"/>
       <c r="F5" s="184"/>
       <c r="G5" s="184"/>
@@ -4921,14 +5099,12 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C6" s="193">
-        <v>1084</v>
-      </c>
-      <c r="D6" s="184">
-        <v>1129</v>
-      </c>
+        <v>2297566</v>
+      </c>
+      <c r="D6" s="184"/>
       <c r="E6" s="184"/>
       <c r="F6" s="184"/>
       <c r="G6" s="184"/>
@@ -4941,9 +5117,11 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="70" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="194"/>
+        <v>62</v>
+      </c>
+      <c r="C7" s="194">
+        <v>2043459</v>
+      </c>
       <c r="D7" s="192"/>
       <c r="E7" s="192"/>
       <c r="F7" s="192"/>
@@ -4957,7 +5135,7 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="193"/>
       <c r="D8" s="184"/>
@@ -4973,14 +5151,12 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="40" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C9" s="193">
         <v>639</v>
       </c>
-      <c r="D9" s="184">
-        <v>927</v>
-      </c>
+      <c r="D9" s="184"/>
       <c r="E9" s="184"/>
       <c r="F9" s="184"/>
       <c r="G9" s="184"/>
@@ -4993,7 +5169,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C10" s="193"/>
       <c r="D10" s="184"/>
@@ -5009,7 +5185,7 @@
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C11" s="193"/>
       <c r="D11" s="184"/>
@@ -5028,11 +5204,9 @@
         <v>39</v>
       </c>
       <c r="C12" s="193">
-        <v>43</v>
-      </c>
-      <c r="D12" s="184">
-        <v>40.775368</v>
-      </c>
+        <v>59596</v>
+      </c>
+      <c r="D12" s="184"/>
       <c r="E12" s="184"/>
       <c r="F12" s="184"/>
       <c r="G12" s="184"/>
@@ -5045,14 +5219,12 @@
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C13" s="193">
-        <v>2340</v>
-      </c>
-      <c r="D13" s="184">
-        <v>1390.845307</v>
-      </c>
+        <v>28977</v>
+      </c>
+      <c r="D13" s="184"/>
       <c r="E13" s="184"/>
       <c r="F13" s="184"/>
       <c r="G13" s="184"/>
@@ -5065,14 +5237,12 @@
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" s="193">
-        <v>519</v>
-      </c>
-      <c r="D14" s="184">
-        <v>860.83482800000002</v>
-      </c>
+        <v>327166</v>
+      </c>
+      <c r="D14" s="184"/>
       <c r="E14" s="184"/>
       <c r="F14" s="184"/>
       <c r="G14" s="184"/>
@@ -5085,14 +5255,12 @@
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" s="195">
-        <v>4251</v>
-      </c>
-      <c r="D15" s="185">
-        <v>5880</v>
-      </c>
+        <v>1767305</v>
+      </c>
+      <c r="D15" s="185"/>
       <c r="E15" s="185"/>
       <c r="F15" s="185"/>
       <c r="G15" s="185"/>
@@ -5105,14 +5273,12 @@
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" s="193">
-        <v>-151</v>
-      </c>
-      <c r="D16" s="184">
-        <v>31</v>
-      </c>
+        <v>-9467</v>
+      </c>
+      <c r="D16" s="184"/>
       <c r="E16" s="184"/>
       <c r="F16" s="184"/>
       <c r="G16" s="184"/>
@@ -5125,20 +5291,18 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C19" s="184">
-        <v>160</v>
-      </c>
-      <c r="D19" s="184">
-        <v>198</v>
-      </c>
+        <v>463424</v>
+      </c>
+      <c r="D19" s="184"/>
       <c r="E19" s="184"/>
       <c r="F19" s="184"/>
       <c r="G19" s="184"/>
@@ -5151,14 +5315,12 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" s="184">
-        <v>69</v>
-      </c>
-      <c r="D20" s="184">
-        <v>108</v>
-      </c>
+        <v>676387</v>
+      </c>
+      <c r="D20" s="184"/>
       <c r="E20" s="184"/>
       <c r="F20" s="184"/>
       <c r="G20" s="184"/>
@@ -5171,14 +5333,12 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21" s="184">
-        <v>910</v>
-      </c>
-      <c r="D21" s="184">
-        <v>2541</v>
-      </c>
+        <v>626583</v>
+      </c>
+      <c r="D21" s="184"/>
       <c r="E21" s="184"/>
       <c r="F21" s="184"/>
       <c r="G21" s="184"/>
@@ -5190,149 +5350,165 @@
       <c r="M21" s="184"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B22" s="24" t="str">
+      <c r="B22" s="27" t="s">
+        <v>392</v>
+      </c>
+      <c r="C22" s="184"/>
+      <c r="D22" s="184"/>
+      <c r="E22" s="184"/>
+      <c r="F22" s="184"/>
+      <c r="G22" s="184"/>
+      <c r="H22" s="184"/>
+      <c r="I22" s="184"/>
+      <c r="J22" s="184"/>
+      <c r="K22" s="184"/>
+      <c r="L22" s="184"/>
+      <c r="M22" s="184"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B23" s="27" t="s">
+        <v>394</v>
+      </c>
+      <c r="C23" s="184"/>
+      <c r="D23" s="184"/>
+      <c r="E23" s="184"/>
+      <c r="F23" s="184"/>
+      <c r="G23" s="184"/>
+      <c r="H23" s="184"/>
+      <c r="I23" s="184"/>
+      <c r="J23" s="184"/>
+      <c r="K23" s="184"/>
+      <c r="L23" s="184"/>
+      <c r="M23" s="184"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B24" s="27" t="s">
+        <v>393</v>
+      </c>
+      <c r="C24" s="184"/>
+      <c r="D24" s="184"/>
+      <c r="E24" s="184"/>
+      <c r="F24" s="184"/>
+      <c r="G24" s="184"/>
+      <c r="H24" s="184"/>
+      <c r="I24" s="184"/>
+      <c r="J24" s="184"/>
+      <c r="K24" s="184"/>
+      <c r="L24" s="184"/>
+      <c r="M24" s="184"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
       </c>
-      <c r="C22" s="39">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="D22" s="39">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B24" s="16" t="s">
+      <c r="C25" s="39">
+        <v>1.36</v>
+      </c>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="9"/>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B25" s="26" t="s">
+      <c r="C27" s="9"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="186"/>
-      <c r="D25" s="184">
-        <v>7251</v>
-      </c>
-      <c r="E25" s="184"/>
-      <c r="F25" s="184"/>
-      <c r="G25" s="184"/>
-      <c r="H25" s="184"/>
-      <c r="I25" s="184"/>
-      <c r="J25" s="184"/>
-      <c r="K25" s="184"/>
-      <c r="L25" s="184"/>
-      <c r="M25" s="184"/>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B26" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="186"/>
-      <c r="D26" s="184">
-        <v>16389</v>
-      </c>
-      <c r="E26" s="184"/>
-      <c r="F26" s="184"/>
-      <c r="G26" s="184"/>
-      <c r="H26" s="184"/>
-      <c r="I26" s="184"/>
-      <c r="J26" s="184"/>
-      <c r="K26" s="184"/>
-      <c r="L26" s="184"/>
-      <c r="M26" s="184"/>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B27" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" s="185">
-        <v>14028</v>
-      </c>
-      <c r="D27" s="185">
-        <v>10902</v>
-      </c>
-      <c r="E27" s="185"/>
-      <c r="F27" s="185"/>
-      <c r="G27" s="185"/>
-      <c r="H27" s="185"/>
-      <c r="I27" s="185"/>
-      <c r="J27" s="185"/>
-      <c r="K27" s="185"/>
-      <c r="L27" s="185"/>
-      <c r="M27" s="185"/>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B28" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28" s="185">
-        <v>166316</v>
-      </c>
-      <c r="D28" s="185">
-        <v>163105</v>
-      </c>
-      <c r="E28" s="185"/>
-      <c r="F28" s="185"/>
-      <c r="G28" s="185"/>
-      <c r="H28" s="185"/>
-      <c r="I28" s="185"/>
-      <c r="J28" s="185"/>
-      <c r="K28" s="185"/>
-      <c r="L28" s="185"/>
-      <c r="M28" s="185"/>
+      <c r="C28" s="186"/>
+      <c r="D28" s="184"/>
+      <c r="E28" s="184"/>
+      <c r="F28" s="184"/>
+      <c r="G28" s="184"/>
+      <c r="H28" s="184"/>
+      <c r="I28" s="184"/>
+      <c r="J28" s="184"/>
+      <c r="K28" s="184"/>
+      <c r="L28" s="184"/>
+      <c r="M28" s="184"/>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="C29" s="184"/>
+        <v>32</v>
+      </c>
+      <c r="C29" s="186"/>
       <c r="D29" s="184"/>
       <c r="E29" s="184"/>
       <c r="F29" s="184"/>
-      <c r="G29" s="185"/>
-      <c r="H29" s="185"/>
-      <c r="I29" s="185"/>
-      <c r="J29" s="185"/>
-      <c r="K29" s="185"/>
-      <c r="L29" s="185"/>
-      <c r="M29" s="185"/>
+      <c r="G29" s="184"/>
+      <c r="H29" s="184"/>
+      <c r="I29" s="184"/>
+      <c r="J29" s="184"/>
+      <c r="K29" s="184"/>
+      <c r="L29" s="184"/>
+      <c r="M29" s="184"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B30" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="185">
+        <v>3990166</v>
+      </c>
+      <c r="D30" s="185"/>
+      <c r="E30" s="185"/>
+      <c r="F30" s="185"/>
+      <c r="G30" s="185"/>
+      <c r="H30" s="185"/>
+      <c r="I30" s="185"/>
+      <c r="J30" s="185"/>
+      <c r="K30" s="185"/>
+      <c r="L30" s="185"/>
+      <c r="M30" s="185"/>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B31" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="9"/>
+      <c r="B31" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="185">
+        <v>12863898</v>
+      </c>
+      <c r="D31" s="185"/>
+      <c r="E31" s="185"/>
+      <c r="F31" s="185"/>
+      <c r="G31" s="185"/>
+      <c r="H31" s="185"/>
+      <c r="I31" s="185"/>
+      <c r="J31" s="185"/>
+      <c r="K31" s="185"/>
+      <c r="L31" s="185"/>
+      <c r="M31" s="185"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B32" s="26" t="s">
-        <v>41</v>
+        <v>174</v>
       </c>
       <c r="C32" s="184"/>
       <c r="D32" s="184"/>
       <c r="E32" s="184"/>
       <c r="F32" s="184"/>
-      <c r="G32" s="184"/>
-      <c r="H32" s="184"/>
-      <c r="I32" s="184"/>
-      <c r="J32" s="184"/>
-      <c r="K32" s="184"/>
-      <c r="L32" s="184"/>
-      <c r="M32" s="184"/>
+      <c r="G32" s="185"/>
+      <c r="H32" s="185"/>
+      <c r="I32" s="185"/>
+      <c r="J32" s="185"/>
+      <c r="K32" s="185"/>
+      <c r="L32" s="185"/>
+      <c r="M32" s="185"/>
     </row>
     <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B34" s="36" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -5357,11 +5533,11 @@
       </c>
       <c r="C36" s="186">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
-        <v>8765</v>
-      </c>
-      <c r="D36" s="186">
+        <v>15325962</v>
+      </c>
+      <c r="D36" s="186" t="str">
         <f t="shared" si="1"/>
-        <v>11881</v>
+        <v/>
       </c>
       <c r="E36" s="186" t="str">
         <f t="shared" si="1"/>
@@ -5402,15 +5578,15 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C37" s="186">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
-        <v>-5344</v>
-      </c>
-      <c r="D37" s="186">
+        <v>-11151623</v>
+      </c>
+      <c r="D37" s="186" t="str">
         <f t="shared" si="2"/>
-        <v>-6492</v>
+        <v/>
       </c>
       <c r="E37" s="186" t="str">
         <f t="shared" si="2"/>
@@ -5451,15 +5627,15 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="31" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C38" s="187">
         <f>IF(C36="","",C36+C37)</f>
-        <v>3421</v>
-      </c>
-      <c r="D38" s="187">
+        <v>4174339</v>
+      </c>
+      <c r="D38" s="187" t="str">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
-        <v>5389</v>
+        <v/>
       </c>
       <c r="E38" s="187" t="str">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
@@ -5500,15 +5676,15 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C39" s="186">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
-        <v>-1084</v>
-      </c>
-      <c r="D39" s="186">
+        <v>-2297566</v>
+      </c>
+      <c r="D39" s="186" t="str">
         <f t="shared" si="13"/>
-        <v>-1129</v>
+        <v/>
       </c>
       <c r="E39" s="186" t="str">
         <f t="shared" si="13"/>
@@ -5549,15 +5725,15 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="70" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C40" s="188">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
-        <v>0</v>
-      </c>
-      <c r="D40" s="188">
+        <v>-2043459</v>
+      </c>
+      <c r="D40" s="188" t="str">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E40" s="188" t="str">
         <f t="shared" si="14"/>
@@ -5598,15 +5774,15 @@
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="70" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C41" s="188">
         <f>IF(C$4="","",C39-C40)</f>
-        <v>-1084</v>
-      </c>
-      <c r="D41" s="188">
+        <v>-254107</v>
+      </c>
+      <c r="D41" s="188" t="str">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
-        <v>-1129</v>
+        <v/>
       </c>
       <c r="E41" s="188" t="str">
         <f t="shared" si="15"/>
@@ -5647,15 +5823,15 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B42" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C42" s="186">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="186">
+      <c r="D42" s="186" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E42" s="186" t="str">
         <f t="shared" si="16"/>
@@ -5696,15 +5872,15 @@
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B43" s="43" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C43" s="189">
         <f>IF(C$4="","",C38+C39+C42)</f>
-        <v>2337</v>
-      </c>
-      <c r="D43" s="189">
+        <v>1876773</v>
+      </c>
+      <c r="D43" s="189" t="str">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
-        <v>4260</v>
+        <v/>
       </c>
       <c r="E43" s="189" t="str">
         <f t="shared" si="17"/>
@@ -5745,15 +5921,15 @@
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="43" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C44" s="190">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
-        <v>136</v>
-      </c>
-      <c r="D44" s="190">
+        <v>248317</v>
+      </c>
+      <c r="D44" s="190" t="str">
         <f t="shared" si="18"/>
-        <v>1130.764889</v>
+        <v/>
       </c>
       <c r="E44" s="190" t="str">
         <f t="shared" si="18"/>
@@ -5794,15 +5970,15 @@
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="40" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C45" s="191">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
-        <v>2297</v>
-      </c>
-      <c r="D45" s="191">
+        <v>-30619</v>
+      </c>
+      <c r="D45" s="191" t="str">
         <f t="shared" si="19"/>
-        <v>1350.069939</v>
+        <v/>
       </c>
       <c r="E45" s="191" t="str">
         <f t="shared" si="19"/>
@@ -5843,15 +6019,15 @@
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C46" s="186">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
-        <v>-519</v>
-      </c>
-      <c r="D46" s="186">
+        <v>-327166</v>
+      </c>
+      <c r="D46" s="186" t="str">
         <f t="shared" si="20"/>
-        <v>-860.83482800000002</v>
+        <v/>
       </c>
       <c r="E46" s="186" t="str">
         <f t="shared" si="20"/>
@@ -5892,15 +6068,15 @@
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C47" s="189">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
-        <v>4251</v>
-      </c>
-      <c r="D47" s="189">
+        <v>1767305</v>
+      </c>
+      <c r="D47" s="189" t="str">
         <f t="shared" si="21"/>
-        <v>5880</v>
+        <v/>
       </c>
       <c r="E47" s="189" t="str">
         <f t="shared" si="21"/>
@@ -5941,15 +6117,15 @@
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B48" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C48" s="186">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>0</v>
       </c>
-      <c r="D48" s="186">
+      <c r="D48" s="186" t="str">
         <f t="shared" si="22"/>
-        <v>-31</v>
+        <v/>
       </c>
       <c r="E48" s="186" t="str">
         <f t="shared" si="22"/>
@@ -5990,7 +6166,7 @@
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B50" s="16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.35">
@@ -5999,11 +6175,11 @@
       </c>
       <c r="C51" s="186">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
-        <v>-43</v>
-      </c>
-      <c r="D51" s="186">
+        <v>-59596</v>
+      </c>
+      <c r="D51" s="186" t="str">
         <f t="shared" si="23"/>
-        <v>-40.775368</v>
+        <v/>
       </c>
       <c r="E51" s="186" t="str">
         <f t="shared" si="23"/>
@@ -6044,15 +6220,15 @@
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B52" s="40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C52" s="186">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
-        <v>2340</v>
-      </c>
-      <c r="D52" s="186">
+        <v>28977</v>
+      </c>
+      <c r="D52" s="186" t="str">
         <f t="shared" si="24"/>
-        <v>1390.845307</v>
+        <v/>
       </c>
       <c r="E52" s="186" t="str">
         <f t="shared" si="24"/>
@@ -6093,20 +6269,20 @@
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B54" s="178" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B55" s="40" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C55" s="191">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
         <v>639</v>
       </c>
-      <c r="D55" s="191">
+      <c r="D55" s="191" t="str">
         <f t="shared" si="25"/>
-        <v>927</v>
+        <v/>
       </c>
       <c r="E55" s="191" t="str">
         <f t="shared" si="25"/>
@@ -6147,15 +6323,15 @@
     </row>
     <row r="56" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B56" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C56" s="191">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
         <v>0</v>
       </c>
-      <c r="D56" s="191">
+      <c r="D56" s="191" t="str">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="E56" s="191" t="str">
         <f t="shared" si="26"/>
@@ -6196,15 +6372,15 @@
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C57" s="191">
-        <f>IF(C$4="","",C11)</f>
+        <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
         <v>0</v>
       </c>
-      <c r="D57" s="191">
-        <f t="shared" ref="D57:M57" si="27">IF(D$4="","",D11)</f>
-        <v>0</v>
+      <c r="D57" s="191" t="str">
+        <f t="shared" si="27"/>
+        <v/>
       </c>
       <c r="E57" s="191" t="str">
         <f t="shared" si="27"/>
@@ -6245,15 +6421,15 @@
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B58" s="40" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C58" s="191">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
-        <v>-503</v>
-      </c>
-      <c r="D58" s="191">
+        <v>247678</v>
+      </c>
+      <c r="D58" s="191" t="str">
         <f t="shared" ref="D58:M58" si="28">IF(D$4="","",D44-D55-D56-D57)</f>
-        <v>203.76488900000004</v>
+        <v/>
       </c>
       <c r="E58" s="191" t="str">
         <f t="shared" si="28"/>
@@ -6294,21 +6470,21 @@
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B60" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B61" s="27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C61" s="186">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
-        <v>-160</v>
-      </c>
-      <c r="D61" s="186">
+        <v>-463424</v>
+      </c>
+      <c r="D61" s="186" t="str">
         <f t="shared" si="29"/>
-        <v>-198</v>
+        <v/>
       </c>
       <c r="E61" s="186" t="str">
         <f t="shared" si="29"/>
@@ -6349,15 +6525,15 @@
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B62" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C62" s="186">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
-        <v>-69</v>
-      </c>
-      <c r="D62" s="186">
+        <v>-676387</v>
+      </c>
+      <c r="D62" s="186" t="str">
         <f t="shared" si="30"/>
-        <v>-108</v>
+        <v/>
       </c>
       <c r="E62" s="186" t="str">
         <f t="shared" si="30"/>
@@ -6398,15 +6574,15 @@
     </row>
     <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B63" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C63" s="186">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
-        <v>-910</v>
-      </c>
-      <c r="D63" s="186">
+        <v>-626583</v>
+      </c>
+      <c r="D63" s="186" t="str">
         <f t="shared" si="31"/>
-        <v>-2541</v>
+        <v/>
       </c>
       <c r="E63" s="186" t="str">
         <f t="shared" si="31"/>
@@ -6450,12 +6626,12 @@
         <v>36</v>
       </c>
       <c r="C64" s="75">
-        <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C22)</f>
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="D64" s="75">
+        <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C25)</f>
+        <v>1.36</v>
+      </c>
+      <c r="D64" s="75" t="str">
         <f t="shared" si="32"/>
-        <v>0.57999999999999996</v>
+        <v/>
       </c>
       <c r="E64" s="75" t="str">
         <f t="shared" si="32"/>
@@ -6496,7 +6672,7 @@
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B66" s="93" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="67" spans="2:13" x14ac:dyDescent="0.35">
@@ -6504,9 +6680,9 @@
         <f>B36</f>
         <v>Sales</v>
       </c>
-      <c r="C67" s="94">
+      <c r="C67" s="94" t="str">
         <f t="shared" ref="C67:M67" si="33">IF(D$36="","",C36/D36-1)</f>
-        <v>-0.26226748590186011</v>
+        <v/>
       </c>
       <c r="D67" s="94" t="str">
         <f t="shared" si="33"/>
@@ -6554,9 +6730,9 @@
         <f>B43</f>
         <v>Operating EBIT</v>
       </c>
-      <c r="C68" s="104">
+      <c r="C68" s="104" t="str">
         <f t="shared" ref="C68:M68" si="34">IF(D$36="","",C37/D37-1)</f>
-        <v>-0.17683302526186073</v>
+        <v/>
       </c>
       <c r="D68" s="104" t="str">
         <f t="shared" si="34"/>
@@ -6604,9 +6780,9 @@
         <f>B58</f>
         <v>Other Non-operating Income</v>
       </c>
-      <c r="C69" s="94">
+      <c r="C69" s="94" t="str">
         <f t="shared" ref="C69:M69" si="35">IF(D$36="","",C38/D38-1)</f>
-        <v>-0.36518834663202826</v>
+        <v/>
       </c>
       <c r="D69" s="94" t="str">
         <f t="shared" si="35"/>
@@ -6654,9 +6830,9 @@
         <f>B47</f>
         <v>Reported Net Income</v>
       </c>
-      <c r="C70" s="104">
+      <c r="C70" s="104" t="str">
         <f t="shared" ref="C70:M70" si="36">IF(D$36="","",C39/D39-1)</f>
-        <v>-3.9858281665190454E-2</v>
+        <v/>
       </c>
       <c r="D70" s="104" t="str">
         <f t="shared" si="36"/>
@@ -6704,9 +6880,9 @@
         <f>B48</f>
         <v>Non-controling Interests</v>
       </c>
-      <c r="C71" s="94">
+      <c r="C71" s="94" t="str">
         <f>IF(D$36="","",C64/D64-1)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D71" s="94" t="str">
         <f t="shared" ref="D71:M71" si="37">IF(E$36="","",D64/E64-1)</f>
@@ -6751,7 +6927,7 @@
     </row>
     <row r="73" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B73" s="36" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C73" s="37"/>
       <c r="D73" s="37"/>
@@ -6777,11 +6953,11 @@
       </c>
       <c r="C75" s="78">
         <f>IF(C$4="","",C78+C79)</f>
-        <v>180344</v>
-      </c>
-      <c r="D75" s="78">
+        <v>16854064</v>
+      </c>
+      <c r="D75" s="78" t="str">
         <f t="shared" ref="D75:M75" si="38">IF(D$4="","",D78+D79)</f>
-        <v>174007</v>
+        <v/>
       </c>
       <c r="E75" s="78" t="str">
         <f t="shared" si="38"/>
@@ -6822,15 +6998,15 @@
     </row>
     <row r="76" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B76" s="95" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C76" s="74">
-        <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C25)</f>
+        <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C28)</f>
         <v>0</v>
       </c>
-      <c r="D76" s="74">
+      <c r="D76" s="74" t="str">
         <f t="shared" si="39"/>
-        <v>7251</v>
+        <v/>
       </c>
       <c r="E76" s="74" t="str">
         <f t="shared" si="39"/>
@@ -6856,15 +7032,15 @@
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="95" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C77" s="74">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="D77" s="74">
+      <c r="D77" s="74" t="str">
         <f t="shared" si="39"/>
-        <v>16389</v>
+        <v/>
       </c>
       <c r="E77" s="74" t="str">
         <f t="shared" si="39"/>
@@ -6893,12 +7069,12 @@
         <v>40</v>
       </c>
       <c r="C78" s="58">
-        <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C27)</f>
-        <v>14028</v>
-      </c>
-      <c r="D78" s="58">
+        <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C30)</f>
+        <v>3990166</v>
+      </c>
+      <c r="D78" s="58" t="str">
         <f t="shared" si="40"/>
-        <v>10902</v>
+        <v/>
       </c>
       <c r="E78" s="58" t="str">
         <f t="shared" si="40"/>
@@ -6942,12 +7118,12 @@
         <v>30</v>
       </c>
       <c r="C79" s="58">
-        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C28)</f>
-        <v>166316</v>
-      </c>
-      <c r="D79" s="58">
+        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C31)</f>
+        <v>12863898</v>
+      </c>
+      <c r="D79" s="58" t="str">
         <f t="shared" si="41"/>
-        <v>163105</v>
+        <v/>
       </c>
       <c r="E79" s="58" t="str">
         <f t="shared" si="41"/>
@@ -6988,14 +7164,14 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C4:M16 C19:M22 C32:M32 C39:M43 C45:M48 C51:M52 C55:M58 C76:H77 C78:M79">
+  <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C76:H77 C78:M79">
     <cfRule type="expression" dxfId="5" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C25:M29">
+  <conditionalFormatting sqref="C28:M32">
     <cfRule type="expression" dxfId="4" priority="1">
-      <formula>ISBLANK(C25)</formula>
+      <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:M37 C61:M64">
@@ -7038,16 +7214,16 @@
       </c>
       <c r="F1" s="88" t="str">
         <f>IF(MONTH(C1)=MONTH(Normalized_FCF!G1),"FY","Quarter")&amp;" Report"</f>
-        <v>FY Report</v>
+        <v>Quarter Report</v>
       </c>
       <c r="H1" s="110">
         <f>Data!C3</f>
-        <v>1000000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="81" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7058,19 +7234,19 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C3" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D3" s="210" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G3" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H3" s="210" t="s">
         <v>35</v>
@@ -7081,17 +7257,17 @@
         <v>24</v>
       </c>
       <c r="C4" s="19">
-        <v>8029</v>
+        <v>265773</v>
       </c>
       <c r="D4" s="300">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G4" s="19">
-        <v>45665</v>
+        <v>1998219</v>
       </c>
       <c r="H4" s="300">
         <v>0.9</v>
@@ -7112,7 +7288,7 @@
         <v>29</v>
       </c>
       <c r="G5" s="19">
-        <v>2014</v>
+        <v>0</v>
       </c>
       <c r="H5" s="300">
         <v>0.7</v>
@@ -7123,17 +7299,17 @@
         <v>10</v>
       </c>
       <c r="C6" s="19">
-        <v>9844</v>
+        <v>9672256</v>
       </c>
       <c r="D6" s="300">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G6" s="19">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H6" s="300">
         <v>0.6</v>
@@ -7141,17 +7317,17 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" s="19">
-        <v>5466</v>
+        <v>0</v>
       </c>
       <c r="D7" s="300">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -7162,7 +7338,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -7172,7 +7348,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -7186,14 +7362,14 @@
         <v>25</v>
       </c>
       <c r="C9" s="19">
-        <v>0</v>
+        <v>366595</v>
       </c>
       <c r="D9" s="300">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -7207,7 +7383,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="19">
-        <v>10</v>
+        <v>29465</v>
       </c>
       <c r="D10" s="300">
         <v>0.9</v>
@@ -7228,26 +7404,26 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C12" s="83">
         <f>SUM(C4:C11)</f>
-        <v>23349</v>
+        <v>10334089</v>
       </c>
       <c r="D12" s="20">
         <f>C4*D4+C5*D5+C9*D9+C6*D6+C8*D8+C7*D7+C10*D10+C11*D11</f>
-        <v>13028</v>
+        <v>5058769.8</v>
       </c>
       <c r="F12" s="82" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G12" s="83">
         <f>SUM(G4:G9)</f>
-        <v>47835</v>
+        <v>1998219</v>
       </c>
       <c r="H12" s="20">
         <f>G4*H4+G5*H5+G6*H6+G7*H7+G8*H8+G9*H9</f>
-        <v>42601.9</v>
+        <v>1798397.1</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7257,19 +7433,19 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C14" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D14" s="210" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G14" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H14" s="210" t="s">
         <v>35</v>
@@ -7277,16 +7453,16 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C15" s="19">
-        <v>2757</v>
+        <v>103050</v>
       </c>
       <c r="D15" s="300">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
@@ -7306,10 +7482,10 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G16" s="19">
-        <v>1373</v>
+        <v>0</v>
       </c>
       <c r="H16" s="300">
         <v>0.6</v>
@@ -7317,19 +7493,19 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C17" s="19">
-        <v>67668</v>
+        <v>0</v>
       </c>
       <c r="D17" s="300">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G17" s="19">
-        <v>13024</v>
+        <v>0</v>
       </c>
       <c r="H17" s="300">
         <v>0.6</v>
@@ -7337,7 +7513,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -7346,10 +7522,10 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G18" s="19">
-        <v>23696</v>
+        <v>0</v>
       </c>
       <c r="H18" s="300">
         <v>0.1</v>
@@ -7360,13 +7536,13 @@
         <v>26</v>
       </c>
       <c r="C19" s="19">
-        <v>1284</v>
+        <v>2522337</v>
       </c>
       <c r="D19" s="300">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -7386,7 +7562,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -7400,16 +7576,16 @@
         <v>19</v>
       </c>
       <c r="C21" s="19">
-        <v>0</v>
+        <v>538321</v>
       </c>
       <c r="D21" s="300">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G21" s="19">
-        <v>0</v>
+        <v>925726</v>
       </c>
       <c r="H21" s="300">
         <v>0.1</v>
@@ -7420,7 +7596,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="19">
-        <v>10</v>
+        <v>154648</v>
       </c>
       <c r="D22" s="300">
         <v>0.9</v>
@@ -7432,7 +7608,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="19">
-        <v>0</v>
+        <v>277674</v>
       </c>
       <c r="D23" s="300">
         <v>0</v>
@@ -7441,40 +7617,40 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C24" s="83">
         <f>SUM(C15:C23)</f>
-        <v>71719</v>
+        <v>3596030</v>
       </c>
       <c r="D24" s="20">
         <f>C15*D15+C16*D16+C18*D18+C17*D17+C19*D19+C20*D20+C21*D21+C22*D22+C23*D23</f>
-        <v>41841</v>
+        <v>459552.95</v>
       </c>
       <c r="F24" s="82" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G24" s="83">
         <f>SUM(G15:G21)</f>
-        <v>38093</v>
+        <v>925726</v>
       </c>
       <c r="H24" s="20">
         <f>G15*H15+G16*H16+G17*H17+G18*H18+G19*H19+G20*H20+G21*H21</f>
-        <v>11007.8</v>
+        <v>92572.6</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="16" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C26" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F26" s="211" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G26" s="212" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H26" s="213" t="s">
         <v>35</v>
@@ -7485,18 +7661,18 @@
         <v>5</v>
       </c>
       <c r="C27" s="19">
-        <v>967</v>
+        <v>1427805</v>
       </c>
       <c r="F27" s="214" t="s">
         <v>30</v>
       </c>
       <c r="G27" s="87">
         <f>G32-G30</f>
-        <v>167107</v>
+        <v>12863898</v>
       </c>
       <c r="H27" s="215">
         <f>H32-G30</f>
-        <v>94589.7</v>
+        <v>3419126.45</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7504,13 +7680,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="19">
-        <v>37</v>
+        <v>287697</v>
       </c>
       <c r="F28" s="216" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G28" s="184">
-        <v>519</v>
+        <v>-26962</v>
       </c>
       <c r="H28" s="215"/>
     </row>
@@ -7522,15 +7698,15 @@
         <v>0</v>
       </c>
       <c r="F29" s="217" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
-        <v>166588</v>
+        <v>12890860</v>
       </c>
       <c r="H29" s="215">
         <f>H27-G28</f>
-        <v>94070.7</v>
+        <v>3446088.45</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7545,24 +7721,24 @@
       </c>
       <c r="G30" s="87">
         <f>C33+C42</f>
-        <v>13889</v>
+        <v>3990166</v>
       </c>
       <c r="H30" s="215"/>
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="82" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C31" s="83">
         <f>SUM(C27:C30)</f>
-        <v>1004</v>
+        <v>1715502</v>
       </c>
       <c r="F31" s="217" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G31" s="218">
         <f>C31+C40</f>
-        <v>3093</v>
+        <v>2034922</v>
       </c>
       <c r="H31" s="215"/>
     </row>
@@ -7572,18 +7748,18 @@
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
-        <v>8048</v>
+        <v>1801307</v>
       </c>
       <c r="F32" s="219" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G32" s="220">
         <f>G35+G40</f>
-        <v>180996</v>
+        <v>16854064</v>
       </c>
       <c r="H32" s="215">
         <f>H35+H40</f>
-        <v>108478.7</v>
+        <v>7409292.4500000002</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7591,7 +7767,7 @@
         <v>4</v>
       </c>
       <c r="C33" s="86">
-        <v>9052</v>
+        <v>3516809</v>
       </c>
       <c r="F33" s="221"/>
       <c r="G33" s="2"/>
@@ -7601,10 +7777,10 @@
       <c r="B34" s="85"/>
       <c r="C34" s="86"/>
       <c r="F34" s="223" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G34" s="224" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H34" s="225" t="s">
         <v>35</v>
@@ -7612,21 +7788,21 @@
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C35" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F35" s="226" t="s">
         <v>31</v>
       </c>
       <c r="G35" s="220">
         <f>C12+C24</f>
-        <v>95068</v>
+        <v>13930119</v>
       </c>
       <c r="H35" s="227">
         <f>D12+D24</f>
-        <v>54869</v>
+        <v>5518322.75</v>
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7634,14 +7810,14 @@
         <v>13</v>
       </c>
       <c r="C36" s="19">
-        <v>832</v>
+        <v>0</v>
       </c>
       <c r="F36" s="217" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G36" s="218">
         <f>C4+C15</f>
-        <v>10786</v>
+        <v>368823</v>
       </c>
       <c r="H36" s="222"/>
     </row>
@@ -7650,14 +7826,14 @@
         <v>14</v>
       </c>
       <c r="C37" s="19">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F37" s="217" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G37" s="218">
         <f>C6</f>
-        <v>9844</v>
+        <v>9672256</v>
       </c>
       <c r="H37" s="222"/>
     </row>
@@ -7666,14 +7842,14 @@
         <v>15</v>
       </c>
       <c r="C38" s="19">
-        <v>1230</v>
+        <v>319420</v>
       </c>
       <c r="F38" s="217" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G38" s="218">
         <f>C7+C17</f>
-        <v>73134</v>
+        <v>0</v>
       </c>
       <c r="H38" s="222"/>
     </row>
@@ -7685,35 +7861,35 @@
         <v>0</v>
       </c>
       <c r="F39" s="217" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G39" s="218">
         <f>C7+C17+C19+C20</f>
-        <v>74418</v>
+        <v>2522337</v>
       </c>
       <c r="H39" s="215">
         <f>C7*D7+C17*D17+C19*D19+C20*D20</f>
-        <v>44008.799999999996</v>
+        <v>252233.7</v>
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="82" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C40" s="83">
         <f>SUM(C36:C39)</f>
-        <v>2089</v>
+        <v>319420</v>
       </c>
       <c r="F40" s="226" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G40" s="220">
         <f>G12+G24</f>
-        <v>85928</v>
+        <v>2923945</v>
       </c>
       <c r="H40" s="227">
         <f>H12+H24</f>
-        <v>53609.7</v>
+        <v>1890969.7000000002</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7722,18 +7898,18 @@
       </c>
       <c r="C41" s="21">
         <f>C42-C40</f>
-        <v>2748</v>
+        <v>153937</v>
       </c>
       <c r="F41" s="217" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G41" s="218">
         <f>C70</f>
-        <v>72904</v>
+        <v>1998219</v>
       </c>
       <c r="H41" s="227">
         <f>H40-H42</f>
-        <v>45795.299999999996</v>
+        <v>1798397.1</v>
       </c>
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7741,23 +7917,23 @@
         <v>22</v>
       </c>
       <c r="C42" s="86">
-        <v>4837</v>
+        <v>473357</v>
       </c>
       <c r="F42" s="228" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G42" s="229">
         <f>C82</f>
-        <v>13024</v>
+        <v>925726</v>
       </c>
       <c r="H42" s="230">
         <f>D82</f>
-        <v>7814.4</v>
+        <v>92572.6</v>
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="81" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -7768,29 +7944,29 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="C45" s="267" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D45" s="209" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="F45" s="293" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="C46" s="191">
         <f>G29</f>
-        <v>166588</v>
+        <v>12890860</v>
       </c>
       <c r="D46" s="191">
         <f>H29</f>
-        <v>94070.7</v>
+        <v>3446088.45</v>
       </c>
       <c r="F46" s="289"/>
     </row>
@@ -7801,11 +7977,11 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>20.385517323391081</v>
+        <v>21.956545121990789</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>11.511512740854835</v>
+        <v>5.8696003638854428</v>
       </c>
       <c r="F47" s="289"/>
     </row>
@@ -7814,39 +7990,39 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="161" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C49" s="268" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D49" s="224" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="289"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C50" s="98">
         <f>G31/Normalized_FCF!C8</f>
-        <v>1.1933697905849452</v>
+        <v>1.0842664509772892</v>
       </c>
       <c r="D50" s="98">
         <f>G31/Normalized_FCF!G8</f>
-        <v>1.3234916559691912</v>
+        <v>1.0842664509772892</v>
       </c>
       <c r="F50" s="289"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C51" s="208"/>
       <c r="D51" s="94">
         <f>G29/G32</f>
-        <v>0.92039603085151056</v>
+        <v>0.76485172952944758</v>
       </c>
       <c r="F51" s="289"/>
     </row>
@@ -7855,41 +8031,41 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="161" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C53" s="268" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D53" s="224" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F53" s="289"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C54" s="94">
         <f>Normalized_FCF!C8/G35</f>
-        <v>2.7262804090098017E-2</v>
+        <v>0.13472770763839131</v>
       </c>
       <c r="D54" s="94">
         <f>Normalized_FCF!G8/G35</f>
-        <v>2.4582404173854506E-2</v>
+        <v>0.13472770763839131</v>
       </c>
       <c r="F54" s="289"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C11/G40</f>
-        <v>7.4364584303137507E-3</v>
+        <v>0</v>
       </c>
       <c r="D55" s="94">
         <f>Normalized_FCF!G11/G40</f>
-        <v>7.4364584303137507E-3</v>
+        <v>2.1854036242131779E-4</v>
       </c>
       <c r="F55" s="289"/>
     </row>
@@ -7898,35 +8074,35 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="161" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C57" s="268" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D57" s="224" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F57" s="289"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C58" s="101"/>
       <c r="D58" s="23">
         <f>Normalized_FCF!G9/BS!$G$39</f>
-        <v>2.1500174688919346E-3</v>
+        <v>0.1837280268259158</v>
       </c>
       <c r="F58" s="5"/>
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C59" s="101"/>
       <c r="D59" s="94">
         <f>G39/G32</f>
-        <v>0.41115825764105285</v>
+        <v>0.14965749507062509</v>
       </c>
       <c r="F59" s="289"/>
     </row>
@@ -7935,35 +8111,35 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="161" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C61" s="268" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D61" s="224" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F61" s="289"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C62" s="94">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
-        <v>3.1154705020769802E-3</v>
+        <v>0</v>
       </c>
       <c r="D62" s="94">
         <f>G28/G29</f>
-        <v>3.1154705020769802E-3</v>
+        <v>-2.0915594459950692E-3</v>
       </c>
       <c r="F62" s="289" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="81" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -7974,57 +8150,57 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C65" s="267" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D65" s="210" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="F65" s="293" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="108" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
-        <v>47679</v>
+        <v>1998219</v>
       </c>
       <c r="D66" s="191">
         <f>C66-D75</f>
-        <v>42222.564948178719</v>
+        <v>810914.36033333349</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="108" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
-        <v>1529</v>
+        <v>0</v>
       </c>
       <c r="F67" s="289"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
-        <v>23696</v>
+        <v>0</v>
       </c>
       <c r="F68" s="289"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -8034,11 +8210,11 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C70" s="83">
         <f>SUM(C66:C69)</f>
-        <v>72904</v>
+        <v>1998219</v>
       </c>
       <c r="F70" s="289"/>
     </row>
@@ -8047,72 +8223,72 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="291" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="C72" s="267" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D72" s="209" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F72" s="289"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-930.64086357333326</v>
+        <v>-1187304.6396666665</v>
       </c>
       <c r="D73" s="191">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-909.4058419702136</v>
+        <v>-1187304.6396666665</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>388</v>
+        <v>366</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="294" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="C74" s="295">
         <f>-$C$66/C73</f>
-        <v>51.232437631128107</v>
+        <v>1.6829876118070222</v>
       </c>
       <c r="D74" s="295">
         <f>-$C$66/D73</f>
-        <v>52.428737313479523</v>
+        <v>1.6829876118070222</v>
       </c>
       <c r="F74" s="289" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="C75" s="299"/>
       <c r="D75" s="298">
         <f>MAX(-D73*D76,G5)</f>
-        <v>5456.4350518212814</v>
+        <v>1187304.6396666665</v>
       </c>
       <c r="F75" s="289" t="s">
-        <v>389</v>
+        <v>367</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="296" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="C76" s="297"/>
       <c r="D76" s="333">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F76" s="289" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8120,10 +8296,10 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C78" s="267" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D78" s="210" t="s">
         <v>35</v>
@@ -8132,21 +8308,21 @@
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
-        <v>13024</v>
+        <v>0</v>
       </c>
       <c r="D79" s="191">
         <f>G7*H7+G17*H17</f>
-        <v>7814.4</v>
+        <v>0</v>
       </c>
       <c r="F79" s="289"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -8160,35 +8336,35 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
-        <v>0</v>
+        <v>925726</v>
       </c>
       <c r="D81" s="191">
         <f>G9*H9+G21*H21</f>
-        <v>0</v>
+        <v>92572.6</v>
       </c>
       <c r="F81" s="289"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C82" s="83">
         <f>SUM(C79:C81)</f>
-        <v>13024</v>
+        <v>925726</v>
       </c>
       <c r="D82" s="83">
         <f>SUM(D79:D81)</f>
-        <v>7814.4</v>
+        <v>92572.6</v>
       </c>
       <c r="F82" s="289"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8199,23 +8375,23 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="D85" s="276" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="273" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-3093</v>
+        <v>-2034922</v>
       </c>
       <c r="D86" s="254">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-0.37849307922088393</v>
+        <v>-3.4660105464438944</v>
       </c>
       <c r="E86" s="275" t="str">
         <f>Market_currency</f>
@@ -8224,15 +8400,15 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="273" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>42222.564948178719</v>
+        <v>810914.36033333349</v>
       </c>
       <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
-        <v>5.1668117102618574</v>
+        <v>1.3812016997104255</v>
       </c>
       <c r="E87" s="275" t="str">
         <f>Market_currency</f>
@@ -8241,15 +8417,15 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B88" s="274" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>7814.4</v>
+        <v>92572.6</v>
       </c>
       <c r="D88" s="254">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.95625487173090062</v>
+        <v>0.15767562978420405</v>
       </c>
       <c r="E88" s="275" t="str">
         <f>Market_currency</f>
@@ -8258,15 +8434,15 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
-        <v>46943.96494817872</v>
+        <v>-1131435.0396666664</v>
       </c>
       <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
-        <v>5.7445735027718738</v>
+        <v>-1.9271332169492648</v>
       </c>
       <c r="E89" s="275" t="str">
         <f>Market_currency</f>
@@ -8306,65 +8482,65 @@
         <v>HKD</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
       <c r="F1" s="53"/>
       <c r="G1" s="38">
         <f>Data!C1</f>
-        <v>45473</v>
+        <v>45382</v>
       </c>
       <c r="H1" s="38">
         <f>EOMONTH(EDATE(G1,-12),0)</f>
-        <v>45107</v>
+        <v>45016</v>
       </c>
       <c r="I1" s="38">
         <f t="shared" ref="I1:Q1" si="0">EOMONTH(EDATE(H1,-12),0)</f>
-        <v>44742</v>
+        <v>44651</v>
       </c>
       <c r="J1" s="38">
         <f t="shared" si="0"/>
-        <v>44377</v>
+        <v>44286</v>
       </c>
       <c r="K1" s="38">
         <f t="shared" si="0"/>
-        <v>44012</v>
+        <v>43921</v>
       </c>
       <c r="L1" s="38">
         <f t="shared" si="0"/>
-        <v>43646</v>
+        <v>43555</v>
       </c>
       <c r="M1" s="38">
         <f t="shared" si="0"/>
-        <v>43281</v>
+        <v>43190</v>
       </c>
       <c r="N1" s="38">
         <f t="shared" si="0"/>
-        <v>42916</v>
+        <v>42825</v>
       </c>
       <c r="O1" s="38">
         <f t="shared" si="0"/>
-        <v>42551</v>
+        <v>42460</v>
       </c>
       <c r="P1" s="38">
         <f t="shared" si="0"/>
-        <v>42185</v>
+        <v>42094</v>
       </c>
       <c r="Q1" s="38">
         <f t="shared" si="0"/>
-        <v>41820</v>
+        <v>41729</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -8382,11 +8558,11 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C3" s="110">
         <f>Data!C3</f>
-        <v>1000000</v>
+        <v>1000</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="308"/>
@@ -8399,19 +8575,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="196">
-        <f>G4</f>
-        <v>8765</v>
+        <f>AVERAGE(G4:J4)</f>
+        <v>15325962</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="306"/>
       <c r="F4" s="57"/>
       <c r="G4" s="186">
         <f>Data!C36</f>
-        <v>8765</v>
-      </c>
-      <c r="H4" s="186">
+        <v>15325962</v>
+      </c>
+      <c r="H4" s="186" t="str">
         <f>Data!D36</f>
-        <v>11881</v>
+        <v/>
       </c>
       <c r="I4" s="186" t="str">
         <f>Data!E36</f>
@@ -8453,20 +8629,20 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" s="197">
         <f>C25</f>
-        <v>-5066.6797407625618</v>
+        <v>-13195082</v>
       </c>
       <c r="E5" s="308"/>
       <c r="G5" s="186">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
-        <v>-5344</v>
-      </c>
-      <c r="H5" s="186">
+        <v>-13195082</v>
+      </c>
+      <c r="H5" s="186" t="str">
         <f t="shared" si="1"/>
-        <v>-6492</v>
+        <v/>
       </c>
       <c r="I5" s="186" t="str">
         <f t="shared" si="1"/>
@@ -8508,20 +8684,20 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6" s="187">
         <f>C4+C5</f>
-        <v>3698.3202592374382</v>
+        <v>2130880</v>
       </c>
       <c r="E6" s="308"/>
       <c r="G6" s="187">
         <f>IF(G4="","",G4+G5)</f>
-        <v>3421</v>
-      </c>
-      <c r="H6" s="187">
+        <v>2130880</v>
+      </c>
+      <c r="H6" s="187" t="str">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
-        <v>5389</v>
+        <v/>
       </c>
       <c r="I6" s="187" t="str">
         <f t="shared" si="2"/>
@@ -8563,20 +8739,20 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="197">
         <f>C35</f>
-        <v>-1106.5</v>
+        <v>-254107</v>
       </c>
       <c r="E7" s="308"/>
       <c r="G7" s="197">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
-        <v>-1084</v>
-      </c>
-      <c r="H7" s="197">
+        <v>-254107</v>
+      </c>
+      <c r="H7" s="197" t="str">
         <f t="shared" si="3"/>
-        <v>-1129</v>
+        <v/>
       </c>
       <c r="I7" s="197" t="str">
         <f t="shared" si="3"/>
@@ -8618,22 +8794,22 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C8" s="198">
         <f>C6+C7</f>
-        <v>2591.8202592374382</v>
+        <v>1876773</v>
       </c>
       <c r="D8" s="60"/>
       <c r="E8" s="314"/>
       <c r="F8" s="60"/>
       <c r="G8" s="187">
         <f>IF(G$4="","",G6+G7)</f>
-        <v>2337</v>
-      </c>
-      <c r="H8" s="187">
+        <v>1876773</v>
+      </c>
+      <c r="H8" s="187" t="str">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
-        <v>4260</v>
+        <v/>
       </c>
       <c r="I8" s="187" t="str">
         <f t="shared" si="4"/>
@@ -8675,20 +8851,20 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C9" s="197">
         <f>BS!$G$39*BS!D58</f>
-        <v>159.99999999999997</v>
+        <v>463424</v>
       </c>
       <c r="E9" s="308"/>
       <c r="G9" s="197">
         <f>IF(Data!C61="","",-Data!C61)</f>
-        <v>160</v>
-      </c>
-      <c r="H9" s="197">
+        <v>463424</v>
+      </c>
+      <c r="H9" s="197" t="str">
         <f>IF(Data!D61="","",-Data!D61)</f>
-        <v>198</v>
+        <v/>
       </c>
       <c r="I9" s="197" t="str">
         <f>IF(Data!E61="","",-Data!E61)</f>
@@ -8730,20 +8906,20 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C10" s="197">
         <f>-C4*C78</f>
-        <v>-159.99999999999997</v>
+        <v>-676387</v>
       </c>
       <c r="E10" s="308"/>
       <c r="G10" s="197">
         <f>Data!C62</f>
-        <v>-69</v>
-      </c>
-      <c r="H10" s="197">
+        <v>-676387</v>
+      </c>
+      <c r="H10" s="197" t="str">
         <f>Data!D62</f>
-        <v>-108</v>
+        <v/>
       </c>
       <c r="I10" s="197" t="str">
         <f>Data!E62</f>
@@ -8785,11 +8961,11 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C11" s="199">
         <f>C63</f>
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="D11" s="172"/>
       <c r="E11" s="307"/>
@@ -8798,9 +8974,9 @@
         <f>G61</f>
         <v>639</v>
       </c>
-      <c r="H11" s="189">
+      <c r="H11" s="189" t="str">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
-        <v>927</v>
+        <v/>
       </c>
       <c r="I11" s="189" t="str">
         <f t="shared" si="5"/>
@@ -8842,20 +9018,20 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C12" s="197">
         <f>C50</f>
-        <v>120.69305155463843</v>
+        <v>-42378.404459360565</v>
       </c>
       <c r="E12" s="308"/>
       <c r="G12" s="197">
         <f>G50</f>
-        <v>224.79206823259295</v>
-      </c>
-      <c r="H12" s="197">
+        <v>-42378.404459360565</v>
+      </c>
+      <c r="H12" s="197" t="str">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>118.39443599706225</v>
+        <v/>
       </c>
       <c r="I12" s="197" t="str">
         <f t="shared" si="6"/>
@@ -8897,20 +9073,20 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="71" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
-        <v>3351.5133107920765</v>
+        <v>1621431.5955406395</v>
       </c>
       <c r="E13" s="308"/>
       <c r="G13" s="187">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>3291.792068232593</v>
-      </c>
-      <c r="H13" s="187">
+        <v>1622070.5955406395</v>
+      </c>
+      <c r="H13" s="187" t="str">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>5395.3944359970619</v>
+        <v/>
       </c>
       <c r="I13" s="187" t="str">
         <f t="shared" si="7"/>
@@ -8952,20 +9128,20 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-804.36319459009837</v>
+        <v>-458598.64888515987</v>
       </c>
       <c r="E14" s="308"/>
       <c r="G14" s="197">
         <f>Data!C46</f>
-        <v>-519</v>
-      </c>
-      <c r="H14" s="197">
+        <v>-327166</v>
+      </c>
+      <c r="H14" s="197" t="str">
         <f>Data!D46</f>
-        <v>-860.83482800000002</v>
+        <v/>
       </c>
       <c r="I14" s="197" t="str">
         <f>Data!E46</f>
@@ -9007,11 +9183,11 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C15" s="197">
         <f>-C4*C83</f>
-        <v>-22.869707937042335</v>
+        <v>0</v>
       </c>
       <c r="D15" s="61"/>
       <c r="E15" s="315"/>
@@ -9020,9 +9196,9 @@
         <f>Data!C48</f>
         <v>0</v>
       </c>
-      <c r="H15" s="186">
+      <c r="H15" s="186" t="str">
         <f>Data!D48</f>
-        <v>-31</v>
+        <v/>
       </c>
       <c r="I15" s="186" t="str">
         <f>Data!E48</f>
@@ -9064,22 +9240,22 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
-        <v>2524.2804082649359</v>
+        <v>1162832.9466554797</v>
       </c>
       <c r="D16" s="62"/>
       <c r="E16" s="316"/>
       <c r="F16" s="62"/>
       <c r="G16" s="187">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>2772.792068232593</v>
-      </c>
-      <c r="H16" s="187">
+        <v>1294904.5955406395</v>
+      </c>
+      <c r="H16" s="187" t="str">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>4503.5596079970619</v>
+        <v/>
       </c>
       <c r="I16" s="187" t="str">
         <f t="shared" si="8"/>
@@ -9121,7 +9297,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C17" s="197">
         <f>-C4*C85</f>
@@ -9129,7 +9305,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="307" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="201"/>
@@ -9147,14 +9323,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C18" s="197">
         <v>0</v>
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="307" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="202"/>
@@ -9172,22 +9348,22 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C19" s="187">
         <f>C16+C17</f>
-        <v>2524.2804082649359</v>
+        <v>1162832.9466554797</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="305"/>
       <c r="F19" s="27"/>
       <c r="G19" s="189">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>2772.792068232593</v>
-      </c>
-      <c r="H19" s="189">
+        <v>1294904.5955406395</v>
+      </c>
+      <c r="H19" s="189" t="str">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>4503.5596079970619</v>
+        <v/>
       </c>
       <c r="I19" s="189" t="str">
         <f t="shared" si="9"/>
@@ -9248,12 +9424,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -9271,7 +9447,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
@@ -9292,22 +9468,22 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" s="203">
         <f>-C4*C28</f>
-        <v>-5066.6797407625618</v>
+        <v>-11151623</v>
       </c>
       <c r="D23" s="59"/>
       <c r="E23" s="307"/>
       <c r="F23" s="59"/>
       <c r="G23" s="186">
         <f>Data!C37</f>
-        <v>-5344</v>
-      </c>
-      <c r="H23" s="186">
+        <v>-11151623</v>
+      </c>
+      <c r="H23" s="186" t="str">
         <f>Data!D37</f>
-        <v>-6492</v>
+        <v/>
       </c>
       <c r="I23" s="186" t="str">
         <f>Data!E37</f>
@@ -9349,22 +9525,22 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10"/>
       <c r="B24" s="69" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C24" s="197">
         <f>-C4*C29</f>
-        <v>0</v>
+        <v>-2043458.9999999998</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="305"/>
       <c r="F24" s="27"/>
       <c r="G24" s="186">
         <f>Data!C40</f>
-        <v>0</v>
-      </c>
-      <c r="H24" s="186">
+        <v>-2043459</v>
+      </c>
+      <c r="H24" s="186" t="str">
         <f>Data!D40</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="I24" s="186" t="str">
         <f>Data!E40</f>
@@ -9406,22 +9582,22 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C25" s="187">
         <f>C23+C24</f>
-        <v>-5066.6797407625618</v>
+        <v>-13195082</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="313"/>
       <c r="F25" s="9"/>
       <c r="G25" s="187">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
-        <v>-5344</v>
-      </c>
-      <c r="H25" s="187">
+        <v>-13195082</v>
+      </c>
+      <c r="H25" s="187" t="str">
         <f t="shared" si="10"/>
-        <v>-6492</v>
+        <v/>
       </c>
       <c r="I25" s="187" t="str">
         <f t="shared" si="10"/>
@@ -9467,31 +9643,31 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E27" s="308"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" s="64">
-        <f>AVERAGE(G28:H28)</f>
-        <v>0.57805815639048053</v>
+        <f>AVERAGE(G28:J28)</f>
+        <v>0.72762956087193742</v>
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="306" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
         <f t="shared" ref="G28:Q28" si="11">IF(G$4="","",ABS(G23/G$4))</f>
-        <v>0.60969766115231028</v>
-      </c>
-      <c r="H28" s="13">
+        <v>0.72762956087193742</v>
+      </c>
+      <c r="H28" s="13" t="str">
         <f t="shared" si="11"/>
-        <v>0.54641865162865078</v>
+        <v/>
       </c>
       <c r="I28" s="13" t="str">
         <f t="shared" si="11"/>
@@ -9538,20 +9714,20 @@
       </c>
       <c r="C29" s="64">
         <f>AVERAGE(G29:J29)</f>
-        <v>0</v>
+        <v>0.13333316368656009</v>
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="306" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
         <f t="shared" ref="G29:Q29" si="12">IF(G$4="","",ABS(G24/G$4))</f>
-        <v>0</v>
-      </c>
-      <c r="H29" s="13">
+        <v>0.13333316368656009</v>
+      </c>
+      <c r="H29" s="13" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="I29" s="13" t="str">
         <f t="shared" si="12"/>
@@ -9593,20 +9769,20 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10"/>
       <c r="B30" s="71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C30" s="72">
         <f>ABS(C25/$C$4)</f>
-        <v>0.57805815639048053</v>
+        <v>0.86096272455849754</v>
       </c>
       <c r="E30" s="308"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
-        <v>0.60969766115231028</v>
-      </c>
-      <c r="H30" s="30">
+        <v>0.86096272455849754</v>
+      </c>
+      <c r="H30" s="30" t="str">
         <f t="shared" si="13"/>
-        <v>0.54641865162865078</v>
+        <v/>
       </c>
       <c r="I30" s="30" t="str">
         <f t="shared" si="13"/>
@@ -9652,29 +9828,29 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E32" s="308"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C33" s="204">
-        <f>AVERAGE(G33:H33)</f>
-        <v>-1106.5</v>
+        <f>AVERAGE(G33:J33)</f>
+        <v>-254107</v>
       </c>
       <c r="E33" s="306" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
-        <v>-1084</v>
-      </c>
-      <c r="H33" s="197">
+        <v>-254107</v>
+      </c>
+      <c r="H33" s="197" t="str">
         <f>Data!D41</f>
-        <v>-1129</v>
+        <v/>
       </c>
       <c r="I33" s="197" t="str">
         <f>Data!E41</f>
@@ -9716,7 +9892,7 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C34" s="204">
         <f>AVERAGE(G34:J34)</f>
@@ -9724,16 +9900,16 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="306" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="186">
         <f>Data!C42</f>
         <v>0</v>
       </c>
-      <c r="H34" s="186">
+      <c r="H34" s="186" t="str">
         <f>Data!D42</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="I34" s="186" t="str">
         <f>Data!E42</f>
@@ -9775,22 +9951,22 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10"/>
       <c r="B35" s="71" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C35" s="187">
         <f>C33+C34</f>
-        <v>-1106.5</v>
+        <v>-254107</v>
       </c>
       <c r="D35" s="59"/>
       <c r="E35" s="307"/>
       <c r="F35" s="59"/>
       <c r="G35" s="187">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
-        <v>-1084</v>
-      </c>
-      <c r="H35" s="187">
+        <v>-254107</v>
+      </c>
+      <c r="H35" s="187" t="str">
         <f t="shared" si="14"/>
-        <v>-1129</v>
+        <v/>
       </c>
       <c r="I35" s="187" t="str">
         <f t="shared" si="14"/>
@@ -9836,7 +10012,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E37" s="308"/>
     </row>
@@ -9848,18 +10024,18 @@
       </c>
       <c r="C38" s="23">
         <f>ABS(C33/$C$4)</f>
-        <v>0.1262407301768397</v>
+        <v>1.6580166386945237E-2</v>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="305"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
-        <v>0.12367370222475756</v>
-      </c>
-      <c r="H38" s="13">
+        <v>1.6580166386945237E-2</v>
+      </c>
+      <c r="H38" s="13" t="str">
         <f t="shared" si="15"/>
-        <v>9.5025671239794635E-2</v>
+        <v/>
       </c>
       <c r="I38" s="13" t="str">
         <f t="shared" si="15"/>
@@ -9915,9 +10091,9 @@
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
         <v>0</v>
       </c>
-      <c r="H39" s="13">
+      <c r="H39" s="13" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="I39" s="13" t="str">
         <f t="shared" si="16"/>
@@ -9959,20 +10135,20 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10"/>
       <c r="B40" s="71" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C40" s="72">
         <f>ABS(C35/$C$4)</f>
-        <v>0.1262407301768397</v>
+        <v>1.6580166386945237E-2</v>
       </c>
       <c r="E40" s="308"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
-        <v>0.12367370222475756</v>
-      </c>
-      <c r="H40" s="30">
+        <v>1.6580166386945237E-2</v>
+      </c>
+      <c r="H40" s="30" t="str">
         <f t="shared" si="17"/>
-        <v>9.5025671239794635E-2</v>
+        <v/>
       </c>
       <c r="I40" s="30" t="str">
         <f t="shared" si="17"/>
@@ -10018,30 +10194,30 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E42" s="308"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C43" s="302">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="305" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.16214736506972799</v>
-      </c>
-      <c r="H43" s="6">
+        <v>0.17828883394563139</v>
+      </c>
+      <c r="H43" s="6" t="str">
         <f t="shared" si="18"/>
-        <v>0.16225651803742283</v>
+        <v/>
       </c>
       <c r="I43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10086,12 +10262,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -10109,7 +10285,7 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="10"/>
       <c r="B46" s="65" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E46" s="308"/>
     </row>
@@ -10120,16 +10296,16 @@
       </c>
       <c r="C47" s="197">
         <f>-BS!G31*Normalized_FCF!C54</f>
-        <v>-43</v>
+        <v>-59596</v>
       </c>
       <c r="E47" s="308"/>
       <c r="G47" s="197">
         <f>Data!C51</f>
-        <v>-43</v>
-      </c>
-      <c r="H47" s="197">
+        <v>-59596</v>
+      </c>
+      <c r="H47" s="197" t="str">
         <f>Data!D51</f>
-        <v>-40.775368</v>
+        <v/>
       </c>
       <c r="I47" s="197" t="str">
         <f>Data!E51</f>
@@ -10171,20 +10347,20 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
-        <v>163.69305155463843</v>
+        <v>17217.595540639435</v>
       </c>
       <c r="E48" s="308"/>
       <c r="G48" s="334">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
-        <v>267.79206823259295</v>
-      </c>
-      <c r="H48" s="334">
+        <v>17217.595540639435</v>
+      </c>
+      <c r="H48" s="334" t="str">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
-        <v>159.16980399706225</v>
+        <v/>
       </c>
       <c r="I48" s="334" t="str">
         <f t="shared" si="19"/>
@@ -10226,22 +10402,22 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="329" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
-        <v>1430.37</v>
+        <v>28977</v>
       </c>
       <c r="D49" s="331"/>
       <c r="E49" s="332"/>
       <c r="F49" s="331"/>
       <c r="G49" s="330">
         <f>Data!C52</f>
-        <v>2340</v>
-      </c>
-      <c r="H49" s="330">
+        <v>28977</v>
+      </c>
+      <c r="H49" s="330" t="str">
         <f>Data!D52</f>
-        <v>1390.845307</v>
+        <v/>
       </c>
       <c r="I49" s="330" t="str">
         <f>Data!E52</f>
@@ -10283,20 +10459,20 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="10"/>
       <c r="B50" s="71" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C50" s="187">
         <f>C47+C48</f>
-        <v>120.69305155463843</v>
+        <v>-42378.404459360565</v>
       </c>
       <c r="E50" s="308"/>
       <c r="G50" s="187">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>224.79206823259295</v>
-      </c>
-      <c r="H50" s="187">
+        <v>-42378.404459360565</v>
+      </c>
+      <c r="H50" s="187" t="str">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>118.39443599706225</v>
+        <v/>
       </c>
       <c r="I50" s="187" t="str">
         <f t="shared" si="20"/>
@@ -10342,27 +10518,28 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10"/>
       <c r="B52" s="73" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E52" s="308"/>
       <c r="G52" s="100" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C53" s="89">
-        <v>0.03</v>
+        <f>G53</f>
+        <v>1.4501413508729523E-2</v>
       </c>
       <c r="E53" s="305" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
-        <v>4.907821053293903E-2</v>
+        <v>1.4501413508729523E-2</v>
       </c>
       <c r="H53" s="173"/>
       <c r="I53" s="173"/>
@@ -10378,18 +10555,18 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C54" s="84">
         <f>G54</f>
-        <v>1.3902360168121564E-2</v>
+        <v>2.9286626219579916E-2</v>
       </c>
       <c r="E54" s="305" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
-        <v>1.3902360168121564E-2</v>
+        <v>2.9286626219579916E-2</v>
       </c>
       <c r="H54" s="173"/>
       <c r="I54" s="173"/>
@@ -10405,20 +10582,20 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
-        <v>60.274889749707867</v>
+        <v>31.4915933955299</v>
       </c>
       <c r="E55" s="308"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
-        <v>54.348837209302324</v>
-      </c>
-      <c r="H55" s="42">
+        <v>31.4915933955299</v>
+      </c>
+      <c r="H55" s="42" t="str">
         <f t="shared" si="21"/>
-        <v>104.47483882916765</v>
+        <v/>
       </c>
       <c r="I55" s="42" t="str">
         <f t="shared" si="21"/>
@@ -10464,17 +10641,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10"/>
       <c r="B57" s="65" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E57" s="308"/>
       <c r="G57" s="100" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C58" s="197">
         <f>BS!$C79*C66</f>
@@ -10485,9 +10662,9 @@
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="197">
+      <c r="H58" s="197" t="str">
         <f>Data!D56</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="I58" s="197" t="str">
         <f>Data!E56</f>
@@ -10529,20 +10706,20 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C59" s="197">
         <f>BS!$C68*C67</f>
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="E59" s="308"/>
       <c r="G59" s="197">
         <f>Data!C55</f>
         <v>639</v>
       </c>
-      <c r="H59" s="197">
+      <c r="H59" s="197" t="str">
         <f>Data!D55</f>
-        <v>927</v>
+        <v/>
       </c>
       <c r="I59" s="197" t="str">
         <f>Data!E55</f>
@@ -10584,7 +10761,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C60" s="197">
         <f>BS!$C81*C68</f>
@@ -10595,9 +10772,9 @@
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="197">
+      <c r="H60" s="197" t="str">
         <f>Data!D57</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="I60" s="197" t="str">
         <f>Data!E57</f>
@@ -10639,20 +10816,20 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C61" s="187">
         <f>SUM(C58:C60)</f>
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="E61" s="308"/>
       <c r="G61" s="187">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>639</v>
       </c>
-      <c r="H61" s="187">
+      <c r="H61" s="187" t="str">
         <f t="shared" si="22"/>
-        <v>927</v>
+        <v/>
       </c>
       <c r="I61" s="187" t="str">
         <f t="shared" si="22"/>
@@ -10694,21 +10871,21 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C62" s="303">
         <v>0</v>
       </c>
       <c r="E62" s="306" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
-        <v>-503</v>
-      </c>
-      <c r="H62" s="197">
+        <v>247678</v>
+      </c>
+      <c r="H62" s="197" t="str">
         <f>Data!D58</f>
-        <v>203.76488900000004</v>
+        <v/>
       </c>
       <c r="I62" s="197" t="str">
         <f>Data!E58</f>
@@ -10750,20 +10927,20 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C63" s="187">
         <f>C61+C62</f>
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="E63" s="308"/>
       <c r="G63" s="187">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
-        <v>136</v>
-      </c>
-      <c r="H63" s="187">
+        <v>248317</v>
+      </c>
+      <c r="H63" s="187" t="str">
         <f t="shared" si="23"/>
-        <v>1130.764889</v>
+        <v/>
       </c>
       <c r="I63" s="187" t="str">
         <f t="shared" si="23"/>
@@ -10809,17 +10986,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10"/>
       <c r="B65" s="99" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E65" s="308"/>
       <c r="G65" s="100" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C66" s="180">
         <f>G66</f>
@@ -10844,16 +11021,16 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10"/>
       <c r="B67" s="108" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C67" s="180">
         <f>G67</f>
-        <v>2.6966576637407157E-2</v>
+        <v>0</v>
       </c>
       <c r="E67" s="308"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
-        <v>2.6966576637407157E-2</v>
+        <v>0</v>
       </c>
       <c r="H67" s="179"/>
       <c r="I67" s="179"/>
@@ -10869,7 +11046,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="10"/>
       <c r="B68" s="108" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C68" s="180">
         <f>G68</f>
@@ -10894,18 +11071,18 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C69" s="72">
         <f>C61/BS!C70</f>
-        <v>8.7649511686601553E-3</v>
+        <v>0</v>
       </c>
       <c r="D69" s="9"/>
       <c r="E69" s="313"/>
       <c r="F69" s="9"/>
       <c r="G69" s="72">
         <f>G61/BS!C70</f>
-        <v>8.7649511686601553E-3</v>
+        <v>3.197847683362034E-4</v>
       </c>
       <c r="H69" s="179"/>
       <c r="I69" s="179"/>
@@ -10924,12 +11101,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -10947,7 +11124,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="10"/>
       <c r="B72" s="73" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C72" s="63"/>
       <c r="D72" s="27"/>
@@ -10968,22 +11145,22 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C73" s="79">
         <f>ABS(C5/C$4)</f>
-        <v>0.57805815639048053</v>
+        <v>0.86096272455849754</v>
       </c>
       <c r="D73" s="27"/>
       <c r="E73" s="305"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
-        <v>0.60969766115231028</v>
-      </c>
-      <c r="H73" s="6">
+        <v>0.86096272455849754</v>
+      </c>
+      <c r="H73" s="6" t="str">
         <f t="shared" si="24"/>
-        <v>0.54641865162865078</v>
+        <v/>
       </c>
       <c r="I73" s="6" t="str">
         <f t="shared" si="24"/>
@@ -11025,22 +11202,22 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C74" s="80">
         <f>ABS(C6/C$4)</f>
-        <v>0.42194184360951947</v>
+        <v>0.13903727544150246</v>
       </c>
       <c r="D74" s="27"/>
       <c r="E74" s="305"/>
       <c r="F74" s="27"/>
       <c r="G74" s="66">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
-        <v>0.39030233884768967</v>
-      </c>
-      <c r="H74" s="66">
+        <v>0.13903727544150246</v>
+      </c>
+      <c r="H74" s="66" t="str">
         <f t="shared" si="25"/>
-        <v>0.45358134837134922</v>
+        <v/>
       </c>
       <c r="I74" s="66" t="str">
         <f t="shared" si="25"/>
@@ -11082,22 +11259,22 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C75" s="79">
         <f>ABS(C7/C$4)</f>
-        <v>0.1262407301768397</v>
+        <v>1.6580166386945237E-2</v>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="305"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
-        <v>0.12367370222475756</v>
-      </c>
-      <c r="H75" s="6">
+        <v>1.6580166386945237E-2</v>
+      </c>
+      <c r="H75" s="6" t="str">
         <f t="shared" si="26"/>
-        <v>9.5025671239794635E-2</v>
+        <v/>
       </c>
       <c r="I75" s="6" t="str">
         <f t="shared" si="26"/>
@@ -11139,22 +11316,22 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C76" s="80">
         <f>ABS(C8/C$4)</f>
-        <v>0.2957011134326798</v>
+        <v>0.12245710905455723</v>
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="305"/>
       <c r="F76" s="27"/>
       <c r="G76" s="66">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
-        <v>0.26662863662293212</v>
-      </c>
-      <c r="H76" s="66">
+        <v>0.12245710905455723</v>
+      </c>
+      <c r="H76" s="66" t="str">
         <f t="shared" si="27"/>
-        <v>0.35855567713155456</v>
+        <v/>
       </c>
       <c r="I76" s="66" t="str">
         <f t="shared" si="27"/>
@@ -11196,22 +11373,22 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C77" s="79">
         <f>ABS(C9/C$4)</f>
-        <v>1.8254420992584137E-2</v>
+        <v>3.0237840861147901E-2</v>
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="305"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
-        <v>1.825442099258414E-2</v>
-      </c>
-      <c r="H77" s="6">
+        <v>3.0237840861147901E-2</v>
+      </c>
+      <c r="H77" s="6" t="str">
         <f t="shared" si="28"/>
-        <v>1.6665263866677889E-2</v>
+        <v/>
       </c>
       <c r="I77" s="6" t="str">
         <f t="shared" si="28"/>
@@ -11253,11 +11430,11 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C78" s="90">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
-        <v>1.8254420992584137E-2</v>
+        <v>4.413341231043115E-2</v>
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="306" t="s">
@@ -11266,11 +11443,11 @@
       <c r="F78" s="27"/>
       <c r="G78" s="6">
         <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",-G10/G$4)</f>
-        <v>7.8722190530519116E-3</v>
-      </c>
-      <c r="H78" s="6">
+        <v>4.413341231043115E-2</v>
+      </c>
+      <c r="H78" s="6" t="str">
         <f t="shared" si="29"/>
-        <v>9.0901439272788494E-3</v>
+        <v/>
       </c>
       <c r="I78" s="6" t="str">
         <f t="shared" si="29"/>
@@ -11312,22 +11489,22 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C79" s="80">
         <f>ABS(C11/C$4)</f>
-        <v>7.2903593839132919E-2</v>
+        <v>0</v>
       </c>
       <c r="D79" s="27"/>
       <c r="E79" s="305"/>
       <c r="F79" s="27"/>
       <c r="G79" s="66">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
-        <v>7.2903593839132919E-2</v>
-      </c>
-      <c r="H79" s="66">
+        <v>4.1693956960091643E-5</v>
+      </c>
+      <c r="H79" s="66" t="str">
         <f t="shared" si="30"/>
-        <v>7.8023735375810116E-2</v>
+        <v/>
       </c>
       <c r="I79" s="66" t="str">
         <f t="shared" si="30"/>
@@ -11369,22 +11546,22 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C80" s="79">
         <f>ABS(C12/C$4)</f>
-        <v>1.3769886087237698E-2</v>
+        <v>2.7651382966603051E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="305"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>2.5646556558196573E-2</v>
-      </c>
-      <c r="H80" s="6">
+        <v>2.7651382966603051E-3</v>
+      </c>
+      <c r="H80" s="6" t="str">
         <f t="shared" si="31"/>
-        <v>9.9650228092805528E-3</v>
+        <v/>
       </c>
       <c r="I80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -11426,22 +11603,22 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="10"/>
       <c r="B81" s="71" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C81" s="80">
         <f>C13/C4</f>
-        <v>0.38237459335905039</v>
+        <v>0.10579639930861368</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="305"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.37556098895979384</v>
-      </c>
-      <c r="H81" s="66">
+        <v>0.10583809326557377</v>
+      </c>
+      <c r="H81" s="66" t="str">
         <f t="shared" si="32"/>
-        <v>0.45411955525604425</v>
+        <v/>
       </c>
       <c r="I81" s="66" t="str">
         <f t="shared" si="32"/>
@@ -11483,22 +11660,22 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C82" s="79">
         <f>ABS(C14/C$4)</f>
-        <v>9.1769902406172096E-2</v>
+        <v>2.992299268947423E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="305"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>5.9212778094694808E-2</v>
-      </c>
-      <c r="H82" s="6">
+        <v>2.134717546604905E-2</v>
+      </c>
+      <c r="H82" s="6" t="str">
         <f t="shared" si="33"/>
-        <v>7.2454745223466038E-2</v>
+        <v/>
       </c>
       <c r="I82" s="6" t="str">
         <f t="shared" si="33"/>
@@ -11545,7 +11722,7 @@
       </c>
       <c r="C83" s="304">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
-        <v>2.6092079791263361E-3</v>
+        <v>0</v>
       </c>
       <c r="D83" s="27"/>
       <c r="E83" s="305"/>
@@ -11554,9 +11731,9 @@
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
         <v>0</v>
       </c>
-      <c r="H83" s="6">
+      <c r="H83" s="6" t="str">
         <f t="shared" si="34"/>
-        <v>2.6092079791263361E-3</v>
+        <v/>
       </c>
       <c r="I83" s="6" t="str">
         <f t="shared" si="34"/>
@@ -11598,22 +11775,22 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C84" s="80">
         <f>ABS(C16/C$4)</f>
-        <v>0.28799548297375194</v>
+        <v>7.5873406619139452E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="305"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>0.31634821086509901</v>
-      </c>
-      <c r="H84" s="66">
+        <v>8.4490917799524723E-2</v>
+      </c>
+      <c r="H84" s="66" t="str">
         <f t="shared" si="35"/>
-        <v>0.3790556020534519</v>
+        <v/>
       </c>
       <c r="I84" s="66" t="str">
         <f t="shared" si="35"/>
@@ -11655,7 +11832,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C85" s="304">
         <v>0</v>
@@ -11681,7 +11858,7 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C86" s="79">
         <v>0</v>
@@ -11705,22 +11882,22 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C87" s="80">
         <f>ABS(C19/C$4)</f>
-        <v>0.28799548297375194</v>
+        <v>7.5873406619139452E-2</v>
       </c>
       <c r="D87" s="77"/>
       <c r="E87" s="305"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>0.31634821086509901</v>
-      </c>
-      <c r="H87" s="66">
+        <v>8.4490917799524723E-2</v>
+      </c>
+      <c r="H87" s="66" t="str">
         <f t="shared" si="36"/>
-        <v>0.3790556020534519</v>
+        <v/>
       </c>
       <c r="I87" s="66" t="str">
         <f t="shared" si="36"/>
@@ -11766,7 +11943,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10"/>
       <c r="B89" s="65" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E89" s="308"/>
     </row>
@@ -11778,16 +11955,16 @@
       </c>
       <c r="C90" s="117">
         <f>G90</f>
-        <v>0.57999999999999996</v>
+        <v>1.36</v>
       </c>
       <c r="E90" s="308"/>
       <c r="G90" s="116">
         <f>Data!C64</f>
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="H90" s="116">
+        <v>1.36</v>
+      </c>
+      <c r="H90" s="116" t="str">
         <f>Data!D64</f>
-        <v>0.57999999999999996</v>
+        <v/>
       </c>
       <c r="I90" s="116" t="str">
         <f>Data!E64</f>
@@ -11834,16 +12011,16 @@
       </c>
       <c r="C91" s="76">
         <f>C90*Common_Shares/$C$3</f>
-        <v>4739.6903628800001</v>
+        <v>798466.67599999998</v>
       </c>
       <c r="E91" s="308"/>
       <c r="G91" s="76">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>4739.6903628800001</v>
-      </c>
-      <c r="H91" s="76">
+        <v>798466.67599999998</v>
+      </c>
+      <c r="H91" s="76" t="str">
         <f t="shared" si="37"/>
-        <v>4739.6903628800001</v>
+        <v/>
       </c>
       <c r="I91" s="76" t="str">
         <f t="shared" si="37"/>
@@ -11885,20 +12062,20 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>1.8776401969295582</v>
+        <v>0.68665639230169417</v>
       </c>
       <c r="E92" s="308"/>
       <c r="G92" s="174">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>1.7093565785843898</v>
-      </c>
-      <c r="H92" s="174">
+        <v>0.61662201118888604</v>
+      </c>
+      <c r="H92" s="174" t="str">
         <f t="shared" si="38"/>
-        <v>1.0524320260941227</v>
+        <v/>
       </c>
       <c r="I92" s="174" t="str">
         <f t="shared" si="38"/>
@@ -11940,20 +12117,20 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.3417721518987331E-2</v>
+        <v>8.8311688311688313E-2</v>
       </c>
       <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.3417721518987331E-2</v>
-      </c>
-      <c r="H93" s="23">
+        <v>8.8311688311688313E-2</v>
+      </c>
+      <c r="H93" s="23" t="str">
         <f t="shared" si="39"/>
-        <v>7.3417721518987331E-2</v>
+        <v/>
       </c>
       <c r="I93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -11999,7 +12176,7 @@
     <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10"/>
       <c r="B95" s="161" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C95" s="63"/>
       <c r="D95" s="27"/>
@@ -12020,7 +12197,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C96" s="79">
         <f>C4/G4-1</f>
@@ -12029,9 +12206,9 @@
       <c r="D96" s="27"/>
       <c r="E96" s="305"/>
       <c r="F96" s="27"/>
-      <c r="G96" s="6">
+      <c r="G96" s="6" t="str">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
-        <v>-0.26226748590186011</v>
+        <v/>
       </c>
       <c r="H96" s="6" t="str">
         <f t="shared" si="40"/>
@@ -12077,18 +12254,18 @@
     <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="10"/>
       <c r="B97" s="71" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
-        <v>1.8142471128666626E-2</v>
+        <v>-3.9394093065781011E-4</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="305"/>
       <c r="F97" s="27"/>
-      <c r="G97" s="6">
+      <c r="G97" s="6" t="str">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-0.38988852302060206</v>
+        <v/>
       </c>
       <c r="H97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -12137,12 +12314,12 @@
     <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C99" s="54"/>
       <c r="D99" s="56"/>
       <c r="E99" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F99" s="56"/>
       <c r="G99" s="37"/>
@@ -12164,7 +12341,7 @@
       </c>
       <c r="E100" s="308"/>
       <c r="G100" s="100" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -12174,18 +12351,18 @@
       </c>
       <c r="C101" s="205">
         <f>BS!G32</f>
-        <v>180996</v>
+        <v>16854064</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="309"/>
       <c r="F101" s="26"/>
       <c r="G101" s="186">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
-        <v>180344</v>
-      </c>
-      <c r="H101" s="186">
+        <v>16854064</v>
+      </c>
+      <c r="H101" s="186" t="str">
         <f t="shared" si="42"/>
-        <v>174007</v>
+        <v/>
       </c>
       <c r="I101" s="186" t="str">
         <f t="shared" si="42"/>
@@ -12227,18 +12404,18 @@
     <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="10"/>
       <c r="B102" s="95" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C102" s="206">
         <f>BS!C4</f>
-        <v>8029</v>
+        <v>265773</v>
       </c>
       <c r="D102" s="91"/>
       <c r="E102" s="310"/>
       <c r="F102" s="91"/>
-      <c r="G102" s="188">
+      <c r="G102" s="188" t="str">
         <f>IF(G$4="","",Data!D76)</f>
-        <v>7251</v>
+        <v/>
       </c>
       <c r="H102" s="188" t="str">
         <f>IF(H$4="","",Data!E76)</f>
@@ -12284,18 +12461,18 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="10"/>
       <c r="B103" s="95" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C103" s="206">
         <f>BS!C6+BS!C7</f>
-        <v>15310</v>
+        <v>9672256</v>
       </c>
       <c r="D103" s="91"/>
       <c r="E103" s="310"/>
       <c r="F103" s="91"/>
-      <c r="G103" s="188">
+      <c r="G103" s="188" t="str">
         <f>IF(G$4="","",Data!D77)</f>
-        <v>16389</v>
+        <v/>
       </c>
       <c r="H103" s="188" t="str">
         <f>IF(H$4="","",Data!E77)</f>
@@ -12345,18 +12522,18 @@
       </c>
       <c r="C104" s="205">
         <f>BS!G30</f>
-        <v>13889</v>
+        <v>3990166</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="309"/>
       <c r="F104" s="26"/>
       <c r="G104" s="186">
         <f>Data!C78</f>
-        <v>14028</v>
-      </c>
-      <c r="H104" s="186">
+        <v>3990166</v>
+      </c>
+      <c r="H104" s="186" t="str">
         <f>Data!D78</f>
-        <v>10902</v>
+        <v/>
       </c>
       <c r="I104" s="186" t="str">
         <f>Data!E78</f>
@@ -12402,18 +12579,18 @@
       </c>
       <c r="C105" s="205">
         <f>BS!G27</f>
-        <v>167107</v>
+        <v>12863898</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="309"/>
       <c r="F105" s="26"/>
       <c r="G105" s="186">
         <f>Data!C79</f>
-        <v>166316</v>
-      </c>
-      <c r="H105" s="186">
+        <v>12863898</v>
+      </c>
+      <c r="H105" s="186" t="str">
         <f>Data!D79</f>
-        <v>163105</v>
+        <v/>
       </c>
       <c r="I105" s="186" t="str">
         <f>Data!E79</f>
@@ -12459,14 +12636,14 @@
     <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10"/>
       <c r="B107" s="93" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
       <c r="E107" s="309"/>
       <c r="F107" s="26"/>
       <c r="G107" s="100" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
@@ -12482,22 +12659,22 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C108" s="97">
         <f>C102/C$4</f>
-        <v>0.91602966343411296</v>
+        <v>1.7341358408692387E-2</v>
       </c>
       <c r="D108" s="26"/>
       <c r="E108" s="309"/>
       <c r="F108" s="26"/>
-      <c r="G108" s="97">
+      <c r="G108" s="97" t="e">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
-        <v>0.82726754135767255</v>
-      </c>
-      <c r="H108" s="97" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H108" s="97" t="str">
         <f t="shared" si="43"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
       <c r="I108" s="97" t="str">
         <f t="shared" si="43"/>
@@ -12539,22 +12716,22 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C109" s="97">
         <f>C103/C$4</f>
-        <v>1.7467199087278951</v>
+        <v>0.63110270011109249</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="309"/>
       <c r="F109" s="26"/>
-      <c r="G109" s="97">
+      <c r="G109" s="97" t="e">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
-        <v>1.8698231602966344</v>
-      </c>
-      <c r="H109" s="97" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H109" s="97" t="str">
         <f t="shared" si="44"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
       <c r="I109" s="97" t="str">
         <f t="shared" si="44"/>
@@ -12596,18 +12773,18 @@
     <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C110" s="97">
         <f>BS!$G$38/C$4</f>
-        <v>8.343867655447804</v>
+        <v>0</v>
       </c>
       <c r="D110" s="26"/>
       <c r="E110" s="309"/>
       <c r="F110" s="26"/>
       <c r="G110" s="97">
         <f>BS!$G$38/G$4</f>
-        <v>8.343867655447804</v>
+        <v>0</v>
       </c>
       <c r="H110" s="231"/>
       <c r="I110" s="231"/>
@@ -12681,20 +12858,20 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C113" s="23">
         <f>C81</f>
-        <v>0.38237459335905039</v>
+        <v>0.10579639930861368</v>
       </c>
       <c r="E113" s="308"/>
       <c r="G113" s="23">
         <f t="shared" ref="G113:Q113" si="45">G81</f>
-        <v>0.37556098895979384</v>
-      </c>
-      <c r="H113" s="23">
+        <v>0.10583809326557377</v>
+      </c>
+      <c r="H113" s="23" t="str">
         <f t="shared" si="45"/>
-        <v>0.45411955525604425</v>
+        <v/>
       </c>
       <c r="I113" s="23" t="str">
         <f t="shared" si="45"/>
@@ -12735,20 +12912,20 @@
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C114" s="42">
         <f>C4/C101</f>
-        <v>4.8426484563194767E-2</v>
+        <v>0.90933332162498015</v>
       </c>
       <c r="E114" s="308"/>
       <c r="G114" s="42">
         <f t="shared" ref="G114:Q114" si="46">IF(G4="","",G4/G101)</f>
-        <v>4.8601561460320276E-2</v>
-      </c>
-      <c r="H114" s="42">
+        <v>0.90933332162498015</v>
+      </c>
+      <c r="H114" s="42" t="str">
         <f t="shared" si="46"/>
-        <v>6.8278862344618316E-2</v>
+        <v/>
       </c>
       <c r="I114" s="42" t="str">
         <f t="shared" si="46"/>
@@ -12789,22 +12966,22 @@
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B115" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C115" s="15">
         <f>C101/C105</f>
-        <v>1.0831144117242246</v>
+        <v>1.3101832741522048</v>
       </c>
       <c r="D115" s="11"/>
       <c r="E115" s="312"/>
       <c r="F115" s="11"/>
       <c r="G115" s="15">
         <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G101/G105)</f>
-        <v>1.0843454628538445</v>
-      </c>
-      <c r="H115" s="15">
+        <v>1.3101832741522048</v>
+      </c>
+      <c r="H115" s="15" t="str">
         <f t="shared" si="47"/>
-        <v>1.0668403788970295</v>
+        <v/>
       </c>
       <c r="I115" s="15" t="str">
         <f t="shared" si="47"/>
@@ -12846,22 +13023,22 @@
     <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="10"/>
       <c r="B116" s="71" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C116" s="105">
         <f>C8/C105</f>
-        <v>1.5509944282629921E-2</v>
+        <v>0.14589458032083277</v>
       </c>
       <c r="D116" s="106"/>
       <c r="E116" s="311"/>
       <c r="F116" s="106"/>
       <c r="G116" s="105">
         <f t="shared" ref="G116:Q116" si="48">IF(G$4="","",G8/G105)</f>
-        <v>1.4051564491690517E-2</v>
-      </c>
-      <c r="H116" s="105">
+        <v>0.14589458032083277</v>
+      </c>
+      <c r="H116" s="105" t="str">
         <f t="shared" si="48"/>
-        <v>2.6118144753379726E-2</v>
+        <v/>
       </c>
       <c r="I116" s="105" t="str">
         <f t="shared" si="48"/>
@@ -12922,12 +13099,12 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A118" s="10"/>
       <c r="B118" s="54" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C118" s="54"/>
       <c r="D118" s="56"/>
       <c r="E118" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F118" s="56"/>
       <c r="G118" s="37"/>
@@ -12945,7 +13122,7 @@
     <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="10"/>
       <c r="B119" s="182" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C119" s="183"/>
       <c r="D119" s="27"/>
@@ -12971,18 +13148,18 @@
       </c>
       <c r="C120" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.308898371982265</v>
+        <v>1.9806121595129067</v>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="305"/>
       <c r="F120" s="27"/>
       <c r="G120" s="181">
         <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.33930895827500729</v>
-      </c>
-      <c r="H120" s="181">
+        <v>2.205565119833842</v>
+      </c>
+      <c r="H120" s="181" t="str">
         <f t="shared" si="49"/>
-        <v>0.55110447574704324</v>
+        <v/>
       </c>
       <c r="I120" s="181" t="str">
         <f t="shared" si="49"/>
@@ -13024,22 +13201,22 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="10"/>
       <c r="B121" s="27" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.9101059744590508E-2</v>
+        <v>0.12861117918914977</v>
       </c>
       <c r="D121" s="27"/>
       <c r="E121" s="305"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>4.2950501047469274E-2</v>
-      </c>
-      <c r="H121" s="79">
+        <v>0.1432185142749248</v>
+      </c>
+      <c r="H121" s="79" t="str">
         <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v>6.9760060221144712E-2</v>
+        <v/>
       </c>
       <c r="I121" s="79" t="str">
         <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
@@ -13793,134 +13970,134 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="134" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="112" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C3" s="110">
         <f>Normalized_FCF!C3</f>
-        <v>1000000</v>
+        <v>1000</v>
       </c>
       <c r="E3" s="112" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H3" s="124"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" s="103" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
-        <v>2524.2804082649359</v>
+        <v>1162832.9466554797</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F4" s="138">
-        <f>Thesis!C75</f>
+        <f>Thesis!C76</f>
         <v>0</v>
       </c>
       <c r="H4" s="124"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" s="233" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C5" s="234">
         <f>Thesis!C70</f>
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E5" s="152"/>
       <c r="H5" s="124"/>
     </row>
     <row r="6" spans="2:8" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="153" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>28047.560091832624</v>
+        <v>14535411.833193496</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="344" t="s">
-        <v>255</v>
-      </c>
-      <c r="F6" s="344"/>
+      <c r="E6" s="345" t="s">
+        <v>251</v>
+      </c>
+      <c r="F6" s="345"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="152" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C7" s="232">
         <f>BS!G31</f>
-        <v>3093</v>
+        <v>2034922</v>
       </c>
       <c r="D7" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
+      <c r="E7" s="345"/>
+      <c r="F7" s="345"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="152" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C8" s="207">
         <f>BS!D66</f>
-        <v>42222.564948178719</v>
+        <v>810914.36033333349</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="344"/>
-      <c r="F8" s="344"/>
+      <c r="E8" s="345"/>
+      <c r="F8" s="345"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" s="233" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C9" s="235">
         <f>BS!H42</f>
-        <v>7814.4</v>
+        <v>92572.6</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="344"/>
-      <c r="F9" s="344"/>
+      <c r="E9" s="345"/>
+      <c r="F9" s="345"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
-        <v>74991.525040011329</v>
+        <v>13403976.793526828</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -13930,7 +14107,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="236" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C11" s="237">
         <f>Exchange_Rate</f>
@@ -13944,11 +14121,11 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B12" s="153" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>9.1767776359081505</v>
+        <v>22.830518776962066</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -13961,7 +14138,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B14" s="36" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -13971,23 +14148,23 @@
     </row>
     <row r="15" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B15" s="123" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H15" s="124"/>
     </row>
     <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C16" s="165">
         <f>Scenarios!C65</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>6.4006284479398504E-3</v>
       </c>
       <c r="H16" s="124"/>
     </row>
     <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C17" s="166">
         <f>Scenarios!C64</f>
@@ -13997,11 +14174,11 @@
     </row>
     <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="157" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>9.0981264288878361</v>
+        <v>23.325699825167451</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14014,19 +14191,19 @@
     </row>
     <row r="20" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="132" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="132" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="132" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" s="132" t="s">
         <v>111</v>
       </c>
-      <c r="C20" s="132" t="s">
+      <c r="F20" s="133" t="s">
         <v>112</v>
-      </c>
-      <c r="D20" s="132" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" s="132" t="s">
-        <v>113</v>
-      </c>
-      <c r="F20" s="133" t="s">
-        <v>114</v>
       </c>
       <c r="H20" s="124"/>
     </row>
@@ -14036,19 +14213,19 @@
       </c>
       <c r="C21" s="127">
         <f>C4*(1+D21)</f>
-        <v>2505.8531612846018</v>
+        <v>1170275.8082940446</v>
       </c>
       <c r="D21" s="142">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>6.4006284479398504E-3</v>
       </c>
       <c r="E21" s="128">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.9174311926605504</v>
+        <v>0.92592592592592582</v>
       </c>
       <c r="F21" s="129">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2298.947854389543</v>
+        <v>1083588.7113833744</v>
       </c>
       <c r="H21" s="124"/>
     </row>
@@ -14058,19 +14235,19 @@
       </c>
       <c r="C22" s="127">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>2487.5604332072244</v>
+        <v>1177766.3089245472</v>
       </c>
       <c r="D22" s="142">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>6.4006284479398504E-3</v>
       </c>
       <c r="E22" s="128">
         <f t="shared" si="0"/>
-        <v>0.84167999326655996</v>
+        <v>0.85733882030178321</v>
       </c>
       <c r="F22" s="129">
         <f t="shared" si="1"/>
-        <v>2093.7298486720174</v>
+        <v>1009744.7778845568</v>
       </c>
       <c r="H22" s="124"/>
     </row>
@@ -14080,19 +14257,19 @@
       </c>
       <c r="C23" s="127">
         <f t="shared" si="2"/>
-        <v>2469.4012420448116</v>
+        <v>1185304.7534664748</v>
       </c>
       <c r="D23" s="142">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>6.4006284479398504E-3</v>
       </c>
       <c r="E23" s="128">
         <f t="shared" si="0"/>
-        <v>0.77218348006106419</v>
+        <v>0.79383224102016958</v>
       </c>
       <c r="F23" s="129">
         <f t="shared" si="1"/>
-        <v>1906.830844749277</v>
+        <v>940933.12873615138</v>
       </c>
       <c r="H23" s="124"/>
     </row>
@@ -14102,19 +14279,19 @@
       </c>
       <c r="C24" s="127">
         <f t="shared" si="2"/>
-        <v>2451.3746129778847</v>
+        <v>1192891.4487909905</v>
       </c>
       <c r="D24" s="142">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>6.4006284479398504E-3</v>
       </c>
       <c r="E24" s="128">
         <f t="shared" si="0"/>
-        <v>0.7084252110651964</v>
+        <v>0.73502985279645328</v>
       </c>
       <c r="F24" s="129">
         <f t="shared" si="1"/>
-        <v>1736.6155775987222</v>
+        <v>876810.82600698969</v>
       </c>
       <c r="H24" s="124"/>
     </row>
@@ -14124,19 +14301,19 @@
       </c>
       <c r="C25" s="127">
         <f t="shared" si="2"/>
-        <v>2433.4795783031459</v>
+        <v>1200526.7037334265</v>
       </c>
       <c r="D25" s="142">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>6.4006284479398504E-3</v>
       </c>
       <c r="E25" s="128">
         <f t="shared" si="0"/>
-        <v>0.64993138629834524</v>
+        <v>0.68058319703375303</v>
       </c>
       <c r="F25" s="129">
         <f t="shared" si="1"/>
-        <v>1581.5947558552762</v>
+        <v>817058.30215128872</v>
       </c>
       <c r="H25" s="124"/>
     </row>
@@ -14146,19 +14323,19 @@
       </c>
       <c r="C26" s="127">
         <f t="shared" si="2"/>
-        <v>2415.7151773815331</v>
+        <v>1208210.8291058543</v>
       </c>
       <c r="D26" s="142">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>6.4006284479398504E-3</v>
       </c>
       <c r="E26" s="128">
         <f t="shared" si="0"/>
-        <v>0.5962673268792158</v>
+        <v>0.63016962688310452</v>
       </c>
       <c r="F26" s="129">
         <f t="shared" si="1"/>
-        <v>1440.4120313188373</v>
+        <v>761377.76737376256</v>
       </c>
       <c r="H26" s="124"/>
     </row>
@@ -14168,19 +14345,19 @@
       </c>
       <c r="C27" s="127">
         <f t="shared" si="2"/>
-        <v>2398.0804565866479</v>
+        <v>1215944.137709738</v>
       </c>
       <c r="D27" s="142">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>6.4006284479398504E-3</v>
       </c>
       <c r="E27" s="128">
         <f t="shared" si="0"/>
-        <v>0.54703424484331731</v>
+        <v>0.58349039526213387</v>
       </c>
       <c r="F27" s="129">
         <f t="shared" si="1"/>
-        <v>1311.8321316423944</v>
+        <v>709491.7255289295</v>
       </c>
       <c r="H27" s="124"/>
     </row>
@@ -14190,19 +14367,19 @@
       </c>
       <c r="C28" s="127">
         <f t="shared" si="2"/>
-        <v>2380.5744692535654</v>
+        <v>1223726.9443486687</v>
       </c>
       <c r="D28" s="142">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>6.4006284479398504E-3</v>
       </c>
       <c r="E28" s="128">
         <f t="shared" si="0"/>
-        <v>0.50186627967276809</v>
+        <v>0.54026888450197574</v>
       </c>
       <c r="F28" s="129">
         <f t="shared" si="1"/>
-        <v>1194.7300523682613</v>
+        <v>661141.59115826653</v>
       </c>
       <c r="H28" s="124"/>
     </row>
@@ -14212,19 +14389,19 @@
       </c>
       <c r="C29" s="127">
         <f t="shared" si="2"/>
-        <v>2363.1962756280145</v>
+        <v>1231559.5658411772</v>
       </c>
       <c r="D29" s="142">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>6.4006284479398504E-3</v>
       </c>
       <c r="E29" s="128">
         <f t="shared" si="0"/>
-        <v>0.46042777951630098</v>
+        <v>0.50024896713145905</v>
       </c>
       <c r="F29" s="129">
         <f t="shared" si="1"/>
-        <v>1088.0812137485991</v>
+        <v>616086.40077291708</v>
       </c>
       <c r="H29" s="124"/>
     </row>
@@ -14234,19 +14411,19 @@
       </c>
       <c r="C30" s="127">
         <f t="shared" si="2"/>
-        <v>2345.9449428159301</v>
+        <v>1239442.3210336328</v>
       </c>
       <c r="D30" s="142">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>6.4006284479398504E-3</v>
       </c>
       <c r="E30" s="128">
         <f t="shared" si="0"/>
-        <v>0.42241080689568894</v>
+        <v>0.46319348808468425</v>
       </c>
       <c r="F30" s="129">
         <f t="shared" si="1"/>
-        <v>990.95249622773781</v>
+        <v>574101.61195934541</v>
       </c>
       <c r="H30" s="124"/>
     </row>
@@ -14692,11 +14869,11 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B51" s="130" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>27842.812903162245</v>
+        <v>14628447.603675557</v>
       </c>
       <c r="D51" s="143">
         <f>Terminal_Growth</f>
@@ -14704,22 +14881,22 @@
       </c>
       <c r="E51" s="128">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.42241080689568894</v>
+        <v>0.46319348808468425</v>
       </c>
       <c r="F51" s="129">
         <f t="shared" si="1"/>
-        <v>11761.105064670463</v>
+        <v>6775801.6708105225</v>
       </c>
       <c r="H51" s="124"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C52" s="118"/>
       <c r="E52" s="131" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
-        <v>27404.831871241127</v>
+        <v>14826136.513766104</v>
       </c>
       <c r="H52" s="124"/>
     </row>
@@ -14729,7 +14906,7 @@
     </row>
     <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B54" s="123" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C54" s="140"/>
       <c r="D54" s="140"/>
@@ -14740,11 +14917,11 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="137">
         <f>F52</f>
-        <v>27404.831871241127</v>
+        <v>14826136.513766104</v>
       </c>
       <c r="B55" s="135">
         <f>C78</f>
-        <v>-0.2</v>
+        <v>-0.08</v>
       </c>
       <c r="C55" s="135">
         <f>C77</f>
@@ -14752,15 +14929,15 @@
       </c>
       <c r="D55" s="135">
         <f>C76</f>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E55" s="135">
         <f>C75</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="F55" s="135">
         <f>C74</f>
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H55" s="124"/>
     </row>
@@ -14770,19 +14947,19 @@
       </c>
       <c r="B56" s="127">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>20063.703772414767</v>
+        <v>12788241.211071908</v>
       </c>
       <c r="C56" s="127">
-        <v>25832.311334807477</v>
+        <v>13420515.524325915</v>
       </c>
       <c r="D56" s="127">
-        <v>28047.560091832616</v>
+        <v>15004400.307915099</v>
       </c>
       <c r="E56" s="127">
-        <v>28981.765727242848</v>
+        <v>15734411.148311835</v>
       </c>
       <c r="F56" s="127">
-        <v>30438.473405950401</v>
+        <v>15985131.641699184</v>
       </c>
       <c r="H56" s="124"/>
     </row>
@@ -14791,19 +14968,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="127">
-        <v>16125.768083282397</v>
+        <v>11535059.995283656</v>
       </c>
       <c r="C57" s="127">
-        <v>24052.100970487048</v>
+        <v>12537042.701494243</v>
       </c>
       <c r="D57" s="127">
-        <v>28047.560091832609</v>
+        <v>15473820.646910066</v>
       </c>
       <c r="E57" s="127">
-        <v>29927.068993812412</v>
+        <v>17061254.876979411</v>
       </c>
       <c r="F57" s="127">
-        <v>33109.67442910144</v>
+        <v>17644056.388321832</v>
       </c>
       <c r="H57" s="124"/>
     </row>
@@ -14812,19 +14989,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="127">
-        <v>13056.366048742024</v>
+        <v>10298427.120539103</v>
       </c>
       <c r="C58" s="127">
-        <v>22265.500140079126</v>
+        <v>11609617.700964648</v>
       </c>
       <c r="D58" s="127">
-        <v>28047.560091832613</v>
+        <v>16054858.474479713</v>
       </c>
       <c r="E58" s="127">
-        <v>31045.702134284722</v>
+        <v>18837634.59315075</v>
       </c>
       <c r="F58" s="127">
-        <v>36528.586558529481</v>
+        <v>19925971.38051375</v>
       </c>
       <c r="H58" s="124"/>
     </row>
@@ -14833,19 +15010,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="127">
-        <v>10952.84788723816</v>
+        <v>9284665.7634038813</v>
       </c>
       <c r="C59" s="127">
-        <v>20787.710421208605</v>
+        <v>10806670.890222374</v>
       </c>
       <c r="D59" s="127">
-        <v>28047.560091832613</v>
+        <v>16646842.841164071</v>
       </c>
       <c r="E59" s="127">
-        <v>32134.575636798087</v>
+        <v>20805216.260669909</v>
       </c>
       <c r="F59" s="127">
-        <v>40146.532024878717</v>
+        <v>22529016.1300468</v>
       </c>
       <c r="H59" s="124"/>
     </row>
@@ -14854,19 +15031,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="127">
-        <v>9562.5732082856211</v>
+        <v>8517506.3067681082</v>
       </c>
       <c r="C60" s="127">
-        <v>19668.01798494067</v>
+        <v>10169747.747799639</v>
       </c>
       <c r="D60" s="127">
-        <v>28047.560091832605</v>
+        <v>17197421.151398726</v>
       </c>
       <c r="E60" s="127">
-        <v>33101.915756911323</v>
+        <v>22803257.715964336</v>
       </c>
       <c r="F60" s="127">
-        <v>43655.830383979846</v>
+        <v>25256927.882247664</v>
       </c>
       <c r="H60" s="124"/>
     </row>
@@ -14875,19 +15052,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="127">
-        <v>8654.0636045229312</v>
+        <v>7960756.9389042351</v>
       </c>
       <c r="C61" s="127">
-        <v>18860.216981993442</v>
+        <v>9688635.0268338043</v>
       </c>
       <c r="D61" s="127">
-        <v>28047.560091832605</v>
+        <v>17683107.810972057</v>
       </c>
       <c r="E61" s="127">
-        <v>33916.937156575856</v>
+        <v>24735455.482912373</v>
       </c>
       <c r="F61" s="127">
-        <v>46897.091415208801</v>
+        <v>27984492.970261224</v>
       </c>
       <c r="H61" s="124"/>
     </row>
@@ -14900,7 +15077,7 @@
     </row>
     <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B63" s="123" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C63" s="118"/>
       <c r="D63" s="118"/>
@@ -14911,7 +15088,7 @@
     <row r="64" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B64" s="136">
         <f>B55</f>
-        <v>-0.2</v>
+        <v>-0.08</v>
       </c>
       <c r="C64" s="136">
         <f>C55</f>
@@ -14919,15 +15096,15 @@
       </c>
       <c r="D64" s="136">
         <f>D55</f>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E64" s="136">
         <f>E55</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="F64" s="136">
         <f>F55</f>
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H64" s="124"/>
     </row>
@@ -14937,23 +15114,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>9.1767776359081505</v>
+        <v>22.830518776962066</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>9.1767776359081505</v>
+        <v>22.830518776962066</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>9.1767776359081505</v>
+        <v>22.830518776962066</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>9.1767776359081505</v>
+        <v>22.830518776962066</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>9.1767776359081505</v>
+        <v>22.830518776962066</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -14964,23 +15141,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>8.1997862481313746</v>
+        <v>19.854624957586992</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>8.9056957337786056</v>
+        <v>20.931555394224837</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>9.1767776359081505</v>
+        <v>23.629330229954228</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>9.2910971857212523</v>
+        <v>24.872731830523417</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>9.4693557614854704</v>
+        <v>25.299775164022275</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -14991,23 +15168,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>7.7178976594622748</v>
+        <v>17.720125792249224</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>8.6878498551971095</v>
+        <v>19.426767436047015</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>9.1767776359081505</v>
+        <v>24.428877262062496</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>9.4067747622364397</v>
+        <v>27.132697744226626</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>9.7962329359020277</v>
+        <v>28.125362910162355</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -15018,23 +15195,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>7.3422922836394369</v>
+        <v>15.613812829912655</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>8.4692219697655933</v>
+        <v>17.847117290797563</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>9.1767776359081505</v>
+        <v>25.418538407914397</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>9.5436628650026503</v>
+        <v>30.158342378634668</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>10.214608163659173</v>
+        <v>32.012067869382236</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -15045,23 +15222,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>7.0848829509059597</v>
+        <v>13.887109027305996</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>8.2883835665530903</v>
+        <v>16.479486436019734</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>9.1767776359081505</v>
+        <v>26.426844406010588</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>9.6769092551896243</v>
+        <v>33.509654522594523</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>10.65733927261868</v>
+        <v>36.445741766832334</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15072,23 +15249,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>6.9147538386526222</v>
+        <v>12.580433504851692</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>8.1513658368462085</v>
+        <v>15.394637813364223</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>9.1767776359081488</v>
+        <v>27.364624935149575</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>9.7952835004904841</v>
+        <v>36.912847743898624</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>11.086775141303123</v>
+        <v>41.092097205957991</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15098,40 +15275,40 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>6.8035787344075898</v>
+        <v>11.63214203189</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>8.0525145309932462</v>
+        <v>14.575175561299575</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>9.1767776359081488</v>
+        <v>28.191877814792271</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>9.8950183725208571</v>
+        <v>40.203891743647631</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>11.483411050862937</v>
+        <v>45.737862184255519</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B73" s="175" t="s">
+        <v>119</v>
+      </c>
+      <c r="C73" s="175" t="s">
+        <v>134</v>
+      </c>
+      <c r="D73" s="175" t="s">
+        <v>114</v>
+      </c>
+      <c r="E73" s="176" t="s">
+        <v>115</v>
+      </c>
+      <c r="F73" s="176" t="s">
         <v>121</v>
-      </c>
-      <c r="C73" s="175" t="s">
-        <v>136</v>
-      </c>
-      <c r="D73" s="175" t="s">
-        <v>116</v>
-      </c>
-      <c r="E73" s="176" t="s">
-        <v>117</v>
-      </c>
-      <c r="F73" s="176" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
@@ -15141,19 +15318,19 @@
       </c>
       <c r="C74" s="146">
         <f>Scenarios!C56</f>
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="D74" s="149">
         <f>Scenarios!C55</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>10.214608163659173</v>
+        <v>28.125362910162355</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
@@ -15163,19 +15340,19 @@
       </c>
       <c r="C75" s="146">
         <f>Scenarios!C38</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="D75" s="149">
         <f>Scenarios!C37</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>9.4067747622364397</v>
+        <v>24.872731830523417</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
-        <v>0.22499999999999992</v>
+        <v>0.192</v>
       </c>
       <c r="H75" s="124"/>
     </row>
@@ -15186,19 +15363,19 @@
       </c>
       <c r="C76" s="146">
         <f>Scenarios!C26</f>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D76" s="149">
         <f>Scenarios!C25</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>9.1767776359081505</v>
+        <v>23.629330229954228</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
-        <v>0.495</v>
+        <v>0.57599999999999996</v>
       </c>
       <c r="H76" s="124"/>
     </row>
@@ -15213,15 +15390,15 @@
       </c>
       <c r="D77" s="149">
         <f>Scenarios!C31</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>8.6878498551971095</v>
+        <v>20.931555394224837</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
-        <v>0.18</v>
+        <v>0.192</v>
       </c>
       <c r="H77" s="124"/>
     </row>
@@ -15232,19 +15409,19 @@
       </c>
       <c r="C78" s="146">
         <f>Scenarios!C50</f>
-        <v>-0.2</v>
+        <v>-0.08</v>
       </c>
       <c r="D78" s="149">
         <f>Scenarios!C49</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>7.3422922836394369</v>
+        <v>17.720125792249224</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
@@ -15256,20 +15433,20 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="159" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="C80" s="159" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C81" s="159" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C82" s="159" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="92" spans="3:3" x14ac:dyDescent="0.35">
@@ -15321,39 +15498,39 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="283" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="I2" s="284"/>
     </row>
     <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="163" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H3" s="282">
         <v>0</v>
       </c>
       <c r="I3" s="270">
         <f>-Market_Price</f>
-        <v>-7.9</v>
+        <v>-15.4</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" s="156" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C4" s="124">
         <v>3</v>
       </c>
       <c r="D4" s="124"/>
       <c r="E4" s="159" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F4" s="159"/>
       <c r="H4" s="282">
@@ -15361,7 +15538,7 @@
       </c>
       <c r="I4" s="270">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.57999999999999996</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -15370,19 +15547,19 @@
       </c>
       <c r="I5" s="270">
         <f t="shared" si="0"/>
-        <v>0.57999999999999996</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B6" s="163" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C6" s="110">
         <f>Valuation_Model!C3</f>
-        <v>1000000</v>
+        <v>1000</v>
       </c>
       <c r="E6" s="103" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="F6" s="103"/>
       <c r="H6" s="282">
@@ -15390,26 +15567,26 @@
       </c>
       <c r="I6" s="270">
         <f t="shared" si="0"/>
-        <v>9.6806872475781418</v>
+        <v>24.681827133653531</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="103" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
-        <v>2337</v>
+        <v>1876773</v>
       </c>
       <c r="D7" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="346" t="str">
+      <c r="E7" s="347" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
-        <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for SINO LAND(0083.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
-      </c>
-      <c r="F7" s="346"/>
+        <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 六福珠宝(0590.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
+      </c>
+      <c r="F7" s="347"/>
       <c r="H7" s="282">
         <v>4</v>
       </c>
@@ -15420,18 +15597,18 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="103" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
-        <v>2772.792068232593</v>
+        <v>1294904.5955406395</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="346"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="282">
         <v>5</v>
       </c>
@@ -15442,18 +15619,18 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" s="103" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
-        <v>2524.2804082649359</v>
+        <v>1162832.9466554797</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="282">
         <v>6</v>
       </c>
@@ -15463,8 +15640,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="346"/>
-      <c r="F10" s="346"/>
+      <c r="E10" s="347"/>
+      <c r="F10" s="347"/>
       <c r="H10" s="282">
         <v>7</v>
       </c>
@@ -15475,10 +15652,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="163" t="s">
-        <v>294</v>
-      </c>
-      <c r="E11" s="346"/>
-      <c r="F11" s="346"/>
+        <v>283</v>
+      </c>
+      <c r="E11" s="347"/>
+      <c r="F11" s="347"/>
       <c r="H11" s="282">
         <v>8</v>
       </c>
@@ -15489,15 +15666,15 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B12" s="122" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C12" s="162" t="e">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
       <c r="D12" s="162"/>
-      <c r="E12" s="346"/>
-      <c r="F12" s="346"/>
+      <c r="E12" s="347"/>
+      <c r="F12" s="347"/>
       <c r="H12" s="282">
         <v>9</v>
       </c>
@@ -15508,14 +15685,14 @@
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B13" s="152" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C13" s="162" t="e">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E13" s="346"/>
-      <c r="F13" s="346"/>
+      <c r="E13" s="347"/>
+      <c r="F13" s="347"/>
       <c r="H13" s="282">
         <v>10</v>
       </c>
@@ -15526,18 +15703,18 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="103" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C14" s="162" t="e">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E14" s="346"/>
-      <c r="F14" s="346"/>
+      <c r="E14" s="347"/>
+      <c r="F14" s="347"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -15546,247 +15723,247 @@
     </row>
     <row r="17" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B17" s="112" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E17" s="163" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C18" s="154">
-        <v>10</v>
-      </c>
-      <c r="E18" s="346" t="s">
-        <v>360</v>
-      </c>
-      <c r="F18" s="347"/>
+        <v>5</v>
+      </c>
+      <c r="E18" s="347" t="s">
+        <v>345</v>
+      </c>
+      <c r="F18" s="348"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="347"/>
-      <c r="F19" s="347"/>
+      <c r="E19" s="348"/>
+      <c r="F19" s="348"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
-        <v>329</v>
-      </c>
-      <c r="E20" s="347"/>
-      <c r="F20" s="347"/>
+        <v>315</v>
+      </c>
+      <c r="E20" s="348"/>
+      <c r="F20" s="348"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
-        <v>7.9</v>
+        <v>15.4</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="347"/>
-      <c r="F21" s="347"/>
+      <c r="E21" s="348"/>
+      <c r="F21" s="348"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
-        <v>9.1767776359081505</v>
+        <v>22.830518776962066</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="347"/>
-      <c r="F22" s="347"/>
+      <c r="E22" s="348"/>
+      <c r="F22" s="348"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E24" s="163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F24" s="163"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C25" s="170">
         <f>C18</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D25" s="167"/>
-      <c r="E25" s="345"/>
-      <c r="F25" s="345"/>
+      <c r="E25" s="346"/>
+      <c r="F25" s="346"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C26" s="168">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D26" s="168"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="E26" s="346"/>
+      <c r="F26" s="346"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
-        <v>9.1767776359081505</v>
+        <v>23.629330229954228</v>
       </c>
       <c r="D27" s="164" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="345"/>
-      <c r="F27" s="345"/>
+      <c r="E27" s="346"/>
+      <c r="F27" s="346"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C28" s="169">
-        <v>0.55000000000000004</v>
+        <v>0.6</v>
       </c>
       <c r="D28" s="169"/>
-      <c r="E28" s="345"/>
-      <c r="F28" s="345"/>
+      <c r="E28" s="346"/>
+      <c r="F28" s="346"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E30" s="163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F30" s="163"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C31" s="170">
         <f>C18</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D31" s="167"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="E31" s="346"/>
+      <c r="F31" s="346"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C32" s="168">
         <v>-0.05</v>
       </c>
       <c r="D32" s="168"/>
-      <c r="E32" s="345"/>
-      <c r="F32" s="345"/>
+      <c r="E32" s="346"/>
+      <c r="F32" s="346"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
-        <v>8.6878498551971095</v>
+        <v>20.931555394224837</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="345"/>
-      <c r="F33" s="345"/>
+      <c r="E33" s="346"/>
+      <c r="F33" s="346"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C34" s="169">
         <v>0.2</v>
       </c>
       <c r="D34" s="169"/>
-      <c r="E34" s="345"/>
-      <c r="F34" s="345"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E36" s="163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F36" s="163"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C37" s="170">
         <f>C18</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D37" s="167"/>
-      <c r="E37" s="345"/>
-      <c r="F37" s="345"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C38" s="168">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="D38" s="168"/>
-      <c r="E38" s="345"/>
-      <c r="F38" s="345"/>
+      <c r="E38" s="346"/>
+      <c r="F38" s="346"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
-        <v>9.4067747622364397</v>
+        <v>24.872731830523417</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="345"/>
-      <c r="F39" s="345"/>
+      <c r="E39" s="346"/>
+      <c r="F39" s="346"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C40" s="171">
         <f>1-C28-C34</f>
-        <v>0.24999999999999994</v>
+        <v>0.2</v>
       </c>
       <c r="D40" s="169"/>
-      <c r="E40" s="345"/>
-      <c r="F40" s="345"/>
+      <c r="E40" s="346"/>
+      <c r="F40" s="346"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>9.1364913613480141</v>
+        <v>23.338455582922187</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -15795,7 +15972,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B44" s="36" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -15804,15 +15981,15 @@
     </row>
     <row r="45" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B45" s="112" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C46" s="154">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E46" s="103"/>
       <c r="F46" s="103"/>
@@ -15824,134 +16001,134 @@
     </row>
     <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B48" s="163" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E48" s="163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F48" s="163"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C49" s="170">
         <f>C46</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D49" s="167"/>
-      <c r="E49" s="345"/>
-      <c r="F49" s="345"/>
+      <c r="E49" s="346"/>
+      <c r="F49" s="346"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C50" s="168">
-        <v>-0.2</v>
+        <v>-0.08</v>
       </c>
       <c r="D50" s="168"/>
-      <c r="E50" s="345"/>
-      <c r="F50" s="345"/>
+      <c r="E50" s="346"/>
+      <c r="F50" s="346"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
-        <v>7.3422922836394369</v>
+        <v>17.720125792249224</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="345"/>
-      <c r="F51" s="345"/>
+      <c r="E51" s="346"/>
+      <c r="F51" s="346"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C52" s="169">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="D52" s="169"/>
-      <c r="E52" s="345"/>
-      <c r="F52" s="345"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="E54" s="163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F54" s="163"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C55" s="170">
         <f>C46</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D55" s="167"/>
-      <c r="E55" s="345"/>
-      <c r="F55" s="345"/>
+      <c r="E55" s="346"/>
+      <c r="F55" s="346"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C56" s="168">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="D56" s="168"/>
-      <c r="E56" s="345"/>
-      <c r="F56" s="345"/>
+      <c r="E56" s="346"/>
+      <c r="F56" s="346"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
-        <v>10.214608163659173</v>
+        <v>28.125362910162355</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="345"/>
-      <c r="F57" s="345"/>
+      <c r="E57" s="346"/>
+      <c r="F57" s="346"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C58" s="169">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="D58" s="169"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="E58" s="346"/>
+      <c r="F58" s="346"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>9.1006872475781417</v>
+        <v>23.321827133653532</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="F60" s="318">
         <f>Thesis!E20</f>
@@ -15960,7 +16137,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -15969,85 +16146,85 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="E63" s="288" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C64" s="170">
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="287" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B65" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C65" s="155">
-        <v>-7.3000000000000001E-3</v>
+        <v>6.4006284479398504E-3</v>
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="287" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B66" s="103" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
-        <v>9.0981264288878361</v>
+        <v>23.325699825167451</v>
       </c>
       <c r="D66" s="164" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E66" s="287" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="E68" s="288" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E69" s="138"/>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E70" s="287" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="C71" s="279" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16057,23 +16234,23 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="C72" s="278" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E72" s="138" t="s">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="F72" s="335">
         <f>BS!D89/C60</f>
-        <v>0.63122414236360114</v>
+        <v>-8.2632171394856124E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B74" s="36" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -16082,12 +16259,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B75" s="112" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="281" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="C76" s="280">
         <f>F60</f>
@@ -16097,11 +16274,11 @@
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="103" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C77" s="177">
         <f>Normalized_FCF!C90</f>
-        <v>0.57999999999999996</v>
+        <v>1.36</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -16110,25 +16287,25 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="C80" s="171">
-        <f>Thesis!C121</f>
+        <f>Thesis!C123</f>
         <v>0.2</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B81" s="103" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.2217592592592592</v>
+        <v>2.8648148148148147</v>
       </c>
       <c r="D81" s="120"/>
       <c r="E81" s="103"/>
@@ -16136,32 +16313,32 @@
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B82" s="103" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>5.2666014164225361</v>
+        <v>13.496427739382831</v>
       </c>
       <c r="D82" s="120"/>
     </row>
     <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B83" s="114" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>6.4883606756817951</v>
+        <v>16.361242554197645</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E83" s="150" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F83" s="335">
         <f>(1-C83/C60)</f>
-        <v>0.28704717576043881</v>
+        <v>0.29845794412101279</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16169,16 +16346,16 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
-        <v>7.9</v>
+        <v>15.4</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16187,11 +16364,11 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1185224959199922</v>
+        <v>0.22622690546409729</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
@@ -16199,7 +16376,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="326" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="F89" s="323"/>
       <c r="G89" s="2"/>
@@ -16207,30 +16384,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="319" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="F90" s="324" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="322"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="320" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="F91" s="324" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="322"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="321" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="F92" s="325" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="322"/>

--- a/financial_models/templates/Valuation_v2.0.xlsx
+++ b/financial_models/templates/Valuation_v2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43BD4BA1-65E2-4CF1-9AF6-8D236ED45627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20802F47-1D5C-4D80-A2D1-23D4EC2E0B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="411">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1353,10 +1353,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>FCFE/Market Cap =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Latest FCFE =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2172,6 +2168,149 @@
   </si>
   <si>
     <t>CFI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 6:  Risk Analysis</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Key Risk Factors</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>To identify and assess the key risk factors inherent in this valuation model, focusing on those with the greatest potential impact on the final result.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Sustainable Revenue &amp; Margins</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Capital Expenditures</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Working Capital</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Accuracy of Normalized FCFE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>, which is affacted by uncertainties include:</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation, prioritizing consistency and long-term decision-making over market-derived metrics.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium to account for ownership risks.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- The Expected Equity Value is heavily dependent on the specific growth rates (HGR), durations (HGP), and probabilities assigned to each scenario. These are inherently forecasts about an uncertain future.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- The extreme scenarios (“Snowball”, “Devil’s Advocate”) have low probabilities; if market conditions shift drastically, these might become more relevant than anticipated.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Appropriateness of Cost of Equity</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Reliability of Growth Scenarios</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Macroeconomic Sensitivity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Input Cost Volatility</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Intense Competition</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>External &amp; Company-Specific Risks</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normalized FCFE/Market Cap =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2839,7 +2978,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="349">
+  <cellXfs count="351">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3543,23 +3682,29 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3849,7 +3994,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:J152"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -3869,10 +4014,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="337" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F1" s="290" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -3901,13 +4046,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C5" s="48" t="s">
+        <v>368</v>
+      </c>
+      <c r="D5" s="49" t="s">
         <v>369</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -3934,7 +4079,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C8" s="285">
         <v>6</v>
@@ -3970,24 +4115,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="341" t="s">
-        <v>380</v>
-      </c>
-      <c r="C12" s="341"/>
-      <c r="D12" s="341"/>
-      <c r="E12" s="341"/>
-      <c r="F12" s="341"/>
+      <c r="B12" s="339" t="s">
+        <v>379</v>
+      </c>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3997,7 +4142,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C16" s="48" t="s">
         <v>41</v>
@@ -4023,13 +4168,13 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C19" s="255">
         <v>0.2</v>
@@ -4046,7 +4191,7 @@
         <v>16.361242554197645</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E20" s="336">
         <v>3</v>
@@ -4054,7 +4199,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
@@ -4069,7 +4214,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="253" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4078,22 +4223,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="341" t="s">
-        <v>381</v>
-      </c>
-      <c r="C25" s="341"/>
-      <c r="D25" s="341"/>
-      <c r="E25" s="341"/>
-      <c r="F25" s="341"/>
+      <c r="B25" s="339" t="s">
+        <v>380</v>
+      </c>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="339" t="s">
-        <v>354</v>
-      </c>
-      <c r="C26" s="339"/>
-      <c r="D26" s="339"/>
-      <c r="E26" s="339"/>
-      <c r="F26" s="339"/>
+      <c r="B26" s="341" t="s">
+        <v>353</v>
+      </c>
+      <c r="C26" s="341"/>
+      <c r="D26" s="341"/>
+      <c r="E26" s="341"/>
+      <c r="F26" s="341"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -4198,7 +4343,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
@@ -4213,7 +4358,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
@@ -4281,12 +4426,12 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B50" s="340" t="s">
-        <v>353</v>
-      </c>
-      <c r="C50" s="344"/>
-      <c r="D50" s="344"/>
-      <c r="E50" s="344"/>
-      <c r="F50" s="344"/>
+        <v>352</v>
+      </c>
+      <c r="C50" s="343"/>
+      <c r="D50" s="343"/>
+      <c r="E50" s="343"/>
+      <c r="F50" s="343"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4302,26 +4447,26 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="341" t="s">
-        <v>358</v>
-      </c>
-      <c r="C53" s="341"/>
-      <c r="D53" s="341"/>
-      <c r="E53" s="341"/>
-      <c r="F53" s="341"/>
+      <c r="B53" s="339" t="s">
+        <v>357</v>
+      </c>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="341" t="s">
-        <v>382</v>
-      </c>
-      <c r="C54" s="341"/>
-      <c r="D54" s="341"/>
-      <c r="E54" s="341"/>
-      <c r="F54" s="341"/>
+      <c r="B54" s="339" t="s">
+        <v>381</v>
+      </c>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
@@ -4347,7 +4492,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="260" t="s">
-        <v>273</v>
+        <v>410</v>
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
@@ -4356,7 +4501,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="260" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
@@ -4365,7 +4510,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="253" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4378,22 +4523,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="341" t="s">
-        <v>383</v>
-      </c>
-      <c r="C63" s="341"/>
-      <c r="D63" s="341"/>
-      <c r="E63" s="341"/>
-      <c r="F63" s="341"/>
+      <c r="B63" s="339" t="s">
+        <v>382</v>
+      </c>
+      <c r="C63" s="339"/>
+      <c r="D63" s="339"/>
+      <c r="E63" s="339"/>
+      <c r="F63" s="339"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="339" t="s">
+      <c r="B64" s="341" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="339"/>
-      <c r="D64" s="339"/>
-      <c r="E64" s="339"/>
-      <c r="F64" s="339"/>
+      <c r="C64" s="341"/>
+      <c r="D64" s="341"/>
+      <c r="E64" s="341"/>
+      <c r="F64" s="341"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4402,7 +4547,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C67" s="317">
         <v>0.08</v>
@@ -4410,26 +4555,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C68" s="269">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="292" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C69" s="269">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="292" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4446,27 +4591,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="338" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C72" s="125"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="341" t="s">
+      <c r="B73" s="339" t="s">
+        <v>383</v>
+      </c>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="339" t="s">
         <v>384</v>
       </c>
-      <c r="C73" s="341"/>
-      <c r="D73" s="341"/>
-      <c r="E73" s="341"/>
-      <c r="F73" s="341"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="341" t="s">
-        <v>385</v>
-      </c>
-      <c r="C74" s="341"/>
-      <c r="D74" s="341"/>
-      <c r="E74" s="341"/>
-      <c r="F74" s="341"/>
+      <c r="C74" s="339"/>
+      <c r="D74" s="339"/>
+      <c r="E74" s="339"/>
+      <c r="F74" s="339"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4478,7 +4623,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C77" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4491,7 +4636,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="253" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4503,13 +4648,13 @@
       <c r="A80" s="239"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="341" t="s">
-        <v>386</v>
-      </c>
-      <c r="C81" s="341"/>
-      <c r="D81" s="341"/>
-      <c r="E81" s="341"/>
-      <c r="F81" s="341"/>
+      <c r="B81" s="339" t="s">
+        <v>385</v>
+      </c>
+      <c r="C81" s="339"/>
+      <c r="D81" s="339"/>
+      <c r="E81" s="339"/>
+      <c r="F81" s="339"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4522,13 +4667,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="341" t="s">
-        <v>359</v>
-      </c>
-      <c r="C85" s="341"/>
-      <c r="D85" s="341"/>
-      <c r="E85" s="341"/>
-      <c r="F85" s="341"/>
+      <c r="B85" s="339" t="s">
+        <v>358</v>
+      </c>
+      <c r="C85" s="339"/>
+      <c r="D85" s="339"/>
+      <c r="E85" s="339"/>
+      <c r="F85" s="339"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4545,7 +4690,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C87" s="254">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4589,7 +4734,7 @@
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="47" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C92" s="254">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
@@ -4620,7 +4765,7 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="47" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C96" s="254">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
@@ -4632,17 +4777,17 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="341" t="s">
-        <v>387</v>
-      </c>
-      <c r="C98" s="341"/>
-      <c r="D98" s="341"/>
-      <c r="E98" s="341"/>
-      <c r="F98" s="341"/>
+      <c r="B98" s="339" t="s">
+        <v>386</v>
+      </c>
+      <c r="C98" s="339"/>
+      <c r="D98" s="339"/>
+      <c r="E98" s="339"/>
+      <c r="F98" s="339"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C100" s="254">
         <f>Valuation_Model!C12</f>
@@ -4655,7 +4800,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="253" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4665,7 +4810,7 @@
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B104" s="340" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C104" s="340"/>
       <c r="D104" s="340"/>
@@ -4813,17 +4958,17 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
-        <v>391</v>
-      </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="B115" s="344" t="s">
+        <v>390</v>
+      </c>
+      <c r="C115" s="344"/>
+      <c r="D115" s="344"/>
+      <c r="E115" s="344"/>
+      <c r="F115" s="344"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="253" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4832,22 +4977,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
+      <c r="B119" s="342" t="s">
+        <v>388</v>
+      </c>
+      <c r="C119" s="342"/>
+      <c r="D119" s="342"/>
+      <c r="E119" s="342"/>
+      <c r="F119" s="342"/>
+    </row>
+    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B120" s="339" t="s">
         <v>389</v>
       </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
-    </row>
-    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="341" t="s">
-        <v>390</v>
-      </c>
-      <c r="C120" s="341"/>
-      <c r="D120" s="341"/>
-      <c r="E120" s="341"/>
-      <c r="F120" s="341"/>
+      <c r="C120" s="339"/>
+      <c r="D120" s="339"/>
+      <c r="E120" s="339"/>
+      <c r="F120" s="339"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="240" t="s">
@@ -4865,7 +5010,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B123" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C123" s="256">
         <f>C19</f>
@@ -4910,7 +5055,7 @@
         <v>13.496427739382831</v>
       </c>
     </row>
-    <row r="129" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B129" s="82" t="s">
         <v>262</v>
       </c>
@@ -4923,7 +5068,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B130" s="244" t="s">
         <v>264</v>
       </c>
@@ -4932,8 +5077,124 @@
         <v>0.29845794412101279</v>
       </c>
     </row>
+    <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A132" s="253" t="s">
+        <v>394</v>
+      </c>
+      <c r="B132" s="36"/>
+      <c r="C132" s="36"/>
+      <c r="D132" s="36"/>
+      <c r="E132" s="36"/>
+      <c r="F132" s="36"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="346" t="s">
+        <v>396</v>
+      </c>
+      <c r="C134" s="339"/>
+      <c r="D134" s="339"/>
+      <c r="E134" s="339"/>
+      <c r="F134" s="339"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="240" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B137" s="343" t="s">
+        <v>400</v>
+      </c>
+      <c r="C137" s="343"/>
+      <c r="D137" s="343"/>
+      <c r="E137" s="343"/>
+      <c r="F137" s="343"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B138" s="244" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B139" s="244" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="244" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B142" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B143" s="340" t="s">
+        <v>401</v>
+      </c>
+      <c r="C143" s="340"/>
+      <c r="D143" s="340"/>
+      <c r="E143" s="340"/>
+      <c r="F143" s="340"/>
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B145" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B146" s="345" t="s">
+        <v>402</v>
+      </c>
+      <c r="C146" s="345"/>
+      <c r="D146" s="345"/>
+      <c r="E146" s="345"/>
+      <c r="F146" s="345"/>
+    </row>
+    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B147" s="345" t="s">
+        <v>403</v>
+      </c>
+      <c r="C147" s="345"/>
+      <c r="D147" s="345"/>
+      <c r="E147" s="345"/>
+      <c r="F147" s="345"/>
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B149" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B150" s="244" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B151" s="244" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B152" s="244" t="s">
+        <v>408</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -4950,15 +5211,9 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5351,7 +5606,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C22" s="184"/>
       <c r="D22" s="184"/>
@@ -5367,7 +5622,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C23" s="184"/>
       <c r="D23" s="184"/>
@@ -5383,7 +5638,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C24" s="184"/>
       <c r="D24" s="184"/>
@@ -7944,13 +8199,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C45" s="267" t="s">
         <v>138</v>
       </c>
       <c r="D45" s="209" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F45" s="293" t="s">
         <v>60</v>
@@ -7958,7 +8213,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C46" s="191">
         <f>G29</f>
@@ -8111,7 +8366,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="161" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C61" s="268" t="s">
         <v>139</v>
@@ -8134,7 +8389,7 @@
         <v>-2.0915594459950692E-3</v>
       </c>
       <c r="F62" s="289" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8156,7 +8411,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="210" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F65" s="293" t="s">
         <v>60</v>
@@ -8223,7 +8478,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="291" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C72" s="267" t="s">
         <v>97</v>
@@ -8235,7 +8490,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8246,12 +8501,12 @@
         <v>-1187304.6396666665</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="294" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C74" s="295">
         <f>-$C$66/C73</f>
@@ -8262,12 +8517,12 @@
         <v>1.6829876118070222</v>
       </c>
       <c r="F74" s="289" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C75" s="299"/>
       <c r="D75" s="298">
@@ -8275,12 +8530,12 @@
         <v>1187304.6396666665</v>
       </c>
       <c r="F75" s="289" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="296" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C76" s="297"/>
       <c r="D76" s="333">
@@ -8288,7 +8543,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="289" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8364,7 +8619,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8375,15 +8630,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="D85" s="276" t="s">
         <v>301</v>
-      </c>
-      <c r="D85" s="276" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="273" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8400,7 +8655,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="273" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8434,7 +8689,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
@@ -9305,7 +9560,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="307" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="201"/>
@@ -9330,7 +9585,7 @@
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="307" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="202"/>
@@ -9658,7 +9913,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="306" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9718,7 +9973,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="306" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9842,7 +10097,7 @@
         <v>-254107</v>
       </c>
       <c r="E33" s="306" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
@@ -9900,7 +10155,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="306" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="186">
@@ -10208,7 +10463,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="305" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10347,7 +10602,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
@@ -10402,7 +10657,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="329" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
@@ -10535,7 +10790,7 @@
         <v>1.4501413508729523E-2</v>
       </c>
       <c r="E53" s="305" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10562,7 +10817,7 @@
         <v>2.9286626219579916E-2</v>
       </c>
       <c r="E54" s="305" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10877,7 +11132,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="306" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
@@ -11438,7 +11693,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="306" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12117,7 +12372,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -14037,10 +14292,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="347" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="345"/>
+      <c r="F6" s="347"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14055,8 +14310,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="345"/>
-      <c r="F7" s="345"/>
+      <c r="E7" s="347"/>
+      <c r="F7" s="347"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14071,8 +14326,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="345"/>
-      <c r="F8" s="345"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14087,8 +14342,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="345"/>
-      <c r="F9" s="345"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15433,7 +15688,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="159" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C80" s="159" t="s">
         <v>107</v>
@@ -15505,7 +15760,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="283" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I2" s="284"/>
     </row>
@@ -15559,7 +15814,7 @@
         <v>1000</v>
       </c>
       <c r="E6" s="103" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F6" s="103"/>
       <c r="H6" s="282">
@@ -15572,7 +15827,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="103" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
@@ -15582,11 +15837,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="347" t="str">
+      <c r="E7" s="349" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 六福珠宝(0590.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="347"/>
+      <c r="F7" s="349"/>
       <c r="H7" s="282">
         <v>4</v>
       </c>
@@ -15607,8 +15862,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="347"/>
-      <c r="F8" s="347"/>
+      <c r="E8" s="349"/>
+      <c r="F8" s="349"/>
       <c r="H8" s="282">
         <v>5</v>
       </c>
@@ -15629,8 +15884,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
+      <c r="E9" s="349"/>
+      <c r="F9" s="349"/>
       <c r="H9" s="282">
         <v>6</v>
       </c>
@@ -15640,8 +15895,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="347"/>
-      <c r="F10" s="347"/>
+      <c r="E10" s="349"/>
+      <c r="F10" s="349"/>
       <c r="H10" s="282">
         <v>7</v>
       </c>
@@ -15652,10 +15907,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="163" t="s">
-        <v>283</v>
-      </c>
-      <c r="E11" s="347"/>
-      <c r="F11" s="347"/>
+        <v>282</v>
+      </c>
+      <c r="E11" s="349"/>
+      <c r="F11" s="349"/>
       <c r="H11" s="282">
         <v>8</v>
       </c>
@@ -15673,8 +15928,8 @@
         <v>#VALUE!</v>
       </c>
       <c r="D12" s="162"/>
-      <c r="E12" s="347"/>
-      <c r="F12" s="347"/>
+      <c r="E12" s="349"/>
+      <c r="F12" s="349"/>
       <c r="H12" s="282">
         <v>9</v>
       </c>
@@ -15691,8 +15946,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E13" s="347"/>
-      <c r="F13" s="347"/>
+      <c r="E13" s="349"/>
+      <c r="F13" s="349"/>
       <c r="H13" s="282">
         <v>10</v>
       </c>
@@ -15709,8 +15964,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E14" s="347"/>
-      <c r="F14" s="347"/>
+      <c r="E14" s="349"/>
+      <c r="F14" s="349"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -15726,7 +15981,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="163" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -15736,25 +15991,25 @@
       <c r="C18" s="154">
         <v>5</v>
       </c>
-      <c r="E18" s="347" t="s">
-        <v>345</v>
-      </c>
-      <c r="F18" s="348"/>
+      <c r="E18" s="349" t="s">
+        <v>344</v>
+      </c>
+      <c r="F18" s="350"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="348"/>
-      <c r="F19" s="348"/>
+      <c r="E19" s="350"/>
+      <c r="F19" s="350"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
-        <v>315</v>
-      </c>
-      <c r="E20" s="348"/>
-      <c r="F20" s="348"/>
+        <v>314</v>
+      </c>
+      <c r="E20" s="350"/>
+      <c r="F20" s="350"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
@@ -15764,12 +16019,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="348"/>
-      <c r="F21" s="348"/>
+      <c r="E21" s="350"/>
+      <c r="F21" s="350"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
@@ -15779,8 +16034,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="348"/>
-      <c r="F22" s="348"/>
+      <c r="E22" s="350"/>
+      <c r="F22" s="350"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
@@ -15800,8 +16055,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="167"/>
-      <c r="E25" s="346"/>
-      <c r="F25" s="346"/>
+      <c r="E25" s="348"/>
+      <c r="F25" s="348"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
@@ -15811,8 +16066,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="168"/>
-      <c r="E26" s="346"/>
-      <c r="F26" s="346"/>
+      <c r="E26" s="348"/>
+      <c r="F26" s="348"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
@@ -15826,8 +16081,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="346"/>
-      <c r="F27" s="346"/>
+      <c r="E27" s="348"/>
+      <c r="F27" s="348"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
@@ -15837,8 +16092,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="169"/>
-      <c r="E28" s="346"/>
-      <c r="F28" s="346"/>
+      <c r="E28" s="348"/>
+      <c r="F28" s="348"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
@@ -15858,8 +16113,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="167"/>
-      <c r="E31" s="346"/>
-      <c r="F31" s="346"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
@@ -15869,8 +16124,8 @@
         <v>-0.05</v>
       </c>
       <c r="D32" s="168"/>
-      <c r="E32" s="346"/>
-      <c r="F32" s="346"/>
+      <c r="E32" s="348"/>
+      <c r="F32" s="348"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
@@ -15884,8 +16139,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="346"/>
-      <c r="F33" s="346"/>
+      <c r="E33" s="348"/>
+      <c r="F33" s="348"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
@@ -15895,8 +16150,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="169"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="E34" s="348"/>
+      <c r="F34" s="348"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
@@ -15916,8 +16171,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="167"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="E37" s="348"/>
+      <c r="F37" s="348"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
@@ -15927,8 +16182,8 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="168"/>
-      <c r="E38" s="346"/>
-      <c r="F38" s="346"/>
+      <c r="E38" s="348"/>
+      <c r="F38" s="348"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
@@ -15942,8 +16197,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="346"/>
-      <c r="F39" s="346"/>
+      <c r="E39" s="348"/>
+      <c r="F39" s="348"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
@@ -15954,8 +16209,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="169"/>
-      <c r="E40" s="346"/>
-      <c r="F40" s="346"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
@@ -16017,8 +16272,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="167"/>
-      <c r="E49" s="346"/>
-      <c r="F49" s="346"/>
+      <c r="E49" s="348"/>
+      <c r="F49" s="348"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
@@ -16028,8 +16283,8 @@
         <v>-0.08</v>
       </c>
       <c r="D50" s="168"/>
-      <c r="E50" s="346"/>
-      <c r="F50" s="346"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
@@ -16043,8 +16298,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="346"/>
-      <c r="F51" s="346"/>
+      <c r="E51" s="348"/>
+      <c r="F51" s="348"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
@@ -16054,12 +16309,12 @@
         <v>0.02</v>
       </c>
       <c r="D52" s="169"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="E52" s="348"/>
+      <c r="F52" s="348"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E54" s="163" t="s">
         <v>151</v>
@@ -16075,8 +16330,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="167"/>
-      <c r="E55" s="346"/>
-      <c r="F55" s="346"/>
+      <c r="E55" s="348"/>
+      <c r="F55" s="348"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
@@ -16086,8 +16341,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="168"/>
-      <c r="E56" s="346"/>
-      <c r="F56" s="346"/>
+      <c r="E56" s="348"/>
+      <c r="F56" s="348"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
@@ -16101,8 +16356,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="346"/>
-      <c r="F57" s="346"/>
+      <c r="E57" s="348"/>
+      <c r="F57" s="348"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
@@ -16112,8 +16367,8 @@
         <v>0.02</v>
       </c>
       <c r="D58" s="169"/>
-      <c r="E58" s="346"/>
-      <c r="F58" s="346"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
@@ -16128,7 +16383,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F60" s="318">
         <f>Thesis!E20</f>
@@ -16137,7 +16392,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16146,10 +16401,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E63" s="288" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16161,7 +16416,7 @@
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="287" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16173,7 +16428,7 @@
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="287" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16189,20 +16444,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="287" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E68" s="288" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16212,19 +16467,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="287" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C71" s="279" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16234,14 +16489,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C72" s="278" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="138" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F72" s="335">
         <f>BS!D89/C60</f>
@@ -16264,7 +16519,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="281" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C76" s="280">
         <f>F60</f>
@@ -16287,12 +16542,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C80" s="171">
         <f>Thesis!C123</f>
@@ -16346,12 +16601,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
@@ -16364,7 +16619,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -16376,7 +16631,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="326" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F89" s="323"/>
       <c r="G89" s="2"/>
@@ -16384,30 +16639,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="319" t="s">
+        <v>339</v>
+      </c>
+      <c r="F90" s="324" t="s">
         <v>340</v>
-      </c>
-      <c r="F90" s="324" t="s">
-        <v>341</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="322"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="320" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F91" s="324" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="322"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="321" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F92" s="325" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="322"/>

--- a/financial_models/templates/Valuation_v2.0.xlsx
+++ b/financial_models/templates/Valuation_v2.0.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20802F47-1D5C-4D80-A2D1-23D4EC2E0B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAAAD931-CCEA-46A1-AC8B-04B64F444114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="415">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1805,14 +1805,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>六福珠宝</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>0590.HK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CNS_05</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2311,6 +2303,30 @@
   </si>
   <si>
     <t>Normalized FCFE/Market Cap =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0857.HK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国石油股份</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFO/Net Income</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFO/FCFE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Net Change in Cash</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2338,7 +2354,7 @@
     <numFmt numFmtId="192" formatCode="0.0\x"/>
     <numFmt numFmtId="193" formatCode="0\x"/>
   </numFmts>
-  <fonts count="58" x14ac:knownFonts="1">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2771,6 +2787,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -2978,7 +3001,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="351">
+  <cellXfs count="353">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3682,6 +3705,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4010,7 +4037,7 @@
         <v>42</v>
       </c>
       <c r="C1" s="44">
-        <v>45730</v>
+        <v>45754</v>
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="337" t="s">
@@ -4037,22 +4064,22 @@
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B4" s="45" t="str">
         <f>D5&amp;" Stock Information"</f>
-        <v>0590.HK Stock Information</v>
+        <v>0857.HK Stock Information</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="C5" s="48" t="s">
-        <v>368</v>
+      <c r="C5" s="339" t="s">
+        <v>411</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>369</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4060,7 +4087,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>15.4</v>
+        <v>5.55</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4072,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="51">
-        <v>587107850</v>
+        <v>183020977818</v>
       </c>
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
@@ -4105,7 +4132,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>9041.4608900000003</v>
+        <v>1015766.4268899</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4115,13 +4142,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
-        <v>379</v>
-      </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="B12" s="341" t="s">
+        <v>377</v>
+      </c>
+      <c r="C12" s="341"/>
+      <c r="D12" s="341"/>
+      <c r="E12" s="341"/>
+      <c r="F12" s="341"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4136,7 +4163,7 @@
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
-        <v xml:space="preserve">Low Growth </v>
+        <v xml:space="preserve">Negative Growth </v>
       </c>
       <c r="E15" s="5"/>
     </row>
@@ -4145,7 +4172,7 @@
         <v>361</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>41</v>
+        <v>410</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4155,11 +4182,11 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1</v>
+        <v>0.94030000000000002</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
-        <v>HKD</v>
+        <v>CNY/HKD</v>
       </c>
       <c r="E17" s="5"/>
     </row>
@@ -4168,7 +4195,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4188,7 +4215,7 @@
       </c>
       <c r="C20" s="258">
         <f>C129</f>
-        <v>16.361242554197645</v>
+        <v>6.9522077911095632</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -4199,11 +4226,11 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22622690546409729</v>
+        <v>0.29981048955907563</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4214,7 +4241,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="253" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4223,22 +4250,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
-        <v>380</v>
-      </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="B25" s="341" t="s">
+        <v>378</v>
+      </c>
+      <c r="C25" s="341"/>
+      <c r="D25" s="341"/>
+      <c r="E25" s="341"/>
+      <c r="F25" s="341"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="343" t="s">
         <v>353</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="343"/>
+      <c r="D26" s="343"/>
+      <c r="E26" s="343"/>
+      <c r="F26" s="343"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -4246,17 +4273,17 @@
       </c>
       <c r="C28" s="111">
         <f>Data!C3</f>
-        <v>1000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
+      <c r="B29" s="342" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="C29" s="342"/>
+      <c r="D29" s="342"/>
+      <c r="E29" s="342"/>
+      <c r="F29" s="342"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4264,11 +4291,11 @@
       </c>
       <c r="C30" s="191">
         <f>Normalized_FCF!C8</f>
-        <v>1876773</v>
+        <v>266372</v>
       </c>
       <c r="D30" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -4276,13 +4303,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
+      <c r="B32" s="342" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="C32" s="342"/>
+      <c r="D32" s="342"/>
+      <c r="E32" s="342"/>
+      <c r="F32" s="342"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4290,11 +4317,11 @@
       </c>
       <c r="C33" s="191">
         <f>Normalized_FCF!C9</f>
-        <v>463424</v>
+        <v>229584</v>
       </c>
       <c r="D33" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
@@ -4303,21 +4330,21 @@
       </c>
       <c r="C34" s="191">
         <f>Normalized_FCF!C10</f>
-        <v>-676387</v>
+        <v>-229584</v>
       </c>
       <c r="D34" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
+      <c r="B36" s="342" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="C36" s="342"/>
+      <c r="D36" s="342"/>
+      <c r="E36" s="342"/>
+      <c r="F36" s="342"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4325,21 +4352,21 @@
       </c>
       <c r="C37" s="191">
         <f>Normalized_FCF!C11</f>
-        <v>0</v>
+        <v>18538.000000000004</v>
       </c>
       <c r="D37" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
+      <c r="B39" s="342" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="C39" s="342"/>
+      <c r="D39" s="342"/>
+      <c r="E39" s="342"/>
+      <c r="F39" s="342"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4347,11 +4374,11 @@
       </c>
       <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
-        <v>17217.595540639435</v>
+        <v>8177.2376941676157</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E40" s="327"/>
       <c r="F40" s="327"/>
@@ -4362,11 +4389,11 @@
       </c>
       <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
-        <v>-59596</v>
+        <v>-24063</v>
       </c>
       <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E41" s="327"/>
       <c r="F41" s="327"/>
@@ -4377,11 +4404,11 @@
       </c>
       <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
-        <v>-42378.404459360565</v>
+        <v>-15885.762305832384</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.35">
@@ -4395,21 +4422,21 @@
       </c>
       <c r="C45" s="191">
         <f>Normalized_FCF!C15</f>
-        <v>0</v>
+        <v>-19147</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
+      <c r="B47" s="342" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="C47" s="342"/>
+      <c r="D47" s="342"/>
+      <c r="E47" s="342"/>
+      <c r="F47" s="342"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4417,21 +4444,21 @@
       </c>
       <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
-        <v>-458598.64888515987</v>
+        <v>-67256.059423541898</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
+      <c r="B50" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C50" s="343"/>
-      <c r="D50" s="343"/>
-      <c r="E50" s="343"/>
-      <c r="F50" s="343"/>
+      <c r="C50" s="345"/>
+      <c r="D50" s="345"/>
+      <c r="E50" s="345"/>
+      <c r="F50" s="345"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4443,26 +4470,26 @@
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
+      <c r="B53" s="341" t="s">
         <v>357</v>
       </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="C53" s="341"/>
+      <c r="D53" s="341"/>
+      <c r="E53" s="341"/>
+      <c r="F53" s="341"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
-        <v>381</v>
-      </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="B54" s="341" t="s">
+        <v>379</v>
+      </c>
+      <c r="C54" s="341"/>
+      <c r="D54" s="341"/>
+      <c r="E54" s="341"/>
+      <c r="F54" s="341"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4470,11 +4497,11 @@
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
-        <v>1294904.5955406395</v>
+        <v>306997.23769416759</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
@@ -4483,20 +4510,20 @@
       </c>
       <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
-        <v>1162832.9466554797</v>
+        <v>182621.17827062571</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="260" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C58" s="94">
-        <f>Normalized_FCF!C121</f>
-        <v>0.12861117918914977</v>
+        <f>Normalized_FCF!C125</f>
+        <v>0.16905332700711728</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4505,12 +4532,12 @@
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>8.8311688311688313E-2</v>
+        <v>9.0061347106970835E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="253" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4523,22 +4550,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="339" t="s">
-        <v>382</v>
-      </c>
-      <c r="C63" s="339"/>
-      <c r="D63" s="339"/>
-      <c r="E63" s="339"/>
-      <c r="F63" s="339"/>
+      <c r="B63" s="341" t="s">
+        <v>380</v>
+      </c>
+      <c r="C63" s="341"/>
+      <c r="D63" s="341"/>
+      <c r="E63" s="341"/>
+      <c r="F63" s="341"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="343" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="343"/>
+      <c r="D64" s="343"/>
+      <c r="E64" s="343"/>
+      <c r="F64" s="343"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4591,27 +4618,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="338" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C72" s="125"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
-        <v>383</v>
-      </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
+      <c r="B73" s="341" t="s">
+        <v>381</v>
+      </c>
+      <c r="C73" s="341"/>
+      <c r="D73" s="341"/>
+      <c r="E73" s="341"/>
+      <c r="F73" s="341"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="339" t="s">
-        <v>384</v>
-      </c>
-      <c r="C74" s="339"/>
-      <c r="D74" s="339"/>
-      <c r="E74" s="339"/>
-      <c r="F74" s="339"/>
+      <c r="B74" s="341" t="s">
+        <v>382</v>
+      </c>
+      <c r="C74" s="341"/>
+      <c r="D74" s="341"/>
+      <c r="E74" s="341"/>
+      <c r="F74" s="341"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4627,7 +4654,7 @@
       </c>
       <c r="C77" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>24.757651993911335</v>
+        <v>11.728074561118762</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4636,7 +4663,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="253" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4648,13 +4675,13 @@
       <c r="A80" s="239"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="339" t="s">
-        <v>385</v>
-      </c>
-      <c r="C81" s="339"/>
-      <c r="D81" s="339"/>
-      <c r="E81" s="339"/>
-      <c r="F81" s="339"/>
+      <c r="B81" s="341" t="s">
+        <v>383</v>
+      </c>
+      <c r="C81" s="341"/>
+      <c r="D81" s="341"/>
+      <c r="E81" s="341"/>
+      <c r="F81" s="341"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4667,13 +4694,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="339" t="s">
+      <c r="B85" s="341" t="s">
         <v>358</v>
       </c>
-      <c r="C85" s="339"/>
-      <c r="D85" s="339"/>
-      <c r="E85" s="339"/>
-      <c r="F85" s="339"/>
+      <c r="C85" s="341"/>
+      <c r="D85" s="341"/>
+      <c r="E85" s="341"/>
+      <c r="F85" s="341"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4681,11 +4708,11 @@
       </c>
       <c r="C86" s="191">
         <f>Valuation_Model!C7</f>
-        <v>2034922</v>
+        <v>245714</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
@@ -4694,7 +4721,7 @@
       </c>
       <c r="C87" s="254">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>3.4660105464438944</v>
+        <v>1.2623955841267334</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4712,11 +4739,11 @@
       </c>
       <c r="C90" s="191">
         <f>BS!C66</f>
-        <v>1998219</v>
+        <v>238880</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
@@ -4725,11 +4752,11 @@
       </c>
       <c r="C91" s="191">
         <f>Valuation_Model!C8</f>
-        <v>810914.36033333349</v>
+        <v>2536.5589373550902</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.35">
@@ -4738,7 +4765,7 @@
       </c>
       <c r="C92" s="254">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.3812016997104255</v>
+        <v>1.3031983531236581E-2</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4756,11 +4783,11 @@
       </c>
       <c r="C95" s="191">
         <f>Valuation_Model!C9</f>
-        <v>92572.6</v>
+        <v>6352.8</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.35">
@@ -4769,7 +4796,7 @@
       </c>
       <c r="C96" s="254">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.15767562978420405</v>
+        <v>3.2638541828468509E-2</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4777,13 +4804,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="339" t="s">
-        <v>386</v>
-      </c>
-      <c r="C98" s="339"/>
-      <c r="D98" s="339"/>
-      <c r="E98" s="339"/>
-      <c r="F98" s="339"/>
+      <c r="B98" s="341" t="s">
+        <v>384</v>
+      </c>
+      <c r="C98" s="341"/>
+      <c r="D98" s="341"/>
+      <c r="E98" s="341"/>
+      <c r="F98" s="341"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4791,7 +4818,7 @@
       </c>
       <c r="C100" s="254">
         <f>Valuation_Model!C12</f>
-        <v>22.830518776962066</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4800,7 +4827,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="253" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4809,13 +4836,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="340" t="s">
-        <v>387</v>
-      </c>
-      <c r="C104" s="340"/>
-      <c r="D104" s="340"/>
-      <c r="E104" s="340"/>
-      <c r="F104" s="340"/>
+      <c r="B104" s="342" t="s">
+        <v>385</v>
+      </c>
+      <c r="C104" s="342"/>
+      <c r="D104" s="342"/>
+      <c r="E104" s="342"/>
+      <c r="F104" s="342"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="266" t="s">
@@ -4849,11 +4876,11 @@
       </c>
       <c r="E107" s="264" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>28.13 HKD</v>
+        <v>13.02 HKD</v>
       </c>
       <c r="F107" s="265">
         <f>Valuation_Model!F74</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
@@ -4863,7 +4890,7 @@
       </c>
       <c r="C108" s="249">
         <f>Valuation_Model!C75</f>
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="D108" s="250">
         <f>Valuation_Model!D75</f>
@@ -4871,11 +4898,11 @@
       </c>
       <c r="E108" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>24.87 HKD</v>
+        <v>10.89 HKD</v>
       </c>
       <c r="F108" s="252">
         <f>Valuation_Model!F75</f>
-        <v>0.192</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
@@ -4885,7 +4912,7 @@
       </c>
       <c r="C109" s="249">
         <f>Valuation_Model!C76</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D109" s="250">
         <f>Valuation_Model!D76</f>
@@ -4893,11 +4920,11 @@
       </c>
       <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>23.63 HKD</v>
+        <v>10.51 HKD</v>
       </c>
       <c r="F109" s="252">
         <f>Valuation_Model!F76</f>
-        <v>0.57599999999999996</v>
+        <v>0.53999999999999992</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
@@ -4907,7 +4934,7 @@
       </c>
       <c r="C110" s="249">
         <f>Valuation_Model!C77</f>
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="D110" s="250">
         <f>Valuation_Model!D77</f>
@@ -4915,11 +4942,11 @@
       </c>
       <c r="E110" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>20.93 HKD</v>
+        <v>8.77 HKD</v>
       </c>
       <c r="F110" s="252">
         <f>Valuation_Model!F77</f>
-        <v>0.192</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
@@ -4929,7 +4956,7 @@
       </c>
       <c r="C111" s="249">
         <f>Valuation_Model!C78</f>
-        <v>-0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="D111" s="250">
         <f>Valuation_Model!D78</f>
@@ -4937,11 +4964,11 @@
       </c>
       <c r="E111" s="251" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>17.72 HKD</v>
+        <v>6.55 HKD</v>
       </c>
       <c r="F111" s="252">
         <f>Valuation_Model!F78</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
@@ -4950,7 +4977,7 @@
       </c>
       <c r="C113" s="247">
         <f>Scenarios!C60</f>
-        <v>23.321827133653532</v>
+        <v>10.1939957287823</v>
       </c>
       <c r="D113" s="242" t="str">
         <f>Market_currency</f>
@@ -4958,17 +4985,17 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="344" t="s">
-        <v>390</v>
-      </c>
-      <c r="C115" s="344"/>
-      <c r="D115" s="344"/>
-      <c r="E115" s="344"/>
-      <c r="F115" s="344"/>
+      <c r="B115" s="346" t="s">
+        <v>388</v>
+      </c>
+      <c r="C115" s="346"/>
+      <c r="D115" s="346"/>
+      <c r="E115" s="346"/>
+      <c r="F115" s="346"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="253" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4977,22 +5004,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="342" t="s">
-        <v>388</v>
-      </c>
-      <c r="C119" s="342"/>
-      <c r="D119" s="342"/>
-      <c r="E119" s="342"/>
-      <c r="F119" s="342"/>
+      <c r="B119" s="344" t="s">
+        <v>386</v>
+      </c>
+      <c r="C119" s="344"/>
+      <c r="D119" s="344"/>
+      <c r="E119" s="344"/>
+      <c r="F119" s="344"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="339" t="s">
-        <v>389</v>
-      </c>
-      <c r="C120" s="339"/>
-      <c r="D120" s="339"/>
-      <c r="E120" s="339"/>
-      <c r="F120" s="339"/>
+      <c r="B120" s="341" t="s">
+        <v>387</v>
+      </c>
+      <c r="C120" s="341"/>
+      <c r="D120" s="341"/>
+      <c r="E120" s="341"/>
+      <c r="F120" s="341"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="240" t="s">
@@ -5023,7 +5050,7 @@
       </c>
       <c r="C124" s="243">
         <f>Scenarios!C77</f>
-        <v>1.36</v>
+        <v>0.49984047644368812</v>
       </c>
       <c r="D124" s="242" t="str">
         <f>Market_currency</f>
@@ -5042,7 +5069,7 @@
       </c>
       <c r="C127" s="246">
         <f>Scenarios!C81</f>
-        <v>2.8648148148148147</v>
+        <v>1.0529047073235096</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5052,7 +5079,7 @@
       </c>
       <c r="C128" s="246">
         <f>Scenarios!C82</f>
-        <v>13.496427739382831</v>
+        <v>5.8993030837860534</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5061,11 +5088,11 @@
       </c>
       <c r="C129" s="245">
         <f>Scenarios!C83</f>
-        <v>16.361242554197645</v>
+        <v>6.9522077911095632</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.35">
@@ -5074,12 +5101,12 @@
       </c>
       <c r="C130" s="94">
         <f>Scenarios!F83</f>
-        <v>0.29845794412101279</v>
+        <v>0.31800954443405249</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A132" s="253" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B132" s="36"/>
       <c r="C132" s="36"/>
@@ -5088,98 +5115,98 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="346" t="s">
-        <v>396</v>
-      </c>
-      <c r="C134" s="339"/>
-      <c r="D134" s="339"/>
-      <c r="E134" s="339"/>
-      <c r="F134" s="339"/>
+      <c r="B134" s="348" t="s">
+        <v>394</v>
+      </c>
+      <c r="C134" s="341"/>
+      <c r="D134" s="341"/>
+      <c r="E134" s="341"/>
+      <c r="F134" s="341"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="240" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B137" s="343" t="s">
-        <v>400</v>
-      </c>
-      <c r="C137" s="343"/>
-      <c r="D137" s="343"/>
-      <c r="E137" s="343"/>
-      <c r="F137" s="343"/>
+      <c r="B137" s="345" t="s">
+        <v>398</v>
+      </c>
+      <c r="C137" s="345"/>
+      <c r="D137" s="345"/>
+      <c r="E137" s="345"/>
+      <c r="F137" s="345"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B138" s="244" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B139" s="244" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B140" s="244" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B142" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="340" t="s">
-        <v>401</v>
-      </c>
-      <c r="C143" s="340"/>
-      <c r="D143" s="340"/>
-      <c r="E143" s="340"/>
-      <c r="F143" s="340"/>
+      <c r="B143" s="342" t="s">
+        <v>399</v>
+      </c>
+      <c r="C143" s="342"/>
+      <c r="D143" s="342"/>
+      <c r="E143" s="342"/>
+      <c r="F143" s="342"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="345" t="s">
-        <v>402</v>
-      </c>
-      <c r="C146" s="345"/>
-      <c r="D146" s="345"/>
-      <c r="E146" s="345"/>
-      <c r="F146" s="345"/>
+      <c r="B146" s="347" t="s">
+        <v>400</v>
+      </c>
+      <c r="C146" s="347"/>
+      <c r="D146" s="347"/>
+      <c r="E146" s="347"/>
+      <c r="F146" s="347"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="345" t="s">
-        <v>403</v>
-      </c>
-      <c r="C147" s="345"/>
-      <c r="D147" s="345"/>
-      <c r="E147" s="345"/>
-      <c r="F147" s="345"/>
+      <c r="B147" s="347" t="s">
+        <v>401</v>
+      </c>
+      <c r="C147" s="347"/>
+      <c r="D147" s="347"/>
+      <c r="E147" s="347"/>
+      <c r="F147" s="347"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B150" s="244" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B151" s="244" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B152" s="244" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -5213,7 +5240,7 @@
     <mergeCell ref="B63:F63"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5225,7 +5252,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="87" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5234,7 +5261,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:M79"/>
+  <dimension ref="B1:M80"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
@@ -5246,50 +5273,50 @@
     <row r="1" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B1" s="92" t="str">
         <f>Thesis!C16</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="C1" s="107">
-        <v>45382</v>
+        <v>45291</v>
       </c>
       <c r="D1" s="38">
         <f>EOMONTH(EDATE(C1,-12),0)</f>
-        <v>45016</v>
+        <v>44926</v>
       </c>
       <c r="E1" s="38">
         <f t="shared" ref="E1:M1" si="0">EOMONTH(EDATE(D1,-12),0)</f>
-        <v>44651</v>
+        <v>44561</v>
       </c>
       <c r="F1" s="38">
         <f t="shared" si="0"/>
-        <v>44286</v>
+        <v>44196</v>
       </c>
       <c r="G1" s="38">
         <f t="shared" si="0"/>
-        <v>43921</v>
+        <v>43830</v>
       </c>
       <c r="H1" s="38">
         <f t="shared" si="0"/>
-        <v>43555</v>
+        <v>43465</v>
       </c>
       <c r="I1" s="38">
         <f t="shared" si="0"/>
-        <v>43190</v>
+        <v>43100</v>
       </c>
       <c r="J1" s="38">
         <f t="shared" si="0"/>
-        <v>42825</v>
+        <v>42735</v>
       </c>
       <c r="K1" s="38">
         <f t="shared" si="0"/>
-        <v>42460</v>
+        <v>42369</v>
       </c>
       <c r="L1" s="38">
         <f t="shared" si="0"/>
-        <v>42094</v>
+        <v>42004</v>
       </c>
       <c r="M1" s="38">
         <f t="shared" si="0"/>
-        <v>41729</v>
+        <v>41639</v>
       </c>
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
@@ -5313,7 +5340,7 @@
         <v>27</v>
       </c>
       <c r="C3" s="109">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.35">
@@ -5321,7 +5348,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="193">
-        <v>15325962</v>
+        <v>3011012</v>
       </c>
       <c r="D4" s="184"/>
       <c r="E4" s="184"/>
@@ -5339,7 +5366,7 @@
         <v>44</v>
       </c>
       <c r="C5" s="193">
-        <v>11151623</v>
+        <v>2302385</v>
       </c>
       <c r="D5" s="184"/>
       <c r="E5" s="184"/>
@@ -5357,7 +5384,7 @@
         <v>55</v>
       </c>
       <c r="C6" s="193">
-        <v>2297566</v>
+        <v>420298</v>
       </c>
       <c r="D6" s="184"/>
       <c r="E6" s="184"/>
@@ -5375,7 +5402,7 @@
         <v>62</v>
       </c>
       <c r="C7" s="194">
-        <v>2043459</v>
+        <v>70260</v>
       </c>
       <c r="D7" s="192"/>
       <c r="E7" s="192"/>
@@ -5392,7 +5419,9 @@
       <c r="B8" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="193"/>
+      <c r="C8" s="193">
+        <v>21957</v>
+      </c>
       <c r="D8" s="184"/>
       <c r="E8" s="184"/>
       <c r="F8" s="184"/>
@@ -5409,7 +5438,7 @@
         <v>161</v>
       </c>
       <c r="C9" s="193">
-        <v>639</v>
+        <v>18538</v>
       </c>
       <c r="D9" s="184"/>
       <c r="E9" s="184"/>
@@ -5426,7 +5455,9 @@
       <c r="B10" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="C10" s="193"/>
+      <c r="C10" s="184">
+        <v>0</v>
+      </c>
       <c r="D10" s="184"/>
       <c r="E10" s="184"/>
       <c r="F10" s="184"/>
@@ -5442,7 +5473,9 @@
       <c r="B11" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C11" s="193"/>
+      <c r="C11" s="193">
+        <v>0</v>
+      </c>
       <c r="D11" s="184"/>
       <c r="E11" s="184"/>
       <c r="F11" s="184"/>
@@ -5459,7 +5492,7 @@
         <v>39</v>
       </c>
       <c r="C12" s="193">
-        <v>59596</v>
+        <v>24063</v>
       </c>
       <c r="D12" s="184"/>
       <c r="E12" s="184"/>
@@ -5477,7 +5510,7 @@
         <v>68</v>
       </c>
       <c r="C13" s="193">
-        <v>28977</v>
+        <v>8265</v>
       </c>
       <c r="D13" s="184"/>
       <c r="E13" s="184"/>
@@ -5495,7 +5528,7 @@
         <v>51</v>
       </c>
       <c r="C14" s="193">
-        <v>327166</v>
+        <v>57167</v>
       </c>
       <c r="D14" s="184"/>
       <c r="E14" s="184"/>
@@ -5513,7 +5546,7 @@
         <v>43</v>
       </c>
       <c r="C15" s="195">
-        <v>1767305</v>
+        <v>180291</v>
       </c>
       <c r="D15" s="185"/>
       <c r="E15" s="185"/>
@@ -5531,7 +5564,7 @@
         <v>45</v>
       </c>
       <c r="C16" s="193">
-        <v>-9467</v>
+        <v>19147</v>
       </c>
       <c r="D16" s="184"/>
       <c r="E16" s="184"/>
@@ -5555,7 +5588,7 @@
         <v>48</v>
       </c>
       <c r="C19" s="184">
-        <v>463424</v>
+        <v>229584</v>
       </c>
       <c r="D19" s="184"/>
       <c r="E19" s="184"/>
@@ -5573,7 +5606,7 @@
         <v>54</v>
       </c>
       <c r="C20" s="184">
-        <v>676387</v>
+        <v>115297</v>
       </c>
       <c r="D20" s="184"/>
       <c r="E20" s="184"/>
@@ -5591,7 +5624,7 @@
         <v>53</v>
       </c>
       <c r="C21" s="184">
-        <v>626583</v>
+        <v>31061</v>
       </c>
       <c r="D21" s="184"/>
       <c r="E21" s="184"/>
@@ -5606,9 +5639,11 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>391</v>
-      </c>
-      <c r="C22" s="184"/>
+        <v>389</v>
+      </c>
+      <c r="C22" s="184">
+        <v>456596</v>
+      </c>
       <c r="D22" s="184"/>
       <c r="E22" s="184"/>
       <c r="F22" s="184"/>
@@ -5622,9 +5657,11 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>393</v>
-      </c>
-      <c r="C23" s="184"/>
+        <v>391</v>
+      </c>
+      <c r="C23" s="184">
+        <v>-255789</v>
+      </c>
       <c r="D23" s="184"/>
       <c r="E23" s="184"/>
       <c r="F23" s="184"/>
@@ -5638,9 +5675,11 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>392</v>
-      </c>
-      <c r="C24" s="184"/>
+        <v>390</v>
+      </c>
+      <c r="C24" s="184">
+        <v>-146572</v>
+      </c>
       <c r="D24" s="184"/>
       <c r="E24" s="184"/>
       <c r="F24" s="184"/>
@@ -5658,7 +5697,8 @@
         <v>Dividend per share (HKD)</v>
       </c>
       <c r="C25" s="39">
-        <v>1.36</v>
+        <f>(0.25+0.22)/Exchange_Rate</f>
+        <v>0.49984047644368812</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -5681,7 +5721,10 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="186"/>
+      <c r="C28" s="184">
+        <f>68761+31090</f>
+        <v>99851</v>
+      </c>
       <c r="D28" s="184"/>
       <c r="E28" s="184"/>
       <c r="F28" s="184"/>
@@ -5697,7 +5740,9 @@
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="186"/>
+      <c r="C29" s="184">
+        <v>180533</v>
+      </c>
       <c r="D29" s="184"/>
       <c r="E29" s="184"/>
       <c r="F29" s="184"/>
@@ -5714,7 +5759,7 @@
         <v>40</v>
       </c>
       <c r="C30" s="185">
-        <v>3990166</v>
+        <v>1122089</v>
       </c>
       <c r="D30" s="185"/>
       <c r="E30" s="185"/>
@@ -5732,7 +5777,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="185">
-        <v>12863898</v>
+        <v>1630621</v>
       </c>
       <c r="D31" s="185"/>
       <c r="E31" s="185"/>
@@ -5749,7 +5794,9 @@
       <c r="B32" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="C32" s="184"/>
+      <c r="C32" s="184">
+        <v>184211</v>
+      </c>
       <c r="D32" s="184"/>
       <c r="E32" s="184"/>
       <c r="F32" s="184"/>
@@ -5788,7 +5835,7 @@
       </c>
       <c r="C36" s="186">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
-        <v>15325962</v>
+        <v>3011012</v>
       </c>
       <c r="D36" s="186" t="str">
         <f t="shared" si="1"/>
@@ -5837,7 +5884,7 @@
       </c>
       <c r="C37" s="186">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
-        <v>-11151623</v>
+        <v>-2302385</v>
       </c>
       <c r="D37" s="186" t="str">
         <f t="shared" si="2"/>
@@ -5886,7 +5933,7 @@
       </c>
       <c r="C38" s="187">
         <f>IF(C36="","",C36+C37)</f>
-        <v>4174339</v>
+        <v>708627</v>
       </c>
       <c r="D38" s="187" t="str">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
@@ -5935,7 +5982,7 @@
       </c>
       <c r="C39" s="186">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
-        <v>-2297566</v>
+        <v>-420298</v>
       </c>
       <c r="D39" s="186" t="str">
         <f t="shared" si="13"/>
@@ -5984,7 +6031,7 @@
       </c>
       <c r="C40" s="188">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
-        <v>-2043459</v>
+        <v>-70260</v>
       </c>
       <c r="D40" s="188" t="str">
         <f t="shared" si="14"/>
@@ -6033,7 +6080,7 @@
       </c>
       <c r="C41" s="188">
         <f>IF(C$4="","",C39-C40)</f>
-        <v>-254107</v>
+        <v>-350038</v>
       </c>
       <c r="D41" s="188" t="str">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
@@ -6082,7 +6129,7 @@
       </c>
       <c r="C42" s="186">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
-        <v>0</v>
+        <v>-21957</v>
       </c>
       <c r="D42" s="186" t="str">
         <f t="shared" si="16"/>
@@ -6131,7 +6178,7 @@
       </c>
       <c r="C43" s="189">
         <f>IF(C$4="","",C38+C39+C42)</f>
-        <v>1876773</v>
+        <v>266372</v>
       </c>
       <c r="D43" s="189" t="str">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
@@ -6180,7 +6227,7 @@
       </c>
       <c r="C44" s="190">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
-        <v>248317</v>
+        <v>-13116</v>
       </c>
       <c r="D44" s="190" t="str">
         <f t="shared" si="18"/>
@@ -6229,7 +6276,7 @@
       </c>
       <c r="C45" s="191">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
-        <v>-30619</v>
+        <v>-15798</v>
       </c>
       <c r="D45" s="191" t="str">
         <f t="shared" si="19"/>
@@ -6278,7 +6325,7 @@
       </c>
       <c r="C46" s="186">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
-        <v>-327166</v>
+        <v>-57167</v>
       </c>
       <c r="D46" s="186" t="str">
         <f t="shared" si="20"/>
@@ -6327,7 +6374,7 @@
       </c>
       <c r="C47" s="189">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
-        <v>1767305</v>
+        <v>180291</v>
       </c>
       <c r="D47" s="189" t="str">
         <f t="shared" si="21"/>
@@ -6376,7 +6423,7 @@
       </c>
       <c r="C48" s="186">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
-        <v>0</v>
+        <v>-19147</v>
       </c>
       <c r="D48" s="186" t="str">
         <f t="shared" si="22"/>
@@ -6430,7 +6477,7 @@
       </c>
       <c r="C51" s="186">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
-        <v>-59596</v>
+        <v>-24063</v>
       </c>
       <c r="D51" s="186" t="str">
         <f t="shared" si="23"/>
@@ -6479,7 +6526,7 @@
       </c>
       <c r="C52" s="186">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
-        <v>28977</v>
+        <v>8265</v>
       </c>
       <c r="D52" s="186" t="str">
         <f t="shared" si="24"/>
@@ -6533,7 +6580,7 @@
       </c>
       <c r="C55" s="191">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
-        <v>639</v>
+        <v>18538</v>
       </c>
       <c r="D55" s="191" t="str">
         <f t="shared" si="25"/>
@@ -6680,7 +6727,7 @@
       </c>
       <c r="C58" s="191">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
-        <v>247678</v>
+        <v>-31654</v>
       </c>
       <c r="D58" s="191" t="str">
         <f t="shared" ref="D58:M58" si="28">IF(D$4="","",D44-D55-D56-D57)</f>
@@ -6735,7 +6782,7 @@
       </c>
       <c r="C61" s="186">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
-        <v>-463424</v>
+        <v>-229584</v>
       </c>
       <c r="D61" s="186" t="str">
         <f t="shared" si="29"/>
@@ -6784,7 +6831,7 @@
       </c>
       <c r="C62" s="186">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
-        <v>-676387</v>
+        <v>-115297</v>
       </c>
       <c r="D62" s="186" t="str">
         <f t="shared" si="30"/>
@@ -6833,7 +6880,7 @@
       </c>
       <c r="C63" s="186">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
-        <v>-626583</v>
+        <v>-31061</v>
       </c>
       <c r="D63" s="186" t="str">
         <f t="shared" si="31"/>
@@ -6877,440 +6924,455 @@
       </c>
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B64" s="24" t="s">
+      <c r="B64" s="27" t="s">
+        <v>414</v>
+      </c>
+      <c r="C64" s="186">
+        <f>IF(C$4="","",C22+C23+C24)</f>
+        <v>54235</v>
+      </c>
+      <c r="D64" s="186" t="str">
+        <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
+        <v/>
+      </c>
+      <c r="E64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="F64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="G64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="H64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="I64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="J64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="K64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="L64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="M64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="C64" s="75">
-        <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C25)</f>
-        <v>1.36</v>
-      </c>
-      <c r="D64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="E64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="F64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="G64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="H64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="I64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="J64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="K64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="L64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B66" s="93" t="s">
+      <c r="C65" s="75">
+        <f t="shared" ref="C65:M65" si="33">IF(C$4="","",C25)</f>
+        <v>0.49984047644368812</v>
+      </c>
+      <c r="D65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="E65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="F65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="G65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="H65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="I65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="J65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="K65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="L65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="M65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B67" s="93" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B67" s="1" t="str">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
       </c>
-      <c r="C67" s="94" t="str">
-        <f t="shared" ref="C67:M67" si="33">IF(D$36="","",C36/D36-1)</f>
-        <v/>
-      </c>
-      <c r="D67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="E67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="F67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="G67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="H67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="I67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="J67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="K67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="L67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="M67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B68" s="82" t="str">
+      <c r="C68" s="94" t="str">
+        <f t="shared" ref="C68:M68" si="34">IF(D$36="","",C36/D36-1)</f>
+        <v/>
+      </c>
+      <c r="D68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="E68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="F68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="G68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="H68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="I68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="J68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="K68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="L68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="M68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B69" s="82" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
       </c>
-      <c r="C68" s="104" t="str">
-        <f t="shared" ref="C68:M68" si="34">IF(D$36="","",C37/D37-1)</f>
-        <v/>
-      </c>
-      <c r="D68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="E68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="F68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="G68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="H68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="I68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="J68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="K68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="L68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="M68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B69" s="1" t="str">
+      <c r="C69" s="104" t="str">
+        <f t="shared" ref="C69:M69" si="35">IF(D$36="","",C37/D37-1)</f>
+        <v/>
+      </c>
+      <c r="D69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="E69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="F69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="G69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="H69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="I69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="J69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="K69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="L69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="M69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B70" s="1" t="str">
         <f>B58</f>
         <v>Other Non-operating Income</v>
       </c>
-      <c r="C69" s="94" t="str">
-        <f t="shared" ref="C69:M69" si="35">IF(D$36="","",C38/D38-1)</f>
-        <v/>
-      </c>
-      <c r="D69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="E69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="F69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="G69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="H69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="I69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="J69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="K69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="L69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="M69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B70" s="82" t="str">
+      <c r="C70" s="94" t="str">
+        <f t="shared" ref="C70:M70" si="36">IF(D$36="","",C38/D38-1)</f>
+        <v/>
+      </c>
+      <c r="D70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="E70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="F70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="G70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="H70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="I70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="J70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="K70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="L70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="M70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B71" s="82" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
       </c>
-      <c r="C70" s="104" t="str">
-        <f t="shared" ref="C70:M70" si="36">IF(D$36="","",C39/D39-1)</f>
-        <v/>
-      </c>
-      <c r="D70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="E70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="F70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="G70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="H70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="I70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="J70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="K70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="L70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="M70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B71" s="1" t="str">
+      <c r="C71" s="104" t="str">
+        <f t="shared" ref="C71:M71" si="37">IF(D$36="","",C39/D39-1)</f>
+        <v/>
+      </c>
+      <c r="D71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="E71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="F71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="G71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="H71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="I71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="J71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="K71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="L71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="M71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B72" s="1" t="str">
         <f>B48</f>
         <v>Non-controling Interests</v>
       </c>
-      <c r="C71" s="94" t="str">
-        <f>IF(D$36="","",C64/D64-1)</f>
-        <v/>
-      </c>
-      <c r="D71" s="94" t="str">
-        <f t="shared" ref="D71:M71" si="37">IF(E$36="","",D64/E64-1)</f>
-        <v/>
-      </c>
-      <c r="E71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="F71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="G71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="H71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="I71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="J71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="K71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="L71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="M71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="B73" s="36" t="s">
+      <c r="C72" s="94" t="str">
+        <f>IF(D$36="","",C65/D65-1)</f>
+        <v/>
+      </c>
+      <c r="D72" s="94" t="str">
+        <f t="shared" ref="D72:M72" si="38">IF(E$36="","",D65/E65-1)</f>
+        <v/>
+      </c>
+      <c r="E72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="F72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="G72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="H72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="I72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="J72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="K72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="L72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="M72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="B74" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="37"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="37"/>
-      <c r="I73" s="37"/>
-      <c r="J73" s="37"/>
-      <c r="K73" s="37"/>
-      <c r="L73" s="37"/>
-      <c r="M73" s="37"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B74" s="16" t="s">
+      <c r="C74" s="37"/>
+      <c r="D74" s="37"/>
+      <c r="E74" s="37"/>
+      <c r="F74" s="37"/>
+      <c r="G74" s="37"/>
+      <c r="H74" s="37"/>
+      <c r="I74" s="37"/>
+      <c r="J74" s="37"/>
+      <c r="K74" s="37"/>
+      <c r="L74" s="37"/>
+      <c r="M74" s="37"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C74" s="9"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B75" s="26" t="s">
+      <c r="C75" s="9"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C75" s="78">
-        <f>IF(C$4="","",C78+C79)</f>
-        <v>16854064</v>
-      </c>
-      <c r="D75" s="78" t="str">
-        <f t="shared" ref="D75:M75" si="38">IF(D$4="","",D78+D79)</f>
-        <v/>
-      </c>
-      <c r="E75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="F75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="G75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="H75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="I75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="J75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="K75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="L75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="M75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B76" s="95" t="s">
-        <v>87</v>
-      </c>
-      <c r="C76" s="74">
-        <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C28)</f>
-        <v>0</v>
-      </c>
-      <c r="D76" s="74" t="str">
+      <c r="C76" s="78">
+        <f>IF(C$4="","",C79+C80)</f>
+        <v>2752710</v>
+      </c>
+      <c r="D76" s="78" t="str">
+        <f t="shared" ref="D76:M76" si="39">IF(D$4="","",D79+D80)</f>
+        <v/>
+      </c>
+      <c r="E76" s="78" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="E76" s="74" t="str">
+      <c r="F76" s="78" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="F76" s="74" t="str">
+      <c r="G76" s="78" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="G76" s="74" t="str">
+      <c r="H76" s="78" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="H76" s="74" t="str">
+      <c r="I76" s="78" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="I76" s="96"/>
-      <c r="J76" s="96"/>
-      <c r="K76" s="96"/>
-      <c r="L76" s="96"/>
-      <c r="M76" s="96"/>
+      <c r="J76" s="78" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K76" s="78" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="L76" s="78" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="M76" s="78" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="95" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C77" s="74">
-        <f t="shared" si="39"/>
-        <v>0</v>
+        <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
+        <v>99851</v>
       </c>
       <c r="D77" s="74" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="E77" s="74" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="F77" s="74" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="G77" s="74" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="H77" s="74" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="I77" s="96"/>
@@ -7320,61 +7382,46 @@
       <c r="M77" s="96"/>
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B78" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C78" s="58">
-        <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C30)</f>
-        <v>3990166</v>
-      </c>
-      <c r="D78" s="58" t="str">
+      <c r="B78" s="95" t="s">
+        <v>88</v>
+      </c>
+      <c r="C78" s="74">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="E78" s="58" t="str">
+        <v>180533</v>
+      </c>
+      <c r="D78" s="74" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="F78" s="58" t="str">
+      <c r="E78" s="74" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="G78" s="58" t="str">
+      <c r="F78" s="74" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="H78" s="58" t="str">
+      <c r="G78" s="74" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="I78" s="58" t="str">
+      <c r="H78" s="74" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="J78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="K78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="L78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="M78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
+      <c r="I78" s="96"/>
+      <c r="J78" s="96"/>
+      <c r="K78" s="96"/>
+      <c r="L78" s="96"/>
+      <c r="M78" s="96"/>
     </row>
     <row r="79" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B79" s="26" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C79" s="58">
-        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C31)</f>
-        <v>12863898</v>
+        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
+        <v>1122089</v>
       </c>
       <c r="D79" s="58" t="str">
         <f t="shared" si="41"/>
@@ -7417,9 +7464,58 @@
         <v/>
       </c>
     </row>
+    <row r="80" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B80" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C80" s="58">
+        <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
+        <v>1630621</v>
+      </c>
+      <c r="D80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="E80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="F80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="G80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="H80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="I80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="J80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="K80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="L80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="M80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C76:H77 C78:M79">
+  <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
     <cfRule type="expression" dxfId="5" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
@@ -7429,7 +7525,7 @@
       <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C36:M37 C61:M64">
+  <conditionalFormatting sqref="C36:M37 C61:M65">
     <cfRule type="expression" dxfId="3" priority="2">
       <formula>ISBLANK(C36)</formula>
     </cfRule>
@@ -7473,7 +7569,7 @@
       </c>
       <c r="H1" s="110">
         <f>Data!C3</f>
-        <v>1000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7512,7 +7608,8 @@
         <v>24</v>
       </c>
       <c r="C4" s="19">
-        <v>265773</v>
+        <f>90108+11142+41629</f>
+        <v>142879</v>
       </c>
       <c r="D4" s="300">
         <v>0.6</v>
@@ -7522,7 +7619,7 @@
         <v>79</v>
       </c>
       <c r="G4" s="19">
-        <v>1998219</v>
+        <v>238880</v>
       </c>
       <c r="H4" s="300">
         <v>0.9</v>
@@ -7533,7 +7630,7 @@
         <v>33</v>
       </c>
       <c r="C5" s="19">
-        <v>0</v>
+        <v>11851</v>
       </c>
       <c r="D5" s="300">
         <v>0.6</v>
@@ -7554,7 +7651,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="19">
-        <v>9672256</v>
+        <v>182674</v>
       </c>
       <c r="D6" s="300">
         <v>0.5</v>
@@ -7585,7 +7682,7 @@
         <v>180</v>
       </c>
       <c r="G7" s="19">
-        <v>0</v>
+        <v>9895</v>
       </c>
       <c r="H7" s="300">
         <v>0.6</v>
@@ -7617,7 +7714,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="19">
-        <v>366595</v>
+        <v>24847</v>
       </c>
       <c r="D9" s="300">
         <v>0.1</v>
@@ -7638,7 +7735,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="19">
-        <v>29465</v>
+        <v>0</v>
       </c>
       <c r="D10" s="300">
         <v>0.9</v>
@@ -7650,7 +7747,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="19">
-        <v>0</v>
+        <v>61345</v>
       </c>
       <c r="D11" s="300">
         <v>0.05</v>
@@ -7663,22 +7760,22 @@
       </c>
       <c r="C12" s="83">
         <f>SUM(C4:C11)</f>
-        <v>10334089</v>
+        <v>423596</v>
       </c>
       <c r="D12" s="20">
         <f>C4*D4+C5*D5+C9*D9+C6*D6+C8*D8+C7*D7+C10*D10+C11*D11</f>
-        <v>5058769.8</v>
+        <v>189726.95</v>
       </c>
       <c r="F12" s="82" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="83">
         <f>SUM(G4:G9)</f>
-        <v>1998219</v>
+        <v>248775</v>
       </c>
       <c r="H12" s="20">
         <f>G4*H4+G5*H5+G6*H6+G7*H7+G8*H8+G9*H9</f>
-        <v>1798397.1</v>
+        <v>220929</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7711,7 +7808,7 @@
         <v>74</v>
       </c>
       <c r="C15" s="19">
-        <v>103050</v>
+        <v>0</v>
       </c>
       <c r="D15" s="300">
         <v>0.4</v>
@@ -7760,7 +7857,7 @@
         <v>180</v>
       </c>
       <c r="G17" s="19">
-        <v>0</v>
+        <v>693</v>
       </c>
       <c r="H17" s="300">
         <v>0.6</v>
@@ -7780,7 +7877,8 @@
         <v>183</v>
       </c>
       <c r="G18" s="19">
-        <v>0</v>
+        <f>292606</f>
+        <v>292606</v>
       </c>
       <c r="H18" s="300">
         <v>0.1</v>
@@ -7791,7 +7889,8 @@
         <v>26</v>
       </c>
       <c r="C19" s="19">
-        <v>2522337</v>
+        <f>458868+831001+201156+123479+13153</f>
+        <v>1627657</v>
       </c>
       <c r="D19" s="300">
         <v>0.1</v>
@@ -7831,7 +7930,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="19">
-        <v>538321</v>
+        <v>91529</v>
       </c>
       <c r="D21" s="300">
         <v>0.05</v>
@@ -7840,7 +7939,7 @@
         <v>182</v>
       </c>
       <c r="G21" s="19">
-        <v>925726</v>
+        <v>0</v>
       </c>
       <c r="H21" s="300">
         <v>0.1</v>
@@ -7851,7 +7950,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="19">
-        <v>154648</v>
+        <v>24707</v>
       </c>
       <c r="D22" s="300">
         <v>0.9</v>
@@ -7863,7 +7962,8 @@
         <v>21</v>
       </c>
       <c r="C23" s="19">
-        <v>277674</v>
+        <f>7476+51258</f>
+        <v>58734</v>
       </c>
       <c r="D23" s="300">
         <v>0</v>
@@ -7876,22 +7976,22 @@
       </c>
       <c r="C24" s="83">
         <f>SUM(C15:C23)</f>
-        <v>3596030</v>
+        <v>1802627</v>
       </c>
       <c r="D24" s="20">
         <f>C15*D15+C16*D16+C18*D18+C17*D17+C19*D19+C20*D20+C21*D21+C22*D22+C23*D23</f>
-        <v>459552.95</v>
+        <v>189578.45</v>
       </c>
       <c r="F24" s="82" t="s">
         <v>72</v>
       </c>
       <c r="G24" s="83">
         <f>SUM(G15:G21)</f>
-        <v>925726</v>
+        <v>293299</v>
       </c>
       <c r="H24" s="20">
         <f>G15*H15+G16*H16+G17*H17+G18*H18+G19*H19+G20*H20+G21*H21</f>
-        <v>92572.6</v>
+        <v>29676.400000000001</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7916,18 +8016,18 @@
         <v>5</v>
       </c>
       <c r="C27" s="19">
-        <v>1427805</v>
+        <v>40594</v>
       </c>
       <c r="F27" s="214" t="s">
         <v>30</v>
       </c>
       <c r="G27" s="87">
         <f>G32-G30</f>
-        <v>12863898</v>
+        <v>1678153</v>
       </c>
       <c r="H27" s="215">
         <f>H32-G30</f>
-        <v>3419126.45</v>
+        <v>-460233.19999999995</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7935,13 +8035,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="19">
-        <v>287697</v>
+        <v>0</v>
       </c>
       <c r="F28" s="216" t="s">
         <v>246</v>
       </c>
       <c r="G28" s="184">
-        <v>-26962</v>
+        <v>188249</v>
       </c>
       <c r="H28" s="215"/>
     </row>
@@ -7957,11 +8057,11 @@
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
-        <v>12890860</v>
+        <v>1489904</v>
       </c>
       <c r="H29" s="215">
         <f>H27-G28</f>
-        <v>3446088.45</v>
+        <v>-648482.19999999995</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7969,14 +8069,15 @@
         <v>8</v>
       </c>
       <c r="C30" s="19">
-        <v>0</v>
+        <f>4685+7139</f>
+        <v>11824</v>
       </c>
       <c r="F30" s="214" t="s">
         <v>23</v>
       </c>
       <c r="G30" s="87">
         <f>C33+C42</f>
-        <v>3990166</v>
+        <v>1090144</v>
       </c>
       <c r="H30" s="215"/>
     </row>
@@ -7986,14 +8087,14 @@
       </c>
       <c r="C31" s="83">
         <f>SUM(C27:C30)</f>
-        <v>1715502</v>
+        <v>52418</v>
       </c>
       <c r="F31" s="217" t="s">
         <v>78</v>
       </c>
       <c r="G31" s="218">
         <f>C31+C40</f>
-        <v>2034922</v>
+        <v>245714</v>
       </c>
       <c r="H31" s="215"/>
     </row>
@@ -8003,18 +8104,18 @@
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
-        <v>1801307</v>
+        <v>664223</v>
       </c>
       <c r="F32" s="219" t="s">
         <v>76</v>
       </c>
       <c r="G32" s="220">
         <f>G35+G40</f>
-        <v>16854064</v>
+        <v>2768297</v>
       </c>
       <c r="H32" s="215">
         <f>H35+H40</f>
-        <v>7409292.4500000002</v>
+        <v>629910.80000000005</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8022,7 +8123,7 @@
         <v>4</v>
       </c>
       <c r="C33" s="86">
-        <v>3516809</v>
+        <v>716641</v>
       </c>
       <c r="F33" s="221"/>
       <c r="G33" s="2"/>
@@ -8053,11 +8154,11 @@
       </c>
       <c r="G35" s="220">
         <f>C12+C24</f>
-        <v>13930119</v>
+        <v>2226223</v>
       </c>
       <c r="H35" s="227">
         <f>D12+D24</f>
-        <v>5518322.75</v>
+        <v>379305.4</v>
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8065,14 +8166,15 @@
         <v>13</v>
       </c>
       <c r="C36" s="19">
-        <v>0</v>
+        <f>70126+11000</f>
+        <v>81126</v>
       </c>
       <c r="F36" s="217" t="s">
         <v>199</v>
       </c>
       <c r="G36" s="218">
         <f>C4+C15</f>
-        <v>368823</v>
+        <v>142879</v>
       </c>
       <c r="H36" s="222"/>
     </row>
@@ -8081,14 +8183,14 @@
         <v>14</v>
       </c>
       <c r="C37" s="19">
-        <v>0</v>
+        <v>112170</v>
       </c>
       <c r="F37" s="217" t="s">
         <v>200</v>
       </c>
       <c r="G37" s="218">
         <f>C6</f>
-        <v>9672256</v>
+        <v>182674</v>
       </c>
       <c r="H37" s="222"/>
     </row>
@@ -8097,7 +8199,7 @@
         <v>15</v>
       </c>
       <c r="C38" s="19">
-        <v>319420</v>
+        <v>0</v>
       </c>
       <c r="F38" s="217" t="s">
         <v>201</v>
@@ -8120,11 +8222,11 @@
       </c>
       <c r="G39" s="218">
         <f>C7+C17+C19+C20</f>
-        <v>2522337</v>
+        <v>1627657</v>
       </c>
       <c r="H39" s="215">
         <f>C7*D7+C17*D17+C19*D19+C20*D20</f>
-        <v>252233.7</v>
+        <v>162765.70000000001</v>
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8133,18 +8235,18 @@
       </c>
       <c r="C40" s="83">
         <f>SUM(C36:C39)</f>
-        <v>319420</v>
+        <v>193296</v>
       </c>
       <c r="F40" s="226" t="s">
         <v>140</v>
       </c>
       <c r="G40" s="220">
         <f>G12+G24</f>
-        <v>2923945</v>
+        <v>542074</v>
       </c>
       <c r="H40" s="227">
         <f>H12+H24</f>
-        <v>1890969.7000000002</v>
+        <v>250605.4</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8153,18 +8255,18 @@
       </c>
       <c r="C41" s="21">
         <f>C42-C40</f>
-        <v>153937</v>
+        <v>180207</v>
       </c>
       <c r="F41" s="217" t="s">
         <v>193</v>
       </c>
       <c r="G41" s="218">
         <f>C70</f>
-        <v>1998219</v>
+        <v>531486</v>
       </c>
       <c r="H41" s="227">
         <f>H40-H42</f>
-        <v>1798397.1</v>
+        <v>244252.6</v>
       </c>
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8172,18 +8274,18 @@
         <v>22</v>
       </c>
       <c r="C42" s="86">
-        <v>473357</v>
+        <v>373503</v>
       </c>
       <c r="F42" s="228" t="s">
         <v>194</v>
       </c>
       <c r="G42" s="229">
         <f>C82</f>
-        <v>925726</v>
+        <v>10588</v>
       </c>
       <c r="H42" s="230">
         <f>D82</f>
-        <v>92572.6</v>
+        <v>6352.8</v>
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8217,11 +8319,11 @@
       </c>
       <c r="C46" s="191">
         <f>G29</f>
-        <v>12890860</v>
+        <v>1489904</v>
       </c>
       <c r="D46" s="191">
         <f>H29</f>
-        <v>3446088.45</v>
+        <v>-648482.19999999995</v>
       </c>
       <c r="F46" s="289"/>
     </row>
@@ -8232,11 +8334,11 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.956545121990789</v>
+        <v>7.6546237917772562</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>5.8696003638854428</v>
+        <v>-3.3316826296620832</v>
       </c>
       <c r="F47" s="289"/>
     </row>
@@ -8262,11 +8364,11 @@
       </c>
       <c r="C50" s="98">
         <f>G31/Normalized_FCF!C8</f>
-        <v>1.0842664509772892</v>
+        <v>0.9224468037181085</v>
       </c>
       <c r="D50" s="98">
         <f>G31/Normalized_FCF!G8</f>
-        <v>1.0842664509772892</v>
+        <v>0.9224468037181085</v>
       </c>
       <c r="F50" s="289"/>
     </row>
@@ -8277,7 +8379,7 @@
       <c r="C51" s="208"/>
       <c r="D51" s="94">
         <f>G29/G32</f>
-        <v>0.76485172952944758</v>
+        <v>0.5382023677372767</v>
       </c>
       <c r="F51" s="289"/>
     </row>
@@ -8302,11 +8404,11 @@
       </c>
       <c r="C54" s="94">
         <f>Normalized_FCF!C8/G35</f>
-        <v>0.13472770763839131</v>
+        <v>0.11965198454961611</v>
       </c>
       <c r="D54" s="94">
         <f>Normalized_FCF!G8/G35</f>
-        <v>0.13472770763839131</v>
+        <v>0.11965198454961611</v>
       </c>
       <c r="F54" s="289"/>
     </row>
@@ -8316,11 +8418,11 @@
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C11/G40</f>
-        <v>0</v>
+        <v>3.4198282891265773E-2</v>
       </c>
       <c r="D55" s="94">
         <f>Normalized_FCF!G11/G40</f>
-        <v>2.1854036242131779E-4</v>
+        <v>3.4198282891265766E-2</v>
       </c>
       <c r="F55" s="289"/>
     </row>
@@ -8346,7 +8448,7 @@
       <c r="C58" s="101"/>
       <c r="D58" s="23">
         <f>Normalized_FCF!G9/BS!$G$39</f>
-        <v>0.1837280268259158</v>
+        <v>0.14105183094472606</v>
       </c>
       <c r="F58" s="5"/>
     </row>
@@ -8357,7 +8459,7 @@
       <c r="C59" s="101"/>
       <c r="D59" s="94">
         <f>G39/G32</f>
-        <v>0.14965749507062509</v>
+        <v>0.58796328573126366</v>
       </c>
       <c r="F59" s="289"/>
     </row>
@@ -8382,11 +8484,11 @@
       </c>
       <c r="C62" s="94">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
-        <v>0</v>
+        <v>0.12634975139337837</v>
       </c>
       <c r="D62" s="94">
         <f>G28/G29</f>
-        <v>-2.0915594459950692E-3</v>
+        <v>0.12634975139337837</v>
       </c>
       <c r="F62" s="289" t="s">
         <v>276</v>
@@ -8423,11 +8525,11 @@
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
-        <v>1998219</v>
+        <v>238880</v>
       </c>
       <c r="D66" s="191">
         <f>C66-D75</f>
-        <v>810914.36033333349</v>
+        <v>2536.5589373550902</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8449,7 +8551,7 @@
       </c>
       <c r="C68" s="20">
         <f>G18</f>
-        <v>0</v>
+        <v>292606</v>
       </c>
       <c r="F68" s="289"/>
     </row>
@@ -8469,7 +8571,7 @@
       </c>
       <c r="C70" s="83">
         <f>SUM(C66:C69)</f>
-        <v>1998219</v>
+        <v>531486</v>
       </c>
       <c r="F70" s="289"/>
     </row>
@@ -8494,11 +8596,11 @@
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-1187304.6396666665</v>
+        <v>-236343.44106264491</v>
       </c>
       <c r="D73" s="191">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-1187304.6396666665</v>
+        <v>-236343.44106264491</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>365</v>
@@ -8510,11 +8612,11 @@
       </c>
       <c r="C74" s="295">
         <f>-$C$66/C73</f>
-        <v>1.6829876118070222</v>
+        <v>1.0107325125078581</v>
       </c>
       <c r="D74" s="295">
         <f>-$C$66/D73</f>
-        <v>1.6829876118070222</v>
+        <v>1.0107325125078581</v>
       </c>
       <c r="F74" s="289" t="s">
         <v>332</v>
@@ -8527,7 +8629,7 @@
       <c r="C75" s="299"/>
       <c r="D75" s="298">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1187304.6396666665</v>
+        <v>236343.44106264491</v>
       </c>
       <c r="F75" s="289" t="s">
         <v>366</v>
@@ -8567,11 +8669,11 @@
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
-        <v>0</v>
+        <v>10588</v>
       </c>
       <c r="D79" s="191">
         <f>G7*H7+G17*H17</f>
-        <v>0</v>
+        <v>6352.8</v>
       </c>
       <c r="F79" s="289"/>
     </row>
@@ -8595,11 +8697,11 @@
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
-        <v>925726</v>
+        <v>0</v>
       </c>
       <c r="D81" s="191">
         <f>G9*H9+G21*H21</f>
-        <v>92572.6</v>
+        <v>0</v>
       </c>
       <c r="F81" s="289"/>
     </row>
@@ -8609,11 +8711,11 @@
       </c>
       <c r="C82" s="83">
         <f>SUM(C79:C81)</f>
-        <v>925726</v>
+        <v>10588</v>
       </c>
       <c r="D82" s="83">
         <f>SUM(D79:D81)</f>
-        <v>92572.6</v>
+        <v>6352.8</v>
       </c>
       <c r="F82" s="289"/>
     </row>
@@ -8642,11 +8744,11 @@
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2034922</v>
+        <v>-231044.87420000002</v>
       </c>
       <c r="D86" s="254">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-3.4660105464438944</v>
+        <v>-1.2623955841267334</v>
       </c>
       <c r="E86" s="275" t="str">
         <f>Market_currency</f>
@@ -8659,11 +8761,11 @@
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>810914.36033333349</v>
+        <v>2385.1263687949913</v>
       </c>
       <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.3812016997104255</v>
+        <v>1.3031983531236581E-2</v>
       </c>
       <c r="E87" s="275" t="str">
         <f>Market_currency</f>
@@ -8676,11 +8778,11 @@
       </c>
       <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>92572.6</v>
+        <v>5973.53784</v>
       </c>
       <c r="D88" s="254">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.15767562978420405</v>
+        <v>3.2638541828468509E-2</v>
       </c>
       <c r="E88" s="275" t="str">
         <f>Market_currency</f>
@@ -8693,11 +8795,11 @@
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
-        <v>-1131435.0396666664</v>
+        <v>-222686.20999120502</v>
       </c>
       <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
-        <v>-1.9271332169492648</v>
+        <v>-1.2167250587670282</v>
       </c>
       <c r="E89" s="275" t="str">
         <f>Market_currency</f>
@@ -8717,7 +8819,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q804"/>
+  <dimension ref="A1:Q808"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
@@ -8734,7 +8836,7 @@
       <c r="A1" s="3"/>
       <c r="B1" s="92" t="str">
         <f>Thesis!C16</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
         <v>58</v>
@@ -8744,47 +8846,47 @@
       <c r="F1" s="53"/>
       <c r="G1" s="38">
         <f>Data!C1</f>
-        <v>45382</v>
+        <v>45291</v>
       </c>
       <c r="H1" s="38">
         <f>EOMONTH(EDATE(G1,-12),0)</f>
-        <v>45016</v>
+        <v>44926</v>
       </c>
       <c r="I1" s="38">
         <f t="shared" ref="I1:Q1" si="0">EOMONTH(EDATE(H1,-12),0)</f>
-        <v>44651</v>
+        <v>44561</v>
       </c>
       <c r="J1" s="38">
         <f t="shared" si="0"/>
-        <v>44286</v>
+        <v>44196</v>
       </c>
       <c r="K1" s="38">
         <f t="shared" si="0"/>
-        <v>43921</v>
+        <v>43830</v>
       </c>
       <c r="L1" s="38">
         <f t="shared" si="0"/>
-        <v>43555</v>
+        <v>43465</v>
       </c>
       <c r="M1" s="38">
         <f t="shared" si="0"/>
-        <v>43190</v>
+        <v>43100</v>
       </c>
       <c r="N1" s="38">
         <f t="shared" si="0"/>
-        <v>42825</v>
+        <v>42735</v>
       </c>
       <c r="O1" s="38">
         <f t="shared" si="0"/>
-        <v>42460</v>
+        <v>42369</v>
       </c>
       <c r="P1" s="38">
         <f t="shared" si="0"/>
-        <v>42094</v>
+        <v>42004</v>
       </c>
       <c r="Q1" s="38">
         <f t="shared" si="0"/>
-        <v>41729</v>
+        <v>41639</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
@@ -8817,7 +8919,7 @@
       </c>
       <c r="C3" s="110">
         <f>Data!C3</f>
-        <v>1000</v>
+        <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="308"/>
@@ -8831,14 +8933,14 @@
       </c>
       <c r="C4" s="196">
         <f>AVERAGE(G4:J4)</f>
-        <v>15325962</v>
+        <v>3011012</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="306"/>
       <c r="F4" s="57"/>
       <c r="G4" s="186">
         <f>Data!C36</f>
-        <v>15325962</v>
+        <v>3011012</v>
       </c>
       <c r="H4" s="186" t="str">
         <f>Data!D36</f>
@@ -8888,12 +8990,12 @@
       </c>
       <c r="C5" s="197">
         <f>C25</f>
-        <v>-13195082</v>
+        <v>-2372645</v>
       </c>
       <c r="E5" s="308"/>
       <c r="G5" s="186">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
-        <v>-13195082</v>
+        <v>-2372645</v>
       </c>
       <c r="H5" s="186" t="str">
         <f t="shared" si="1"/>
@@ -8943,12 +9045,12 @@
       </c>
       <c r="C6" s="187">
         <f>C4+C5</f>
-        <v>2130880</v>
+        <v>638367</v>
       </c>
       <c r="E6" s="308"/>
       <c r="G6" s="187">
         <f>IF(G4="","",G4+G5)</f>
-        <v>2130880</v>
+        <v>638367</v>
       </c>
       <c r="H6" s="187" t="str">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
@@ -8998,12 +9100,12 @@
       </c>
       <c r="C7" s="197">
         <f>C35</f>
-        <v>-254107</v>
+        <v>-371995</v>
       </c>
       <c r="E7" s="308"/>
       <c r="G7" s="197">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
-        <v>-254107</v>
+        <v>-371995</v>
       </c>
       <c r="H7" s="197" t="str">
         <f t="shared" si="3"/>
@@ -9053,14 +9155,14 @@
       </c>
       <c r="C8" s="198">
         <f>C6+C7</f>
-        <v>1876773</v>
+        <v>266372</v>
       </c>
       <c r="D8" s="60"/>
       <c r="E8" s="314"/>
       <c r="F8" s="60"/>
       <c r="G8" s="187">
         <f>IF(G$4="","",G6+G7)</f>
-        <v>1876773</v>
+        <v>266372</v>
       </c>
       <c r="H8" s="187" t="str">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
@@ -9110,12 +9212,12 @@
       </c>
       <c r="C9" s="197">
         <f>BS!$G$39*BS!D58</f>
-        <v>463424</v>
+        <v>229584</v>
       </c>
       <c r="E9" s="308"/>
       <c r="G9" s="197">
         <f>IF(Data!C61="","",-Data!C61)</f>
-        <v>463424</v>
+        <v>229584</v>
       </c>
       <c r="H9" s="197" t="str">
         <f>IF(Data!D61="","",-Data!D61)</f>
@@ -9165,12 +9267,12 @@
       </c>
       <c r="C10" s="197">
         <f>-C4*C78</f>
-        <v>-676387</v>
+        <v>-229584</v>
       </c>
       <c r="E10" s="308"/>
       <c r="G10" s="197">
         <f>Data!C62</f>
-        <v>-676387</v>
+        <v>-115297</v>
       </c>
       <c r="H10" s="197" t="str">
         <f>Data!D62</f>
@@ -9220,14 +9322,14 @@
       </c>
       <c r="C11" s="199">
         <f>C63</f>
-        <v>0</v>
+        <v>18538.000000000004</v>
       </c>
       <c r="D11" s="172"/>
       <c r="E11" s="307"/>
       <c r="F11" s="172"/>
       <c r="G11" s="189">
         <f>G61</f>
-        <v>639</v>
+        <v>18538</v>
       </c>
       <c r="H11" s="189" t="str">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
@@ -9277,12 +9379,12 @@
       </c>
       <c r="C12" s="197">
         <f>C50</f>
-        <v>-42378.404459360565</v>
+        <v>-15885.762305832384</v>
       </c>
       <c r="E12" s="308"/>
       <c r="G12" s="197">
         <f>G50</f>
-        <v>-42378.404459360565</v>
+        <v>-15885.762305832384</v>
       </c>
       <c r="H12" s="197" t="str">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
@@ -9332,12 +9434,12 @@
       </c>
       <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
-        <v>1621431.5955406395</v>
+        <v>269024.23769416759</v>
       </c>
       <c r="E13" s="308"/>
       <c r="G13" s="187">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>1622070.5955406395</v>
+        <v>383311.23769416759</v>
       </c>
       <c r="H13" s="187" t="str">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
@@ -9387,12 +9489,12 @@
       </c>
       <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-458598.64888515987</v>
+        <v>-67256.059423541898</v>
       </c>
       <c r="E14" s="308"/>
       <c r="G14" s="197">
         <f>Data!C46</f>
-        <v>-327166</v>
+        <v>-57167</v>
       </c>
       <c r="H14" s="197" t="str">
         <f>Data!D46</f>
@@ -9442,14 +9544,14 @@
       </c>
       <c r="C15" s="197">
         <f>-C4*C83</f>
-        <v>0</v>
+        <v>-19147</v>
       </c>
       <c r="D15" s="61"/>
       <c r="E15" s="315"/>
       <c r="F15" s="61"/>
       <c r="G15" s="186">
         <f>Data!C48</f>
-        <v>0</v>
+        <v>-19147</v>
       </c>
       <c r="H15" s="186" t="str">
         <f>Data!D48</f>
@@ -9499,14 +9601,14 @@
       </c>
       <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
-        <v>1162832.9466554797</v>
+        <v>182621.17827062571</v>
       </c>
       <c r="D16" s="62"/>
       <c r="E16" s="316"/>
       <c r="F16" s="62"/>
       <c r="G16" s="187">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>1294904.5955406395</v>
+        <v>306997.23769416759</v>
       </c>
       <c r="H16" s="187" t="str">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
@@ -9607,14 +9709,14 @@
       </c>
       <c r="C19" s="187">
         <f>C16+C17</f>
-        <v>1162832.9466554797</v>
+        <v>182621.17827062571</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="305"/>
       <c r="F19" s="27"/>
       <c r="G19" s="189">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>1294904.5955406395</v>
+        <v>306997.23769416759</v>
       </c>
       <c r="H19" s="189" t="str">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
@@ -9727,14 +9829,14 @@
       </c>
       <c r="C23" s="203">
         <f>-C4*C28</f>
-        <v>-11151623</v>
+        <v>-2302385</v>
       </c>
       <c r="D23" s="59"/>
       <c r="E23" s="307"/>
       <c r="F23" s="59"/>
       <c r="G23" s="186">
         <f>Data!C37</f>
-        <v>-11151623</v>
+        <v>-2302385</v>
       </c>
       <c r="H23" s="186" t="str">
         <f>Data!D37</f>
@@ -9784,14 +9886,14 @@
       </c>
       <c r="C24" s="197">
         <f>-C4*C29</f>
-        <v>-2043458.9999999998</v>
+        <v>-70260</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="305"/>
       <c r="F24" s="27"/>
       <c r="G24" s="186">
         <f>Data!C40</f>
-        <v>-2043459</v>
+        <v>-70260</v>
       </c>
       <c r="H24" s="186" t="str">
         <f>Data!D40</f>
@@ -9841,14 +9943,14 @@
       </c>
       <c r="C25" s="187">
         <f>C23+C24</f>
-        <v>-13195082</v>
+        <v>-2372645</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="313"/>
       <c r="F25" s="9"/>
       <c r="G25" s="187">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
-        <v>-13195082</v>
+        <v>-2372645</v>
       </c>
       <c r="H25" s="187" t="str">
         <f t="shared" si="10"/>
@@ -9909,7 +10011,7 @@
       </c>
       <c r="C28" s="64">
         <f>AVERAGE(G28:J28)</f>
-        <v>0.72762956087193742</v>
+        <v>0.76465487351096573</v>
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="306" t="s">
@@ -9918,7 +10020,7 @@
       <c r="F28" s="26"/>
       <c r="G28" s="13">
         <f t="shared" ref="G28:Q28" si="11">IF(G$4="","",ABS(G23/G$4))</f>
-        <v>0.72762956087193742</v>
+        <v>0.76465487351096573</v>
       </c>
       <c r="H28" s="13" t="str">
         <f t="shared" si="11"/>
@@ -9969,7 +10071,7 @@
       </c>
       <c r="C29" s="64">
         <f>AVERAGE(G29:J29)</f>
-        <v>0.13333316368656009</v>
+        <v>2.3334347388851324E-2</v>
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="306" t="s">
@@ -9978,7 +10080,7 @@
       <c r="F29" s="26"/>
       <c r="G29" s="13">
         <f t="shared" ref="G29:Q29" si="12">IF(G$4="","",ABS(G24/G$4))</f>
-        <v>0.13333316368656009</v>
+        <v>2.3334347388851324E-2</v>
       </c>
       <c r="H29" s="13" t="str">
         <f t="shared" si="12"/>
@@ -10028,12 +10130,12 @@
       </c>
       <c r="C30" s="72">
         <f>ABS(C25/$C$4)</f>
-        <v>0.86096272455849754</v>
+        <v>0.78798922089981704</v>
       </c>
       <c r="E30" s="308"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
-        <v>0.86096272455849754</v>
+        <v>0.78798922089981704</v>
       </c>
       <c r="H30" s="30" t="str">
         <f t="shared" si="13"/>
@@ -10094,14 +10196,14 @@
       </c>
       <c r="C33" s="204">
         <f>AVERAGE(G33:J33)</f>
-        <v>-254107</v>
+        <v>-350038</v>
       </c>
       <c r="E33" s="306" t="s">
         <v>347</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
-        <v>-254107</v>
+        <v>-350038</v>
       </c>
       <c r="H33" s="197" t="str">
         <f>Data!D41</f>
@@ -10151,7 +10253,7 @@
       </c>
       <c r="C34" s="204">
         <f>AVERAGE(G34:J34)</f>
-        <v>0</v>
+        <v>-21957</v>
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="306" t="s">
@@ -10160,7 +10262,7 @@
       <c r="F34" s="59"/>
       <c r="G34" s="186">
         <f>Data!C42</f>
-        <v>0</v>
+        <v>-21957</v>
       </c>
       <c r="H34" s="186" t="str">
         <f>Data!D42</f>
@@ -10210,14 +10312,14 @@
       </c>
       <c r="C35" s="187">
         <f>C33+C34</f>
-        <v>-254107</v>
+        <v>-371995</v>
       </c>
       <c r="D35" s="59"/>
       <c r="E35" s="307"/>
       <c r="F35" s="59"/>
       <c r="G35" s="187">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
-        <v>-254107</v>
+        <v>-371995</v>
       </c>
       <c r="H35" s="187" t="str">
         <f t="shared" si="14"/>
@@ -10279,14 +10381,14 @@
       </c>
       <c r="C38" s="23">
         <f>ABS(C33/$C$4)</f>
-        <v>1.6580166386945237E-2</v>
+        <v>0.1162526087574543</v>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="305"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
-        <v>1.6580166386945237E-2</v>
+        <v>0.1162526087574543</v>
       </c>
       <c r="H38" s="13" t="str">
         <f t="shared" si="15"/>
@@ -10337,14 +10439,14 @@
       </c>
       <c r="C39" s="23">
         <f>ABS(C34/$C$4)</f>
-        <v>0</v>
+        <v>7.2922326447055008E-3</v>
       </c>
       <c r="D39" s="27"/>
       <c r="E39" s="305"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
-        <v>0</v>
+        <v>7.2922326447055008E-3</v>
       </c>
       <c r="H39" s="13" t="str">
         <f t="shared" si="16"/>
@@ -10394,12 +10496,12 @@
       </c>
       <c r="C40" s="72">
         <f>ABS(C35/$C$4)</f>
-        <v>1.6580166386945237E-2</v>
+        <v>0.12354484140215981</v>
       </c>
       <c r="E40" s="308"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
-        <v>1.6580166386945237E-2</v>
+        <v>0.12354484140215981</v>
       </c>
       <c r="H40" s="30" t="str">
         <f t="shared" si="17"/>
@@ -10468,7 +10570,7 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.17828883394563139</v>
+        <v>0.21249758196504454</v>
       </c>
       <c r="H43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10551,12 +10653,12 @@
       </c>
       <c r="C47" s="197">
         <f>-BS!G31*Normalized_FCF!C54</f>
-        <v>-59596</v>
+        <v>-24063</v>
       </c>
       <c r="E47" s="308"/>
       <c r="G47" s="197">
         <f>Data!C51</f>
-        <v>-59596</v>
+        <v>-24063</v>
       </c>
       <c r="H47" s="197" t="str">
         <f>Data!D51</f>
@@ -10606,12 +10708,12 @@
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
-        <v>17217.595540639435</v>
+        <v>8177.2376941676157</v>
       </c>
       <c r="E48" s="308"/>
       <c r="G48" s="334">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
-        <v>17217.595540639435</v>
+        <v>8177.2376941676157</v>
       </c>
       <c r="H48" s="334" t="str">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
@@ -10661,14 +10763,14 @@
       </c>
       <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
-        <v>28977</v>
+        <v>8265</v>
       </c>
       <c r="D49" s="331"/>
       <c r="E49" s="332"/>
       <c r="F49" s="331"/>
       <c r="G49" s="330">
         <f>Data!C52</f>
-        <v>28977</v>
+        <v>8265</v>
       </c>
       <c r="H49" s="330" t="str">
         <f>Data!D52</f>
@@ -10718,12 +10820,12 @@
       </c>
       <c r="C50" s="187">
         <f>C47+C48</f>
-        <v>-42378.404459360565</v>
+        <v>-15885.762305832384</v>
       </c>
       <c r="E50" s="308"/>
       <c r="G50" s="187">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-42378.404459360565</v>
+        <v>-15885.762305832384</v>
       </c>
       <c r="H50" s="187" t="str">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
@@ -10787,14 +10889,14 @@
       </c>
       <c r="C53" s="89">
         <f>G53</f>
-        <v>1.4501413508729523E-2</v>
+        <v>3.4598961821835229E-2</v>
       </c>
       <c r="E53" s="305" t="s">
         <v>349</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
-        <v>1.4501413508729523E-2</v>
+        <v>3.4598961821835229E-2</v>
       </c>
       <c r="H53" s="173"/>
       <c r="I53" s="173"/>
@@ -10814,14 +10916,14 @@
       </c>
       <c r="C54" s="84">
         <f>G54</f>
-        <v>2.9286626219579916E-2</v>
+        <v>9.7930927826660269E-2</v>
       </c>
       <c r="E54" s="305" t="s">
         <v>350</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
-        <v>2.9286626219579916E-2</v>
+        <v>9.7930927826660269E-2</v>
       </c>
       <c r="H54" s="173"/>
       <c r="I54" s="173"/>
@@ -10841,12 +10943,12 @@
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
-        <v>31.4915933955299</v>
+        <v>11.069775173502888</v>
       </c>
       <c r="E55" s="308"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
-        <v>31.4915933955299</v>
+        <v>11.069775173502888</v>
       </c>
       <c r="H55" s="42" t="str">
         <f t="shared" si="21"/>
@@ -10965,12 +11067,12 @@
       </c>
       <c r="C59" s="197">
         <f>BS!$C68*C67</f>
-        <v>0</v>
+        <v>18538.000000000004</v>
       </c>
       <c r="E59" s="308"/>
       <c r="G59" s="197">
         <f>Data!C55</f>
-        <v>639</v>
+        <v>18538</v>
       </c>
       <c r="H59" s="197" t="str">
         <f>Data!D55</f>
@@ -11075,12 +11177,12 @@
       </c>
       <c r="C61" s="187">
         <f>SUM(C58:C60)</f>
-        <v>0</v>
+        <v>18538.000000000004</v>
       </c>
       <c r="E61" s="308"/>
       <c r="G61" s="187">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
-        <v>639</v>
+        <v>18538</v>
       </c>
       <c r="H61" s="187" t="str">
         <f t="shared" si="22"/>
@@ -11136,7 +11238,7 @@
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
-        <v>247678</v>
+        <v>-31654</v>
       </c>
       <c r="H62" s="197" t="str">
         <f>Data!D58</f>
@@ -11186,12 +11288,12 @@
       </c>
       <c r="C63" s="187">
         <f>C61+C62</f>
-        <v>0</v>
+        <v>18538.000000000004</v>
       </c>
       <c r="E63" s="308"/>
       <c r="G63" s="187">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
-        <v>248317</v>
+        <v>-13116</v>
       </c>
       <c r="H63" s="187" t="str">
         <f t="shared" si="23"/>
@@ -11280,12 +11382,12 @@
       </c>
       <c r="C67" s="180">
         <f>G67</f>
-        <v>0</v>
+        <v>6.3354818424775985E-2</v>
       </c>
       <c r="E67" s="308"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
-        <v>0</v>
+        <v>6.3354818424775985E-2</v>
       </c>
       <c r="H67" s="179"/>
       <c r="I67" s="179"/>
@@ -11330,14 +11432,14 @@
       </c>
       <c r="C69" s="72">
         <f>C61/BS!C70</f>
-        <v>0</v>
+        <v>3.4879564090117152E-2</v>
       </c>
       <c r="D69" s="9"/>
       <c r="E69" s="313"/>
       <c r="F69" s="9"/>
       <c r="G69" s="72">
         <f>G61/BS!C70</f>
-        <v>3.197847683362034E-4</v>
+        <v>3.4879564090117145E-2</v>
       </c>
       <c r="H69" s="179"/>
       <c r="I69" s="179"/>
@@ -11404,14 +11506,14 @@
       </c>
       <c r="C73" s="79">
         <f>ABS(C5/C$4)</f>
-        <v>0.86096272455849754</v>
+        <v>0.78798922089981704</v>
       </c>
       <c r="D73" s="27"/>
       <c r="E73" s="305"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
-        <v>0.86096272455849754</v>
+        <v>0.78798922089981704</v>
       </c>
       <c r="H73" s="6" t="str">
         <f t="shared" si="24"/>
@@ -11461,14 +11563,14 @@
       </c>
       <c r="C74" s="80">
         <f>ABS(C6/C$4)</f>
-        <v>0.13903727544150246</v>
+        <v>0.21201077910018293</v>
       </c>
       <c r="D74" s="27"/>
       <c r="E74" s="305"/>
       <c r="F74" s="27"/>
       <c r="G74" s="66">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
-        <v>0.13903727544150246</v>
+        <v>0.21201077910018293</v>
       </c>
       <c r="H74" s="66" t="str">
         <f t="shared" si="25"/>
@@ -11518,14 +11620,14 @@
       </c>
       <c r="C75" s="79">
         <f>ABS(C7/C$4)</f>
-        <v>1.6580166386945237E-2</v>
+        <v>0.12354484140215981</v>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="305"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
-        <v>1.6580166386945237E-2</v>
+        <v>0.12354484140215981</v>
       </c>
       <c r="H75" s="6" t="str">
         <f t="shared" si="26"/>
@@ -11575,14 +11677,14 @@
       </c>
       <c r="C76" s="80">
         <f>ABS(C8/C$4)</f>
-        <v>0.12245710905455723</v>
+        <v>8.846593769802312E-2</v>
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="305"/>
       <c r="F76" s="27"/>
       <c r="G76" s="66">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
-        <v>0.12245710905455723</v>
+        <v>8.846593769802312E-2</v>
       </c>
       <c r="H76" s="66" t="str">
         <f t="shared" si="27"/>
@@ -11632,14 +11734,14 @@
       </c>
       <c r="C77" s="79">
         <f>ABS(C9/C$4)</f>
-        <v>3.0237840861147901E-2</v>
+        <v>7.6248118572758927E-2</v>
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="305"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
-        <v>3.0237840861147901E-2</v>
+        <v>7.6248118572758927E-2</v>
       </c>
       <c r="H77" s="6" t="str">
         <f t="shared" si="28"/>
@@ -11689,16 +11791,16 @@
       </c>
       <c r="C78" s="90">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
-        <v>4.413341231043115E-2</v>
+        <v>7.6248118572758927E-2</v>
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="306" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
         <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",-G10/G$4)</f>
-        <v>4.413341231043115E-2</v>
+        <v>3.8291776983950913E-2</v>
       </c>
       <c r="H78" s="6" t="str">
         <f t="shared" si="29"/>
@@ -11748,14 +11850,14 @@
       </c>
       <c r="C79" s="80">
         <f>ABS(C11/C$4)</f>
-        <v>0</v>
+        <v>6.1567340150089087E-3</v>
       </c>
       <c r="D79" s="27"/>
       <c r="E79" s="305"/>
       <c r="F79" s="27"/>
       <c r="G79" s="66">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
-        <v>4.1693956960091643E-5</v>
+        <v>6.156734015008907E-3</v>
       </c>
       <c r="H79" s="66" t="str">
         <f t="shared" si="30"/>
@@ -11805,14 +11907,14 @@
       </c>
       <c r="C80" s="79">
         <f>ABS(C12/C$4)</f>
-        <v>2.7651382966603051E-3</v>
+        <v>5.2758880754485149E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="305"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>2.7651382966603051E-3</v>
+        <v>5.2758880754485149E-3</v>
       </c>
       <c r="H80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -11862,14 +11964,14 @@
       </c>
       <c r="C81" s="80">
         <f>C13/C4</f>
-        <v>0.10579639930861368</v>
+        <v>8.9346783637583513E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="305"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.10583809326557377</v>
+        <v>0.12730312522639153</v>
       </c>
       <c r="H81" s="66" t="str">
         <f t="shared" si="32"/>
@@ -11919,14 +12021,14 @@
       </c>
       <c r="C82" s="79">
         <f>ABS(C14/C$4)</f>
-        <v>2.992299268947423E-2</v>
+        <v>2.2336695909395878E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="305"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>2.134717546604905E-2</v>
+        <v>1.89859754793405E-2</v>
       </c>
       <c r="H82" s="6" t="str">
         <f t="shared" si="33"/>
@@ -11977,14 +12079,14 @@
       </c>
       <c r="C83" s="304">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
-        <v>0</v>
+        <v>6.358991594852495E-3</v>
       </c>
       <c r="D83" s="27"/>
       <c r="E83" s="305"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
-        <v>0</v>
+        <v>6.358991594852495E-3</v>
       </c>
       <c r="H83" s="6" t="str">
         <f t="shared" si="34"/>
@@ -12034,14 +12136,14 @@
       </c>
       <c r="C84" s="80">
         <f>ABS(C16/C$4)</f>
-        <v>7.5873406619139452E-2</v>
+        <v>6.0651096133335143E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="305"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>8.4490917799524723E-2</v>
+        <v>0.10195815815219852</v>
       </c>
       <c r="H84" s="66" t="str">
         <f t="shared" si="35"/>
@@ -12141,14 +12243,14 @@
       </c>
       <c r="C87" s="80">
         <f>ABS(C19/C$4)</f>
-        <v>7.5873406619139452E-2</v>
+        <v>6.0651096133335143E-2</v>
       </c>
       <c r="D87" s="77"/>
       <c r="E87" s="305"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>8.4490917799524723E-2</v>
+        <v>0.10195815815219852</v>
       </c>
       <c r="H87" s="66" t="str">
         <f t="shared" si="36"/>
@@ -12210,51 +12312,51 @@
       </c>
       <c r="C90" s="117">
         <f>G90</f>
-        <v>1.36</v>
+        <v>0.49984047644368812</v>
       </c>
       <c r="E90" s="308"/>
       <c r="G90" s="116">
-        <f>Data!C64</f>
-        <v>1.36</v>
+        <f>Data!C65</f>
+        <v>0.49984047644368812</v>
       </c>
       <c r="H90" s="116" t="str">
-        <f>Data!D64</f>
+        <f>Data!D65</f>
         <v/>
       </c>
       <c r="I90" s="116" t="str">
-        <f>Data!E64</f>
+        <f>Data!E65</f>
         <v/>
       </c>
       <c r="J90" s="116" t="str">
-        <f>Data!F64</f>
+        <f>Data!F65</f>
         <v/>
       </c>
       <c r="K90" s="116" t="str">
-        <f>Data!G64</f>
+        <f>Data!G65</f>
         <v/>
       </c>
       <c r="L90" s="116" t="str">
-        <f>Data!H64</f>
+        <f>Data!H65</f>
         <v/>
       </c>
       <c r="M90" s="116" t="str">
-        <f>Data!I64</f>
+        <f>Data!I65</f>
         <v/>
       </c>
       <c r="N90" s="116" t="str">
-        <f>Data!J64</f>
+        <f>Data!J65</f>
         <v/>
       </c>
       <c r="O90" s="116" t="str">
-        <f>Data!K64</f>
+        <f>Data!K65</f>
         <v/>
       </c>
       <c r="P90" s="116" t="str">
-        <f>Data!L64</f>
+        <f>Data!L65</f>
         <v/>
       </c>
       <c r="Q90" s="116" t="str">
-        <f>Data!M64</f>
+        <f>Data!M65</f>
         <v/>
       </c>
     </row>
@@ -12266,12 +12368,12 @@
       </c>
       <c r="C91" s="76">
         <f>C90*Common_Shares/$C$3</f>
-        <v>798466.67599999998</v>
+        <v>91481.292751738802</v>
       </c>
       <c r="E91" s="308"/>
       <c r="G91" s="76">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>798466.67599999998</v>
+        <v>91481.292751738802</v>
       </c>
       <c r="H91" s="76" t="str">
         <f t="shared" si="37"/>
@@ -12321,12 +12423,12 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>0.68665639230169417</v>
+        <v>0.50093474162220653</v>
       </c>
       <c r="E92" s="308"/>
       <c r="G92" s="174">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>0.61662201118888604</v>
+        <v>0.29798734815611916</v>
       </c>
       <c r="H92" s="174" t="str">
         <f t="shared" si="38"/>
@@ -12376,12 +12478,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>8.8311688311688313E-2</v>
+        <v>9.0061347106970835E-2</v>
       </c>
       <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>8.8311688311688313E-2</v>
+        <v>9.0061347106970835E-2</v>
       </c>
       <c r="H93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -12513,7 +12615,7 @@
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
-        <v>-3.9394093065781011E-4</v>
+        <v>-0.29815718601807895</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="305"/>
@@ -12606,14 +12708,14 @@
       </c>
       <c r="C101" s="205">
         <f>BS!G32</f>
-        <v>16854064</v>
+        <v>2768297</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="309"/>
       <c r="F101" s="26"/>
       <c r="G101" s="186">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
-        <v>16854064</v>
+        <v>2752710</v>
       </c>
       <c r="H101" s="186" t="str">
         <f t="shared" si="42"/>
@@ -12663,53 +12765,53 @@
       </c>
       <c r="C102" s="206">
         <f>BS!C4</f>
-        <v>265773</v>
+        <v>142879</v>
       </c>
       <c r="D102" s="91"/>
       <c r="E102" s="310"/>
       <c r="F102" s="91"/>
       <c r="G102" s="188" t="str">
-        <f>IF(G$4="","",Data!D76)</f>
+        <f>IF(G$4="","",Data!D77)</f>
         <v/>
       </c>
       <c r="H102" s="188" t="str">
-        <f>IF(H$4="","",Data!E76)</f>
+        <f>IF(H$4="","",Data!E77)</f>
         <v/>
       </c>
       <c r="I102" s="188" t="str">
-        <f>IF(I$4="","",Data!F76)</f>
+        <f>IF(I$4="","",Data!F77)</f>
         <v/>
       </c>
       <c r="J102" s="188" t="str">
-        <f>IF(J$4="","",Data!G76)</f>
+        <f>IF(J$4="","",Data!G77)</f>
         <v/>
       </c>
       <c r="K102" s="188" t="str">
-        <f>IF(K$4="","",Data!H76)</f>
+        <f>IF(K$4="","",Data!H77)</f>
         <v/>
       </c>
       <c r="L102" s="188" t="str">
-        <f>IF(L$4="","",Data!I76)</f>
+        <f>IF(L$4="","",Data!I77)</f>
         <v/>
       </c>
       <c r="M102" s="188" t="str">
-        <f>IF(M$4="","",Data!J76)</f>
+        <f>IF(M$4="","",Data!J77)</f>
         <v/>
       </c>
       <c r="N102" s="188" t="str">
-        <f>IF(N$4="","",Data!K76)</f>
+        <f>IF(N$4="","",Data!K77)</f>
         <v/>
       </c>
       <c r="O102" s="188" t="str">
-        <f>IF(O$4="","",Data!L76)</f>
+        <f>IF(O$4="","",Data!L77)</f>
         <v/>
       </c>
       <c r="P102" s="188" t="str">
-        <f>IF(P$4="","",Data!M76)</f>
+        <f>IF(P$4="","",Data!M77)</f>
         <v/>
       </c>
       <c r="Q102" s="188" t="str">
-        <f>IF(Q$4="","",Data!N76)</f>
+        <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
     </row>
@@ -12720,53 +12822,53 @@
       </c>
       <c r="C103" s="206">
         <f>BS!C6+BS!C7</f>
-        <v>9672256</v>
+        <v>182674</v>
       </c>
       <c r="D103" s="91"/>
       <c r="E103" s="310"/>
       <c r="F103" s="91"/>
       <c r="G103" s="188" t="str">
-        <f>IF(G$4="","",Data!D77)</f>
+        <f>IF(G$4="","",Data!D78)</f>
         <v/>
       </c>
       <c r="H103" s="188" t="str">
-        <f>IF(H$4="","",Data!E77)</f>
+        <f>IF(H$4="","",Data!E78)</f>
         <v/>
       </c>
       <c r="I103" s="188" t="str">
-        <f>IF(I$4="","",Data!F77)</f>
+        <f>IF(I$4="","",Data!F78)</f>
         <v/>
       </c>
       <c r="J103" s="188" t="str">
-        <f>IF(J$4="","",Data!G77)</f>
+        <f>IF(J$4="","",Data!G78)</f>
         <v/>
       </c>
       <c r="K103" s="188" t="str">
-        <f>IF(K$4="","",Data!H77)</f>
+        <f>IF(K$4="","",Data!H78)</f>
         <v/>
       </c>
       <c r="L103" s="188" t="str">
-        <f>IF(L$4="","",Data!I77)</f>
+        <f>IF(L$4="","",Data!I78)</f>
         <v/>
       </c>
       <c r="M103" s="188" t="str">
-        <f>IF(M$4="","",Data!J77)</f>
+        <f>IF(M$4="","",Data!J78)</f>
         <v/>
       </c>
       <c r="N103" s="188" t="str">
-        <f>IF(N$4="","",Data!K77)</f>
+        <f>IF(N$4="","",Data!K78)</f>
         <v/>
       </c>
       <c r="O103" s="188" t="str">
-        <f>IF(O$4="","",Data!L77)</f>
+        <f>IF(O$4="","",Data!L78)</f>
         <v/>
       </c>
       <c r="P103" s="188" t="str">
-        <f>IF(P$4="","",Data!M77)</f>
+        <f>IF(P$4="","",Data!M78)</f>
         <v/>
       </c>
       <c r="Q103" s="188" t="str">
-        <f>IF(Q$4="","",Data!N77)</f>
+        <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
     </row>
@@ -12777,53 +12879,53 @@
       </c>
       <c r="C104" s="205">
         <f>BS!G30</f>
-        <v>3990166</v>
+        <v>1090144</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="309"/>
       <c r="F104" s="26"/>
       <c r="G104" s="186">
-        <f>Data!C78</f>
-        <v>3990166</v>
+        <f>Data!C79</f>
+        <v>1122089</v>
       </c>
       <c r="H104" s="186" t="str">
-        <f>Data!D78</f>
+        <f>Data!D79</f>
         <v/>
       </c>
       <c r="I104" s="186" t="str">
-        <f>Data!E78</f>
+        <f>Data!E79</f>
         <v/>
       </c>
       <c r="J104" s="186" t="str">
-        <f>Data!F78</f>
+        <f>Data!F79</f>
         <v/>
       </c>
       <c r="K104" s="186" t="str">
-        <f>Data!G78</f>
+        <f>Data!G79</f>
         <v/>
       </c>
       <c r="L104" s="186" t="str">
-        <f>Data!H78</f>
+        <f>Data!H79</f>
         <v/>
       </c>
       <c r="M104" s="186" t="str">
-        <f>Data!I78</f>
+        <f>Data!I79</f>
         <v/>
       </c>
       <c r="N104" s="186" t="str">
-        <f>Data!J78</f>
+        <f>Data!J79</f>
         <v/>
       </c>
       <c r="O104" s="186" t="str">
-        <f>Data!K78</f>
+        <f>Data!K79</f>
         <v/>
       </c>
       <c r="P104" s="186" t="str">
-        <f>Data!L78</f>
+        <f>Data!L79</f>
         <v/>
       </c>
       <c r="Q104" s="186" t="str">
-        <f>Data!M78</f>
+        <f>Data!M79</f>
         <v/>
       </c>
     </row>
@@ -12834,53 +12936,53 @@
       </c>
       <c r="C105" s="205">
         <f>BS!G27</f>
-        <v>12863898</v>
+        <v>1678153</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="309"/>
       <c r="F105" s="26"/>
       <c r="G105" s="186">
-        <f>Data!C79</f>
-        <v>12863898</v>
+        <f>Data!C80</f>
+        <v>1630621</v>
       </c>
       <c r="H105" s="186" t="str">
-        <f>Data!D79</f>
+        <f>Data!D80</f>
         <v/>
       </c>
       <c r="I105" s="186" t="str">
-        <f>Data!E79</f>
+        <f>Data!E80</f>
         <v/>
       </c>
       <c r="J105" s="186" t="str">
-        <f>Data!F79</f>
+        <f>Data!F80</f>
         <v/>
       </c>
       <c r="K105" s="186" t="str">
-        <f>Data!G79</f>
+        <f>Data!G80</f>
         <v/>
       </c>
       <c r="L105" s="186" t="str">
-        <f>Data!H79</f>
+        <f>Data!H80</f>
         <v/>
       </c>
       <c r="M105" s="186" t="str">
-        <f>Data!I79</f>
+        <f>Data!I80</f>
         <v/>
       </c>
       <c r="N105" s="186" t="str">
-        <f>Data!J79</f>
+        <f>Data!J80</f>
         <v/>
       </c>
       <c r="O105" s="186" t="str">
-        <f>Data!K79</f>
+        <f>Data!K80</f>
         <v/>
       </c>
       <c r="P105" s="186" t="str">
-        <f>Data!L79</f>
+        <f>Data!L80</f>
         <v/>
       </c>
       <c r="Q105" s="186" t="str">
-        <f>Data!M79</f>
+        <f>Data!M80</f>
         <v/>
       </c>
     </row>
@@ -12918,7 +13020,7 @@
       </c>
       <c r="C108" s="97">
         <f>C102/C$4</f>
-        <v>1.7341358408692387E-2</v>
+        <v>4.7452152299625509E-2</v>
       </c>
       <c r="D108" s="26"/>
       <c r="E108" s="309"/>
@@ -12975,7 +13077,7 @@
       </c>
       <c r="C109" s="97">
         <f>C103/C$4</f>
-        <v>0.63110270011109249</v>
+        <v>6.0668638982508204E-2</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="309"/>
@@ -13058,462 +13160,573 @@
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10"/>
-      <c r="B112" s="93" t="s">
-        <v>38</v>
-      </c>
-      <c r="C112" s="55"/>
-      <c r="D112" s="55"/>
-      <c r="E112" s="311"/>
-      <c r="F112" s="55"/>
-      <c r="G112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*G114*(1/#REF!)=G116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*H114*(1/#REF!)=H116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*I114*(1/#REF!)=I116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*J114*(1/#REF!)=J116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*K114*(1/#REF!)=K116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*L114*(1/#REF!)=L116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*M114*(1/#REF!)=M116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*N114*(1/#REF!)=N116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*O114*(1/#REF!)=O116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*P114*(1/#REF!)=P116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*Q114*(1/#REF!)=Q116,"","Error"),"")</f>
-        <v/>
-      </c>
+      <c r="B112" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="E112" s="308"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
-      <c r="B113" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="C113" s="23">
-        <f>C81</f>
-        <v>0.10579639930861368</v>
-      </c>
+      <c r="B113" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C113" s="173"/>
       <c r="E113" s="308"/>
-      <c r="G113" s="23">
-        <f t="shared" ref="G113:Q113" si="45">G81</f>
-        <v>0.10583809326557377</v>
-      </c>
-      <c r="H113" s="23" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="I113" s="23" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="J113" s="23" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="K113" s="23" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="L113" s="23" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="M113" s="23" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="N113" s="23" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="O113" s="23" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="P113" s="23" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="Q113" s="23" t="str">
-        <f t="shared" si="45"/>
+      <c r="G113" s="340">
+        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
+        <v>2.5325501550271508</v>
+      </c>
+      <c r="H113" s="340" t="str">
+        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
+        <v/>
+      </c>
+      <c r="I113" s="340" t="str">
+        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
+        <v/>
+      </c>
+      <c r="J113" s="340" t="str">
+        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
+        <v/>
+      </c>
+      <c r="K113" s="340" t="str">
+        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
+        <v/>
+      </c>
+      <c r="L113" s="340" t="str">
+        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
+        <v/>
+      </c>
+      <c r="M113" s="340" t="str">
+        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
+        <v/>
+      </c>
+      <c r="N113" s="340" t="str">
+        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
+        <v/>
+      </c>
+      <c r="O113" s="340" t="str">
+        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
+        <v/>
+      </c>
+      <c r="P113" s="340" t="str">
+        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
+        <v/>
+      </c>
+      <c r="Q113" s="340" t="str">
+        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B114" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C114" s="42">
-        <f>C4/C101</f>
-        <v>0.90933332162498015</v>
-      </c>
+      <c r="A114" s="10"/>
+      <c r="B114" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C114" s="173"/>
       <c r="E114" s="308"/>
-      <c r="G114" s="42">
-        <f t="shared" ref="G114:Q114" si="46">IF(G4="","",G4/G101)</f>
-        <v>0.90933332162498015</v>
-      </c>
-      <c r="H114" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="I114" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="J114" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="K114" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="L114" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="M114" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="N114" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="O114" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="P114" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="Q114" s="42" t="str">
-        <f t="shared" si="46"/>
+      <c r="G114" s="340">
+        <f>IF(G$4="","",Data!C$22/G19)</f>
+        <v>1.4872967699301045</v>
+      </c>
+      <c r="H114" s="340" t="str">
+        <f>IF(H$4="","",Data!D$22/H19)</f>
+        <v/>
+      </c>
+      <c r="I114" s="340" t="str">
+        <f>IF(I$4="","",Data!E$22/I19)</f>
+        <v/>
+      </c>
+      <c r="J114" s="340" t="str">
+        <f>IF(J$4="","",Data!F$22/J19)</f>
+        <v/>
+      </c>
+      <c r="K114" s="340" t="str">
+        <f>IF(K$4="","",Data!G$22/K19)</f>
+        <v/>
+      </c>
+      <c r="L114" s="340" t="str">
+        <f>IF(L$4="","",Data!H$22/L19)</f>
+        <v/>
+      </c>
+      <c r="M114" s="340" t="str">
+        <f>IF(M$4="","",Data!I$22/M19)</f>
+        <v/>
+      </c>
+      <c r="N114" s="340" t="str">
+        <f>IF(N$4="","",Data!J$22/N19)</f>
+        <v/>
+      </c>
+      <c r="O114" s="340" t="str">
+        <f>IF(O$4="","",Data!K$22/O19)</f>
+        <v/>
+      </c>
+      <c r="P114" s="340" t="str">
+        <f>IF(P$4="","",Data!L$22/P19)</f>
+        <v/>
+      </c>
+      <c r="Q114" s="340" t="str">
+        <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C115" s="15">
-        <f>C101/C105</f>
-        <v>1.3101832741522048</v>
-      </c>
-      <c r="D115" s="11"/>
-      <c r="E115" s="312"/>
-      <c r="F115" s="11"/>
-      <c r="G115" s="15">
-        <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G101/G105)</f>
-        <v>1.3101832741522048</v>
-      </c>
-      <c r="H115" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="I115" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="J115" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="K115" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="L115" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="M115" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="N115" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="O115" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="P115" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="Q115" s="15" t="str">
-        <f t="shared" si="47"/>
-        <v/>
-      </c>
+      <c r="A115" s="10"/>
+      <c r="E115" s="308"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="10"/>
-      <c r="B116" s="71" t="s">
-        <v>224</v>
-      </c>
-      <c r="C116" s="105">
-        <f>C8/C105</f>
-        <v>0.14589458032083277</v>
-      </c>
-      <c r="D116" s="106"/>
+      <c r="B116" s="93" t="s">
+        <v>38</v>
+      </c>
+      <c r="C116" s="55"/>
+      <c r="D116" s="55"/>
       <c r="E116" s="311"/>
-      <c r="F116" s="106"/>
-      <c r="G116" s="105">
-        <f t="shared" ref="G116:Q116" si="48">IF(G$4="","",G8/G105)</f>
-        <v>0.14589458032083277</v>
-      </c>
-      <c r="H116" s="105" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="I116" s="105" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="J116" s="105" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="K116" s="105" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="L116" s="105" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="M116" s="105" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="N116" s="105" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="O116" s="105" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="P116" s="105" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="Q116" s="105" t="str">
-        <f t="shared" si="48"/>
+      <c r="F116" s="55"/>
+      <c r="G116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*H118*(1/#REF!)=H120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*I118*(1/#REF!)=I120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*J118*(1/#REF!)=J120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*K118*(1/#REF!)=K120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*L118*(1/#REF!)=L120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*M118*(1/#REF!)=M120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*N118*(1/#REF!)=N120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*O118*(1/#REF!)=O120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*P118*(1/#REF!)=P120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*Q118*(1/#REF!)=Q120,"","Error"),"")</f>
         <v/>
       </c>
     </row>
     <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="10"/>
-      <c r="B117" s="27"/>
-      <c r="C117" s="63"/>
-      <c r="D117" s="27"/>
-      <c r="E117" s="68"/>
-      <c r="F117" s="27"/>
-      <c r="G117" s="12"/>
-      <c r="H117" s="12"/>
-      <c r="I117" s="12"/>
-      <c r="J117" s="12"/>
-      <c r="K117" s="12"/>
-      <c r="L117" s="12"/>
-      <c r="M117" s="12"/>
-      <c r="N117" s="12"/>
-      <c r="O117" s="12"/>
-      <c r="P117" s="12"/>
-      <c r="Q117" s="12"/>
-    </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A118" s="10"/>
-      <c r="B118" s="54" t="s">
-        <v>225</v>
-      </c>
-      <c r="C118" s="54"/>
-      <c r="D118" s="56"/>
-      <c r="E118" s="67" t="s">
-        <v>60</v>
-      </c>
-      <c r="F118" s="56"/>
-      <c r="G118" s="37"/>
-      <c r="H118" s="37"/>
-      <c r="I118" s="37"/>
-      <c r="J118" s="37"/>
-      <c r="K118" s="37"/>
-      <c r="L118" s="37"/>
-      <c r="M118" s="37"/>
-      <c r="N118" s="37"/>
-      <c r="O118" s="37"/>
-      <c r="P118" s="37"/>
-      <c r="Q118" s="37"/>
+      <c r="B117" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C117" s="23">
+        <f>C81</f>
+        <v>8.9346783637583513E-2</v>
+      </c>
+      <c r="E117" s="308"/>
+      <c r="G117" s="23">
+        <f t="shared" ref="G117:Q117" si="45">G81</f>
+        <v>0.12730312522639153</v>
+      </c>
+      <c r="H117" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="I117" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="J117" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="K117" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="L117" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="M117" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="N117" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="O117" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="P117" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="Q117" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B118" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C118" s="42">
+        <f>C4/C101</f>
+        <v>1.0876766474117481</v>
+      </c>
+      <c r="E118" s="308"/>
+      <c r="G118" s="42">
+        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
+        <v>1.0938355293510758</v>
+      </c>
+      <c r="H118" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="I118" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="J118" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="K118" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="L118" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="M118" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="N118" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="O118" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="P118" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="Q118" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
     </row>
     <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="10"/>
-      <c r="B119" s="182" t="s">
-        <v>172</v>
-      </c>
-      <c r="C119" s="183"/>
-      <c r="D119" s="27"/>
-      <c r="E119" s="305"/>
-      <c r="F119" s="27"/>
-      <c r="G119" s="12"/>
-      <c r="H119" s="12"/>
-      <c r="I119" s="12"/>
-      <c r="J119" s="12"/>
-      <c r="K119" s="12"/>
-      <c r="L119" s="12"/>
-      <c r="M119" s="12"/>
-      <c r="N119" s="12"/>
-      <c r="O119" s="12"/>
-      <c r="P119" s="12"/>
-      <c r="Q119" s="12"/>
+      <c r="B119" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C119" s="15">
+        <f>C101/C105</f>
+        <v>1.6496094217869288</v>
+      </c>
+      <c r="D119" s="11"/>
+      <c r="E119" s="312"/>
+      <c r="F119" s="11"/>
+      <c r="G119" s="15">
+        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
+        <v>1.6881359923611925</v>
+      </c>
+      <c r="H119" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="I119" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="J119" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="K119" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="L119" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="M119" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="N119" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="O119" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="P119" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="Q119" s="15" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
     </row>
     <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="10"/>
-      <c r="B120" s="27" t="str">
+      <c r="B120" s="71" t="s">
+        <v>224</v>
+      </c>
+      <c r="C120" s="105">
+        <f>C8/C105</f>
+        <v>0.1587292696196354</v>
+      </c>
+      <c r="D120" s="106"/>
+      <c r="E120" s="311"/>
+      <c r="F120" s="106"/>
+      <c r="G120" s="105">
+        <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
+        <v>0.16335616921406015</v>
+      </c>
+      <c r="H120" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="I120" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="J120" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="K120" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="L120" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="M120" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="N120" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="O120" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="P120" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="Q120" s="105" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="10"/>
+      <c r="B121" s="27"/>
+      <c r="C121" s="63"/>
+      <c r="D121" s="27"/>
+      <c r="E121" s="68"/>
+      <c r="F121" s="27"/>
+      <c r="G121" s="12"/>
+      <c r="H121" s="12"/>
+      <c r="I121" s="12"/>
+      <c r="J121" s="12"/>
+      <c r="K121" s="12"/>
+      <c r="L121" s="12"/>
+      <c r="M121" s="12"/>
+      <c r="N121" s="12"/>
+      <c r="O121" s="12"/>
+      <c r="P121" s="12"/>
+      <c r="Q121" s="12"/>
+    </row>
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A122" s="10"/>
+      <c r="B122" s="54" t="s">
+        <v>225</v>
+      </c>
+      <c r="C122" s="54"/>
+      <c r="D122" s="56"/>
+      <c r="E122" s="67" t="s">
+        <v>60</v>
+      </c>
+      <c r="F122" s="56"/>
+      <c r="G122" s="37"/>
+      <c r="H122" s="37"/>
+      <c r="I122" s="37"/>
+      <c r="J122" s="37"/>
+      <c r="K122" s="37"/>
+      <c r="L122" s="37"/>
+      <c r="M122" s="37"/>
+      <c r="N122" s="37"/>
+      <c r="O122" s="37"/>
+      <c r="P122" s="37"/>
+      <c r="Q122" s="37"/>
+    </row>
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="10"/>
+      <c r="B123" s="182" t="s">
+        <v>172</v>
+      </c>
+      <c r="C123" s="183"/>
+      <c r="D123" s="27"/>
+      <c r="E123" s="305"/>
+      <c r="F123" s="27"/>
+      <c r="G123" s="12"/>
+      <c r="H123" s="12"/>
+      <c r="I123" s="12"/>
+      <c r="J123" s="12"/>
+      <c r="K123" s="12"/>
+      <c r="L123" s="12"/>
+      <c r="M123" s="12"/>
+      <c r="N123" s="12"/>
+      <c r="O123" s="12"/>
+      <c r="P123" s="12"/>
+      <c r="Q123" s="12"/>
+    </row>
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="10"/>
+      <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
         <v>FCFE per share (HKD)</v>
       </c>
-      <c r="C120" s="181">
+      <c r="C124" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.9806121595129067</v>
-      </c>
-      <c r="D120" s="27"/>
-      <c r="E120" s="305"/>
-      <c r="F120" s="27"/>
-      <c r="G120" s="181">
-        <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.205565119833842</v>
-      </c>
-      <c r="H120" s="181" t="str">
+        <v>0.93824596488950096</v>
+      </c>
+      <c r="D124" s="27"/>
+      <c r="E124" s="305"/>
+      <c r="F124" s="27"/>
+      <c r="G124" s="181">
+        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>1.5772481714685458</v>
+      </c>
+      <c r="H124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="I120" s="181" t="str">
+      <c r="I124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="J120" s="181" t="str">
+      <c r="J124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="K120" s="181" t="str">
+      <c r="K124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="L120" s="181" t="str">
+      <c r="L124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="M120" s="181" t="str">
+      <c r="M124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="N120" s="181" t="str">
+      <c r="N124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="O120" s="181" t="str">
+      <c r="O124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="P120" s="181" t="str">
+      <c r="P124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="Q120" s="181" t="str">
+      <c r="Q124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="10"/>
-      <c r="B121" s="27" t="s">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="10"/>
+      <c r="B125" s="27" t="s">
         <v>272</v>
       </c>
-      <c r="C121" s="79">
+      <c r="C125" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12861117918914977</v>
-      </c>
-      <c r="D121" s="27"/>
-      <c r="E121" s="305"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="79">
-        <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>0.1432185142749248</v>
-      </c>
-      <c r="H121" s="79" t="str">
-        <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="I121" s="79" t="str">
-        <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="J121" s="79" t="str">
-        <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="K121" s="79" t="str">
-        <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="L121" s="79" t="str">
-        <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="M121" s="79" t="str">
-        <f t="shared" ref="M121" si="56">IF(M$4="","",M120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="N121" s="79" t="str">
-        <f t="shared" ref="N121" si="57">IF(N$4="","",N120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="O121" s="79" t="str">
-        <f t="shared" ref="O121" si="58">IF(O$4="","",O120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="P121" s="79" t="str">
-        <f t="shared" ref="P121" si="59">IF(P$4="","",P120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="Q121" s="79" t="str">
-        <f t="shared" ref="Q121" si="60">IF(Q$4="","",Q120/Market_Price)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+        <v>0.16905332700711728</v>
+      </c>
+      <c r="D125" s="27"/>
+      <c r="E125" s="305"/>
+      <c r="F125" s="27"/>
+      <c r="G125" s="79">
+        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
+        <v>0.28418885972406233</v>
+      </c>
+      <c r="H125" s="79" t="str">
+        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="I125" s="79" t="str">
+        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="J125" s="79" t="str">
+        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="K125" s="79" t="str">
+        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="L125" s="79" t="str">
+        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="M125" s="79" t="str">
+        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="N125" s="79" t="str">
+        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="O125" s="79" t="str">
+        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="P125" s="79" t="str">
+        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="Q125" s="79" t="str">
+        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
+        <v/>
+      </c>
+    </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -14193,6 +14406,10 @@
     <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -14241,7 +14458,7 @@
       </c>
       <c r="C3" s="110">
         <f>Normalized_FCF!C3</f>
-        <v>1000</v>
+        <v>1000000</v>
       </c>
       <c r="E3" s="112" t="s">
         <v>126</v>
@@ -14254,11 +14471,11 @@
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
-        <v>1162832.9466554797</v>
+        <v>182621.17827062571</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="E4" s="103" t="s">
         <v>252</v>
@@ -14286,16 +14503,16 @@
       </c>
       <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>14535411.833193496</v>
+        <v>2282764.7283828212</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E6" s="347" t="s">
+        <v>CNY</v>
+      </c>
+      <c r="E6" s="349" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="347"/>
+      <c r="F6" s="349"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14304,14 +14521,14 @@
       </c>
       <c r="C7" s="232">
         <f>BS!G31</f>
-        <v>2034922</v>
+        <v>245714</v>
       </c>
       <c r="D7" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E7" s="347"/>
-      <c r="F7" s="347"/>
+        <v>CNY</v>
+      </c>
+      <c r="E7" s="349"/>
+      <c r="F7" s="349"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14320,14 +14537,14 @@
       </c>
       <c r="C8" s="207">
         <f>BS!D66</f>
-        <v>810914.36033333349</v>
+        <v>2536.5589373550902</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E8" s="347"/>
-      <c r="F8" s="347"/>
+        <v>CNY</v>
+      </c>
+      <c r="E8" s="349"/>
+      <c r="F8" s="349"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14336,14 +14553,14 @@
       </c>
       <c r="C9" s="235">
         <f>BS!H42</f>
-        <v>92572.6</v>
+        <v>6352.8</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
+        <v>CNY</v>
+      </c>
+      <c r="E9" s="349"/>
+      <c r="F9" s="349"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14352,11 +14569,11 @@
       </c>
       <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
-        <v>13403976.793526828</v>
+        <v>2045940.0873201764</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
+        <v>CNY</v>
       </c>
       <c r="H10" s="124"/>
     </row>
@@ -14366,11 +14583,11 @@
       </c>
       <c r="C11" s="237">
         <f>Exchange_Rate</f>
-        <v>1</v>
+        <v>0.94030000000000002</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
-        <v>HKD</v>
+        <v>CNY/HKD</v>
       </c>
       <c r="H11" s="124"/>
     </row>
@@ -14380,7 +14597,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>22.830518776962066</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14413,7 +14630,7 @@
       </c>
       <c r="C16" s="165">
         <f>Scenarios!C65</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="H16" s="124"/>
     </row>
@@ -14433,7 +14650,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>23.325699825167451</v>
+        <v>10.189224696681462</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14468,11 +14685,11 @@
       </c>
       <c r="C21" s="127">
         <f>C4*(1+D21)</f>
-        <v>1170275.8082940446</v>
+        <v>180956.72859242809</v>
       </c>
       <c r="D21" s="142">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="E21" s="128">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -14480,7 +14697,7 @@
       </c>
       <c r="F21" s="129">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>1083588.7113833744</v>
+        <v>167552.52647447042</v>
       </c>
       <c r="H21" s="124"/>
     </row>
@@ -14490,11 +14707,11 @@
       </c>
       <c r="C22" s="127">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>1177766.3089245472</v>
+        <v>179307.44907553098</v>
       </c>
       <c r="D22" s="142">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="E22" s="128">
         <f t="shared" si="0"/>
@@ -14502,7 +14719,7 @@
       </c>
       <c r="F22" s="129">
         <f t="shared" si="1"/>
-        <v>1009744.7778845568</v>
+        <v>153727.23686173779</v>
       </c>
       <c r="H22" s="124"/>
     </row>
@@ -14512,11 +14729,11 @@
       </c>
       <c r="C23" s="127">
         <f t="shared" si="2"/>
-        <v>1185304.7534664748</v>
+        <v>177673.20145573994</v>
       </c>
       <c r="D23" s="142">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="E23" s="128">
         <f t="shared" si="0"/>
@@ -14524,7 +14741,7 @@
       </c>
       <c r="F23" s="129">
         <f t="shared" si="1"/>
-        <v>940933.12873615138</v>
+        <v>141042.7156808381</v>
       </c>
       <c r="H23" s="124"/>
     </row>
@@ -14534,11 +14751,11 @@
       </c>
       <c r="C24" s="127">
         <f t="shared" si="2"/>
-        <v>1192891.4487909905</v>
+        <v>176053.84872903093</v>
       </c>
       <c r="D24" s="142">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="E24" s="128">
         <f t="shared" si="0"/>
@@ -14546,7 +14763,7 @@
       </c>
       <c r="F24" s="129">
         <f t="shared" si="1"/>
-        <v>876810.82600698969</v>
+        <v>129404.83451554866</v>
       </c>
       <c r="H24" s="124"/>
     </row>
@@ -14556,11 +14773,11 @@
       </c>
       <c r="C25" s="127">
         <f t="shared" si="2"/>
-        <v>1200526.7037334265</v>
+        <v>174449.25514006481</v>
       </c>
       <c r="D25" s="142">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="E25" s="128">
         <f t="shared" si="0"/>
@@ -14568,7 +14785,7 @@
       </c>
       <c r="F25" s="129">
         <f t="shared" si="1"/>
-        <v>817058.30215128872</v>
+        <v>118727.23178338219</v>
       </c>
       <c r="H25" s="124"/>
     </row>
@@ -14578,11 +14795,11 @@
       </c>
       <c r="C26" s="127">
         <f t="shared" si="2"/>
-        <v>1208210.8291058543</v>
+        <v>172859.28617080644</v>
       </c>
       <c r="D26" s="142">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="E26" s="128">
         <f t="shared" si="0"/>
@@ -14590,7 +14807,7 @@
       </c>
       <c r="F26" s="129">
         <f t="shared" si="1"/>
-        <v>761377.76737376256</v>
+        <v>108930.67186953689</v>
       </c>
       <c r="H26" s="124"/>
     </row>
@@ -14600,11 +14817,11 @@
       </c>
       <c r="C27" s="127">
         <f t="shared" si="2"/>
-        <v>1215944.137709738</v>
+        <v>171283.80852924779</v>
       </c>
       <c r="D27" s="142">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="E27" s="128">
         <f t="shared" si="0"/>
@@ -14612,7 +14829,7 @@
       </c>
       <c r="F27" s="129">
         <f t="shared" si="1"/>
-        <v>709491.7255289295</v>
+        <v>99942.457140734448</v>
       </c>
       <c r="H27" s="124"/>
     </row>
@@ -14622,11 +14839,11 @@
       </c>
       <c r="C28" s="127">
         <f t="shared" si="2"/>
-        <v>1223726.9443486687</v>
+        <v>169722.69013823351</v>
       </c>
       <c r="D28" s="142">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="E28" s="128">
         <f t="shared" si="0"/>
@@ -14634,7 +14851,7 @@
       </c>
       <c r="F28" s="129">
         <f t="shared" si="1"/>
-        <v>661141.59115826653</v>
+        <v>91695.888475657892</v>
       </c>
       <c r="H28" s="124"/>
     </row>
@@ -14644,11 +14861,11 @@
       </c>
       <c r="C29" s="127">
         <f t="shared" si="2"/>
-        <v>1231559.5658411772</v>
+        <v>168175.80012438865</v>
       </c>
       <c r="D29" s="142">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="E29" s="128">
         <f t="shared" si="0"/>
@@ -14656,7 +14873,7 @@
       </c>
       <c r="F29" s="129">
         <f t="shared" si="1"/>
-        <v>616086.40077291708</v>
+        <v>84129.770308732128</v>
       </c>
       <c r="H29" s="124"/>
     </row>
@@ -14666,11 +14883,11 @@
       </c>
       <c r="C30" s="127">
         <f t="shared" si="2"/>
-        <v>1239442.3210336328</v>
+        <v>166643.00880714692</v>
       </c>
       <c r="D30" s="142">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="E30" s="128">
         <f t="shared" si="0"/>
@@ -14678,7 +14895,7 @@
       </c>
       <c r="F30" s="129">
         <f t="shared" si="1"/>
-        <v>574101.61195934541</v>
+        <v>77187.956514309146</v>
       </c>
       <c r="H30" s="124"/>
     </row>
@@ -15128,7 +15345,7 @@
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>14628447.603675557</v>
+        <v>2261959.107405351</v>
       </c>
       <c r="D51" s="143">
         <f>Terminal_Growth</f>
@@ -15140,7 +15357,7 @@
       </c>
       <c r="F51" s="129">
         <f t="shared" si="1"/>
-        <v>6775801.6708105225</v>
+        <v>1047724.7288640034</v>
       </c>
       <c r="H51" s="124"/>
     </row>
@@ -15151,7 +15368,7 @@
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
-        <v>14826136.513766104</v>
+        <v>2220066.018488951</v>
       </c>
       <c r="H52" s="124"/>
     </row>
@@ -15172,23 +15389,23 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="137">
         <f>F52</f>
-        <v>14826136.513766104</v>
+        <v>2220066.018488951</v>
       </c>
       <c r="B55" s="135">
         <f>C78</f>
-        <v>-0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="C55" s="135">
         <f>C77</f>
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="D55" s="135">
         <f>C76</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E55" s="135">
         <f>C75</f>
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="F55" s="135">
         <f>C74</f>
@@ -15202,19 +15419,19 @@
       </c>
       <c r="B56" s="127">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>12788241.211071908</v>
+        <v>1791667.4501565206</v>
       </c>
       <c r="C56" s="127">
-        <v>13420515.524325915</v>
+        <v>1944399.2979690079</v>
       </c>
       <c r="D56" s="127">
-        <v>15004400.307915099</v>
+        <v>2282764.7283828212</v>
       </c>
       <c r="E56" s="127">
-        <v>15734411.148311835</v>
+        <v>2356418.6681816033</v>
       </c>
       <c r="F56" s="127">
-        <v>15985131.641699184</v>
+        <v>2510441.0600115755</v>
       </c>
       <c r="H56" s="124"/>
     </row>
@@ -15223,19 +15440,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="127">
-        <v>11535059.995283656</v>
+        <v>1512116.6840562024</v>
       </c>
       <c r="C57" s="127">
-        <v>12537042.701494243</v>
+        <v>1717259.7734446828</v>
       </c>
       <c r="D57" s="127">
-        <v>15473820.646910066</v>
+        <v>2282764.7283828203</v>
       </c>
       <c r="E57" s="127">
-        <v>17061254.876979411</v>
+        <v>2430140.4316197839</v>
       </c>
       <c r="F57" s="127">
-        <v>17644056.388321832</v>
+        <v>2770972.7148480518</v>
       </c>
       <c r="H57" s="124"/>
     </row>
@@ -15244,19 +15461,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="127">
-        <v>10298427.120539103</v>
+        <v>1267998.2938434205</v>
       </c>
       <c r="C58" s="127">
-        <v>11609617.700964648</v>
+        <v>1501500.7034384492</v>
       </c>
       <c r="D58" s="127">
-        <v>16054858.474479713</v>
+        <v>2282764.7283828198</v>
       </c>
       <c r="E58" s="127">
-        <v>18837634.59315075</v>
+        <v>2521391.5550040705</v>
       </c>
       <c r="F58" s="127">
-        <v>19925971.38051375</v>
+        <v>3129344.0576845901</v>
       </c>
       <c r="H58" s="124"/>
     </row>
@@ -15265,19 +15482,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="127">
-        <v>9284665.7634038813</v>
+        <v>1085590.6113440995</v>
       </c>
       <c r="C59" s="127">
-        <v>10806670.890222374</v>
+        <v>1330075.1609701074</v>
       </c>
       <c r="D59" s="127">
-        <v>16646842.841164071</v>
+        <v>2282764.7283828198</v>
       </c>
       <c r="E59" s="127">
-        <v>20805216.260669909</v>
+        <v>2614361.8160141576</v>
       </c>
       <c r="F59" s="127">
-        <v>22529016.1300468</v>
+        <v>3538148.349494644</v>
       </c>
       <c r="H59" s="124"/>
     </row>
@@ -15286,19 +15503,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="127">
-        <v>8517506.3067681082</v>
+        <v>956535.38724221883</v>
       </c>
       <c r="C60" s="127">
-        <v>10169747.747799639</v>
+        <v>1203526.2419221611</v>
       </c>
       <c r="D60" s="127">
-        <v>17197421.151398726</v>
+        <v>2282764.7283828198</v>
       </c>
       <c r="E60" s="127">
-        <v>22803257.715964336</v>
+        <v>2700829.317674215</v>
       </c>
       <c r="F60" s="127">
-        <v>25256927.882247664</v>
+        <v>3966562.8176588374</v>
       </c>
       <c r="H60" s="124"/>
     </row>
@@ -15307,19 +15524,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="127">
-        <v>7960756.9389042351</v>
+        <v>867219.36706202792</v>
       </c>
       <c r="C61" s="127">
-        <v>9688635.0268338043</v>
+        <v>1113428.7942805844</v>
       </c>
       <c r="D61" s="127">
-        <v>17683107.810972057</v>
+        <v>2282764.7283828198</v>
       </c>
       <c r="E61" s="127">
-        <v>24735455.482912373</v>
+        <v>2777105.6824751217</v>
       </c>
       <c r="F61" s="127">
-        <v>27984492.970261224</v>
+        <v>4394922.8427299513</v>
       </c>
       <c r="H61" s="124"/>
     </row>
@@ -15343,19 +15560,19 @@
     <row r="64" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B64" s="136">
         <f>B55</f>
-        <v>-0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="C64" s="136">
         <f>C55</f>
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="D64" s="136">
         <f>D55</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E64" s="136">
         <f>E55</f>
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="F64" s="136">
         <f>F55</f>
@@ -15369,23 +15586,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>22.830518776962066</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>22.830518776962066</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>22.830518776962066</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>22.830518776962066</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>22.830518776962066</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -15396,23 +15613,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>19.854624957586992</v>
+        <v>7.9882574709268273</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>20.931555394224837</v>
+        <v>8.7729421459311006</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>23.629330229954228</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>24.872731830523417</v>
+        <v>10.889758581018468</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>25.299775164022275</v>
+        <v>11.681073635524092</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -15423,23 +15640,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>17.720125792249224</v>
+        <v>6.5520200051565114</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>19.426767436047015</v>
+        <v>7.605975946446522</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>24.428877262062496</v>
+        <v>10.511349502351729</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>27.132697744226626</v>
+        <v>11.268516114648602</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>28.125362910162355</v>
+        <v>13.019597328072329</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -15450,23 +15667,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>15.613812829912655</v>
+        <v>5.2978221254722335</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>17.847117290797563</v>
+        <v>6.4974786804740496</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>25.418538407914397</v>
+        <v>10.511349502351727</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>30.158342378634668</v>
+        <v>11.737333582138968</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>32.012067869382236</v>
+        <v>14.860788308946084</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -15477,23 +15694,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>13.887109027305996</v>
+        <v>4.3606730297840182</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>16.479486436019734</v>
+        <v>5.6167521129257443</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>26.426844406010588</v>
+        <v>10.511349502351727</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>33.509654522594523</v>
+        <v>12.214983398406025</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>36.445741766832334</v>
+        <v>16.961086756543974</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15504,23 +15721,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>12.580433504851692</v>
+        <v>3.6976308546751522</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>15.394637813364223</v>
+        <v>4.9665864871081711</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>27.364624935149575</v>
+        <v>10.511349502351727</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>36.912847743898624</v>
+        <v>12.659224232327279</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>41.092097205957991</v>
+        <v>19.162135670266764</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15530,23 +15747,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>11.63214203189</v>
+        <v>3.2387552941973317</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>14.575175561299575</v>
+        <v>4.5036962161272101</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>28.191877814792271</v>
+        <v>10.511349502351727</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>40.203891743647631</v>
+        <v>13.051106445379464</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>45.737862184255519</v>
+        <v>21.362904873756147</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15581,11 +15798,11 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>28.125362910162355</v>
+        <v>13.019597328072329</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
@@ -15595,7 +15812,7 @@
       </c>
       <c r="C75" s="146">
         <f>Scenarios!C38</f>
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="D75" s="149">
         <f>Scenarios!C37</f>
@@ -15603,11 +15820,11 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>24.872731830523417</v>
+        <v>10.889758581018468</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
-        <v>0.192</v>
+        <v>0.18</v>
       </c>
       <c r="H75" s="124"/>
     </row>
@@ -15618,7 +15835,7 @@
       </c>
       <c r="C76" s="146">
         <f>Scenarios!C26</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D76" s="149">
         <f>Scenarios!C25</f>
@@ -15626,11 +15843,11 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>23.629330229954228</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
-        <v>0.57599999999999996</v>
+        <v>0.53999999999999992</v>
       </c>
       <c r="H76" s="124"/>
     </row>
@@ -15641,7 +15858,7 @@
       </c>
       <c r="C77" s="146">
         <f>Scenarios!C32</f>
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="D77" s="149">
         <f>Scenarios!C31</f>
@@ -15649,11 +15866,11 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>20.931555394224837</v>
+        <v>8.7729421459311006</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
-        <v>0.192</v>
+        <v>0.18</v>
       </c>
       <c r="H77" s="124"/>
     </row>
@@ -15664,7 +15881,7 @@
       </c>
       <c r="C78" s="146">
         <f>Scenarios!C50</f>
-        <v>-0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="D78" s="149">
         <f>Scenarios!C49</f>
@@ -15672,11 +15889,11 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>17.720125792249224</v>
+        <v>6.5520200051565114</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
@@ -15773,7 +15990,7 @@
       </c>
       <c r="I3" s="270">
         <f>-Market_Price</f>
-        <v>-15.4</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15793,7 +16010,7 @@
       </c>
       <c r="I4" s="270">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>1.36</v>
+        <v>0.49984047644368812</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -15802,7 +16019,7 @@
       </c>
       <c r="I5" s="270">
         <f t="shared" si="0"/>
-        <v>1.36</v>
+        <v>0.49984047644368812</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -15811,7 +16028,7 @@
       </c>
       <c r="C6" s="110">
         <f>Valuation_Model!C3</f>
-        <v>1000</v>
+        <v>1000000</v>
       </c>
       <c r="E6" s="103" t="s">
         <v>285</v>
@@ -15822,7 +16039,7 @@
       </c>
       <c r="I6" s="270">
         <f t="shared" si="0"/>
-        <v>24.681827133653531</v>
+        <v>10.693836205225988</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15831,17 +16048,17 @@
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
-        <v>1876773</v>
+        <v>266372</v>
       </c>
       <c r="D7" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E7" s="349" t="str">
+        <v>CNY</v>
+      </c>
+      <c r="E7" s="351" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
-        <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 六福珠宝(0590.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
-      </c>
-      <c r="F7" s="349"/>
+        <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中国石油股份(0857.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
+      </c>
+      <c r="F7" s="351"/>
       <c r="H7" s="282">
         <v>4</v>
       </c>
@@ -15856,14 +16073,14 @@
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
-        <v>1294904.5955406395</v>
+        <v>306997.23769416759</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E8" s="349"/>
-      <c r="F8" s="349"/>
+        <v>CNY</v>
+      </c>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
       <c r="H8" s="282">
         <v>5</v>
       </c>
@@ -15878,14 +16095,14 @@
       </c>
       <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
-        <v>1162832.9466554797</v>
+        <v>182621.17827062571</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E9" s="349"/>
-      <c r="F9" s="349"/>
+        <v>CNY</v>
+      </c>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
       <c r="H9" s="282">
         <v>6</v>
       </c>
@@ -15895,8 +16112,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="349"/>
-      <c r="F10" s="349"/>
+      <c r="E10" s="351"/>
+      <c r="F10" s="351"/>
       <c r="H10" s="282">
         <v>7</v>
       </c>
@@ -15909,8 +16126,8 @@
       <c r="B11" s="163" t="s">
         <v>282</v>
       </c>
-      <c r="E11" s="349"/>
-      <c r="F11" s="349"/>
+      <c r="E11" s="351"/>
+      <c r="F11" s="351"/>
       <c r="H11" s="282">
         <v>8</v>
       </c>
@@ -15928,8 +16145,8 @@
         <v>#VALUE!</v>
       </c>
       <c r="D12" s="162"/>
-      <c r="E12" s="349"/>
-      <c r="F12" s="349"/>
+      <c r="E12" s="351"/>
+      <c r="F12" s="351"/>
       <c r="H12" s="282">
         <v>9</v>
       </c>
@@ -15946,8 +16163,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E13" s="349"/>
-      <c r="F13" s="349"/>
+      <c r="E13" s="351"/>
+      <c r="F13" s="351"/>
       <c r="H13" s="282">
         <v>10</v>
       </c>
@@ -15964,8 +16181,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E14" s="349"/>
-      <c r="F14" s="349"/>
+      <c r="E14" s="351"/>
+      <c r="F14" s="351"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -15991,21 +16208,21 @@
       <c r="C18" s="154">
         <v>5</v>
       </c>
-      <c r="E18" s="349" t="s">
+      <c r="E18" s="351" t="s">
         <v>344</v>
       </c>
-      <c r="F18" s="350"/>
+      <c r="F18" s="352"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="350"/>
-      <c r="F19" s="350"/>
+      <c r="E19" s="352"/>
+      <c r="F19" s="352"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
         <v>314</v>
       </c>
-      <c r="E20" s="350"/>
-      <c r="F20" s="350"/>
+      <c r="E20" s="352"/>
+      <c r="F20" s="352"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
@@ -16013,14 +16230,14 @@
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
-        <v>15.4</v>
+        <v>5.55</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="350"/>
-      <c r="F21" s="350"/>
+      <c r="E21" s="352"/>
+      <c r="F21" s="352"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
@@ -16028,14 +16245,14 @@
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
-        <v>22.830518776962066</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="350"/>
-      <c r="F22" s="350"/>
+      <c r="E22" s="352"/>
+      <c r="F22" s="352"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
@@ -16055,19 +16272,19 @@
         <v>5</v>
       </c>
       <c r="D25" s="167"/>
-      <c r="E25" s="348"/>
-      <c r="F25" s="348"/>
+      <c r="E25" s="350"/>
+      <c r="F25" s="350"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
         <v>136</v>
       </c>
       <c r="C26" s="168">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D26" s="168"/>
-      <c r="E26" s="348"/>
-      <c r="F26" s="348"/>
+      <c r="E26" s="350"/>
+      <c r="F26" s="350"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
@@ -16075,14 +16292,14 @@
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
-        <v>23.629330229954228</v>
+        <v>10.511349502351733</v>
       </c>
       <c r="D27" s="164" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="348"/>
-      <c r="F27" s="348"/>
+      <c r="E27" s="350"/>
+      <c r="F27" s="350"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
@@ -16092,8 +16309,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="169"/>
-      <c r="E28" s="348"/>
-      <c r="F28" s="348"/>
+      <c r="E28" s="350"/>
+      <c r="F28" s="350"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
@@ -16113,19 +16330,19 @@
         <v>5</v>
       </c>
       <c r="D31" s="167"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="E31" s="350"/>
+      <c r="F31" s="350"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
         <v>136</v>
       </c>
       <c r="C32" s="168">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="D32" s="168"/>
-      <c r="E32" s="348"/>
-      <c r="F32" s="348"/>
+      <c r="E32" s="350"/>
+      <c r="F32" s="350"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
@@ -16133,14 +16350,14 @@
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
-        <v>20.931555394224837</v>
+        <v>8.7729421459311006</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="348"/>
-      <c r="F33" s="348"/>
+      <c r="E33" s="350"/>
+      <c r="F33" s="350"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
@@ -16150,8 +16367,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="169"/>
-      <c r="E34" s="348"/>
-      <c r="F34" s="348"/>
+      <c r="E34" s="350"/>
+      <c r="F34" s="350"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
@@ -16171,19 +16388,19 @@
         <v>5</v>
       </c>
       <c r="D37" s="167"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
         <v>136</v>
       </c>
       <c r="C38" s="168">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="D38" s="168"/>
-      <c r="E38" s="348"/>
-      <c r="F38" s="348"/>
+      <c r="E38" s="350"/>
+      <c r="F38" s="350"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
@@ -16191,14 +16408,14 @@
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
-        <v>24.872731830523417</v>
+        <v>10.889758581018468</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="348"/>
-      <c r="F39" s="348"/>
+      <c r="E39" s="350"/>
+      <c r="F39" s="350"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
@@ -16209,8 +16426,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="169"/>
-      <c r="E40" s="348"/>
-      <c r="F40" s="348"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
@@ -16218,7 +16435,7 @@
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>23.338455582922187</v>
+        <v>10.239349846800954</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16272,19 +16489,19 @@
         <v>10</v>
       </c>
       <c r="D49" s="167"/>
-      <c r="E49" s="348"/>
-      <c r="F49" s="348"/>
+      <c r="E49" s="350"/>
+      <c r="F49" s="350"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
         <v>136</v>
       </c>
       <c r="C50" s="168">
-        <v>-0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="D50" s="168"/>
-      <c r="E50" s="348"/>
-      <c r="F50" s="348"/>
+      <c r="E50" s="350"/>
+      <c r="F50" s="350"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
@@ -16292,25 +16509,25 @@
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
-        <v>17.720125792249224</v>
+        <v>6.5520200051565114</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="348"/>
-      <c r="F51" s="348"/>
+      <c r="E51" s="350"/>
+      <c r="F51" s="350"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
         <v>149</v>
       </c>
       <c r="C52" s="169">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="D52" s="169"/>
-      <c r="E52" s="348"/>
-      <c r="F52" s="348"/>
+      <c r="E52" s="350"/>
+      <c r="F52" s="350"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
@@ -16330,8 +16547,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="167"/>
-      <c r="E55" s="348"/>
-      <c r="F55" s="348"/>
+      <c r="E55" s="350"/>
+      <c r="F55" s="350"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
@@ -16341,8 +16558,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="168"/>
-      <c r="E56" s="348"/>
-      <c r="F56" s="348"/>
+      <c r="E56" s="350"/>
+      <c r="F56" s="350"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
@@ -16350,25 +16567,25 @@
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
-        <v>28.125362910162355</v>
+        <v>13.019597328072329</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="348"/>
-      <c r="F57" s="348"/>
+      <c r="E57" s="350"/>
+      <c r="F57" s="350"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
         <v>149</v>
       </c>
       <c r="C58" s="169">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="D58" s="169"/>
-      <c r="E58" s="348"/>
-      <c r="F58" s="348"/>
+      <c r="E58" s="350"/>
+      <c r="F58" s="350"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
@@ -16376,7 +16593,7 @@
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>23.321827133653532</v>
+        <v>10.1939957287823</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16424,7 +16641,7 @@
         <v>136</v>
       </c>
       <c r="C65" s="155">
-        <v>6.4006284479398504E-3</v>
+        <v>-9.1142204532876307E-3</v>
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="287" t="s">
@@ -16437,7 +16654,7 @@
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
-        <v>23.325699825167451</v>
+        <v>10.189224696681462</v>
       </c>
       <c r="D66" s="164" t="str">
         <f>Market_currency</f>
@@ -16461,7 +16678,7 @@
       </c>
       <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E69" s="138"/>
     </row>
@@ -16471,7 +16688,7 @@
       </c>
       <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E70" s="287" t="s">
         <v>305</v>
@@ -16500,7 +16717,7 @@
       </c>
       <c r="F72" s="335">
         <f>BS!D89/C60</f>
-        <v>-8.2632171394856124E-2</v>
+        <v>-0.11935703046565523</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16533,7 +16750,7 @@
       </c>
       <c r="C77" s="177">
         <f>Normalized_FCF!C90</f>
-        <v>1.36</v>
+        <v>0.49984047644368812</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -16560,7 +16777,7 @@
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.8648148148148147</v>
+        <v>1.0529047073235096</v>
       </c>
       <c r="D81" s="120"/>
       <c r="E81" s="103"/>
@@ -16572,7 +16789,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>13.496427739382831</v>
+        <v>5.8993030837860534</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16582,7 +16799,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>16.361242554197645</v>
+        <v>6.9522077911095632</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16593,7 +16810,7 @@
       </c>
       <c r="F83" s="335">
         <f>(1-C83/C60)</f>
-        <v>0.29845794412101279</v>
+        <v>0.31800954443405249</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16610,7 +16827,7 @@
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
-        <v>15.4</v>
+        <v>5.55</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16623,7 +16840,7 @@
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22622690546409729</v>
+        <v>0.29981048955907563</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/templates/Valuation_v2.0.xlsx
+++ b/financial_models/templates/Valuation_v2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B825E7ED-BE2F-4796-BF86-D2442B627B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33A9E12-9D37-483E-8365-F13704F8D8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="442">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2401,6 +2401,18 @@
   </si>
   <si>
     <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>in contrast to a benchmark yield of</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
   </si>
 </sst>
 </file>
@@ -4094,7 +4106,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J179"/>
+  <dimension ref="A1:J187"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4325,7 +4337,7 @@
         <v>277</v>
       </c>
       <c r="C24" s="249">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>420</v>
@@ -4341,7 +4353,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>17.696787580712193</v>
+        <v>15.9563545799849</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>316</v>
@@ -4358,8 +4370,12 @@
         <f ca="1">Scenarios!C87</f>
         <v>1.2976894231064677</v>
       </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
+      <c r="D26" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E26" s="339">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="27" spans="1:6">
       <c r="D27" s="5"/>
@@ -5207,7 +5223,7 @@
       </c>
       <c r="C132" s="250">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="133" spans="2:6">
@@ -5242,7 +5258,7 @@
       </c>
       <c r="C136" s="337">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="137" spans="2:6">
@@ -5252,7 +5268,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>3.7692908855128362</v>
+        <v>3.5197503065091129</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5262,7 +5278,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>13.927496695199357</v>
+        <v>12.436604273475787</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5271,11 +5287,11 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>17.696787580712193</v>
+        <v>15.9563545799849</v>
       </c>
       <c r="D139" s="342">
         <f>IF($D$11="","",C139*$E$22)</f>
-        <v>16.69508262331339</v>
+        <v>15.053164698098961</v>
       </c>
     </row>
     <row r="140" spans="2:6">
@@ -5297,7 +5313,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.42164923154334921</v>
+        <v>0.47852852439958615</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5314,7 +5330,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="2:4">
       <c r="B145" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5324,7 +5340,7 @@
         <v>4.3719426974143953</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5334,7 +5350,7 @@
         <v>17.707586944070023</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="2:4">
       <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
@@ -5347,7 +5363,7 @@
         <v>20.829744944796619</v>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="2:4">
       <c r="B148" s="290" t="s">
         <v>432</v>
       </c>
@@ -5360,7 +5376,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="2:4">
       <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
@@ -5369,12 +5385,12 @@
         <v>0.27841632968281327</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="2:4">
       <c r="B152" s="1" t="s">
         <v>422</v>
       </c>
@@ -5383,7 +5399,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="2:4">
       <c r="B153" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5393,7 +5409,7 @@
         <v>5.3486918603257889</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5403,7 +5419,7 @@
         <v>24.290242721632399</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="2:4">
       <c r="B155" s="80" t="s">
         <v>412</v>
       </c>
@@ -5416,7 +5432,7 @@
         <v>27.961259039583194</v>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="2:4">
       <c r="B156" s="290" t="s">
         <v>432</v>
       </c>
@@ -5429,7 +5445,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="2:4">
       <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
@@ -5438,108 +5454,177 @@
         <v>3.1366539631478951E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="13.9">
-      <c r="A159" s="247" t="s">
+    <row r="159" spans="2:4">
+      <c r="B159" s="234" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C160" s="92">
+        <f>E26</f>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="B161" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C161" s="240">
+        <f>Scenarios!C103</f>
+        <v>4.9849328208372334</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="B162" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C162" s="240">
+        <f>Scenarios!C104</f>
+        <v>21.77955755693743</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="B163" s="80" t="s">
+        <v>412</v>
+      </c>
+      <c r="C163" s="239">
+        <f>Scenarios!C105</f>
+        <v>26.764490377774663</v>
+      </c>
+      <c r="D163" s="342">
+        <f>IF($D$11="","",C163*$E$22)</f>
+        <v>25.249519224315719</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="B164" s="290" t="s">
+        <v>432</v>
+      </c>
+      <c r="C164" s="340" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D164" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C165" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.19168638951624872</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="13.9">
+      <c r="A167" s="247" t="s">
         <v>385</v>
       </c>
-      <c r="B159" s="36"/>
-      <c r="C159" s="36"/>
-      <c r="D159" s="36"/>
-      <c r="E159" s="36"/>
-      <c r="F159" s="36"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B167" s="36"/>
+      <c r="C167" s="36"/>
+      <c r="D167" s="36"/>
+      <c r="E167" s="36"/>
+      <c r="F167" s="36"/>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="B169" s="344" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
-    </row>
-    <row r="163" spans="2:6">
-      <c r="B163" s="234" t="s">
+      <c r="C169" s="345"/>
+      <c r="D169" s="345"/>
+      <c r="E169" s="345"/>
+      <c r="F169" s="345"/>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="B171" s="234" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="164" spans="2:6">
-      <c r="B164" s="347" t="s">
+    <row r="172" spans="1:6">
+      <c r="B172" s="347" t="s">
         <v>391</v>
       </c>
-      <c r="C164" s="347"/>
-      <c r="D164" s="347"/>
-      <c r="E164" s="347"/>
-      <c r="F164" s="347"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="238" t="s">
+      <c r="C172" s="347"/>
+      <c r="D172" s="347"/>
+      <c r="E172" s="347"/>
+      <c r="F172" s="347"/>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="B173" s="238" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
-      <c r="B166" s="238" t="s">
+    <row r="174" spans="1:6">
+      <c r="B174" s="238" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
-      <c r="B167" s="238" t="s">
+    <row r="175" spans="1:6">
+      <c r="B175" s="238" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="169" spans="2:6">
-      <c r="B169" s="1" t="s">
+    <row r="177" spans="2:6">
+      <c r="B177" s="1" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+    <row r="178" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B178" s="346" t="s">
         <v>392</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
-    </row>
-    <row r="172" spans="2:6">
-      <c r="B172" s="1" t="s">
+      <c r="C178" s="346"/>
+      <c r="D178" s="346"/>
+      <c r="E178" s="346"/>
+      <c r="F178" s="346"/>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="1" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+    <row r="181" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B181" s="343" t="s">
         <v>393</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
-    </row>
-    <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="C181" s="343"/>
+      <c r="D181" s="343"/>
+      <c r="E181" s="343"/>
+      <c r="F181" s="343"/>
+    </row>
+    <row r="182" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B182" s="343" t="s">
         <v>394</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
-    </row>
-    <row r="176" spans="2:6">
-      <c r="B176" s="1" t="s">
+      <c r="C182" s="343"/>
+      <c r="D182" s="343"/>
+      <c r="E182" s="343"/>
+      <c r="F182" s="343"/>
+    </row>
+    <row r="184" spans="2:6">
+      <c r="B184" s="1" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="177" spans="2:2">
-      <c r="B177" s="238" t="s">
+    <row r="185" spans="2:6">
+      <c r="B185" s="238" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="178" spans="2:2">
-      <c r="B178" s="238" t="s">
+    <row r="186" spans="2:6">
+      <c r="B186" s="238" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="179" spans="2:2">
-      <c r="B179" s="238" t="s">
+    <row r="187" spans="2:6">
+      <c r="B187" s="238" t="s">
         <v>399</v>
       </c>
     </row>
@@ -5567,11 +5652,11 @@
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B169:F169"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B172:F172"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -16668,7 +16753,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I104"/>
+  <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -17480,7 +17565,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C132</f>
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17489,7 +17574,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>3.7692908855128362</v>
+        <v>3.5197503065091129</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17501,7 +17586,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>13.927496695199357</v>
+        <v>12.436604273475787</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17511,7 +17596,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>17.696787580712193</v>
+        <v>15.9563545799849</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17522,7 +17607,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.42164923154334921</v>
+        <v>0.47852852439958615</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17678,33 +17763,89 @@
     <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="14.65">
-      <c r="E101" s="320" t="s">
+    <row r="101" spans="2:8" ht="13.15">
+      <c r="B101" s="109" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8">
+      <c r="B102" s="149" t="s">
+        <v>438</v>
+      </c>
+      <c r="C102" s="135">
+        <f>Thesis!E26</f>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
+      <c r="B103" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C103" s="117">
+        <f>PV(C102, C76, -C77, 0)</f>
+        <v>4.9849328208372334</v>
+      </c>
+      <c r="D103" s="117"/>
+    </row>
+    <row r="104" spans="2:8">
+      <c r="B104" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104" s="117">
+        <f>C60/(1+C102)^C76</f>
+        <v>21.77955755693743</v>
+      </c>
+      <c r="D104" s="117"/>
+    </row>
+    <row r="105" spans="2:8" ht="13.15">
+      <c r="B105" s="111" t="s">
+        <v>409</v>
+      </c>
+      <c r="C105" s="112">
+        <f>C103+C104</f>
+        <v>26.764490377774663</v>
+      </c>
+      <c r="D105" t="s">
+        <v>407</v>
+      </c>
+      <c r="E105" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F105" s="329">
+        <f>(1-C105/C66)</f>
+        <v>0.19168638951624872</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
+      <c r="B106" s="100"/>
+    </row>
+    <row r="107" spans="2:8" ht="14.65">
+      <c r="E107" s="320" t="s">
         <v>334</v>
       </c>
-      <c r="F101" s="317"/>
-    </row>
-    <row r="102" spans="2:8" ht="13.9">
-      <c r="E102" s="313" t="s">
+      <c r="F107" s="317"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="313" t="s">
         <v>335</v>
       </c>
-      <c r="F102" s="318" t="s">
+      <c r="F108" s="318" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="13.9">
-      <c r="E103" s="314" t="s">
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="314" t="s">
         <v>335</v>
       </c>
-      <c r="F103" s="318" t="s">
+      <c r="F109" s="318" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="13.9">
-      <c r="E104" s="315" t="s">
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="315" t="s">
         <v>335</v>
       </c>
-      <c r="F104" s="319" t="s">
+      <c r="F110" s="319" t="s">
         <v>338</v>
       </c>
     </row>

--- a/financial_models/templates/Valuation_v2.0.xlsx
+++ b/financial_models/templates/Valuation_v2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565F3CED-1D86-4F12-90FA-FA826D0C0378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E2D098-875B-40F5-86DE-B5027441C465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
     <sheet name="Data" sheetId="4" r:id="rId2"/>
     <sheet name="BS" sheetId="3" r:id="rId3"/>
-    <sheet name="FCF" sheetId="2" r:id="rId4"/>
+    <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
   </sheets>
@@ -3836,29 +3836,29 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4324,13 +4324,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="348" t="s">
+      <c r="B18" s="350" t="s">
         <v>365</v>
       </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="C18" s="350"/>
+      <c r="D18" s="350"/>
+      <c r="E18" s="350"/>
+      <c r="F18" s="350"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4526,22 +4526,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="348" t="s">
+      <c r="B36" s="350" t="s">
         <v>366</v>
       </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="C36" s="350"/>
+      <c r="D36" s="350"/>
+      <c r="E36" s="350"/>
+      <c r="F36" s="350"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="350" t="s">
+      <c r="B37" s="353" t="s">
         <v>344</v>
       </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="C37" s="353"/>
+      <c r="D37" s="353"/>
+      <c r="E37" s="353"/>
+      <c r="F37" s="353"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4553,20 +4553,20 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="351" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="351"/>
+      <c r="D40" s="351"/>
+      <c r="E40" s="351"/>
+      <c r="F40" s="351"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
       <c r="C41" s="188">
-        <f>FCF!C8</f>
+        <f>Normalized_FCF!C8</f>
         <v>370950.79977478832</v>
       </c>
       <c r="D41" s="1" t="str">
@@ -4579,20 +4579,20 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="351" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="351"/>
+      <c r="D43" s="351"/>
+      <c r="E43" s="351"/>
+      <c r="F43" s="351"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
       <c r="C44" s="188">
-        <f>FCF!C9</f>
+        <f>Normalized_FCF!C9</f>
         <v>120714</v>
       </c>
       <c r="D44" s="1" t="str">
@@ -4605,7 +4605,7 @@
         <v>236</v>
       </c>
       <c r="C45" s="188">
-        <f>FCF!C10</f>
+        <f>Normalized_FCF!C10</f>
         <v>-120714</v>
       </c>
       <c r="D45" s="1" t="str">
@@ -4614,20 +4614,20 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="351" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="351"/>
+      <c r="D47" s="351"/>
+      <c r="E47" s="351"/>
+      <c r="F47" s="351"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
       <c r="C48" s="188">
-        <f>FCF!C11</f>
+        <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
       <c r="D48" s="1" t="str">
@@ -4636,20 +4636,20 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="351" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="351"/>
+      <c r="D50" s="351"/>
+      <c r="E50" s="351"/>
+      <c r="F50" s="351"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>345</v>
       </c>
       <c r="C51" s="317">
-        <f>FCF!C48</f>
+        <f>Normalized_FCF!C48</f>
         <v>0</v>
       </c>
       <c r="D51" s="1" t="str">
@@ -4664,7 +4664,7 @@
         <v>346</v>
       </c>
       <c r="C52" s="317">
-        <f>FCF!C47</f>
+        <f>Normalized_FCF!C47</f>
         <v>0</v>
       </c>
       <c r="D52" s="1" t="str">
@@ -4679,7 +4679,7 @@
         <v>239</v>
       </c>
       <c r="C53" s="188">
-        <f>FCF!C12</f>
+        <f>Normalized_FCF!C12</f>
         <v>0</v>
       </c>
       <c r="D53" s="1" t="str">
@@ -4697,7 +4697,7 @@
         <v>266</v>
       </c>
       <c r="C56" s="188">
-        <f>FCF!C15</f>
+        <f>Normalized_FCF!C15</f>
         <v>0</v>
       </c>
       <c r="D56" s="1" t="str">
@@ -4706,20 +4706,20 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="351" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="351"/>
+      <c r="D58" s="351"/>
+      <c r="E58" s="351"/>
+      <c r="F58" s="351"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
       <c r="C59" s="188">
-        <f>FCF!C14</f>
+        <f>Normalized_FCF!C14</f>
         <v>-92737.69994369708</v>
       </c>
       <c r="D59" s="1" t="str">
@@ -4728,7 +4728,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
+      <c r="B61" s="351" t="s">
         <v>343</v>
       </c>
       <c r="C61" s="352"/>
@@ -4741,7 +4741,7 @@
         <v>243</v>
       </c>
       <c r="C62" s="1">
-        <f>FCF!C17</f>
+        <f>Normalized_FCF!C17</f>
         <v>0</v>
       </c>
       <c r="D62" s="1" t="str">
@@ -4750,29 +4750,29 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="348" t="s">
+      <c r="B64" s="350" t="s">
         <v>348</v>
       </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="C64" s="350"/>
+      <c r="D64" s="350"/>
+      <c r="E64" s="350"/>
+      <c r="F64" s="350"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="348" t="s">
+      <c r="B65" s="350" t="s">
         <v>367</v>
       </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="C65" s="350"/>
+      <c r="D65" s="350"/>
+      <c r="E65" s="350"/>
+      <c r="F65" s="350"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
       <c r="C67" s="188">
-        <f>FCF!G19</f>
+        <f>Normalized_FCF!G19</f>
         <v>302168</v>
       </c>
       <c r="D67" s="1" t="str">
@@ -4785,7 +4785,7 @@
         <v>249</v>
       </c>
       <c r="C68" s="188">
-        <f>FCF!C19</f>
+        <f>Normalized_FCF!C19</f>
         <v>278213.09983109124</v>
       </c>
       <c r="D68" s="1" t="str">
@@ -4798,7 +4798,7 @@
         <v>396</v>
       </c>
       <c r="C69" s="92">
-        <f>FCF!C125</f>
+        <f>Normalized_FCF!C125</f>
         <v>0.60941871295938521</v>
       </c>
     </row>
@@ -4807,7 +4807,7 @@
         <v>312</v>
       </c>
       <c r="C70" s="92">
-        <f>FCF!C93</f>
+        <f>Normalized_FCF!C93</f>
         <v>0.52016834539178136</v>
       </c>
     </row>
@@ -4826,22 +4826,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="348" t="s">
+      <c r="B74" s="350" t="s">
         <v>368</v>
       </c>
-      <c r="C74" s="348"/>
-      <c r="D74" s="348"/>
-      <c r="E74" s="348"/>
-      <c r="F74" s="348"/>
+      <c r="C74" s="350"/>
+      <c r="D74" s="350"/>
+      <c r="E74" s="350"/>
+      <c r="F74" s="350"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="350" t="s">
+      <c r="B75" s="353" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="350"/>
-      <c r="D75" s="350"/>
-      <c r="E75" s="350"/>
-      <c r="F75" s="350"/>
+      <c r="C75" s="353"/>
+      <c r="D75" s="353"/>
+      <c r="E75" s="353"/>
+      <c r="F75" s="353"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4885,22 +4885,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="348" t="s">
+      <c r="B83" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C83" s="348"/>
-      <c r="D83" s="348"/>
-      <c r="E83" s="348"/>
-      <c r="F83" s="348"/>
+      <c r="C83" s="350"/>
+      <c r="D83" s="350"/>
+      <c r="E83" s="350"/>
+      <c r="F83" s="350"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="348" t="s">
+      <c r="B84" s="350" t="s">
         <v>370</v>
       </c>
-      <c r="C84" s="348"/>
-      <c r="D84" s="348"/>
-      <c r="E84" s="348"/>
-      <c r="F84" s="348"/>
+      <c r="C84" s="350"/>
+      <c r="D84" s="350"/>
+      <c r="E84" s="350"/>
+      <c r="F84" s="350"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4937,13 +4937,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="348" t="s">
+      <c r="B91" s="350" t="s">
         <v>371</v>
       </c>
-      <c r="C91" s="348"/>
-      <c r="D91" s="348"/>
-      <c r="E91" s="348"/>
-      <c r="F91" s="348"/>
+      <c r="C91" s="350"/>
+      <c r="D91" s="350"/>
+      <c r="E91" s="350"/>
+      <c r="F91" s="350"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4956,13 +4956,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="348" t="s">
+      <c r="B95" s="350" t="s">
         <v>349</v>
       </c>
-      <c r="C95" s="348"/>
-      <c r="D95" s="348"/>
-      <c r="E95" s="348"/>
-      <c r="F95" s="348"/>
+      <c r="C95" s="350"/>
+      <c r="D95" s="350"/>
+      <c r="E95" s="350"/>
+      <c r="F95" s="350"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5093,13 +5093,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="348" t="s">
+      <c r="B111" s="350" t="s">
         <v>372</v>
       </c>
-      <c r="C111" s="348"/>
-      <c r="D111" s="348"/>
-      <c r="E111" s="348"/>
-      <c r="F111" s="348"/>
+      <c r="C111" s="350"/>
+      <c r="D111" s="350"/>
+      <c r="E111" s="350"/>
+      <c r="F111" s="350"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5138,13 +5138,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="349" t="s">
+      <c r="B118" s="351" t="s">
         <v>373</v>
       </c>
-      <c r="C118" s="349"/>
-      <c r="D118" s="349"/>
-      <c r="E118" s="349"/>
-      <c r="F118" s="349"/>
+      <c r="C118" s="351"/>
+      <c r="D118" s="351"/>
+      <c r="E118" s="351"/>
+      <c r="F118" s="351"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="258" t="s">
@@ -5287,13 +5287,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="353" t="s">
+      <c r="B129" s="354" t="s">
         <v>376</v>
       </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="C129" s="354"/>
+      <c r="D129" s="354"/>
+      <c r="E129" s="354"/>
+      <c r="F129" s="354"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5306,22 +5306,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="351" t="s">
+      <c r="B133" s="355" t="s">
         <v>374</v>
       </c>
-      <c r="C133" s="351"/>
-      <c r="D133" s="351"/>
-      <c r="E133" s="351"/>
-      <c r="F133" s="351"/>
+      <c r="C133" s="355"/>
+      <c r="D133" s="355"/>
+      <c r="E133" s="355"/>
+      <c r="F133" s="355"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="348" t="s">
+      <c r="B134" s="350" t="s">
         <v>375</v>
       </c>
-      <c r="C134" s="348"/>
-      <c r="D134" s="348"/>
-      <c r="E134" s="348"/>
-      <c r="F134" s="348"/>
+      <c r="C134" s="350"/>
+      <c r="D134" s="350"/>
+      <c r="E134" s="350"/>
+      <c r="F134" s="350"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5654,13 +5654,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="355" t="s">
+      <c r="B174" s="349" t="s">
         <v>382</v>
       </c>
-      <c r="C174" s="348"/>
-      <c r="D174" s="348"/>
-      <c r="E174" s="348"/>
-      <c r="F174" s="348"/>
+      <c r="C174" s="350"/>
+      <c r="D174" s="350"/>
+      <c r="E174" s="350"/>
+      <c r="F174" s="350"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
@@ -5697,13 +5697,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="349" t="s">
+      <c r="B183" s="351" t="s">
         <v>387</v>
       </c>
-      <c r="C183" s="349"/>
-      <c r="D183" s="349"/>
-      <c r="E183" s="349"/>
-      <c r="F183" s="349"/>
+      <c r="C183" s="351"/>
+      <c r="D183" s="351"/>
+      <c r="E183" s="351"/>
+      <c r="F183" s="351"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5711,22 +5711,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="354" t="s">
+      <c r="B186" s="348" t="s">
         <v>388</v>
       </c>
-      <c r="C186" s="354"/>
-      <c r="D186" s="354"/>
-      <c r="E186" s="354"/>
-      <c r="F186" s="354"/>
+      <c r="C186" s="348"/>
+      <c r="D186" s="348"/>
+      <c r="E186" s="348"/>
+      <c r="F186" s="348"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="354" t="s">
+      <c r="B187" s="348" t="s">
         <v>389</v>
       </c>
-      <c r="C187" s="354"/>
-      <c r="D187" s="354"/>
-      <c r="E187" s="354"/>
-      <c r="F187" s="354"/>
+      <c r="C187" s="348"/>
+      <c r="D187" s="348"/>
+      <c r="E187" s="348"/>
+      <c r="F187" s="348"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5750,17 +5750,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5777,6 +5766,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -8441,7 +8441,7 @@
         <v>45657</v>
       </c>
       <c r="F1" s="86" t="str">
-        <f>IF(MONTH(C1)=MONTH(FCF!G1),"FY","Quarter")&amp;" Report"</f>
+        <f>IF(MONTH(C1)=MONTH(Normalized_FCF!G1),"FY","Quarter")&amp;" Report"</f>
         <v>FY Report</v>
       </c>
       <c r="H1" s="107">
@@ -9234,11 +9234,11 @@
         <v>94</v>
       </c>
       <c r="C50" s="95">
-        <f>G31/FCF!C8</f>
+        <f>G31/Normalized_FCF!C8</f>
         <v>0</v>
       </c>
       <c r="D50" s="95">
-        <f>G31/FCF!G8</f>
+        <f>G31/Normalized_FCF!G8</f>
         <v>0</v>
       </c>
       <c r="F50" s="280"/>
@@ -9274,11 +9274,11 @@
         <v>140</v>
       </c>
       <c r="C54" s="92">
-        <f>FCF!C8/G35</f>
+        <f>Normalized_FCF!C8/G35</f>
         <v>185475.39988739416</v>
       </c>
       <c r="D54" s="92">
-        <f>FCF!G8/G35</f>
+        <f>Normalized_FCF!G8/G35</f>
         <v>170484.5</v>
       </c>
       <c r="F54" s="280"/>
@@ -9288,11 +9288,11 @@
         <v>142</v>
       </c>
       <c r="C55" s="92">
-        <f>FCF!C11/G40</f>
+        <f>Normalized_FCF!C11/G40</f>
         <v>0</v>
       </c>
       <c r="D55" s="92">
-        <f>FCF!G11/G40</f>
+        <f>Normalized_FCF!G11/G40</f>
         <v>0</v>
       </c>
       <c r="F55" s="280"/>
@@ -9318,7 +9318,7 @@
       </c>
       <c r="C58" s="98"/>
       <c r="D58" s="23">
-        <f>FCF!G9/BS!$G$39</f>
+        <f>Normalized_FCF!G9/BS!$G$39</f>
         <v>120714</v>
       </c>
       <c r="F58" s="5"/>
@@ -9466,11 +9466,11 @@
         <v>321</v>
       </c>
       <c r="C73" s="188">
-        <f>(FCF!G25+FCF!G35-FCF!G91)/12</f>
+        <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
         <v>-248775.78636286163</v>
       </c>
       <c r="D73" s="188">
-        <f>(FCF!C25+FCF!C35-FCF!C91)/12</f>
+        <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
         <v>-247268.57388162927</v>
       </c>
       <c r="F73" s="1" t="s">
@@ -11523,7 +11523,7 @@
         <v>39</v>
       </c>
       <c r="C47" s="191">
-        <f>-BS!G31*FCF!C54</f>
+        <f>-BS!G31*Normalized_FCF!C54</f>
         <v>0</v>
       </c>
       <c r="E47" s="298"/>
@@ -11765,7 +11765,7 @@
         <v>340</v>
       </c>
       <c r="G53" s="6">
-        <f>IF(FCF!G4="","",FCF!G49/BS!$C$66)</f>
+        <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
         <v>5935</v>
       </c>
       <c r="H53" s="170"/>
@@ -11792,7 +11792,7 @@
         <v>341</v>
       </c>
       <c r="G54" s="23">
-        <f>IFERROR(ABS(FCF!G47/BS!$G$31),0)</f>
+        <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
         <v>0</v>
       </c>
       <c r="H54" s="170"/>
@@ -15389,7 +15389,7 @@
         <v>129</v>
       </c>
       <c r="C4" s="110">
-        <f>FCF!C19</f>
+        <f>Normalized_FCF!C19</f>
         <v>278213.09983109124</v>
       </c>
       <c r="D4" t="str">
@@ -16966,7 +16966,7 @@
         <v>276</v>
       </c>
       <c r="C7" s="115">
-        <f>FCF!G8</f>
+        <f>Normalized_FCF!G8</f>
         <v>340969</v>
       </c>
       <c r="D7" t="str">
@@ -16991,7 +16991,7 @@
         <v>66</v>
       </c>
       <c r="C8" s="115">
-        <f>FCF!G19</f>
+        <f>Normalized_FCF!G19</f>
         <v>302168</v>
       </c>
       <c r="D8" t="str">
@@ -17013,7 +17013,7 @@
         <v>57</v>
       </c>
       <c r="C9" s="201">
-        <f>FCF!C19</f>
+        <f>Normalized_FCF!C19</f>
         <v>278213.09983109124</v>
       </c>
       <c r="D9" t="str">
@@ -17060,7 +17060,7 @@
         <v>145</v>
       </c>
       <c r="C12" s="159">
-        <f ca="1">(FCF!G4/OFFSET(FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
+        <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>3.9036649512719679E-2</v>
       </c>
       <c r="D12" s="159"/>
@@ -17079,7 +17079,7 @@
         <v>153</v>
       </c>
       <c r="C13" s="159">
-        <f ca="1">(FCF!G8/OFFSET(FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
+        <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-4.5771520730185866E-2</v>
       </c>
       <c r="E13" s="358"/>
@@ -17097,7 +17097,7 @@
         <v>66</v>
       </c>
       <c r="C14" s="159">
-        <f ca="1">(FCF!G19/OFFSET(FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
+        <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-3.8810272916738997E-2</v>
       </c>
       <c r="E14" s="358"/>
@@ -17669,7 +17669,7 @@
         <v>112</v>
       </c>
       <c r="C77" s="174">
-        <f>FCF!C90</f>
+        <f>Normalized_FCF!C90</f>
         <v>2.0754716981132075</v>
       </c>
       <c r="D77" t="str">

--- a/financial_models/templates/Valuation_v2.0.xlsx
+++ b/financial_models/templates/Valuation_v2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2863CD6C-4F45-4944-94B5-5AAFEC6C73F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B244F4FE-5023-42C5-8F30-4E82261EDC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,13 +25,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">Thesis!$C$80</definedName>
+    <definedName name="Equity_Cost">Thesis!$C$86</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">Thesis!$C$86</definedName>
+    <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="463">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2305,10 +2305,6 @@
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
   <si>
-    <t>Liabilities to Equity Ratio =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Debt to Equity Ratio =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2463,13 +2459,25 @@
   </si>
   <si>
     <t>INT</t>
+  </si>
+  <si>
+    <t>DuPont Analysis</t>
+  </si>
+  <si>
+    <t>ROE =</t>
+  </si>
+  <si>
+    <t>Normalized</t>
+  </si>
+  <si>
+    <t>Latest</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="18">
+  <numFmts count="17">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2487,7 +2495,6 @@
     <numFmt numFmtId="178" formatCode="0.0\x"/>
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
-    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\)"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3136,7 +3143,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="359">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3757,7 +3764,6 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3809,82 +3815,90 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="37" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="37" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="37" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="37" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4188,7 +4202,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J192"/>
+  <dimension ref="A1:J197"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4205,8 +4219,8 @@
       <c r="C1" s="44">
         <v>45797</v>
       </c>
-      <c r="D1" s="317" t="s">
-        <v>459</v>
+      <c r="D1" s="316" t="s">
+        <v>458</v>
       </c>
       <c r="E1" s="292" t="s">
         <v>356</v>
@@ -4231,7 +4245,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4243,7 +4257,7 @@
         <v>317</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4280,17 +4294,17 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D11" s="49"/>
       <c r="E11" s="34"/>
@@ -4307,17 +4321,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4331,7 +4345,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4358,13 +4372,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="349" t="s">
+      <c r="B18" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C18" s="349"/>
-      <c r="D18" s="349"/>
-      <c r="E18" s="349"/>
-      <c r="F18" s="349"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4382,10 +4396,10 @@
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="E21" s="309" t="s">
-        <v>448</v>
+        <v>443</v>
+      </c>
+      <c r="E21" s="308" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4393,19 +4407,19 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
         <v>DDM Terminal Value</v>
       </c>
-      <c r="E22" s="314">
+      <c r="E22" s="313">
         <v>0.02</v>
       </c>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C23" s="262" t="s">
         <v>323</v>
@@ -4413,7 +4427,7 @@
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C24" s="262" t="s">
         <v>323</v>
@@ -4424,13 +4438,13 @@
         <v>350</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="300" t="str">
+      <c r="E25" s="299" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4440,14 +4454,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
       </c>
-      <c r="C26" s="305">
-        <f>C127</f>
+      <c r="C26" s="304">
+        <f>C132</f>
         <v>21.752920556327282</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="E26" s="302">
+      <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
         <v>3.3241061492891966E-2</v>
       </c>
@@ -4458,96 +4472,96 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>438</v>
-      </c>
-      <c r="C28" s="310" t="str">
-        <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>437</v>
+      </c>
+      <c r="C28" s="309" t="str">
+        <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>601166.SS (CNY)</v>
       </c>
-      <c r="D28" s="310" t="str">
-        <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
-        <v/>
-      </c>
-      <c r="E28" s="306" t="s">
-        <v>434</v>
-      </c>
-      <c r="F28" s="304">
+      <c r="D28" s="309" t="str">
+        <f>IF(D11="","",D145&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="305" t="s">
+        <v>433</v>
+      </c>
+      <c r="F28" s="303">
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C29" s="311">
-        <f>C144</f>
+        <v>429</v>
+      </c>
+      <c r="C29" s="310">
+        <f>C149</f>
         <v>9.6117057421017815</v>
       </c>
-      <c r="D29" s="311" t="str">
-        <f>D144</f>
-        <v/>
-      </c>
-      <c r="E29" s="307" t="s">
-        <v>429</v>
-      </c>
-      <c r="F29" s="303">
+      <c r="D29" s="310" t="str">
+        <f>D149</f>
+        <v/>
+      </c>
+      <c r="E29" s="306" t="s">
+        <v>428</v>
+      </c>
+      <c r="F29" s="302">
         <v>0.4</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C30" s="312">
-        <f>C152</f>
+        <v>430</v>
+      </c>
+      <c r="C30" s="311">
+        <f>C157</f>
         <v>14.144259076931155</v>
       </c>
-      <c r="D30" s="312" t="str">
-        <f>D152</f>
-        <v/>
-      </c>
-      <c r="E30" s="308" t="s">
-        <v>442</v>
-      </c>
-      <c r="F30" s="313">
+      <c r="D30" s="311" t="str">
+        <f>D157</f>
+        <v/>
+      </c>
+      <c r="E30" s="307" t="s">
+        <v>441</v>
+      </c>
+      <c r="F30" s="312">
         <v>0.22</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="C31" s="312">
-        <f>C160</f>
+        <v>431</v>
+      </c>
+      <c r="C31" s="311">
+        <f>C165</f>
         <v>19.999892480445755</v>
       </c>
-      <c r="D31" s="312" t="str">
-        <f>D160</f>
-        <v/>
-      </c>
-      <c r="E31" s="308" t="s">
-        <v>441</v>
-      </c>
-      <c r="F31" s="313">
+      <c r="D31" s="311" t="str">
+        <f>D165</f>
+        <v/>
+      </c>
+      <c r="E31" s="307" t="s">
+        <v>440</v>
+      </c>
+      <c r="F31" s="312">
         <v>0.08</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="C32" s="312">
-        <f>C168</f>
+        <v>432</v>
+      </c>
+      <c r="C32" s="311">
+        <f>C173</f>
         <v>18.029240328562945</v>
       </c>
-      <c r="D32" s="312" t="str">
-        <f>D168</f>
-        <v/>
-      </c>
-      <c r="E32" s="308" t="s">
-        <v>443</v>
-      </c>
-      <c r="F32" s="313">
+      <c r="D32" s="311" t="str">
+        <f>D173</f>
+        <v/>
+      </c>
+      <c r="E32" s="307" t="s">
+        <v>442</v>
+      </c>
+      <c r="F32" s="312">
         <v>0.12</v>
       </c>
     </row>
@@ -4566,22 +4580,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="349" t="s">
+      <c r="B36" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C36" s="349"/>
-      <c r="D36" s="349"/>
-      <c r="E36" s="349"/>
-      <c r="F36" s="349"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="352" t="s">
+      <c r="B37" s="350" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="352"/>
-      <c r="D37" s="352"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4593,19 +4607,19 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="350" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="350"/>
-      <c r="D40" s="350"/>
-      <c r="E40" s="350"/>
-      <c r="F40" s="350"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="339">
+      <c r="C41" s="76">
         <f>Normalized_FCF!C8</f>
         <v>-721</v>
       </c>
@@ -4619,19 +4633,19 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="350" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="350"/>
-      <c r="D43" s="350"/>
-      <c r="E43" s="350"/>
-      <c r="F43" s="350"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="339">
+      <c r="C44" s="76">
         <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
@@ -4644,7 +4658,7 @@
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C45" s="339">
+      <c r="C45" s="76">
         <f>Normalized_FCF!C10</f>
         <v>0</v>
       </c>
@@ -4654,19 +4668,19 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="350" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="350"/>
-      <c r="D47" s="350"/>
-      <c r="E47" s="350"/>
-      <c r="F47" s="350"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="339">
+      <c r="C48" s="76">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
@@ -4676,19 +4690,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="350" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="350"/>
-      <c r="D50" s="350"/>
-      <c r="E50" s="350"/>
-      <c r="F50" s="350"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>343</v>
       </c>
-      <c r="C51" s="344">
+      <c r="C51" s="340">
         <f>Normalized_FCF!C48</f>
         <v>0</v>
       </c>
@@ -4703,7 +4717,7 @@
       <c r="B52" s="47" t="s">
         <v>344</v>
       </c>
-      <c r="C52" s="344">
+      <c r="C52" s="340">
         <f>Normalized_FCF!C47</f>
         <v>0</v>
       </c>
@@ -4718,7 +4732,7 @@
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C53" s="339">
+      <c r="C53" s="76">
         <f>Normalized_FCF!C12</f>
         <v>0</v>
       </c>
@@ -4736,7 +4750,7 @@
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C56" s="339">
+      <c r="C56" s="76">
         <f>Normalized_FCF!C15</f>
         <v>0</v>
       </c>
@@ -4746,19 +4760,19 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="350" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="350"/>
-      <c r="D58" s="350"/>
-      <c r="E58" s="350"/>
-      <c r="F58" s="350"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C59" s="339">
+      <c r="C59" s="76">
         <f>Normalized_FCF!C14</f>
         <v>180.25</v>
       </c>
@@ -4768,19 +4782,19 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="350" t="s">
+      <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
-      <c r="C61" s="351"/>
-      <c r="D61" s="351"/>
-      <c r="E61" s="351"/>
-      <c r="F61" s="351"/>
+      <c r="C61" s="352"/>
+      <c r="D61" s="352"/>
+      <c r="E61" s="352"/>
+      <c r="F61" s="352"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C62" s="339">
+      <c r="C62" s="76">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
       </c>
@@ -4790,28 +4804,28 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="349" t="s">
+      <c r="B64" s="348" t="s">
         <v>346</v>
       </c>
-      <c r="C64" s="349"/>
-      <c r="D64" s="349"/>
-      <c r="E64" s="349"/>
-      <c r="F64" s="349"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="349" t="s">
+      <c r="B65" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C65" s="349"/>
-      <c r="D65" s="349"/>
-      <c r="E65" s="349"/>
-      <c r="F65" s="349"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="339">
+      <c r="C67" s="76">
         <f>Normalized_FCF!G19</f>
         <v>-206364</v>
       </c>
@@ -4824,7 +4838,7 @@
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="339">
+      <c r="C68" s="76">
         <f>Normalized_FCF!C19</f>
         <v>-540.75</v>
       </c>
@@ -4841,7 +4855,7 @@
         <f>Normalized_FCF!C125</f>
         <v>-1.1466847491076299E-3</v>
       </c>
-      <c r="F69" s="315"/>
+      <c r="F69" s="314"/>
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
@@ -4852,275 +4866,288 @@
         <v>4.6696035242290754E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>457</v>
-      </c>
-      <c r="F70" s="316">
+        <v>456</v>
+      </c>
+      <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
         <v>-40.722644369893672</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="13.9">
-      <c r="A72" s="222" t="s">
+    <row r="72" spans="1:6">
+      <c r="B72" s="210" t="s">
+        <v>459</v>
+      </c>
+      <c r="C72" s="344" t="s">
+        <v>461</v>
+      </c>
+      <c r="D72" s="344" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73" s="47" t="s">
+        <v>460</v>
+      </c>
+      <c r="C73" s="92">
+        <f>Normalized_FCF!C120</f>
+        <v>-240.33333333333334</v>
+      </c>
+      <c r="D73" s="92">
+        <f>Normalized_FCF!G120</f>
+        <v>-65483</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="259" t="str">
+        <f>Normalized_FCF!B117</f>
+        <v>Pre-tax Profit/Sales</v>
+      </c>
+      <c r="C74" s="343">
+        <f>Normalized_FCF!C117</f>
+        <v>-1.1649701082565843E-2</v>
+      </c>
+      <c r="D74" s="343">
+        <f>Normalized_FCF!G117</f>
+        <v>1.4678118322150659</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="259" t="str">
+        <f>Normalized_FCF!B118</f>
+        <v>Sales/Total Assets</v>
+      </c>
+      <c r="C75" s="345">
+        <f>Normalized_FCF!C118</f>
+        <v>15472.5</v>
+      </c>
+      <c r="D75" s="345">
+        <f>Normalized_FCF!G118</f>
+        <v>-33459.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="B76" s="259" t="str">
+        <f>Normalized_FCF!B119</f>
+        <v>Total Assets/Equity</v>
+      </c>
+      <c r="C76" s="345">
+        <f>Normalized_FCF!C119</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="D76" s="345">
+        <f>Normalized_FCF!G119</f>
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="13.9">
+      <c r="A78" s="222" t="s">
         <v>359</v>
       </c>
-      <c r="B72" s="36"/>
-      <c r="C72" s="36"/>
-      <c r="D72" s="36"/>
-      <c r="E72" s="36"/>
-      <c r="F72" s="36"/>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73" s="209"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.5" customHeight="1">
-      <c r="A74" s="17"/>
-      <c r="B74" s="349" t="s">
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="209"/>
+    </row>
+    <row r="80" spans="1:6" ht="24.5" customHeight="1">
+      <c r="A80" s="17"/>
+      <c r="B80" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C74" s="349"/>
-      <c r="D74" s="349"/>
-      <c r="E74" s="349"/>
-      <c r="F74" s="349"/>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="B75" s="352" t="s">
+      <c r="C80" s="348"/>
+      <c r="D80" s="348"/>
+      <c r="E80" s="348"/>
+      <c r="F80" s="348"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="352"/>
-      <c r="D75" s="352"/>
-      <c r="E75" s="352"/>
-      <c r="F75" s="352"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="210" t="s">
+      <c r="C81" s="350"/>
+      <c r="D81" s="350"/>
+      <c r="E81" s="350"/>
+      <c r="F81" s="350"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="B83" s="210" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
-      <c r="B78" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="C78" s="92">
+    <row r="84" spans="1:6">
+      <c r="B84" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C84" s="92">
         <f>F31</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
-      <c r="B79" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="C79" s="92">
+    <row r="85" spans="1:6">
+      <c r="B85" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
-      <c r="B80" s="80" t="s">
+    <row r="86" spans="1:6">
+      <c r="B86" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C80" s="236">
-        <f>F31+C79</f>
+      <c r="C86" s="236">
+        <f>F31+C85</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
-      <c r="C81" s="121"/>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="B82" s="293" t="s">
+    <row r="87" spans="1:6">
+      <c r="C87" s="121"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="B88" s="293" t="s">
         <v>360</v>
       </c>
-      <c r="C82" s="121"/>
-    </row>
-    <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="349" t="s">
+      <c r="C88" s="121"/>
+    </row>
+    <row r="89" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B89" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C83" s="349"/>
-      <c r="D83" s="349"/>
-      <c r="E83" s="349"/>
-      <c r="F83" s="349"/>
-    </row>
-    <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="349" t="s">
+      <c r="C89" s="348"/>
+      <c r="D89" s="348"/>
+      <c r="E89" s="348"/>
+      <c r="F89" s="348"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B90" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C84" s="349"/>
-      <c r="D84" s="349"/>
-      <c r="E84" s="349"/>
-      <c r="F84" s="349"/>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="B86" s="47" t="s">
+      <c r="C90" s="348"/>
+      <c r="D90" s="348"/>
+      <c r="E90" s="348"/>
+      <c r="F90" s="348"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C86" s="236">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="B87" s="47" t="s">
+      <c r="C92" s="236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="B93" s="47" t="s">
         <v>281</v>
       </c>
-      <c r="C87" s="223">
+      <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>-0.32537179755928991</v>
       </c>
-      <c r="D87" s="1" t="str">
+      <c r="D93" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="13.9">
-      <c r="A89" s="222" t="s">
+    <row r="95" spans="1:6" ht="13.9">
+      <c r="A95" s="222" t="s">
         <v>361</v>
       </c>
-      <c r="B89" s="36"/>
-      <c r="C89" s="36"/>
-      <c r="D89" s="36"/>
-      <c r="E89" s="36"/>
-      <c r="F89" s="36"/>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90" s="209"/>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="B91" s="349" t="s">
+      <c r="B95" s="36"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="36"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="209"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="348" t="s">
         <v>369</v>
       </c>
-      <c r="C91" s="349"/>
-      <c r="D91" s="349"/>
-      <c r="E91" s="349"/>
-      <c r="F91" s="349"/>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="B92" s="1" t="s">
+      <c r="C97" s="348"/>
+      <c r="D97" s="348"/>
+      <c r="E97" s="348"/>
+      <c r="F97" s="348"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
-      <c r="B94" s="210" t="s">
+    <row r="100" spans="2:6">
+      <c r="B100" s="210" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="349" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B101" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C95" s="349"/>
-      <c r="D95" s="349"/>
-      <c r="E95" s="349"/>
-      <c r="F95" s="349"/>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="B96" s="47" t="s">
+      <c r="C101" s="348"/>
+      <c r="D101" s="348"/>
+      <c r="E101" s="348"/>
+      <c r="F101" s="348"/>
+    </row>
+    <row r="102" spans="2:6">
+      <c r="B102" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C96" s="339">
+      <c r="C102" s="76">
         <f>DCF!C7</f>
         <v>0</v>
       </c>
-      <c r="D96" s="1" t="str">
+      <c r="D102" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="47" t="s">
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
         <v>282</v>
       </c>
-      <c r="C97" s="223">
-        <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0</v>
-      </c>
-      <c r="D97" s="1" t="str">
+      <c r="C103" s="223">
+        <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0</v>
+      </c>
+      <c r="D103" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="98" spans="2:6">
-      <c r="B98" s="296" t="s">
+    <row r="104" spans="2:6">
+      <c r="B104" s="296" t="s">
         <v>408</v>
       </c>
-      <c r="C98" s="297">
-        <f>BS!G30/BS!G27</f>
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="99" spans="2:6">
-      <c r="B99" s="296" t="s">
-        <v>409</v>
-      </c>
-      <c r="C99" s="297">
-        <f>BS!G31/BS!G27</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="2:6">
-      <c r="B100" s="296" t="s">
-        <v>411</v>
-      </c>
-      <c r="C100" s="298">
-        <f>BS!C50</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="2:6">
-      <c r="B102" s="1" t="s">
+      <c r="C104" s="346">
+        <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="296" t="s">
+        <v>410</v>
+      </c>
+      <c r="C105" s="347">
+        <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
-      <c r="B103" s="47" t="s">
+    <row r="108" spans="2:6">
+      <c r="B108" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C103" s="339">
+      <c r="C108" s="76">
         <f>BS!C66</f>
         <v>2</v>
-      </c>
-      <c r="D103" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="104" spans="2:6">
-      <c r="B104" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C104" s="339">
-        <f>DCF!C8</f>
-        <v>0</v>
-      </c>
-      <c r="D104" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="105" spans="2:6">
-      <c r="B105" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C105" s="223">
-        <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0</v>
-      </c>
-      <c r="D105" s="1" t="str">
-        <f>Market_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="107" spans="2:6">
-      <c r="B107" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="108" spans="2:6">
-      <c r="B108" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C108" s="339">
-        <f>DCF!C9</f>
-        <v>0</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5129,702 +5156,746 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C109" s="223">
-        <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>267</v>
+      </c>
+      <c r="C109" s="76">
+        <f>DCF!C8</f>
         <v>0</v>
       </c>
       <c r="D109" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6">
+      <c r="B110" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C110" s="223">
+        <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0</v>
+      </c>
+      <c r="D110" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="349" t="s">
-        <v>370</v>
-      </c>
-      <c r="C111" s="349"/>
-      <c r="D111" s="349"/>
-      <c r="E111" s="349"/>
-      <c r="F111" s="349"/>
+    <row r="112" spans="2:6">
+      <c r="B112" s="1" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>458</v>
-      </c>
-      <c r="C113" s="223">
-        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>13.25</v>
+        <v>258</v>
+      </c>
+      <c r="C113" s="76">
+        <f>DCF!C9</f>
+        <v>0</v>
       </c>
       <c r="D113" s="1" t="str">
-        <f>Market_currency</f>
+        <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="296" t="s">
-        <v>410</v>
+      <c r="B114" s="47" t="s">
+        <v>284</v>
       </c>
       <c r="C114" s="223">
-        <f>BS!D47</f>
-        <v>4.3322735874745961E-5</v>
+        <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="13.9">
-      <c r="A116" s="222" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B116" s="348" t="s">
+        <v>370</v>
+      </c>
+      <c r="C116" s="348"/>
+      <c r="D116" s="348"/>
+      <c r="E116" s="348"/>
+      <c r="F116" s="348"/>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="B118" s="47" t="s">
+        <v>457</v>
+      </c>
+      <c r="C118" s="223">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
+        <v>13.25</v>
+      </c>
+      <c r="D118" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="B119" s="296" t="s">
+        <v>409</v>
+      </c>
+      <c r="C119" s="223">
+        <f>BS!D47</f>
+        <v>4.3322735874745961E-5</v>
+      </c>
+      <c r="D119" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
+      <c r="A121" s="222" t="s">
         <v>362</v>
       </c>
-      <c r="B116" s="36"/>
-      <c r="C116" s="36"/>
-      <c r="D116" s="36"/>
-      <c r="E116" s="36"/>
-      <c r="F116" s="36"/>
-    </row>
-    <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="350" t="s">
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B123" s="349" t="s">
         <v>371</v>
       </c>
-      <c r="C118" s="350"/>
-      <c r="D118" s="350"/>
-      <c r="E118" s="350"/>
-      <c r="F118" s="350"/>
-    </row>
-    <row r="120" spans="1:6" ht="12.4">
-      <c r="B120" s="233" t="s">
+      <c r="C123" s="349"/>
+      <c r="D123" s="349"/>
+      <c r="E123" s="349"/>
+      <c r="F123" s="349"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
+      <c r="B125" s="233" t="s">
         <v>118</v>
       </c>
-      <c r="C120" s="233" t="s">
+      <c r="C125" s="233" t="s">
         <v>133</v>
       </c>
-      <c r="D120" s="233" t="s">
+      <c r="D125" s="233" t="s">
         <v>113</v>
       </c>
-      <c r="E120" s="233" t="s">
+      <c r="E125" s="233" t="s">
         <v>260</v>
       </c>
-      <c r="F120" s="233" t="s">
+      <c r="F125" s="233" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
-      <c r="B121" s="228" t="str">
+    <row r="126" spans="1:6">
+      <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C121" s="229">
+      <c r="C126" s="229">
         <f>DCF!C74</f>
         <v>0.08</v>
       </c>
-      <c r="D121" s="230">
+      <c r="D126" s="230">
         <f>DCF!D74</f>
         <v>30</v>
       </c>
-      <c r="E121" s="231" t="str">
+      <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
         <v>34.38 CNY</v>
       </c>
-      <c r="F121" s="232">
+      <c r="F126" s="232">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
-      <c r="B122" s="218" t="str">
+    <row r="127" spans="1:6">
+      <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C122" s="219">
+      <c r="C127" s="219">
         <f>DCF!C75</f>
         <v>0.06</v>
       </c>
-      <c r="D122" s="220">
+      <c r="D127" s="220">
         <f>DCF!D75</f>
         <v>30</v>
       </c>
-      <c r="E122" s="231" t="str">
+      <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
         <v>26.64 CNY</v>
       </c>
-      <c r="F122" s="221">
+      <c r="F127" s="221">
         <f>DCF!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
-      <c r="B123" s="218" t="str">
+    <row r="128" spans="1:6">
+      <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
       </c>
-      <c r="C123" s="219">
+      <c r="C128" s="219">
         <f>DCF!C76</f>
         <v>0.04</v>
       </c>
-      <c r="D123" s="220">
+      <c r="D128" s="220">
         <f>DCF!D76</f>
         <v>30</v>
       </c>
-      <c r="E123" s="231" t="str">
+      <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
         <v>21.16 CNY</v>
       </c>
-      <c r="F123" s="221">
+      <c r="F128" s="221">
         <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
-      <c r="B124" s="218" t="str">
+    <row r="129" spans="1:6">
+      <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C124" s="219">
+      <c r="C129" s="219">
         <f>DCF!C77</f>
         <v>0.02</v>
       </c>
-      <c r="D124" s="220">
+      <c r="D129" s="220">
         <f>DCF!D77</f>
         <v>30</v>
       </c>
-      <c r="E124" s="231" t="str">
+      <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
         <v>17.21 CNY</v>
       </c>
-      <c r="F124" s="221">
+      <c r="F129" s="221">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
-      <c r="B125" s="218" t="str">
+    <row r="130" spans="1:6">
+      <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C125" s="219">
+      <c r="C130" s="219">
         <f>DCF!C78</f>
         <v>0</v>
       </c>
-      <c r="D125" s="220">
+      <c r="D130" s="220">
         <f>DCF!D78</f>
         <v>30</v>
       </c>
-      <c r="E125" s="231" t="str">
+      <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
         <v>14.32 CNY</v>
       </c>
-      <c r="F125" s="221">
+      <c r="F130" s="221">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="211" t="s">
+    <row r="132" spans="1:6">
+      <c r="B132" s="211" t="s">
         <v>259</v>
       </c>
-      <c r="C127" s="217">
+      <c r="C132" s="217">
         <f>Scenarios!C60</f>
         <v>21.752920556327282</v>
       </c>
-      <c r="D127" s="212" t="str">
+      <c r="D132" s="212" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="353" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B134" s="353" t="s">
         <v>374</v>
       </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
-    </row>
-    <row r="131" spans="1:6" ht="13.9">
-      <c r="A131" s="222" t="s">
+      <c r="C134" s="353"/>
+      <c r="D134" s="353"/>
+      <c r="E134" s="353"/>
+      <c r="F134" s="353"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
+      <c r="A136" s="222" t="s">
         <v>406</v>
       </c>
-      <c r="B131" s="36"/>
-      <c r="C131" s="36"/>
-      <c r="D131" s="36"/>
-      <c r="E131" s="36"/>
-      <c r="F131" s="36"/>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="B133" s="354" t="s">
+      <c r="B136" s="36"/>
+      <c r="C136" s="36"/>
+      <c r="D136" s="36"/>
+      <c r="E136" s="36"/>
+      <c r="F136" s="36"/>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="B138" s="351" t="s">
         <v>372</v>
       </c>
-      <c r="C133" s="354"/>
-      <c r="D133" s="354"/>
-      <c r="E133" s="354"/>
-      <c r="F133" s="354"/>
-    </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="349" t="s">
+      <c r="C138" s="351"/>
+      <c r="D138" s="351"/>
+      <c r="E138" s="351"/>
+      <c r="F138" s="351"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B139" s="348" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="349"/>
-      <c r="D134" s="349"/>
-      <c r="E134" s="349"/>
-      <c r="F134" s="349"/>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="B135" s="210" t="s">
+      <c r="C139" s="348"/>
+      <c r="D139" s="348"/>
+      <c r="E139" s="348"/>
+      <c r="F139" s="348"/>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="B140" s="210" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
-      <c r="B136" s="1" t="s">
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="225">
+      <c r="C141" s="225">
         <f>F28</f>
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:6">
-      <c r="B137" s="1" t="s">
+    <row r="142" spans="1:6">
+      <c r="B142" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C137" s="224">
+      <c r="C142" s="224">
         <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="212" t="s">
+    <row r="143" spans="1:6">
+      <c r="B143" s="212" t="s">
         <v>262</v>
       </c>
-      <c r="C138" s="213">
+      <c r="C143" s="213">
         <f>Scenarios!C77</f>
         <v>1.06</v>
       </c>
-      <c r="D138" s="212" t="str">
+      <c r="D143" s="212" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
-      <c r="B140" s="210" t="s">
-        <v>413</v>
-      </c>
-      <c r="C140" s="241" t="str">
+    <row r="145" spans="2:4">
+      <c r="B145" s="210" t="s">
+        <v>412</v>
+      </c>
+      <c r="C145" s="241" t="str">
         <f>C11</f>
         <v>601166.SS</v>
       </c>
-      <c r="D140" s="241" t="str">
+      <c r="D145" s="241" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:6">
-      <c r="B141" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="C141" s="297">
+    <row r="146" spans="2:4">
+      <c r="B146" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C146" s="297">
         <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
-      <c r="B142" s="212" t="str">
-        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
+    <row r="147" spans="2:4">
+      <c r="B147" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C142" s="216">
+      <c r="C147" s="216">
         <f>Scenarios!C81</f>
         <v>1.6842565597667636</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
-      <c r="B143" s="212" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
+    <row r="148" spans="2:4">
+      <c r="B148" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C143" s="216">
+      <c r="C148" s="216">
         <f>Scenarios!C82</f>
         <v>7.9274491823350175</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
-      <c r="B144" s="80" t="s">
+    <row r="149" spans="2:4">
+      <c r="B149" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C144" s="215">
+      <c r="C149" s="215">
         <f>Scenarios!C83</f>
         <v>9.6117057421017815</v>
       </c>
-      <c r="D144" s="301" t="str">
-        <f>IF($D$11="","",C144*$E$25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="145" spans="2:4">
-      <c r="B145" s="259" t="s">
-        <v>421</v>
-      </c>
-      <c r="C145" s="299" t="str">
+      <c r="D149" s="300" t="str">
+        <f>IF($D$11="","",C149*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" s="259" t="s">
+        <v>420</v>
+      </c>
+      <c r="C150" s="298" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D145" s="299" t="str">
+      <c r="D150" s="298" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4">
-      <c r="B146" s="214" t="s">
+    <row r="151" spans="2:4">
+      <c r="B151" s="214" t="s">
         <v>263</v>
       </c>
-      <c r="C146" s="92">
+      <c r="C151" s="92">
         <f>Scenarios!F83</f>
         <v>0.55814182664745582</v>
       </c>
     </row>
-    <row r="148" spans="2:4">
-      <c r="B148" s="210" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="149" spans="2:4">
-      <c r="B149" s="1" t="s">
+    <row r="153" spans="2:4">
+      <c r="B153" s="210" t="s">
         <v>415</v>
       </c>
-      <c r="C149" s="297">
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C154" s="297">
         <f>Scenarios!C90</f>
         <v>0.22</v>
       </c>
     </row>
-    <row r="150" spans="2:4">
-      <c r="B150" s="212" t="str">
-        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
+    <row r="155" spans="2:4">
+      <c r="B155" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C150" s="216">
+      <c r="C155" s="216">
         <f>Scenarios!C91</f>
         <v>2.1647759063533951</v>
       </c>
     </row>
-    <row r="151" spans="2:4">
-      <c r="B151" s="212" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
+    <row r="156" spans="2:4">
+      <c r="B156" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C151" s="216">
+      <c r="C156" s="216">
         <f>Scenarios!C92</f>
         <v>11.97948317057776</v>
       </c>
     </row>
-    <row r="152" spans="2:4">
-      <c r="B152" s="80" t="s">
+    <row r="157" spans="2:4">
+      <c r="B157" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C152" s="215">
+      <c r="C157" s="215">
         <f>Scenarios!C93</f>
         <v>14.144259076931155</v>
       </c>
-      <c r="D152" s="301" t="str">
-        <f>IF($D$11="","",C152*$E$25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="153" spans="2:4">
-      <c r="B153" s="259" t="s">
-        <v>421</v>
-      </c>
-      <c r="C153" s="299" t="str">
+      <c r="D157" s="300" t="str">
+        <f>IF($D$11="","",C157*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" s="259" t="s">
+        <v>420</v>
+      </c>
+      <c r="C158" s="298" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D153" s="299" t="str">
+      <c r="D158" s="298" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="154" spans="2:4">
-      <c r="B154" s="214" t="s">
+    <row r="159" spans="2:4">
+      <c r="B159" s="214" t="s">
         <v>263</v>
       </c>
-      <c r="C154" s="92">
+      <c r="C159" s="92">
         <f>Scenarios!F93</f>
         <v>0.34977654884061038</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
-      <c r="B156" s="210" t="s">
+    <row r="161" spans="2:4">
+      <c r="B161" s="210" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="157" spans="2:4">
-      <c r="B157" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C157" s="92">
+    <row r="162" spans="2:4">
+      <c r="B162" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C162" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="158" spans="2:4">
-      <c r="B158" s="212" t="str">
-        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
+    <row r="163" spans="2:4">
+      <c r="B163" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C158" s="216">
+      <c r="C163" s="216">
         <f>Scenarios!C97</f>
         <v>2.731722806482753</v>
       </c>
     </row>
-    <row r="159" spans="2:4">
-      <c r="B159" s="212" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
+    <row r="164" spans="2:4">
+      <c r="B164" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C159" s="216">
+      <c r="C164" s="216">
         <f>Scenarios!C98</f>
         <v>17.268169673963001</v>
       </c>
     </row>
-    <row r="160" spans="2:4">
-      <c r="B160" s="80" t="s">
+    <row r="165" spans="2:4">
+      <c r="B165" s="80" t="s">
         <v>405</v>
       </c>
-      <c r="C160" s="215">
+      <c r="C165" s="215">
         <f>Scenarios!C99</f>
         <v>19.999892480445755</v>
       </c>
-      <c r="D160" s="301" t="str">
-        <f>IF($D$11="","",C160*$E$25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
-      <c r="B161" s="259" t="s">
-        <v>421</v>
-      </c>
-      <c r="C161" s="299" t="str">
+      <c r="D165" s="300" t="str">
+        <f>IF($D$11="","",C165*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" s="259" t="s">
+        <v>420</v>
+      </c>
+      <c r="C166" s="298" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D161" s="299" t="str">
+      <c r="D166" s="298" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:6">
-      <c r="B162" s="214" t="s">
+    <row r="167" spans="2:4">
+      <c r="B167" s="214" t="s">
         <v>263</v>
       </c>
-      <c r="C162" s="92">
+      <c r="C167" s="92">
         <f>Scenarios!F99</f>
         <v>8.0588170739750331E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:6">
-      <c r="B164" s="210" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
-      <c r="B165" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C165" s="92">
+    <row r="169" spans="2:4">
+      <c r="B169" s="210" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C170" s="92">
         <f>F32</f>
         <v>0.12</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
-      <c r="B166" s="212" t="str">
-        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
+    <row r="171" spans="2:4">
+      <c r="B171" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C166" s="216">
+      <c r="C171" s="216">
         <f>Scenarios!C103</f>
         <v>2.5459411443148712</v>
       </c>
     </row>
-    <row r="167" spans="1:6">
-      <c r="B167" s="212" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
+    <row r="172" spans="2:4">
+      <c r="B172" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C167" s="216">
+      <c r="C172" s="216">
         <f>Scenarios!C104</f>
         <v>15.483299184248073</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
-      <c r="B168" s="80" t="s">
+    <row r="173" spans="2:4">
+      <c r="B173" s="80" t="s">
         <v>405</v>
       </c>
-      <c r="C168" s="215">
+      <c r="C173" s="215">
         <f>Scenarios!C105</f>
         <v>18.029240328562945</v>
       </c>
-      <c r="D168" s="301" t="str">
-        <f>IF($D$11="","",C168*$E$25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="B169" s="259" t="s">
-        <v>421</v>
-      </c>
-      <c r="C169" s="299" t="str">
+      <c r="D173" s="300" t="str">
+        <f>IF($D$11="","",C173*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="B174" s="259" t="s">
+        <v>420</v>
+      </c>
+      <c r="C174" s="298" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D169" s="299" t="str">
+      <c r="D174" s="298" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="170" spans="1:6">
-      <c r="B170" s="214" t="s">
+    <row r="175" spans="2:4">
+      <c r="B175" s="214" t="s">
         <v>263</v>
       </c>
-      <c r="C170" s="92">
+      <c r="C175" s="92">
         <f>Scenarios!F105</f>
         <v>0.17104839072722289</v>
       </c>
     </row>
-    <row r="172" spans="1:6" ht="13.9">
-      <c r="A172" s="222" t="s">
+    <row r="177" spans="1:6" ht="13.9">
+      <c r="A177" s="222" t="s">
         <v>378</v>
       </c>
-      <c r="B172" s="36"/>
-      <c r="C172" s="36"/>
-      <c r="D172" s="36"/>
-      <c r="E172" s="36"/>
-      <c r="F172" s="36"/>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="B174" s="348" t="s">
+      <c r="B177" s="36"/>
+      <c r="C177" s="36"/>
+      <c r="D177" s="36"/>
+      <c r="E177" s="36"/>
+      <c r="F177" s="36"/>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="B179" s="355" t="s">
         <v>380</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
-    </row>
-    <row r="176" spans="1:6">
-      <c r="B176" s="210" t="s">
+      <c r="C179" s="348"/>
+      <c r="D179" s="348"/>
+      <c r="E179" s="348"/>
+      <c r="F179" s="348"/>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="B181" s="210" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="177" spans="2:6">
-      <c r="B177" s="351" t="s">
+    <row r="182" spans="1:6">
+      <c r="B182" s="352" t="s">
         <v>384</v>
       </c>
-      <c r="C177" s="351"/>
-      <c r="D177" s="351"/>
-      <c r="E177" s="351"/>
-      <c r="F177" s="351"/>
-    </row>
-    <row r="178" spans="2:6">
-      <c r="B178" s="214" t="s">
+      <c r="C182" s="352"/>
+      <c r="D182" s="352"/>
+      <c r="E182" s="352"/>
+      <c r="F182" s="352"/>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="B183" s="214" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="179" spans="2:6">
-      <c r="B179" s="214" t="s">
+    <row r="184" spans="1:6">
+      <c r="B184" s="214" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="180" spans="2:6">
-      <c r="B180" s="214" t="s">
+    <row r="185" spans="1:6">
+      <c r="B185" s="214" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="182" spans="2:6">
-      <c r="B182" s="1" t="s">
+    <row r="187" spans="1:6">
+      <c r="B187" s="1" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="350" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B188" s="349" t="s">
         <v>385</v>
       </c>
-      <c r="C183" s="350"/>
-      <c r="D183" s="350"/>
-      <c r="E183" s="350"/>
-      <c r="F183" s="350"/>
-    </row>
-    <row r="185" spans="2:6">
-      <c r="B185" s="1" t="s">
+      <c r="C188" s="349"/>
+      <c r="D188" s="349"/>
+      <c r="E188" s="349"/>
+      <c r="F188" s="349"/>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="B190" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="347" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B191" s="354" t="s">
         <v>386</v>
       </c>
-      <c r="C186" s="347"/>
-      <c r="D186" s="347"/>
-      <c r="E186" s="347"/>
-      <c r="F186" s="347"/>
-    </row>
-    <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="347" t="s">
+      <c r="C191" s="354"/>
+      <c r="D191" s="354"/>
+      <c r="E191" s="354"/>
+      <c r="F191" s="354"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B192" s="354" t="s">
         <v>387</v>
       </c>
-      <c r="C187" s="347"/>
-      <c r="D187" s="347"/>
-      <c r="E187" s="347"/>
-      <c r="F187" s="347"/>
-    </row>
-    <row r="189" spans="2:6">
-      <c r="B189" s="1" t="s">
+      <c r="C192" s="354"/>
+      <c r="D192" s="354"/>
+      <c r="E192" s="354"/>
+      <c r="F192" s="354"/>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="190" spans="2:6">
-      <c r="B190" s="214" t="s">
+    <row r="195" spans="2:2">
+      <c r="B195" s="214" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="191" spans="2:6">
-      <c r="B191" s="214" t="s">
+    <row r="196" spans="2:2">
+      <c r="B196" s="214" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="192" spans="2:6">
-      <c r="B192" s="214" t="s">
+    <row r="197" spans="2:2">
+      <c r="B197" s="214" t="s">
         <v>392</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
     <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B84:F84"/>
-    <mergeCell ref="B91:F91"/>
-    <mergeCell ref="B111:F111"/>
-    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B116:F116"/>
+    <mergeCell ref="B138:F138"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B80:F80"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5940,229 +6011,229 @@
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="335">
+      <c r="C4" s="334">
         <v>61890</v>
       </c>
-      <c r="D4" s="335"/>
-      <c r="E4" s="335"/>
-      <c r="F4" s="335"/>
-      <c r="G4" s="335"/>
-      <c r="H4" s="335"/>
-      <c r="I4" s="335"/>
-      <c r="J4" s="335"/>
-      <c r="K4" s="335"/>
-      <c r="L4" s="335"/>
-      <c r="M4" s="335"/>
+      <c r="D4" s="334"/>
+      <c r="E4" s="334"/>
+      <c r="F4" s="334"/>
+      <c r="G4" s="334"/>
+      <c r="H4" s="334"/>
+      <c r="I4" s="334"/>
+      <c r="J4" s="334"/>
+      <c r="K4" s="334"/>
+      <c r="L4" s="334"/>
+      <c r="M4" s="334"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="335">
-        <v>0</v>
-      </c>
-      <c r="D5" s="335"/>
-      <c r="E5" s="335"/>
-      <c r="F5" s="335"/>
-      <c r="G5" s="335"/>
-      <c r="H5" s="335"/>
-      <c r="I5" s="335"/>
-      <c r="J5" s="335"/>
-      <c r="K5" s="335"/>
-      <c r="L5" s="335"/>
-      <c r="M5" s="335"/>
+      <c r="C5" s="334">
+        <v>0</v>
+      </c>
+      <c r="D5" s="334"/>
+      <c r="E5" s="334"/>
+      <c r="F5" s="334"/>
+      <c r="G5" s="334"/>
+      <c r="H5" s="334"/>
+      <c r="I5" s="334"/>
+      <c r="J5" s="334"/>
+      <c r="K5" s="334"/>
+      <c r="L5" s="334"/>
+      <c r="M5" s="334"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="335">
+      <c r="C6" s="334">
         <v>62611</v>
       </c>
-      <c r="D6" s="335"/>
-      <c r="E6" s="335"/>
-      <c r="F6" s="335"/>
-      <c r="G6" s="335"/>
-      <c r="H6" s="335"/>
-      <c r="I6" s="335"/>
-      <c r="J6" s="335"/>
-      <c r="K6" s="335"/>
-      <c r="L6" s="335"/>
-      <c r="M6" s="335"/>
+      <c r="D6" s="334"/>
+      <c r="E6" s="334"/>
+      <c r="F6" s="334"/>
+      <c r="G6" s="334"/>
+      <c r="H6" s="334"/>
+      <c r="I6" s="334"/>
+      <c r="J6" s="334"/>
+      <c r="K6" s="334"/>
+      <c r="L6" s="334"/>
+      <c r="M6" s="334"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="336">
-        <v>0</v>
-      </c>
-      <c r="D7" s="336"/>
-      <c r="E7" s="336"/>
-      <c r="F7" s="336"/>
-      <c r="G7" s="336"/>
-      <c r="H7" s="336"/>
-      <c r="I7" s="336"/>
-      <c r="J7" s="336"/>
-      <c r="K7" s="336"/>
-      <c r="L7" s="336"/>
-      <c r="M7" s="336"/>
+      <c r="C7" s="335">
+        <v>0</v>
+      </c>
+      <c r="D7" s="335"/>
+      <c r="E7" s="335"/>
+      <c r="F7" s="335"/>
+      <c r="G7" s="335"/>
+      <c r="H7" s="335"/>
+      <c r="I7" s="335"/>
+      <c r="J7" s="335"/>
+      <c r="K7" s="335"/>
+      <c r="L7" s="335"/>
+      <c r="M7" s="335"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="335">
-        <v>0</v>
-      </c>
-      <c r="D8" s="335"/>
-      <c r="E8" s="335"/>
-      <c r="F8" s="335"/>
-      <c r="G8" s="335"/>
-      <c r="H8" s="335"/>
-      <c r="I8" s="335"/>
-      <c r="J8" s="335"/>
-      <c r="K8" s="335"/>
-      <c r="L8" s="335"/>
-      <c r="M8" s="335"/>
+      <c r="C8" s="334">
+        <v>0</v>
+      </c>
+      <c r="D8" s="334"/>
+      <c r="E8" s="334"/>
+      <c r="F8" s="334"/>
+      <c r="G8" s="334"/>
+      <c r="H8" s="334"/>
+      <c r="I8" s="334"/>
+      <c r="J8" s="334"/>
+      <c r="K8" s="334"/>
+      <c r="L8" s="334"/>
+      <c r="M8" s="334"/>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="335"/>
-      <c r="D9" s="335"/>
-      <c r="E9" s="335"/>
-      <c r="F9" s="335"/>
-      <c r="G9" s="335"/>
-      <c r="H9" s="335"/>
-      <c r="I9" s="335"/>
-      <c r="J9" s="335"/>
-      <c r="K9" s="335"/>
-      <c r="L9" s="335"/>
-      <c r="M9" s="335"/>
+      <c r="C9" s="334"/>
+      <c r="D9" s="334"/>
+      <c r="E9" s="334"/>
+      <c r="F9" s="334"/>
+      <c r="G9" s="334"/>
+      <c r="H9" s="334"/>
+      <c r="I9" s="334"/>
+      <c r="J9" s="334"/>
+      <c r="K9" s="334"/>
+      <c r="L9" s="334"/>
+      <c r="M9" s="334"/>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="335"/>
-      <c r="D10" s="335"/>
-      <c r="E10" s="335"/>
-      <c r="F10" s="335"/>
-      <c r="G10" s="335"/>
-      <c r="H10" s="335"/>
-      <c r="I10" s="335"/>
-      <c r="J10" s="335"/>
-      <c r="K10" s="335"/>
-      <c r="L10" s="335"/>
-      <c r="M10" s="335"/>
+      <c r="C10" s="334"/>
+      <c r="D10" s="334"/>
+      <c r="E10" s="334"/>
+      <c r="F10" s="334"/>
+      <c r="G10" s="334"/>
+      <c r="H10" s="334"/>
+      <c r="I10" s="334"/>
+      <c r="J10" s="334"/>
+      <c r="K10" s="334"/>
+      <c r="L10" s="334"/>
+      <c r="M10" s="334"/>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C11" s="335"/>
-      <c r="D11" s="335"/>
-      <c r="E11" s="335"/>
-      <c r="F11" s="335"/>
-      <c r="G11" s="335"/>
-      <c r="H11" s="335"/>
-      <c r="I11" s="335"/>
-      <c r="J11" s="335"/>
-      <c r="K11" s="335"/>
-      <c r="L11" s="335"/>
-      <c r="M11" s="335"/>
+      <c r="C11" s="334"/>
+      <c r="D11" s="334"/>
+      <c r="E11" s="334"/>
+      <c r="F11" s="334"/>
+      <c r="G11" s="334"/>
+      <c r="H11" s="334"/>
+      <c r="I11" s="334"/>
+      <c r="J11" s="334"/>
+      <c r="K11" s="334"/>
+      <c r="L11" s="334"/>
+      <c r="M11" s="334"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="335">
+      <c r="C12" s="334">
         <v>195728</v>
       </c>
-      <c r="D12" s="335"/>
-      <c r="E12" s="335"/>
-      <c r="F12" s="335"/>
-      <c r="G12" s="335"/>
-      <c r="H12" s="335"/>
-      <c r="I12" s="335"/>
-      <c r="J12" s="335"/>
-      <c r="K12" s="335"/>
-      <c r="L12" s="335"/>
-      <c r="M12" s="335"/>
+      <c r="D12" s="334"/>
+      <c r="E12" s="334"/>
+      <c r="F12" s="334"/>
+      <c r="G12" s="334"/>
+      <c r="H12" s="334"/>
+      <c r="I12" s="334"/>
+      <c r="J12" s="334"/>
+      <c r="K12" s="334"/>
+      <c r="L12" s="334"/>
+      <c r="M12" s="334"/>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="335">
+      <c r="C13" s="334">
         <v>343835</v>
       </c>
-      <c r="D13" s="335"/>
-      <c r="E13" s="335"/>
-      <c r="F13" s="335"/>
-      <c r="G13" s="335"/>
-      <c r="H13" s="335"/>
-      <c r="I13" s="335"/>
-      <c r="J13" s="335"/>
-      <c r="K13" s="335"/>
-      <c r="L13" s="335"/>
-      <c r="M13" s="335"/>
+      <c r="D13" s="334"/>
+      <c r="E13" s="334"/>
+      <c r="F13" s="334"/>
+      <c r="G13" s="334"/>
+      <c r="H13" s="334"/>
+      <c r="I13" s="334"/>
+      <c r="J13" s="334"/>
+      <c r="K13" s="334"/>
+      <c r="L13" s="334"/>
+      <c r="M13" s="334"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="335">
+      <c r="C14" s="334">
         <v>9629</v>
       </c>
-      <c r="D14" s="335"/>
-      <c r="E14" s="335"/>
-      <c r="F14" s="335"/>
-      <c r="G14" s="335"/>
-      <c r="H14" s="335"/>
-      <c r="I14" s="335"/>
-      <c r="J14" s="335"/>
-      <c r="K14" s="335"/>
-      <c r="L14" s="335"/>
-      <c r="M14" s="335"/>
+      <c r="D14" s="334"/>
+      <c r="E14" s="334"/>
+      <c r="F14" s="334"/>
+      <c r="G14" s="334"/>
+      <c r="H14" s="334"/>
+      <c r="I14" s="334"/>
+      <c r="J14" s="334"/>
+      <c r="K14" s="334"/>
+      <c r="L14" s="334"/>
+      <c r="M14" s="334"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="337">
+      <c r="C15" s="336">
         <v>77491</v>
       </c>
-      <c r="D15" s="337"/>
-      <c r="E15" s="337"/>
-      <c r="F15" s="337"/>
-      <c r="G15" s="337"/>
-      <c r="H15" s="337"/>
-      <c r="I15" s="337"/>
-      <c r="J15" s="337"/>
-      <c r="K15" s="337"/>
-      <c r="L15" s="337"/>
-      <c r="M15" s="337"/>
+      <c r="D15" s="336"/>
+      <c r="E15" s="336"/>
+      <c r="F15" s="336"/>
+      <c r="G15" s="336"/>
+      <c r="H15" s="336"/>
+      <c r="I15" s="336"/>
+      <c r="J15" s="336"/>
+      <c r="K15" s="336"/>
+      <c r="L15" s="336"/>
+      <c r="M15" s="336"/>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="335">
+      <c r="C16" s="334">
         <v>286</v>
       </c>
-      <c r="D16" s="335"/>
-      <c r="E16" s="335"/>
-      <c r="F16" s="335"/>
-      <c r="G16" s="335"/>
-      <c r="H16" s="335"/>
-      <c r="I16" s="335"/>
-      <c r="J16" s="335"/>
-      <c r="K16" s="335"/>
-      <c r="L16" s="335"/>
-      <c r="M16" s="335"/>
+      <c r="D16" s="334"/>
+      <c r="E16" s="334"/>
+      <c r="F16" s="334"/>
+      <c r="G16" s="334"/>
+      <c r="H16" s="334"/>
+      <c r="I16" s="334"/>
+      <c r="J16" s="334"/>
+      <c r="K16" s="334"/>
+      <c r="L16" s="334"/>
+      <c r="M16" s="334"/>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
@@ -6174,103 +6245,103 @@
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="335"/>
-      <c r="D19" s="335"/>
-      <c r="E19" s="335"/>
-      <c r="F19" s="335"/>
-      <c r="G19" s="335"/>
-      <c r="H19" s="335"/>
-      <c r="I19" s="335"/>
-      <c r="J19" s="335"/>
-      <c r="K19" s="335"/>
-      <c r="L19" s="335"/>
-      <c r="M19" s="335"/>
+      <c r="C19" s="334"/>
+      <c r="D19" s="334"/>
+      <c r="E19" s="334"/>
+      <c r="F19" s="334"/>
+      <c r="G19" s="334"/>
+      <c r="H19" s="334"/>
+      <c r="I19" s="334"/>
+      <c r="J19" s="334"/>
+      <c r="K19" s="334"/>
+      <c r="L19" s="334"/>
+      <c r="M19" s="334"/>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="335"/>
-      <c r="D20" s="335"/>
-      <c r="E20" s="335"/>
-      <c r="F20" s="335"/>
-      <c r="G20" s="335"/>
-      <c r="H20" s="335"/>
-      <c r="I20" s="335"/>
-      <c r="J20" s="335"/>
-      <c r="K20" s="335"/>
-      <c r="L20" s="335"/>
-      <c r="M20" s="335"/>
+      <c r="C20" s="334"/>
+      <c r="D20" s="334"/>
+      <c r="E20" s="334"/>
+      <c r="F20" s="334"/>
+      <c r="G20" s="334"/>
+      <c r="H20" s="334"/>
+      <c r="I20" s="334"/>
+      <c r="J20" s="334"/>
+      <c r="K20" s="334"/>
+      <c r="L20" s="334"/>
+      <c r="M20" s="334"/>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="335"/>
-      <c r="D21" s="335"/>
-      <c r="E21" s="335"/>
-      <c r="F21" s="335"/>
-      <c r="G21" s="335"/>
-      <c r="H21" s="335"/>
-      <c r="I21" s="335"/>
-      <c r="J21" s="335"/>
-      <c r="K21" s="335"/>
-      <c r="L21" s="335"/>
-      <c r="M21" s="335"/>
+      <c r="C21" s="334"/>
+      <c r="D21" s="334"/>
+      <c r="E21" s="334"/>
+      <c r="F21" s="334"/>
+      <c r="G21" s="334"/>
+      <c r="H21" s="334"/>
+      <c r="I21" s="334"/>
+      <c r="J21" s="334"/>
+      <c r="K21" s="334"/>
+      <c r="L21" s="334"/>
+      <c r="M21" s="334"/>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>375</v>
       </c>
-      <c r="C22" s="335">
+      <c r="C22" s="334">
         <v>-237258</v>
       </c>
-      <c r="D22" s="335"/>
-      <c r="E22" s="335"/>
-      <c r="F22" s="335"/>
-      <c r="G22" s="335"/>
-      <c r="H22" s="335"/>
-      <c r="I22" s="335"/>
-      <c r="J22" s="335"/>
-      <c r="K22" s="335"/>
-      <c r="L22" s="335"/>
-      <c r="M22" s="335"/>
+      <c r="D22" s="334"/>
+      <c r="E22" s="334"/>
+      <c r="F22" s="334"/>
+      <c r="G22" s="334"/>
+      <c r="H22" s="334"/>
+      <c r="I22" s="334"/>
+      <c r="J22" s="334"/>
+      <c r="K22" s="334"/>
+      <c r="L22" s="334"/>
+      <c r="M22" s="334"/>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>377</v>
       </c>
-      <c r="C23" s="335">
+      <c r="C23" s="334">
         <v>23438</v>
       </c>
-      <c r="D23" s="335"/>
-      <c r="E23" s="335"/>
-      <c r="F23" s="335"/>
-      <c r="G23" s="335"/>
-      <c r="H23" s="335"/>
-      <c r="I23" s="335"/>
-      <c r="J23" s="335"/>
-      <c r="K23" s="335"/>
-      <c r="L23" s="335"/>
-      <c r="M23" s="335"/>
+      <c r="D23" s="334"/>
+      <c r="E23" s="334"/>
+      <c r="F23" s="334"/>
+      <c r="G23" s="334"/>
+      <c r="H23" s="334"/>
+      <c r="I23" s="334"/>
+      <c r="J23" s="334"/>
+      <c r="K23" s="334"/>
+      <c r="L23" s="334"/>
+      <c r="M23" s="334"/>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>376</v>
       </c>
-      <c r="C24" s="335">
+      <c r="C24" s="334">
         <v>194894</v>
       </c>
-      <c r="D24" s="335"/>
-      <c r="E24" s="335"/>
-      <c r="F24" s="335"/>
-      <c r="G24" s="335"/>
-      <c r="H24" s="335"/>
-      <c r="I24" s="335"/>
-      <c r="J24" s="335"/>
-      <c r="K24" s="335"/>
-      <c r="L24" s="335"/>
-      <c r="M24" s="335"/>
+      <c r="D24" s="334"/>
+      <c r="E24" s="334"/>
+      <c r="F24" s="334"/>
+      <c r="G24" s="334"/>
+      <c r="H24" s="334"/>
+      <c r="I24" s="334"/>
+      <c r="J24" s="334"/>
+      <c r="K24" s="334"/>
+      <c r="L24" s="334"/>
+      <c r="M24" s="334"/>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
@@ -6304,96 +6375,96 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="324">
+      <c r="C28" s="323">
         <f>BS!C4</f>
         <v>0</v>
       </c>
-      <c r="D28" s="335"/>
-      <c r="E28" s="335"/>
-      <c r="F28" s="335"/>
-      <c r="G28" s="335"/>
-      <c r="H28" s="335"/>
-      <c r="I28" s="335"/>
-      <c r="J28" s="335"/>
-      <c r="K28" s="335"/>
-      <c r="L28" s="335"/>
-      <c r="M28" s="335"/>
+      <c r="D28" s="334"/>
+      <c r="E28" s="334"/>
+      <c r="F28" s="334"/>
+      <c r="G28" s="334"/>
+      <c r="H28" s="334"/>
+      <c r="I28" s="334"/>
+      <c r="J28" s="334"/>
+      <c r="K28" s="334"/>
+      <c r="L28" s="334"/>
+      <c r="M28" s="334"/>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="324">
+      <c r="C29" s="323">
         <f>BS!C6</f>
         <v>0</v>
       </c>
-      <c r="D29" s="335"/>
-      <c r="E29" s="335"/>
-      <c r="F29" s="335"/>
-      <c r="G29" s="335"/>
-      <c r="H29" s="335"/>
-      <c r="I29" s="335"/>
-      <c r="J29" s="335"/>
-      <c r="K29" s="335"/>
-      <c r="L29" s="335"/>
-      <c r="M29" s="335"/>
+      <c r="D29" s="334"/>
+      <c r="E29" s="334"/>
+      <c r="F29" s="334"/>
+      <c r="G29" s="334"/>
+      <c r="H29" s="334"/>
+      <c r="I29" s="334"/>
+      <c r="J29" s="334"/>
+      <c r="K29" s="334"/>
+      <c r="L29" s="334"/>
+      <c r="M29" s="334"/>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="325">
+      <c r="C30" s="324">
         <f>BS!C33+BS!C42</f>
         <v>1</v>
       </c>
-      <c r="D30" s="337"/>
-      <c r="E30" s="337"/>
-      <c r="F30" s="337"/>
-      <c r="G30" s="337"/>
-      <c r="H30" s="337"/>
-      <c r="I30" s="337"/>
-      <c r="J30" s="337"/>
-      <c r="K30" s="337"/>
-      <c r="L30" s="337"/>
-      <c r="M30" s="337"/>
+      <c r="D30" s="336"/>
+      <c r="E30" s="336"/>
+      <c r="F30" s="336"/>
+      <c r="G30" s="336"/>
+      <c r="H30" s="336"/>
+      <c r="I30" s="336"/>
+      <c r="J30" s="336"/>
+      <c r="K30" s="336"/>
+      <c r="L30" s="336"/>
+      <c r="M30" s="336"/>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="325">
+      <c r="C31" s="324">
         <f>BS!G27</f>
         <v>3</v>
       </c>
-      <c r="D31" s="337"/>
-      <c r="E31" s="337"/>
-      <c r="F31" s="337"/>
-      <c r="G31" s="337"/>
-      <c r="H31" s="337"/>
-      <c r="I31" s="337"/>
-      <c r="J31" s="337"/>
-      <c r="K31" s="337"/>
-      <c r="L31" s="337"/>
-      <c r="M31" s="337"/>
+      <c r="D31" s="336"/>
+      <c r="E31" s="336"/>
+      <c r="F31" s="336"/>
+      <c r="G31" s="336"/>
+      <c r="H31" s="336"/>
+      <c r="I31" s="336"/>
+      <c r="J31" s="336"/>
+      <c r="K31" s="336"/>
+      <c r="L31" s="336"/>
+      <c r="M31" s="336"/>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="324">
+      <c r="C32" s="323">
         <f>BS!G28</f>
         <v>0</v>
       </c>
-      <c r="D32" s="335"/>
-      <c r="E32" s="335"/>
-      <c r="F32" s="335"/>
-      <c r="G32" s="335"/>
-      <c r="H32" s="335"/>
-      <c r="I32" s="335"/>
-      <c r="J32" s="335"/>
-      <c r="K32" s="335"/>
-      <c r="L32" s="335"/>
-      <c r="M32" s="335"/>
+      <c r="D32" s="334"/>
+      <c r="E32" s="334"/>
+      <c r="F32" s="334"/>
+      <c r="G32" s="334"/>
+      <c r="H32" s="334"/>
+      <c r="I32" s="334"/>
+      <c r="J32" s="334"/>
+      <c r="K32" s="334"/>
+      <c r="L32" s="334"/>
+      <c r="M32" s="334"/>
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
@@ -6420,47 +6491,47 @@
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="324">
+      <c r="C36" s="323">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>61890</v>
       </c>
-      <c r="D36" s="324" t="str">
+      <c r="D36" s="323" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E36" s="324" t="str">
+      <c r="E36" s="323" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F36" s="324" t="str">
+      <c r="F36" s="323" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G36" s="324" t="str">
+      <c r="G36" s="323" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H36" s="324" t="str">
+      <c r="H36" s="323" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I36" s="324" t="str">
+      <c r="I36" s="323" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J36" s="324" t="str">
+      <c r="J36" s="323" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K36" s="324" t="str">
+      <c r="K36" s="323" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L36" s="324" t="str">
+      <c r="L36" s="323" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="M36" s="324" t="str">
+      <c r="M36" s="323" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6469,47 +6540,47 @@
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="324">
+      <c r="C37" s="323">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>0</v>
       </c>
-      <c r="D37" s="324" t="str">
+      <c r="D37" s="323" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="E37" s="324" t="str">
+      <c r="E37" s="323" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F37" s="324" t="str">
+      <c r="F37" s="323" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G37" s="324" t="str">
+      <c r="G37" s="323" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H37" s="324" t="str">
+      <c r="H37" s="323" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I37" s="324" t="str">
+      <c r="I37" s="323" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J37" s="324" t="str">
+      <c r="J37" s="323" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K37" s="324" t="str">
+      <c r="K37" s="323" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L37" s="324" t="str">
+      <c r="L37" s="323" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M37" s="324" t="str">
+      <c r="M37" s="323" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -6518,47 +6589,47 @@
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="320">
+      <c r="C38" s="319">
         <f>IF(C36="","",C36+C37)</f>
         <v>61890</v>
       </c>
-      <c r="D38" s="320" t="str">
+      <c r="D38" s="319" t="str">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v/>
       </c>
-      <c r="E38" s="320" t="str">
+      <c r="E38" s="319" t="str">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v/>
       </c>
-      <c r="F38" s="320" t="str">
+      <c r="F38" s="319" t="str">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v/>
       </c>
-      <c r="G38" s="320" t="str">
+      <c r="G38" s="319" t="str">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v/>
       </c>
-      <c r="H38" s="320" t="str">
+      <c r="H38" s="319" t="str">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v/>
       </c>
-      <c r="I38" s="320" t="str">
+      <c r="I38" s="319" t="str">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v/>
       </c>
-      <c r="J38" s="320" t="str">
+      <c r="J38" s="319" t="str">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v/>
       </c>
-      <c r="K38" s="320" t="str">
+      <c r="K38" s="319" t="str">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v/>
       </c>
-      <c r="L38" s="320" t="str">
+      <c r="L38" s="319" t="str">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v/>
       </c>
-      <c r="M38" s="320" t="str">
+      <c r="M38" s="319" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -6567,47 +6638,47 @@
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="324">
+      <c r="C39" s="323">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-62611</v>
       </c>
-      <c r="D39" s="324" t="str">
+      <c r="D39" s="323" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="E39" s="324" t="str">
+      <c r="E39" s="323" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="F39" s="324" t="str">
+      <c r="F39" s="323" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="G39" s="324" t="str">
+      <c r="G39" s="323" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="H39" s="324" t="str">
+      <c r="H39" s="323" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="I39" s="324" t="str">
+      <c r="I39" s="323" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="J39" s="324" t="str">
+      <c r="J39" s="323" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="K39" s="324" t="str">
+      <c r="K39" s="323" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="L39" s="324" t="str">
+      <c r="L39" s="323" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="M39" s="324" t="str">
+      <c r="M39" s="323" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -6616,47 +6687,47 @@
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="334">
+      <c r="C40" s="333">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>0</v>
       </c>
-      <c r="D40" s="334" t="str">
+      <c r="D40" s="333" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="E40" s="334" t="str">
+      <c r="E40" s="333" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="F40" s="334" t="str">
+      <c r="F40" s="333" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="G40" s="334" t="str">
+      <c r="G40" s="333" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="H40" s="334" t="str">
+      <c r="H40" s="333" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="I40" s="334" t="str">
+      <c r="I40" s="333" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="J40" s="334" t="str">
+      <c r="J40" s="333" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="K40" s="334" t="str">
+      <c r="K40" s="333" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L40" s="334" t="str">
+      <c r="L40" s="333" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="M40" s="334" t="str">
+      <c r="M40" s="333" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -6665,47 +6736,47 @@
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="334">
+      <c r="C41" s="333">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-62611</v>
       </c>
-      <c r="D41" s="334" t="str">
+      <c r="D41" s="333" t="str">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v/>
       </c>
-      <c r="E41" s="334" t="str">
+      <c r="E41" s="333" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="F41" s="334" t="str">
+      <c r="F41" s="333" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="G41" s="334" t="str">
+      <c r="G41" s="333" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="H41" s="334" t="str">
+      <c r="H41" s="333" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I41" s="334" t="str">
+      <c r="I41" s="333" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J41" s="334" t="str">
+      <c r="J41" s="333" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K41" s="334" t="str">
+      <c r="K41" s="333" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="L41" s="334" t="str">
+      <c r="L41" s="333" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="M41" s="334" t="str">
+      <c r="M41" s="333" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6714,47 +6785,47 @@
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="324">
+      <c r="C42" s="323">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="324" t="str">
+      <c r="D42" s="323" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="E42" s="324" t="str">
+      <c r="E42" s="323" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="F42" s="324" t="str">
+      <c r="F42" s="323" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="G42" s="324" t="str">
+      <c r="G42" s="323" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="H42" s="324" t="str">
+      <c r="H42" s="323" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="I42" s="324" t="str">
+      <c r="I42" s="323" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="J42" s="324" t="str">
+      <c r="J42" s="323" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="K42" s="324" t="str">
+      <c r="K42" s="323" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="L42" s="324" t="str">
+      <c r="L42" s="323" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="M42" s="324" t="str">
+      <c r="M42" s="323" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -6763,47 +6834,47 @@
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="C43" s="325">
+      <c r="C43" s="324">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>-721</v>
       </c>
-      <c r="D43" s="325" t="str">
+      <c r="D43" s="324" t="str">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v/>
       </c>
-      <c r="E43" s="325" t="str">
+      <c r="E43" s="324" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="F43" s="325" t="str">
+      <c r="F43" s="324" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="G43" s="325" t="str">
+      <c r="G43" s="324" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="H43" s="325" t="str">
+      <c r="H43" s="324" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="I43" s="325" t="str">
+      <c r="I43" s="324" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="J43" s="325" t="str">
+      <c r="J43" s="324" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="K43" s="325" t="str">
+      <c r="K43" s="324" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="L43" s="325" t="str">
+      <c r="L43" s="324" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="M43" s="325" t="str">
+      <c r="M43" s="324" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -6812,47 +6883,47 @@
       <c r="B44" s="43" t="s">
         <v>169</v>
       </c>
-      <c r="C44" s="338">
+      <c r="C44" s="180">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
         <v>-60266</v>
       </c>
-      <c r="D44" s="338" t="str">
+      <c r="D44" s="180" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="E44" s="338" t="str">
+      <c r="E44" s="180" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="F44" s="338" t="str">
+      <c r="F44" s="180" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="G44" s="338" t="str">
+      <c r="G44" s="180" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="H44" s="338" t="str">
+      <c r="H44" s="180" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="I44" s="338" t="str">
+      <c r="I44" s="180" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="J44" s="338" t="str">
+      <c r="J44" s="180" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="K44" s="338" t="str">
+      <c r="K44" s="180" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L44" s="338" t="str">
+      <c r="L44" s="180" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="M44" s="338" t="str">
+      <c r="M44" s="180" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
@@ -6861,47 +6932,47 @@
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="C45" s="339">
+      <c r="C45" s="76">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
         <v>148107</v>
       </c>
-      <c r="D45" s="339" t="str">
+      <c r="D45" s="76" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="E45" s="339" t="str">
+      <c r="E45" s="76" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="F45" s="339" t="str">
+      <c r="F45" s="76" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="G45" s="339" t="str">
+      <c r="G45" s="76" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="H45" s="339" t="str">
+      <c r="H45" s="76" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I45" s="339" t="str">
+      <c r="I45" s="76" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J45" s="339" t="str">
+      <c r="J45" s="76" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="K45" s="339" t="str">
+      <c r="K45" s="76" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="L45" s="339" t="str">
+      <c r="L45" s="76" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M45" s="339" t="str">
+      <c r="M45" s="76" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -6910,47 +6981,47 @@
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="324">
+      <c r="C46" s="323">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-9629</v>
       </c>
-      <c r="D46" s="324" t="str">
+      <c r="D46" s="323" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="E46" s="324" t="str">
+      <c r="E46" s="323" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="F46" s="324" t="str">
+      <c r="F46" s="323" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="G46" s="324" t="str">
+      <c r="G46" s="323" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="H46" s="324" t="str">
+      <c r="H46" s="323" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="I46" s="324" t="str">
+      <c r="I46" s="323" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="J46" s="324" t="str">
+      <c r="J46" s="323" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="K46" s="324" t="str">
+      <c r="K46" s="323" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="L46" s="324" t="str">
+      <c r="L46" s="323" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="M46" s="324" t="str">
+      <c r="M46" s="323" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -6959,47 +7030,47 @@
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="325">
+      <c r="C47" s="324">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>77491</v>
       </c>
-      <c r="D47" s="325" t="str">
+      <c r="D47" s="324" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="E47" s="325" t="str">
+      <c r="E47" s="324" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="F47" s="325" t="str">
+      <c r="F47" s="324" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="G47" s="325" t="str">
+      <c r="G47" s="324" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="H47" s="325" t="str">
+      <c r="H47" s="324" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="I47" s="325" t="str">
+      <c r="I47" s="324" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="J47" s="325" t="str">
+      <c r="J47" s="324" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="K47" s="325" t="str">
+      <c r="K47" s="324" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="L47" s="325" t="str">
+      <c r="L47" s="324" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="M47" s="325" t="str">
+      <c r="M47" s="324" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -7008,47 +7079,47 @@
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="324">
+      <c r="C48" s="323">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>-286</v>
       </c>
-      <c r="D48" s="324" t="str">
+      <c r="D48" s="323" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="E48" s="324" t="str">
+      <c r="E48" s="323" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="F48" s="324" t="str">
+      <c r="F48" s="323" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="G48" s="324" t="str">
+      <c r="G48" s="323" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="H48" s="324" t="str">
+      <c r="H48" s="323" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="I48" s="324" t="str">
+      <c r="I48" s="323" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="J48" s="324" t="str">
+      <c r="J48" s="323" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="K48" s="324" t="str">
+      <c r="K48" s="323" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L48" s="324" t="str">
+      <c r="L48" s="323" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="M48" s="324" t="str">
+      <c r="M48" s="323" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7062,47 +7133,47 @@
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="324">
+      <c r="C51" s="323">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-195728</v>
       </c>
-      <c r="D51" s="324" t="str">
+      <c r="D51" s="323" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="E51" s="324" t="str">
+      <c r="E51" s="323" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="F51" s="324" t="str">
+      <c r="F51" s="323" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="G51" s="324" t="str">
+      <c r="G51" s="323" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="H51" s="324" t="str">
+      <c r="H51" s="323" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="I51" s="324" t="str">
+      <c r="I51" s="323" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="J51" s="324" t="str">
+      <c r="J51" s="323" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="K51" s="324" t="str">
+      <c r="K51" s="323" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="L51" s="324" t="str">
+      <c r="L51" s="323" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="M51" s="324" t="str">
+      <c r="M51" s="323" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -7111,47 +7182,47 @@
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="324">
+      <c r="C52" s="323">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>343835</v>
       </c>
-      <c r="D52" s="324" t="str">
+      <c r="D52" s="323" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="E52" s="324" t="str">
+      <c r="E52" s="323" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="F52" s="324" t="str">
+      <c r="F52" s="323" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="G52" s="324" t="str">
+      <c r="G52" s="323" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="H52" s="324" t="str">
+      <c r="H52" s="323" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="I52" s="324" t="str">
+      <c r="I52" s="323" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="J52" s="324" t="str">
+      <c r="J52" s="323" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="K52" s="324" t="str">
+      <c r="K52" s="323" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="L52" s="324" t="str">
+      <c r="L52" s="323" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="M52" s="324" t="str">
+      <c r="M52" s="323" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
@@ -7165,47 +7236,47 @@
       <c r="B55" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C55" s="339">
+      <c r="C55" s="76">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
         <v>0</v>
       </c>
-      <c r="D55" s="339" t="str">
+      <c r="D55" s="76" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="E55" s="339" t="str">
+      <c r="E55" s="76" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="F55" s="339" t="str">
+      <c r="F55" s="76" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="G55" s="339" t="str">
+      <c r="G55" s="76" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="H55" s="339" t="str">
+      <c r="H55" s="76" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="I55" s="339" t="str">
+      <c r="I55" s="76" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="J55" s="339" t="str">
+      <c r="J55" s="76" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="K55" s="339" t="str">
+      <c r="K55" s="76" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="L55" s="339" t="str">
+      <c r="L55" s="76" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="M55" s="339" t="str">
+      <c r="M55" s="76" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
@@ -7214,47 +7285,47 @@
       <c r="B56" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C56" s="339">
+      <c r="C56" s="76">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
         <v>0</v>
       </c>
-      <c r="D56" s="339" t="str">
+      <c r="D56" s="76" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="E56" s="339" t="str">
+      <c r="E56" s="76" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="F56" s="339" t="str">
+      <c r="F56" s="76" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="G56" s="339" t="str">
+      <c r="G56" s="76" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="H56" s="339" t="str">
+      <c r="H56" s="76" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="I56" s="339" t="str">
+      <c r="I56" s="76" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="J56" s="339" t="str">
+      <c r="J56" s="76" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="K56" s="339" t="str">
+      <c r="K56" s="76" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="L56" s="339" t="str">
+      <c r="L56" s="76" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="M56" s="339" t="str">
+      <c r="M56" s="76" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
@@ -7263,47 +7334,47 @@
       <c r="B57" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C57" s="339">
+      <c r="C57" s="76">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
         <v>0</v>
       </c>
-      <c r="D57" s="339" t="str">
+      <c r="D57" s="76" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="E57" s="339" t="str">
+      <c r="E57" s="76" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="F57" s="339" t="str">
+      <c r="F57" s="76" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="G57" s="339" t="str">
+      <c r="G57" s="76" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="H57" s="339" t="str">
+      <c r="H57" s="76" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="I57" s="339" t="str">
+      <c r="I57" s="76" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="J57" s="339" t="str">
+      <c r="J57" s="76" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="K57" s="339" t="str">
+      <c r="K57" s="76" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="L57" s="339" t="str">
+      <c r="L57" s="76" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="M57" s="339" t="str">
+      <c r="M57" s="76" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -7312,47 +7383,47 @@
       <c r="B58" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C58" s="339">
+      <c r="C58" s="76">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
         <v>-60266</v>
       </c>
-      <c r="D58" s="339" t="str">
+      <c r="D58" s="76" t="str">
         <f t="shared" ref="D58:M58" si="28">IF(D$4="","",D44-D55-D56-D57)</f>
         <v/>
       </c>
-      <c r="E58" s="339" t="str">
+      <c r="E58" s="76" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="F58" s="339" t="str">
+      <c r="F58" s="76" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="G58" s="339" t="str">
+      <c r="G58" s="76" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="H58" s="339" t="str">
+      <c r="H58" s="76" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="I58" s="339" t="str">
+      <c r="I58" s="76" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="J58" s="339" t="str">
+      <c r="J58" s="76" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="K58" s="339" t="str">
+      <c r="K58" s="76" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="L58" s="339" t="str">
+      <c r="L58" s="76" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="M58" s="339" t="str">
+      <c r="M58" s="76" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
@@ -7367,47 +7438,47 @@
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="324">
+      <c r="C61" s="323">
         <f>IF(C$4="","",-C19)</f>
         <v>0</v>
       </c>
-      <c r="D61" s="324" t="str">
+      <c r="D61" s="323" t="str">
         <f t="shared" ref="D61:M61" si="29">IF(D$4="","",-D19)</f>
         <v/>
       </c>
-      <c r="E61" s="324" t="str">
+      <c r="E61" s="323" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="F61" s="324" t="str">
+      <c r="F61" s="323" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="G61" s="324" t="str">
+      <c r="G61" s="323" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="H61" s="324" t="str">
+      <c r="H61" s="323" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="I61" s="324" t="str">
+      <c r="I61" s="323" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="J61" s="324" t="str">
+      <c r="J61" s="323" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="K61" s="324" t="str">
+      <c r="K61" s="323" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="L61" s="324" t="str">
+      <c r="L61" s="323" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="M61" s="324" t="str">
+      <c r="M61" s="323" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -7416,47 +7487,47 @@
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="324">
+      <c r="C62" s="323">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>0</v>
       </c>
-      <c r="D62" s="324" t="str">
+      <c r="D62" s="323" t="str">
         <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v/>
       </c>
-      <c r="E62" s="324" t="str">
+      <c r="E62" s="323" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="F62" s="324" t="str">
+      <c r="F62" s="323" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="G62" s="324" t="str">
+      <c r="G62" s="323" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="H62" s="324" t="str">
+      <c r="H62" s="323" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="I62" s="324" t="str">
+      <c r="I62" s="323" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="J62" s="324" t="str">
+      <c r="J62" s="323" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="K62" s="324" t="str">
+      <c r="K62" s="323" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="L62" s="324" t="str">
+      <c r="L62" s="323" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="M62" s="324" t="str">
+      <c r="M62" s="323" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -7465,47 +7536,47 @@
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="324">
+      <c r="C63" s="323">
         <f>IF(C$4="","",-C21)</f>
         <v>0</v>
       </c>
-      <c r="D63" s="324" t="str">
+      <c r="D63" s="323" t="str">
         <f t="shared" ref="D63:M63" si="31">IF(D$4="","",-D21)</f>
         <v/>
       </c>
-      <c r="E63" s="324" t="str">
+      <c r="E63" s="323" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="F63" s="324" t="str">
+      <c r="F63" s="323" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="G63" s="324" t="str">
+      <c r="G63" s="323" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="H63" s="324" t="str">
+      <c r="H63" s="323" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="I63" s="324" t="str">
+      <c r="I63" s="323" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="J63" s="324" t="str">
+      <c r="J63" s="323" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="K63" s="324" t="str">
+      <c r="K63" s="323" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="L63" s="324" t="str">
+      <c r="L63" s="323" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="M63" s="324" t="str">
+      <c r="M63" s="323" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -7514,47 +7585,47 @@
       <c r="B64" s="27" t="s">
         <v>397</v>
       </c>
-      <c r="C64" s="324">
+      <c r="C64" s="323">
         <f>IF(C$4="","",C22+C23+C24)</f>
         <v>-18926</v>
       </c>
-      <c r="D64" s="324" t="str">
+      <c r="D64" s="323" t="str">
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
         <v/>
       </c>
-      <c r="E64" s="324" t="str">
+      <c r="E64" s="323" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="F64" s="324" t="str">
+      <c r="F64" s="323" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="G64" s="324" t="str">
+      <c r="G64" s="323" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="H64" s="324" t="str">
+      <c r="H64" s="323" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="I64" s="324" t="str">
+      <c r="I64" s="323" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="J64" s="324" t="str">
+      <c r="J64" s="323" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="K64" s="324" t="str">
+      <c r="K64" s="323" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="L64" s="324" t="str">
+      <c r="L64" s="323" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="M64" s="324" t="str">
+      <c r="M64" s="323" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
@@ -7887,47 +7958,47 @@
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C76" s="339">
+      <c r="C76" s="76">
         <f>IF(C$4="","",C79+C80)</f>
         <v>4</v>
       </c>
-      <c r="D76" s="339" t="str">
+      <c r="D76" s="76" t="str">
         <f t="shared" ref="D76:M76" si="39">IF(D$4="","",D79+D80)</f>
         <v/>
       </c>
-      <c r="E76" s="339" t="str">
+      <c r="E76" s="76" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="F76" s="339" t="str">
+      <c r="F76" s="76" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="G76" s="339" t="str">
+      <c r="G76" s="76" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="H76" s="339" t="str">
+      <c r="H76" s="76" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="I76" s="339" t="str">
+      <c r="I76" s="76" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="J76" s="339" t="str">
+      <c r="J76" s="76" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="K76" s="339" t="str">
+      <c r="K76" s="76" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="L76" s="339" t="str">
+      <c r="L76" s="76" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="M76" s="339" t="str">
+      <c r="M76" s="76" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
@@ -7936,115 +8007,115 @@
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="C77" s="334">
+      <c r="C77" s="333">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
         <v>0</v>
       </c>
-      <c r="D77" s="334" t="str">
+      <c r="D77" s="333" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="E77" s="334" t="str">
+      <c r="E77" s="333" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="F77" s="334" t="str">
+      <c r="F77" s="333" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="G77" s="334" t="str">
+      <c r="G77" s="333" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="H77" s="334" t="str">
+      <c r="H77" s="333" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="I77" s="340"/>
-      <c r="J77" s="340"/>
-      <c r="K77" s="340"/>
-      <c r="L77" s="340"/>
-      <c r="M77" s="340"/>
+      <c r="I77" s="337"/>
+      <c r="J77" s="337"/>
+      <c r="K77" s="337"/>
+      <c r="L77" s="337"/>
+      <c r="M77" s="337"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="334">
+      <c r="C78" s="333">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="D78" s="334" t="str">
+      <c r="D78" s="333" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="E78" s="334" t="str">
+      <c r="E78" s="333" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="F78" s="334" t="str">
+      <c r="F78" s="333" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="G78" s="334" t="str">
+      <c r="G78" s="333" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="H78" s="334" t="str">
+      <c r="H78" s="333" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="I78" s="340"/>
-      <c r="J78" s="340"/>
-      <c r="K78" s="340"/>
-      <c r="L78" s="340"/>
-      <c r="M78" s="340"/>
+      <c r="I78" s="337"/>
+      <c r="J78" s="337"/>
+      <c r="K78" s="337"/>
+      <c r="L78" s="337"/>
+      <c r="M78" s="337"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C79" s="324">
+      <c r="C79" s="323">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
         <v>1</v>
       </c>
-      <c r="D79" s="324" t="str">
+      <c r="D79" s="323" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="E79" s="324" t="str">
+      <c r="E79" s="323" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="F79" s="324" t="str">
+      <c r="F79" s="323" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="G79" s="324" t="str">
+      <c r="G79" s="323" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="H79" s="324" t="str">
+      <c r="H79" s="323" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="I79" s="324" t="str">
+      <c r="I79" s="323" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="J79" s="324" t="str">
+      <c r="J79" s="323" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="K79" s="324" t="str">
+      <c r="K79" s="323" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="L79" s="324" t="str">
+      <c r="L79" s="323" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="M79" s="324" t="str">
+      <c r="M79" s="323" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
@@ -8053,47 +8124,47 @@
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C80" s="324">
+      <c r="C80" s="323">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
         <v>3</v>
       </c>
-      <c r="D80" s="324" t="str">
+      <c r="D80" s="323" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="E80" s="324" t="str">
+      <c r="E80" s="323" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="F80" s="324" t="str">
+      <c r="F80" s="323" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="G80" s="324" t="str">
+      <c r="G80" s="323" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="H80" s="324" t="str">
+      <c r="H80" s="323" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="I80" s="324" t="str">
+      <c r="I80" s="323" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="J80" s="324" t="str">
+      <c r="J80" s="323" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="K80" s="324" t="str">
+      <c r="K80" s="323" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="L80" s="324" t="str">
+      <c r="L80" s="323" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="M80" s="324" t="str">
+      <c r="M80" s="323" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -8886,7 +8957,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F45" s="256" t="s">
         <v>59</v>
@@ -9173,11 +9244,11 @@
       <c r="B73" s="105" t="s">
         <v>319</v>
       </c>
-      <c r="C73" s="339">
+      <c r="C73" s="76">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
         <v>-7052.6474952516664</v>
       </c>
-      <c r="D73" s="339">
+      <c r="D73" s="76">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
         <v>-7052.6474952516664</v>
       </c>
@@ -9205,8 +9276,8 @@
       <c r="B75" s="80" t="s">
         <v>322</v>
       </c>
-      <c r="C75" s="345"/>
-      <c r="D75" s="346">
+      <c r="C75" s="341"/>
+      <c r="D75" s="342">
         <f>MAX(-D73*D76,G5)</f>
         <v>2</v>
       </c>
@@ -9510,54 +9581,54 @@
       <c r="B4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="318">
+      <c r="C4" s="317">
         <f>AVERAGE(G4:J4)</f>
         <v>61890</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="266"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="324">
+      <c r="G4" s="323">
         <f>Data!C36</f>
         <v>61890</v>
       </c>
-      <c r="H4" s="324" t="str">
+      <c r="H4" s="323" t="str">
         <f>Data!D36</f>
         <v/>
       </c>
-      <c r="I4" s="324" t="str">
+      <c r="I4" s="323" t="str">
         <f>Data!E36</f>
         <v/>
       </c>
-      <c r="J4" s="324" t="str">
+      <c r="J4" s="323" t="str">
         <f>Data!F36</f>
         <v/>
       </c>
-      <c r="K4" s="324" t="str">
+      <c r="K4" s="323" t="str">
         <f>Data!G36</f>
         <v/>
       </c>
-      <c r="L4" s="324" t="str">
+      <c r="L4" s="323" t="str">
         <f>Data!H36</f>
         <v/>
       </c>
-      <c r="M4" s="324" t="str">
+      <c r="M4" s="323" t="str">
         <f>Data!I36</f>
         <v/>
       </c>
-      <c r="N4" s="324" t="str">
+      <c r="N4" s="323" t="str">
         <f>Data!J36</f>
         <v/>
       </c>
-      <c r="O4" s="324" t="str">
+      <c r="O4" s="323" t="str">
         <f>Data!K36</f>
         <v/>
       </c>
-      <c r="P4" s="324" t="str">
+      <c r="P4" s="323" t="str">
         <f>Data!L36</f>
         <v/>
       </c>
-      <c r="Q4" s="324" t="str">
+      <c r="Q4" s="323" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -9567,52 +9638,52 @@
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="319">
+      <c r="C5" s="318">
         <f>C25</f>
         <v>0</v>
       </c>
       <c r="E5" s="268"/>
-      <c r="G5" s="324">
+      <c r="G5" s="323">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>0</v>
       </c>
-      <c r="H5" s="324" t="str">
+      <c r="H5" s="323" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I5" s="324" t="str">
+      <c r="I5" s="323" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J5" s="324" t="str">
+      <c r="J5" s="323" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K5" s="324" t="str">
+      <c r="K5" s="323" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L5" s="324" t="str">
+      <c r="L5" s="323" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="M5" s="324" t="str">
+      <c r="M5" s="323" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="N5" s="324" t="str">
+      <c r="N5" s="323" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="O5" s="324" t="str">
+      <c r="O5" s="323" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P5" s="324" t="str">
+      <c r="P5" s="323" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q5" s="324" t="str">
+      <c r="Q5" s="323" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9622,52 +9693,52 @@
       <c r="B6" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="320">
+      <c r="C6" s="319">
         <f>C4+C5</f>
         <v>61890</v>
       </c>
       <c r="E6" s="268"/>
-      <c r="G6" s="320">
+      <c r="G6" s="319">
         <f>IF(G4="","",G4+G5)</f>
         <v>61890</v>
       </c>
-      <c r="H6" s="320" t="str">
+      <c r="H6" s="319" t="str">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v/>
       </c>
-      <c r="I6" s="320" t="str">
+      <c r="I6" s="319" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J6" s="320" t="str">
+      <c r="J6" s="319" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K6" s="320" t="str">
+      <c r="K6" s="319" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L6" s="320" t="str">
+      <c r="L6" s="319" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M6" s="320" t="str">
+      <c r="M6" s="319" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="N6" s="320" t="str">
+      <c r="N6" s="319" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O6" s="320" t="str">
+      <c r="O6" s="319" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P6" s="320" t="str">
+      <c r="P6" s="319" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Q6" s="320" t="str">
+      <c r="Q6" s="319" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -9677,52 +9748,52 @@
       <c r="B7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="319">
+      <c r="C7" s="318">
         <f>C35</f>
         <v>-62611</v>
       </c>
       <c r="E7" s="268"/>
-      <c r="G7" s="319">
+      <c r="G7" s="318">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-62611</v>
       </c>
-      <c r="H7" s="319" t="str">
+      <c r="H7" s="318" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I7" s="319" t="str">
+      <c r="I7" s="318" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J7" s="319" t="str">
+      <c r="J7" s="318" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K7" s="319" t="str">
+      <c r="K7" s="318" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L7" s="319" t="str">
+      <c r="L7" s="318" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M7" s="319" t="str">
+      <c r="M7" s="318" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="N7" s="319" t="str">
+      <c r="N7" s="318" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O7" s="319" t="str">
+      <c r="O7" s="318" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P7" s="319" t="str">
+      <c r="P7" s="318" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q7" s="319" t="str">
+      <c r="Q7" s="318" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -9732,54 +9803,54 @@
       <c r="B8" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="321">
+      <c r="C8" s="320">
         <f>C6+C7</f>
         <v>-721</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="274"/>
       <c r="F8" s="59"/>
-      <c r="G8" s="320">
+      <c r="G8" s="319">
         <f>IF(G$4="","",G6+G7)</f>
         <v>-721</v>
       </c>
-      <c r="H8" s="320" t="str">
+      <c r="H8" s="319" t="str">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v/>
       </c>
-      <c r="I8" s="320" t="str">
+      <c r="I8" s="319" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="J8" s="320" t="str">
+      <c r="J8" s="319" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K8" s="320" t="str">
+      <c r="K8" s="319" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="L8" s="320" t="str">
+      <c r="L8" s="319" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M8" s="320" t="str">
+      <c r="M8" s="319" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N8" s="320" t="str">
+      <c r="N8" s="319" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O8" s="320" t="str">
+      <c r="O8" s="319" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P8" s="320" t="str">
+      <c r="P8" s="319" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Q8" s="320" t="str">
+      <c r="Q8" s="319" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -9789,52 +9860,52 @@
       <c r="B9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="319">
+      <c r="C9" s="318">
         <f>BS!$G$39*BS!D58</f>
         <v>0</v>
       </c>
       <c r="E9" s="268"/>
-      <c r="G9" s="319">
+      <c r="G9" s="318">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="319" t="str">
+      <c r="H9" s="318" t="str">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v/>
       </c>
-      <c r="I9" s="319" t="str">
+      <c r="I9" s="318" t="str">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v/>
       </c>
-      <c r="J9" s="319" t="str">
+      <c r="J9" s="318" t="str">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v/>
       </c>
-      <c r="K9" s="319" t="str">
+      <c r="K9" s="318" t="str">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v/>
       </c>
-      <c r="L9" s="319" t="str">
+      <c r="L9" s="318" t="str">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v/>
       </c>
-      <c r="M9" s="319" t="str">
+      <c r="M9" s="318" t="str">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v/>
       </c>
-      <c r="N9" s="319" t="str">
+      <c r="N9" s="318" t="str">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v/>
       </c>
-      <c r="O9" s="319" t="str">
+      <c r="O9" s="318" t="str">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v/>
       </c>
-      <c r="P9" s="319" t="str">
+      <c r="P9" s="318" t="str">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v/>
       </c>
-      <c r="Q9" s="319" t="str">
+      <c r="Q9" s="318" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -9844,52 +9915,52 @@
       <c r="B10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="319">
+      <c r="C10" s="318">
         <f>-C4*C78</f>
         <v>0</v>
       </c>
       <c r="E10" s="268"/>
-      <c r="G10" s="319">
+      <c r="G10" s="318">
         <f>Data!C62</f>
         <v>0</v>
       </c>
-      <c r="H10" s="319" t="str">
+      <c r="H10" s="318" t="str">
         <f>Data!D62</f>
         <v/>
       </c>
-      <c r="I10" s="319" t="str">
+      <c r="I10" s="318" t="str">
         <f>Data!E62</f>
         <v/>
       </c>
-      <c r="J10" s="319" t="str">
+      <c r="J10" s="318" t="str">
         <f>Data!F62</f>
         <v/>
       </c>
-      <c r="K10" s="319" t="str">
+      <c r="K10" s="318" t="str">
         <f>Data!G62</f>
         <v/>
       </c>
-      <c r="L10" s="319" t="str">
+      <c r="L10" s="318" t="str">
         <f>Data!H62</f>
         <v/>
       </c>
-      <c r="M10" s="319" t="str">
+      <c r="M10" s="318" t="str">
         <f>Data!I62</f>
         <v/>
       </c>
-      <c r="N10" s="319" t="str">
+      <c r="N10" s="318" t="str">
         <f>Data!J62</f>
         <v/>
       </c>
-      <c r="O10" s="319" t="str">
+      <c r="O10" s="318" t="str">
         <f>Data!K62</f>
         <v/>
       </c>
-      <c r="P10" s="319" t="str">
+      <c r="P10" s="318" t="str">
         <f>Data!L62</f>
         <v/>
       </c>
-      <c r="Q10" s="319" t="str">
+      <c r="Q10" s="318" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -9899,54 +9970,54 @@
       <c r="B11" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="322">
+      <c r="C11" s="321">
         <f>C63</f>
         <v>0</v>
       </c>
       <c r="D11" s="168"/>
       <c r="E11" s="267"/>
       <c r="F11" s="168"/>
-      <c r="G11" s="325">
+      <c r="G11" s="324">
         <f>G61</f>
         <v>0</v>
       </c>
-      <c r="H11" s="325" t="str">
+      <c r="H11" s="324" t="str">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v/>
       </c>
-      <c r="I11" s="325" t="str">
+      <c r="I11" s="324" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J11" s="325" t="str">
+      <c r="J11" s="324" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="K11" s="325" t="str">
+      <c r="K11" s="324" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="L11" s="325" t="str">
+      <c r="L11" s="324" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="M11" s="325" t="str">
+      <c r="M11" s="324" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N11" s="325" t="str">
+      <c r="N11" s="324" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="O11" s="325" t="str">
+      <c r="O11" s="324" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="P11" s="325" t="str">
+      <c r="P11" s="324" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q11" s="325" t="str">
+      <c r="Q11" s="324" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -9956,52 +10027,52 @@
       <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="319">
+      <c r="C12" s="318">
         <f>C50</f>
         <v>0</v>
       </c>
       <c r="E12" s="268"/>
-      <c r="G12" s="319">
+      <c r="G12" s="318">
         <f>G50</f>
         <v>-195728</v>
       </c>
-      <c r="H12" s="319" t="str">
+      <c r="H12" s="318" t="str">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v/>
       </c>
-      <c r="I12" s="319" t="str">
+      <c r="I12" s="318" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="J12" s="319" t="str">
+      <c r="J12" s="318" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="K12" s="319" t="str">
+      <c r="K12" s="318" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="L12" s="319" t="str">
+      <c r="L12" s="318" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="M12" s="319" t="str">
+      <c r="M12" s="318" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="N12" s="319" t="str">
+      <c r="N12" s="318" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O12" s="319" t="str">
+      <c r="O12" s="318" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="P12" s="319" t="str">
+      <c r="P12" s="318" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q12" s="319" t="str">
+      <c r="Q12" s="318" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10011,52 +10082,52 @@
       <c r="B13" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="320">
+      <c r="C13" s="319">
         <f>SUM(C8:C12)</f>
         <v>-721</v>
       </c>
       <c r="E13" s="268"/>
-      <c r="G13" s="320">
+      <c r="G13" s="319">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>-196449</v>
       </c>
-      <c r="H13" s="320" t="str">
+      <c r="H13" s="319" t="str">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v/>
       </c>
-      <c r="I13" s="320" t="str">
+      <c r="I13" s="319" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J13" s="320" t="str">
+      <c r="J13" s="319" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K13" s="320" t="str">
+      <c r="K13" s="319" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="L13" s="320" t="str">
+      <c r="L13" s="319" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M13" s="320" t="str">
+      <c r="M13" s="319" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N13" s="320" t="str">
+      <c r="N13" s="319" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="O13" s="320" t="str">
+      <c r="O13" s="319" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P13" s="320" t="str">
+      <c r="P13" s="319" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q13" s="320" t="str">
+      <c r="Q13" s="319" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10066,52 +10137,52 @@
       <c r="B14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="319">
+      <c r="C14" s="318">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>180.25</v>
       </c>
       <c r="E14" s="268"/>
-      <c r="G14" s="319">
+      <c r="G14" s="318">
         <f>Data!C46</f>
         <v>-9629</v>
       </c>
-      <c r="H14" s="319" t="str">
+      <c r="H14" s="318" t="str">
         <f>Data!D46</f>
         <v/>
       </c>
-      <c r="I14" s="319" t="str">
+      <c r="I14" s="318" t="str">
         <f>Data!E46</f>
         <v/>
       </c>
-      <c r="J14" s="319" t="str">
+      <c r="J14" s="318" t="str">
         <f>Data!F46</f>
         <v/>
       </c>
-      <c r="K14" s="319" t="str">
+      <c r="K14" s="318" t="str">
         <f>Data!G46</f>
         <v/>
       </c>
-      <c r="L14" s="319" t="str">
+      <c r="L14" s="318" t="str">
         <f>Data!H46</f>
         <v/>
       </c>
-      <c r="M14" s="319" t="str">
+      <c r="M14" s="318" t="str">
         <f>Data!I46</f>
         <v/>
       </c>
-      <c r="N14" s="319" t="str">
+      <c r="N14" s="318" t="str">
         <f>Data!J46</f>
         <v/>
       </c>
-      <c r="O14" s="319" t="str">
+      <c r="O14" s="318" t="str">
         <f>Data!K46</f>
         <v/>
       </c>
-      <c r="P14" s="319" t="str">
+      <c r="P14" s="318" t="str">
         <f>Data!L46</f>
         <v/>
       </c>
-      <c r="Q14" s="319" t="str">
+      <c r="Q14" s="318" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -10121,54 +10192,54 @@
       <c r="B15" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="319">
+      <c r="C15" s="318">
         <f>-C4*C83</f>
         <v>0</v>
       </c>
       <c r="D15" s="60"/>
       <c r="E15" s="275"/>
       <c r="F15" s="60"/>
-      <c r="G15" s="324">
+      <c r="G15" s="323">
         <f>Data!C48</f>
         <v>-286</v>
       </c>
-      <c r="H15" s="324" t="str">
+      <c r="H15" s="323" t="str">
         <f>Data!D48</f>
         <v/>
       </c>
-      <c r="I15" s="324" t="str">
+      <c r="I15" s="323" t="str">
         <f>Data!E48</f>
         <v/>
       </c>
-      <c r="J15" s="324" t="str">
+      <c r="J15" s="323" t="str">
         <f>Data!F48</f>
         <v/>
       </c>
-      <c r="K15" s="324" t="str">
+      <c r="K15" s="323" t="str">
         <f>Data!G48</f>
         <v/>
       </c>
-      <c r="L15" s="324" t="str">
+      <c r="L15" s="323" t="str">
         <f>Data!H48</f>
         <v/>
       </c>
-      <c r="M15" s="324" t="str">
+      <c r="M15" s="323" t="str">
         <f>Data!I48</f>
         <v/>
       </c>
-      <c r="N15" s="324" t="str">
+      <c r="N15" s="323" t="str">
         <f>Data!J48</f>
         <v/>
       </c>
-      <c r="O15" s="324" t="str">
+      <c r="O15" s="323" t="str">
         <f>Data!K48</f>
         <v/>
       </c>
-      <c r="P15" s="324" t="str">
+      <c r="P15" s="323" t="str">
         <f>Data!L48</f>
         <v/>
       </c>
-      <c r="Q15" s="324" t="str">
+      <c r="Q15" s="323" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -10178,54 +10249,54 @@
       <c r="B16" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="323">
+      <c r="C16" s="322">
         <f>SUM(C13:C15)</f>
         <v>-540.75</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
-      <c r="G16" s="320">
+      <c r="G16" s="319">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>-206364</v>
       </c>
-      <c r="H16" s="320" t="str">
+      <c r="H16" s="319" t="str">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v/>
       </c>
-      <c r="I16" s="320" t="str">
+      <c r="I16" s="319" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J16" s="320" t="str">
+      <c r="J16" s="319" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="K16" s="320" t="str">
+      <c r="K16" s="319" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="L16" s="320" t="str">
+      <c r="L16" s="319" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="M16" s="320" t="str">
+      <c r="M16" s="319" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N16" s="320" t="str">
+      <c r="N16" s="319" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="O16" s="320" t="str">
+      <c r="O16" s="319" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P16" s="320" t="str">
+      <c r="P16" s="319" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="Q16" s="320" t="str">
+      <c r="Q16" s="319" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -10235,7 +10306,7 @@
       <c r="B17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="319">
+      <c r="C17" s="318">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
@@ -10244,24 +10315,24 @@
         <v>334</v>
       </c>
       <c r="F17" s="58"/>
-      <c r="G17" s="326"/>
-      <c r="H17" s="326"/>
-      <c r="I17" s="326"/>
-      <c r="J17" s="326"/>
-      <c r="K17" s="326"/>
-      <c r="L17" s="326"/>
-      <c r="M17" s="326"/>
-      <c r="N17" s="326"/>
-      <c r="O17" s="326"/>
-      <c r="P17" s="326"/>
-      <c r="Q17" s="326"/>
+      <c r="G17" s="325"/>
+      <c r="H17" s="325"/>
+      <c r="I17" s="325"/>
+      <c r="J17" s="325"/>
+      <c r="K17" s="325"/>
+      <c r="L17" s="325"/>
+      <c r="M17" s="325"/>
+      <c r="N17" s="325"/>
+      <c r="O17" s="325"/>
+      <c r="P17" s="325"/>
+      <c r="Q17" s="325"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="319">
+      <c r="C18" s="318">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
@@ -10269,71 +10340,71 @@
         <v>335</v>
       </c>
       <c r="F18" s="58"/>
-      <c r="G18" s="327"/>
-      <c r="H18" s="327"/>
-      <c r="I18" s="327"/>
-      <c r="J18" s="327"/>
-      <c r="K18" s="327"/>
-      <c r="L18" s="327"/>
-      <c r="M18" s="327"/>
-      <c r="N18" s="327"/>
-      <c r="O18" s="327"/>
-      <c r="P18" s="327"/>
-      <c r="Q18" s="327"/>
+      <c r="G18" s="326"/>
+      <c r="H18" s="326"/>
+      <c r="I18" s="326"/>
+      <c r="J18" s="326"/>
+      <c r="K18" s="326"/>
+      <c r="L18" s="326"/>
+      <c r="M18" s="326"/>
+      <c r="N18" s="326"/>
+      <c r="O18" s="326"/>
+      <c r="P18" s="326"/>
+      <c r="Q18" s="326"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="320">
+      <c r="C19" s="319">
         <f>C16+C17</f>
         <v>-540.75</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="325">
+      <c r="G19" s="324">
         <f>IF(G$4="","",G16+G17)</f>
         <v>-206364</v>
       </c>
-      <c r="H19" s="325" t="str">
+      <c r="H19" s="324" t="str">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v/>
       </c>
-      <c r="I19" s="325" t="str">
+      <c r="I19" s="324" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J19" s="325" t="str">
+      <c r="J19" s="324" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K19" s="325" t="str">
+      <c r="K19" s="324" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="L19" s="325" t="str">
+      <c r="L19" s="324" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="M19" s="325" t="str">
+      <c r="M19" s="324" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="N19" s="325" t="str">
+      <c r="N19" s="324" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O19" s="325" t="str">
+      <c r="O19" s="324" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="P19" s="325" t="str">
+      <c r="P19" s="324" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="Q19" s="325" t="str">
+      <c r="Q19" s="324" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -10406,54 +10477,54 @@
       <c r="B23" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="328">
+      <c r="C23" s="327">
         <f>-C4*C28</f>
         <v>0</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="267"/>
       <c r="F23" s="58"/>
-      <c r="G23" s="324">
+      <c r="G23" s="323">
         <f>Data!C37</f>
         <v>0</v>
       </c>
-      <c r="H23" s="324" t="str">
+      <c r="H23" s="323" t="str">
         <f>Data!D37</f>
         <v/>
       </c>
-      <c r="I23" s="324" t="str">
+      <c r="I23" s="323" t="str">
         <f>Data!E37</f>
         <v/>
       </c>
-      <c r="J23" s="324" t="str">
+      <c r="J23" s="323" t="str">
         <f>Data!F37</f>
         <v/>
       </c>
-      <c r="K23" s="324" t="str">
+      <c r="K23" s="323" t="str">
         <f>Data!G37</f>
         <v/>
       </c>
-      <c r="L23" s="324" t="str">
+      <c r="L23" s="323" t="str">
         <f>Data!H37</f>
         <v/>
       </c>
-      <c r="M23" s="324" t="str">
+      <c r="M23" s="323" t="str">
         <f>Data!I37</f>
         <v/>
       </c>
-      <c r="N23" s="324" t="str">
+      <c r="N23" s="323" t="str">
         <f>Data!J37</f>
         <v/>
       </c>
-      <c r="O23" s="324" t="str">
+      <c r="O23" s="323" t="str">
         <f>Data!K37</f>
         <v/>
       </c>
-      <c r="P23" s="324" t="str">
+      <c r="P23" s="323" t="str">
         <f>Data!L37</f>
         <v/>
       </c>
-      <c r="Q23" s="324" t="str">
+      <c r="Q23" s="323" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -10463,54 +10534,54 @@
       <c r="B24" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="319">
+      <c r="C24" s="318">
         <f>-C4*C29</f>
         <v>0</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="265"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="324">
+      <c r="G24" s="323">
         <f>Data!C40</f>
         <v>0</v>
       </c>
-      <c r="H24" s="324" t="str">
+      <c r="H24" s="323" t="str">
         <f>Data!D40</f>
         <v/>
       </c>
-      <c r="I24" s="324" t="str">
+      <c r="I24" s="323" t="str">
         <f>Data!E40</f>
         <v/>
       </c>
-      <c r="J24" s="324" t="str">
+      <c r="J24" s="323" t="str">
         <f>Data!F40</f>
         <v/>
       </c>
-      <c r="K24" s="324" t="str">
+      <c r="K24" s="323" t="str">
         <f>Data!G40</f>
         <v/>
       </c>
-      <c r="L24" s="324" t="str">
+      <c r="L24" s="323" t="str">
         <f>Data!H40</f>
         <v/>
       </c>
-      <c r="M24" s="324" t="str">
+      <c r="M24" s="323" t="str">
         <f>Data!I40</f>
         <v/>
       </c>
-      <c r="N24" s="324" t="str">
+      <c r="N24" s="323" t="str">
         <f>Data!J40</f>
         <v/>
       </c>
-      <c r="O24" s="324" t="str">
+      <c r="O24" s="323" t="str">
         <f>Data!K40</f>
         <v/>
       </c>
-      <c r="P24" s="324" t="str">
+      <c r="P24" s="323" t="str">
         <f>Data!L40</f>
         <v/>
       </c>
-      <c r="Q24" s="324" t="str">
+      <c r="Q24" s="323" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -10520,54 +10591,54 @@
       <c r="B25" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="320">
+      <c r="C25" s="319">
         <f>C23+C24</f>
         <v>0</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="273"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="320">
+      <c r="G25" s="319">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="320" t="str">
+      <c r="H25" s="319" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="I25" s="320" t="str">
+      <c r="I25" s="319" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="J25" s="320" t="str">
+      <c r="J25" s="319" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="K25" s="320" t="str">
+      <c r="K25" s="319" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="L25" s="320" t="str">
+      <c r="L25" s="319" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="M25" s="320" t="str">
+      <c r="M25" s="319" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="N25" s="320" t="str">
+      <c r="N25" s="319" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O25" s="320" t="str">
+      <c r="O25" s="319" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="P25" s="320" t="str">
+      <c r="P25" s="319" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Q25" s="320" t="str">
+      <c r="Q25" s="319" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -10773,54 +10844,54 @@
       <c r="B33" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="329">
+      <c r="C33" s="328">
         <f>AVERAGE(G33:J33)</f>
         <v>-62611</v>
       </c>
       <c r="E33" s="266" t="s">
         <v>336</v>
       </c>
-      <c r="G33" s="319">
+      <c r="G33" s="318">
         <f>Data!C41</f>
         <v>-62611</v>
       </c>
-      <c r="H33" s="319" t="str">
+      <c r="H33" s="318" t="str">
         <f>Data!D41</f>
         <v/>
       </c>
-      <c r="I33" s="319" t="str">
+      <c r="I33" s="318" t="str">
         <f>Data!E41</f>
         <v/>
       </c>
-      <c r="J33" s="319" t="str">
+      <c r="J33" s="318" t="str">
         <f>Data!F41</f>
         <v/>
       </c>
-      <c r="K33" s="319" t="str">
+      <c r="K33" s="318" t="str">
         <f>Data!G41</f>
         <v/>
       </c>
-      <c r="L33" s="319" t="str">
+      <c r="L33" s="318" t="str">
         <f>Data!H41</f>
         <v/>
       </c>
-      <c r="M33" s="319" t="str">
+      <c r="M33" s="318" t="str">
         <f>Data!I41</f>
         <v/>
       </c>
-      <c r="N33" s="319" t="str">
+      <c r="N33" s="318" t="str">
         <f>Data!J41</f>
         <v/>
       </c>
-      <c r="O33" s="319" t="str">
+      <c r="O33" s="318" t="str">
         <f>Data!K41</f>
         <v/>
       </c>
-      <c r="P33" s="319" t="str">
+      <c r="P33" s="318" t="str">
         <f>Data!L41</f>
         <v/>
       </c>
-      <c r="Q33" s="319" t="str">
+      <c r="Q33" s="318" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -10830,7 +10901,7 @@
       <c r="B34" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="329">
+      <c r="C34" s="328">
         <f>AVERAGE(G34:J34)</f>
         <v>0</v>
       </c>
@@ -10839,47 +10910,47 @@
         <v>336</v>
       </c>
       <c r="F34" s="58"/>
-      <c r="G34" s="324">
+      <c r="G34" s="323">
         <f>Data!C42</f>
         <v>0</v>
       </c>
-      <c r="H34" s="324" t="str">
+      <c r="H34" s="323" t="str">
         <f>Data!D42</f>
         <v/>
       </c>
-      <c r="I34" s="324" t="str">
+      <c r="I34" s="323" t="str">
         <f>Data!E42</f>
         <v/>
       </c>
-      <c r="J34" s="324" t="str">
+      <c r="J34" s="323" t="str">
         <f>Data!F42</f>
         <v/>
       </c>
-      <c r="K34" s="324" t="str">
+      <c r="K34" s="323" t="str">
         <f>Data!G42</f>
         <v/>
       </c>
-      <c r="L34" s="324" t="str">
+      <c r="L34" s="323" t="str">
         <f>Data!H42</f>
         <v/>
       </c>
-      <c r="M34" s="324" t="str">
+      <c r="M34" s="323" t="str">
         <f>Data!I42</f>
         <v/>
       </c>
-      <c r="N34" s="324" t="str">
+      <c r="N34" s="323" t="str">
         <f>Data!J42</f>
         <v/>
       </c>
-      <c r="O34" s="324" t="str">
+      <c r="O34" s="323" t="str">
         <f>Data!K42</f>
         <v/>
       </c>
-      <c r="P34" s="324" t="str">
+      <c r="P34" s="323" t="str">
         <f>Data!L42</f>
         <v/>
       </c>
-      <c r="Q34" s="324" t="str">
+      <c r="Q34" s="323" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -10889,54 +10960,54 @@
       <c r="B35" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="320">
+      <c r="C35" s="319">
         <f>C33+C34</f>
         <v>-62611</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="267"/>
       <c r="F35" s="58"/>
-      <c r="G35" s="320">
+      <c r="G35" s="319">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-62611</v>
       </c>
-      <c r="H35" s="320" t="str">
+      <c r="H35" s="319" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="I35" s="320" t="str">
+      <c r="I35" s="319" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="J35" s="320" t="str">
+      <c r="J35" s="319" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="K35" s="320" t="str">
+      <c r="K35" s="319" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L35" s="320" t="str">
+      <c r="L35" s="319" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="M35" s="320" t="str">
+      <c r="M35" s="319" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="N35" s="320" t="str">
+      <c r="N35" s="319" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="O35" s="320" t="str">
+      <c r="O35" s="319" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="P35" s="320" t="str">
+      <c r="P35" s="319" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="Q35" s="320" t="str">
+      <c r="Q35" s="319" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -11230,52 +11301,52 @@
       <c r="B47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="319">
+      <c r="C47" s="318">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>0</v>
       </c>
       <c r="E47" s="268"/>
-      <c r="G47" s="319">
+      <c r="G47" s="318">
         <f>Data!C51</f>
         <v>-195728</v>
       </c>
-      <c r="H47" s="319" t="str">
+      <c r="H47" s="318" t="str">
         <f>Data!D51</f>
         <v/>
       </c>
-      <c r="I47" s="319" t="str">
+      <c r="I47" s="318" t="str">
         <f>Data!E51</f>
         <v/>
       </c>
-      <c r="J47" s="319" t="str">
+      <c r="J47" s="318" t="str">
         <f>Data!F51</f>
         <v/>
       </c>
-      <c r="K47" s="319" t="str">
+      <c r="K47" s="318" t="str">
         <f>Data!G51</f>
         <v/>
       </c>
-      <c r="L47" s="319" t="str">
+      <c r="L47" s="318" t="str">
         <f>Data!H51</f>
         <v/>
       </c>
-      <c r="M47" s="319" t="str">
+      <c r="M47" s="318" t="str">
         <f>Data!I51</f>
         <v/>
       </c>
-      <c r="N47" s="319" t="str">
+      <c r="N47" s="318" t="str">
         <f>Data!J51</f>
         <v/>
       </c>
-      <c r="O47" s="319" t="str">
+      <c r="O47" s="318" t="str">
         <f>Data!K51</f>
         <v/>
       </c>
-      <c r="P47" s="319" t="str">
+      <c r="P47" s="318" t="str">
         <f>Data!L51</f>
         <v/>
       </c>
-      <c r="Q47" s="319" t="str">
+      <c r="Q47" s="318" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -11285,52 +11356,52 @@
       <c r="B48" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="C48" s="319">
+      <c r="C48" s="318">
         <f>BS!D75*C53</f>
         <v>0</v>
       </c>
       <c r="E48" s="268"/>
-      <c r="G48" s="328">
+      <c r="G48" s="327">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="328" t="str">
+      <c r="H48" s="327" t="str">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v/>
       </c>
-      <c r="I48" s="328" t="str">
+      <c r="I48" s="327" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J48" s="328" t="str">
+      <c r="J48" s="327" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="K48" s="328" t="str">
+      <c r="K48" s="327" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="L48" s="328" t="str">
+      <c r="L48" s="327" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M48" s="328" t="str">
+      <c r="M48" s="327" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="N48" s="328" t="str">
+      <c r="N48" s="327" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="O48" s="328" t="str">
+      <c r="O48" s="327" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="P48" s="328" t="str">
+      <c r="P48" s="327" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="328" t="str">
+      <c r="Q48" s="327" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -11340,54 +11411,54 @@
       <c r="B49" s="287" t="s">
         <v>345</v>
       </c>
-      <c r="C49" s="330">
+      <c r="C49" s="329">
         <f>BS!$C$66*C53</f>
         <v>0</v>
       </c>
       <c r="D49" s="288"/>
       <c r="E49" s="289"/>
       <c r="F49" s="288"/>
-      <c r="G49" s="330">
+      <c r="G49" s="329">
         <f>Data!C52</f>
         <v>343835</v>
       </c>
-      <c r="H49" s="330" t="str">
+      <c r="H49" s="329" t="str">
         <f>Data!D52</f>
         <v/>
       </c>
-      <c r="I49" s="330" t="str">
+      <c r="I49" s="329" t="str">
         <f>Data!E52</f>
         <v/>
       </c>
-      <c r="J49" s="330" t="str">
+      <c r="J49" s="329" t="str">
         <f>Data!F52</f>
         <v/>
       </c>
-      <c r="K49" s="330" t="str">
+      <c r="K49" s="329" t="str">
         <f>Data!G52</f>
         <v/>
       </c>
-      <c r="L49" s="330" t="str">
+      <c r="L49" s="329" t="str">
         <f>Data!H52</f>
         <v/>
       </c>
-      <c r="M49" s="330" t="str">
+      <c r="M49" s="329" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N49" s="330" t="str">
+      <c r="N49" s="329" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="330" t="str">
+      <c r="O49" s="329" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="330" t="str">
+      <c r="P49" s="329" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="330" t="str">
+      <c r="Q49" s="329" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11397,52 +11468,52 @@
       <c r="B50" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="320">
+      <c r="C50" s="319">
         <f>C47+C48</f>
         <v>0</v>
       </c>
       <c r="E50" s="268"/>
-      <c r="G50" s="320">
+      <c r="G50" s="319">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-195728</v>
       </c>
-      <c r="H50" s="320" t="str">
+      <c r="H50" s="319" t="str">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v/>
       </c>
-      <c r="I50" s="320" t="str">
+      <c r="I50" s="319" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="J50" s="320" t="str">
+      <c r="J50" s="319" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="K50" s="320" t="str">
+      <c r="K50" s="319" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="L50" s="320" t="str">
+      <c r="L50" s="319" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="M50" s="320" t="str">
+      <c r="M50" s="319" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="N50" s="320" t="str">
+      <c r="N50" s="319" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="O50" s="320" t="str">
+      <c r="O50" s="319" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="P50" s="320" t="str">
+      <c r="P50" s="319" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="Q50" s="320" t="str">
+      <c r="Q50" s="319" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -11588,52 +11659,52 @@
       <c r="B58" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="319">
+      <c r="C58" s="318">
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="268"/>
-      <c r="G58" s="319">
+      <c r="G58" s="318">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="319" t="str">
+      <c r="H58" s="318" t="str">
         <f>Data!D56</f>
         <v/>
       </c>
-      <c r="I58" s="319" t="str">
+      <c r="I58" s="318" t="str">
         <f>Data!E56</f>
         <v/>
       </c>
-      <c r="J58" s="319" t="str">
+      <c r="J58" s="318" t="str">
         <f>Data!F56</f>
         <v/>
       </c>
-      <c r="K58" s="319" t="str">
+      <c r="K58" s="318" t="str">
         <f>Data!G56</f>
         <v/>
       </c>
-      <c r="L58" s="319" t="str">
+      <c r="L58" s="318" t="str">
         <f>Data!H56</f>
         <v/>
       </c>
-      <c r="M58" s="319" t="str">
+      <c r="M58" s="318" t="str">
         <f>Data!I56</f>
         <v/>
       </c>
-      <c r="N58" s="319" t="str">
+      <c r="N58" s="318" t="str">
         <f>Data!J56</f>
         <v/>
       </c>
-      <c r="O58" s="319" t="str">
+      <c r="O58" s="318" t="str">
         <f>Data!K56</f>
         <v/>
       </c>
-      <c r="P58" s="319" t="str">
+      <c r="P58" s="318" t="str">
         <f>Data!L56</f>
         <v/>
       </c>
-      <c r="Q58" s="319" t="str">
+      <c r="Q58" s="318" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -11643,52 +11714,52 @@
       <c r="B59" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C59" s="319">
+      <c r="C59" s="318">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
       <c r="E59" s="268"/>
-      <c r="G59" s="319">
+      <c r="G59" s="318">
         <f>Data!C55</f>
         <v>0</v>
       </c>
-      <c r="H59" s="319" t="str">
+      <c r="H59" s="318" t="str">
         <f>Data!D55</f>
         <v/>
       </c>
-      <c r="I59" s="319" t="str">
+      <c r="I59" s="318" t="str">
         <f>Data!E55</f>
         <v/>
       </c>
-      <c r="J59" s="319" t="str">
+      <c r="J59" s="318" t="str">
         <f>Data!F55</f>
         <v/>
       </c>
-      <c r="K59" s="319" t="str">
+      <c r="K59" s="318" t="str">
         <f>Data!G55</f>
         <v/>
       </c>
-      <c r="L59" s="319" t="str">
+      <c r="L59" s="318" t="str">
         <f>Data!H55</f>
         <v/>
       </c>
-      <c r="M59" s="319" t="str">
+      <c r="M59" s="318" t="str">
         <f>Data!I55</f>
         <v/>
       </c>
-      <c r="N59" s="319" t="str">
+      <c r="N59" s="318" t="str">
         <f>Data!J55</f>
         <v/>
       </c>
-      <c r="O59" s="319" t="str">
+      <c r="O59" s="318" t="str">
         <f>Data!K55</f>
         <v/>
       </c>
-      <c r="P59" s="319" t="str">
+      <c r="P59" s="318" t="str">
         <f>Data!L55</f>
         <v/>
       </c>
-      <c r="Q59" s="319" t="str">
+      <c r="Q59" s="318" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -11698,52 +11769,52 @@
       <c r="B60" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C60" s="319">
+      <c r="C60" s="318">
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="268"/>
-      <c r="G60" s="319">
+      <c r="G60" s="318">
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="319" t="str">
+      <c r="H60" s="318" t="str">
         <f>Data!D57</f>
         <v/>
       </c>
-      <c r="I60" s="319" t="str">
+      <c r="I60" s="318" t="str">
         <f>Data!E57</f>
         <v/>
       </c>
-      <c r="J60" s="319" t="str">
+      <c r="J60" s="318" t="str">
         <f>Data!F57</f>
         <v/>
       </c>
-      <c r="K60" s="319" t="str">
+      <c r="K60" s="318" t="str">
         <f>Data!G57</f>
         <v/>
       </c>
-      <c r="L60" s="319" t="str">
+      <c r="L60" s="318" t="str">
         <f>Data!H57</f>
         <v/>
       </c>
-      <c r="M60" s="319" t="str">
+      <c r="M60" s="318" t="str">
         <f>Data!I57</f>
         <v/>
       </c>
-      <c r="N60" s="319" t="str">
+      <c r="N60" s="318" t="str">
         <f>Data!J57</f>
         <v/>
       </c>
-      <c r="O60" s="319" t="str">
+      <c r="O60" s="318" t="str">
         <f>Data!K57</f>
         <v/>
       </c>
-      <c r="P60" s="319" t="str">
+      <c r="P60" s="318" t="str">
         <f>Data!L57</f>
         <v/>
       </c>
-      <c r="Q60" s="319" t="str">
+      <c r="Q60" s="318" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -11753,52 +11824,52 @@
       <c r="B61" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="320">
+      <c r="C61" s="319">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
       <c r="E61" s="268"/>
-      <c r="G61" s="320">
+      <c r="G61" s="319">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
       </c>
-      <c r="H61" s="320" t="str">
+      <c r="H61" s="319" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="I61" s="320" t="str">
+      <c r="I61" s="319" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="J61" s="320" t="str">
+      <c r="J61" s="319" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="K61" s="320" t="str">
+      <c r="K61" s="319" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L61" s="320" t="str">
+      <c r="L61" s="319" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="M61" s="320" t="str">
+      <c r="M61" s="319" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="N61" s="320" t="str">
+      <c r="N61" s="319" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="O61" s="320" t="str">
+      <c r="O61" s="319" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="P61" s="320" t="str">
+      <c r="P61" s="319" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Q61" s="320" t="str">
+      <c r="Q61" s="319" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -11808,53 +11879,53 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="331">
+      <c r="C62" s="330">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
         <v>340</v>
       </c>
-      <c r="G62" s="319">
+      <c r="G62" s="318">
         <f>Data!C58</f>
         <v>-60266</v>
       </c>
-      <c r="H62" s="319" t="str">
+      <c r="H62" s="318" t="str">
         <f>Data!D58</f>
         <v/>
       </c>
-      <c r="I62" s="319" t="str">
+      <c r="I62" s="318" t="str">
         <f>Data!E58</f>
         <v/>
       </c>
-      <c r="J62" s="319" t="str">
+      <c r="J62" s="318" t="str">
         <f>Data!F58</f>
         <v/>
       </c>
-      <c r="K62" s="319" t="str">
+      <c r="K62" s="318" t="str">
         <f>Data!G58</f>
         <v/>
       </c>
-      <c r="L62" s="319" t="str">
+      <c r="L62" s="318" t="str">
         <f>Data!H58</f>
         <v/>
       </c>
-      <c r="M62" s="319" t="str">
+      <c r="M62" s="318" t="str">
         <f>Data!I58</f>
         <v/>
       </c>
-      <c r="N62" s="319" t="str">
+      <c r="N62" s="318" t="str">
         <f>Data!J58</f>
         <v/>
       </c>
-      <c r="O62" s="319" t="str">
+      <c r="O62" s="318" t="str">
         <f>Data!K58</f>
         <v/>
       </c>
-      <c r="P62" s="319" t="str">
+      <c r="P62" s="318" t="str">
         <f>Data!L58</f>
         <v/>
       </c>
-      <c r="Q62" s="319" t="str">
+      <c r="Q62" s="318" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -11864,52 +11935,52 @@
       <c r="B63" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C63" s="320">
+      <c r="C63" s="319">
         <f>C61+C62</f>
         <v>0</v>
       </c>
       <c r="E63" s="268"/>
-      <c r="G63" s="320">
+      <c r="G63" s="319">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-60266</v>
       </c>
-      <c r="H63" s="320" t="str">
+      <c r="H63" s="319" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="I63" s="320" t="str">
+      <c r="I63" s="319" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="J63" s="320" t="str">
+      <c r="J63" s="319" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="K63" s="320" t="str">
+      <c r="K63" s="319" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="L63" s="320" t="str">
+      <c r="L63" s="319" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="M63" s="320" t="str">
+      <c r="M63" s="319" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="N63" s="320" t="str">
+      <c r="N63" s="319" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="O63" s="320" t="str">
+      <c r="O63" s="319" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="P63" s="320" t="str">
+      <c r="P63" s="319" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="Q63" s="320" t="str">
+      <c r="Q63" s="319" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -13284,54 +13355,54 @@
       <c r="B101" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="332">
+      <c r="C101" s="331">
         <f>BS!G32</f>
         <v>4</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="269"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="324">
+      <c r="G101" s="323">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>4</v>
       </c>
-      <c r="H101" s="324" t="str">
+      <c r="H101" s="323" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="I101" s="324" t="str">
+      <c r="I101" s="323" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="J101" s="324" t="str">
+      <c r="J101" s="323" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="K101" s="324" t="str">
+      <c r="K101" s="323" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="L101" s="324" t="str">
+      <c r="L101" s="323" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="M101" s="324" t="str">
+      <c r="M101" s="323" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="N101" s="324" t="str">
+      <c r="N101" s="323" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="O101" s="324" t="str">
+      <c r="O101" s="323" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="P101" s="324" t="str">
+      <c r="P101" s="323" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="Q101" s="324" t="str">
+      <c r="Q101" s="323" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -13341,54 +13412,54 @@
       <c r="B102" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="C102" s="333">
+      <c r="C102" s="332">
         <f>BS!C4</f>
         <v>0</v>
       </c>
       <c r="D102" s="89"/>
       <c r="E102" s="270"/>
       <c r="F102" s="89"/>
-      <c r="G102" s="334" t="str">
+      <c r="G102" s="333" t="str">
         <f>IF(G$4="","",Data!D77)</f>
         <v/>
       </c>
-      <c r="H102" s="334" t="str">
+      <c r="H102" s="333" t="str">
         <f>IF(H$4="","",Data!E77)</f>
         <v/>
       </c>
-      <c r="I102" s="334" t="str">
+      <c r="I102" s="333" t="str">
         <f>IF(I$4="","",Data!F77)</f>
         <v/>
       </c>
-      <c r="J102" s="334" t="str">
+      <c r="J102" s="333" t="str">
         <f>IF(J$4="","",Data!G77)</f>
         <v/>
       </c>
-      <c r="K102" s="334" t="str">
+      <c r="K102" s="333" t="str">
         <f>IF(K$4="","",Data!H77)</f>
         <v/>
       </c>
-      <c r="L102" s="334" t="str">
+      <c r="L102" s="333" t="str">
         <f>IF(L$4="","",Data!I77)</f>
         <v/>
       </c>
-      <c r="M102" s="334" t="str">
+      <c r="M102" s="333" t="str">
         <f>IF(M$4="","",Data!J77)</f>
         <v/>
       </c>
-      <c r="N102" s="334" t="str">
+      <c r="N102" s="333" t="str">
         <f>IF(N$4="","",Data!K77)</f>
         <v/>
       </c>
-      <c r="O102" s="334" t="str">
+      <c r="O102" s="333" t="str">
         <f>IF(O$4="","",Data!L77)</f>
         <v/>
       </c>
-      <c r="P102" s="334" t="str">
+      <c r="P102" s="333" t="str">
         <f>IF(P$4="","",Data!M77)</f>
         <v/>
       </c>
-      <c r="Q102" s="334" t="str">
+      <c r="Q102" s="333" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -13398,54 +13469,54 @@
       <c r="B103" s="93" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="333">
+      <c r="C103" s="332">
         <f>BS!C6+BS!C7</f>
         <v>0</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
-      <c r="G103" s="334" t="str">
+      <c r="G103" s="333" t="str">
         <f>IF(G$4="","",Data!D78)</f>
         <v/>
       </c>
-      <c r="H103" s="334" t="str">
+      <c r="H103" s="333" t="str">
         <f>IF(H$4="","",Data!E78)</f>
         <v/>
       </c>
-      <c r="I103" s="334" t="str">
+      <c r="I103" s="333" t="str">
         <f>IF(I$4="","",Data!F78)</f>
         <v/>
       </c>
-      <c r="J103" s="334" t="str">
+      <c r="J103" s="333" t="str">
         <f>IF(J$4="","",Data!G78)</f>
         <v/>
       </c>
-      <c r="K103" s="334" t="str">
+      <c r="K103" s="333" t="str">
         <f>IF(K$4="","",Data!H78)</f>
         <v/>
       </c>
-      <c r="L103" s="334" t="str">
+      <c r="L103" s="333" t="str">
         <f>IF(L$4="","",Data!I78)</f>
         <v/>
       </c>
-      <c r="M103" s="334" t="str">
+      <c r="M103" s="333" t="str">
         <f>IF(M$4="","",Data!J78)</f>
         <v/>
       </c>
-      <c r="N103" s="334" t="str">
+      <c r="N103" s="333" t="str">
         <f>IF(N$4="","",Data!K78)</f>
         <v/>
       </c>
-      <c r="O103" s="334" t="str">
+      <c r="O103" s="333" t="str">
         <f>IF(O$4="","",Data!L78)</f>
         <v/>
       </c>
-      <c r="P103" s="334" t="str">
+      <c r="P103" s="333" t="str">
         <f>IF(P$4="","",Data!M78)</f>
         <v/>
       </c>
-      <c r="Q103" s="334" t="str">
+      <c r="Q103" s="333" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
@@ -13455,54 +13526,54 @@
       <c r="B104" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C104" s="332">
+      <c r="C104" s="331">
         <f>BS!G30</f>
         <v>1</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="269"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="324">
+      <c r="G104" s="323">
         <f>Data!C79</f>
         <v>1</v>
       </c>
-      <c r="H104" s="324" t="str">
+      <c r="H104" s="323" t="str">
         <f>Data!D79</f>
         <v/>
       </c>
-      <c r="I104" s="324" t="str">
+      <c r="I104" s="323" t="str">
         <f>Data!E79</f>
         <v/>
       </c>
-      <c r="J104" s="324" t="str">
+      <c r="J104" s="323" t="str">
         <f>Data!F79</f>
         <v/>
       </c>
-      <c r="K104" s="324" t="str">
+      <c r="K104" s="323" t="str">
         <f>Data!G79</f>
         <v/>
       </c>
-      <c r="L104" s="324" t="str">
+      <c r="L104" s="323" t="str">
         <f>Data!H79</f>
         <v/>
       </c>
-      <c r="M104" s="324" t="str">
+      <c r="M104" s="323" t="str">
         <f>Data!I79</f>
         <v/>
       </c>
-      <c r="N104" s="324" t="str">
+      <c r="N104" s="323" t="str">
         <f>Data!J79</f>
         <v/>
       </c>
-      <c r="O104" s="324" t="str">
+      <c r="O104" s="323" t="str">
         <f>Data!K79</f>
         <v/>
       </c>
-      <c r="P104" s="324" t="str">
+      <c r="P104" s="323" t="str">
         <f>Data!L79</f>
         <v/>
       </c>
-      <c r="Q104" s="324" t="str">
+      <c r="Q104" s="323" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
@@ -13512,54 +13583,54 @@
       <c r="B105" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C105" s="332">
+      <c r="C105" s="331">
         <f>BS!G27</f>
         <v>3</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="324">
+      <c r="G105" s="323">
         <f>Data!C80</f>
         <v>3</v>
       </c>
-      <c r="H105" s="324" t="str">
+      <c r="H105" s="323" t="str">
         <f>Data!D80</f>
         <v/>
       </c>
-      <c r="I105" s="324" t="str">
+      <c r="I105" s="323" t="str">
         <f>Data!E80</f>
         <v/>
       </c>
-      <c r="J105" s="324" t="str">
+      <c r="J105" s="323" t="str">
         <f>Data!F80</f>
         <v/>
       </c>
-      <c r="K105" s="324" t="str">
+      <c r="K105" s="323" t="str">
         <f>Data!G80</f>
         <v/>
       </c>
-      <c r="L105" s="324" t="str">
+      <c r="L105" s="323" t="str">
         <f>Data!H80</f>
         <v/>
       </c>
-      <c r="M105" s="324" t="str">
+      <c r="M105" s="323" t="str">
         <f>Data!I80</f>
         <v/>
       </c>
-      <c r="N105" s="324" t="str">
+      <c r="N105" s="323" t="str">
         <f>Data!J80</f>
         <v/>
       </c>
-      <c r="O105" s="324" t="str">
+      <c r="O105" s="323" t="str">
         <f>Data!K80</f>
         <v/>
       </c>
-      <c r="P105" s="324" t="str">
+      <c r="P105" s="323" t="str">
         <f>Data!L80</f>
         <v/>
       </c>
-      <c r="Q105" s="324" t="str">
+      <c r="Q105" s="323" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
@@ -13911,52 +13982,52 @@
         <v>222</v>
       </c>
       <c r="C117" s="23">
-        <f>C81</f>
+        <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
         <v>-1.1649701082565843E-2</v>
       </c>
       <c r="E117" s="268"/>
       <c r="G117" s="23">
-        <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>-3.1741638390693163</v>
+        <f>IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
+        <v>1.4678118322150659</v>
       </c>
       <c r="H117" s="23" t="str">
-        <f t="shared" si="45"/>
+        <f>IF(H4="","",IF(valuation_method="DDM",H13/(H4+H12),H81))</f>
         <v/>
       </c>
       <c r="I117" s="23" t="str">
-        <f t="shared" si="45"/>
+        <f>IF(I4="","",IF(valuation_method="DDM",I13/(I4+I12),I81))</f>
         <v/>
       </c>
       <c r="J117" s="23" t="str">
-        <f t="shared" si="45"/>
+        <f>IF(J4="","",IF(valuation_method="DDM",J13/(J4+J12),J81))</f>
         <v/>
       </c>
       <c r="K117" s="23" t="str">
-        <f t="shared" si="45"/>
+        <f>IF(K4="","",IF(valuation_method="DDM",K13/(K4+K12),K81))</f>
         <v/>
       </c>
       <c r="L117" s="23" t="str">
-        <f t="shared" si="45"/>
+        <f>IF(L4="","",IF(valuation_method="DDM",L13/(L4+L12),L81))</f>
         <v/>
       </c>
       <c r="M117" s="23" t="str">
-        <f t="shared" si="45"/>
+        <f>IF(M4="","",IF(valuation_method="DDM",M13/(M4+M12),M81))</f>
         <v/>
       </c>
       <c r="N117" s="23" t="str">
-        <f t="shared" si="45"/>
+        <f>IF(N4="","",IF(valuation_method="DDM",N13/(N4+N12),N81))</f>
         <v/>
       </c>
       <c r="O117" s="23" t="str">
-        <f t="shared" si="45"/>
+        <f>IF(O4="","",IF(valuation_method="DDM",O13/(O4+O12),O81))</f>
         <v/>
       </c>
       <c r="P117" s="23" t="str">
-        <f t="shared" si="45"/>
+        <f>IF(P4="","",IF(valuation_method="DDM",P13/(P4+P12),P81))</f>
         <v/>
       </c>
       <c r="Q117" s="23" t="str">
-        <f t="shared" si="45"/>
+        <f>IF(Q4="","",IF(valuation_method="DDM",Q13/(Q4+Q12),Q81))</f>
         <v/>
       </c>
     </row>
@@ -13965,52 +14036,52 @@
         <v>84</v>
       </c>
       <c r="C118" s="42">
-        <f>C4/C101</f>
+        <f>IF(valuation_method="DDM",(C4+C12)/C101,C4/C101)</f>
         <v>15472.5</v>
       </c>
       <c r="E118" s="268"/>
       <c r="G118" s="42">
-        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
-        <v>15472.5</v>
+        <f>IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G101,G4/G101))</f>
+        <v>-33459.5</v>
       </c>
       <c r="H118" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f>IF(H4="","",IF(valuation_method="DDM",(H4+H12)/H101,H4/H101))</f>
         <v/>
       </c>
       <c r="I118" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f>IF(I4="","",IF(valuation_method="DDM",(I4+I12)/I101,I4/I101))</f>
         <v/>
       </c>
       <c r="J118" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f>IF(J4="","",IF(valuation_method="DDM",(J4+J12)/J101,J4/J101))</f>
         <v/>
       </c>
       <c r="K118" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f>IF(K4="","",IF(valuation_method="DDM",(K4+K12)/K101,K4/K101))</f>
         <v/>
       </c>
       <c r="L118" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f>IF(L4="","",IF(valuation_method="DDM",(L4+L12)/L101,L4/L101))</f>
         <v/>
       </c>
       <c r="M118" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f>IF(M4="","",IF(valuation_method="DDM",(M4+M12)/M101,M4/M101))</f>
         <v/>
       </c>
       <c r="N118" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f>IF(N4="","",IF(valuation_method="DDM",(N4+N12)/N101,N4/N101))</f>
         <v/>
       </c>
       <c r="O118" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f>IF(O4="","",IF(valuation_method="DDM",(O4+O12)/O101,O4/O101))</f>
         <v/>
       </c>
       <c r="P118" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f>IF(P4="","",IF(valuation_method="DDM",(P4+P12)/P101,P4/P101))</f>
         <v/>
       </c>
       <c r="Q118" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f>IF(Q4="","",IF(valuation_method="DDM",(Q4+Q12)/Q101,Q4/Q101))</f>
         <v/>
       </c>
     </row>
@@ -14026,47 +14097,47 @@
       <c r="E119" s="272"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
-        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
+        <f t="shared" ref="G119:Q119" si="45">IF(G$4="","",G101/G105)</f>
         <v>1.3333333333333333</v>
       </c>
       <c r="H119" s="15" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K119" s="15" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="L119" s="15" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="M119" s="15" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="N119" s="15" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="O119" s="15" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="P119" s="15" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="Q119" s="15" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
@@ -14087,43 +14158,43 @@
         <v>-65483</v>
       </c>
       <c r="H120" s="102" t="str">
-        <f t="shared" ref="H120:Q120" si="48">IF(H$4="","",H13/H105)</f>
+        <f t="shared" ref="H120:Q120" si="46">IF(H$4="","",H13/H105)</f>
         <v/>
       </c>
       <c r="I120" s="102" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J120" s="102" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="K120" s="102" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="L120" s="102" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="M120" s="102" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="N120" s="102" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="O120" s="102" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="P120" s="102" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="Q120" s="102" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
@@ -14204,47 +14275,47 @@
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
       <c r="G124" s="177">
-        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <f t="shared" ref="G124:Q124" si="47">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
         <v>-9.9336145178400823</v>
       </c>
       <c r="H124" s="177" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="I124" s="177" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="J124" s="177" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K124" s="177" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="L124" s="177" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="M124" s="177" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="N124" s="177" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="O124" s="177" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="P124" s="177" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="Q124" s="177" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
@@ -14261,47 +14332,47 @@
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
-        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
+        <f t="shared" ref="G125" si="48">IF(G$4="","",G124/Market_Price)</f>
         <v>-0.43760416378150141</v>
       </c>
       <c r="H125" s="77" t="str">
-        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
+        <f t="shared" ref="H125" si="49">IF(H$4="","",H124/Market_Price)</f>
         <v/>
       </c>
       <c r="I125" s="77" t="str">
-        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
+        <f t="shared" ref="I125" si="50">IF(I$4="","",I124/Market_Price)</f>
         <v/>
       </c>
       <c r="J125" s="77" t="str">
-        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
+        <f t="shared" ref="J125" si="51">IF(J$4="","",J124/Market_Price)</f>
         <v/>
       </c>
       <c r="K125" s="77" t="str">
-        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
+        <f t="shared" ref="K125" si="52">IF(K$4="","",K124/Market_Price)</f>
         <v/>
       </c>
       <c r="L125" s="77" t="str">
-        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
+        <f t="shared" ref="L125" si="53">IF(L$4="","",L124/Market_Price)</f>
         <v/>
       </c>
       <c r="M125" s="77" t="str">
-        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
+        <f t="shared" ref="M125" si="54">IF(M$4="","",M124/Market_Price)</f>
         <v/>
       </c>
       <c r="N125" s="77" t="str">
-        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
+        <f t="shared" ref="N125" si="55">IF(N$4="","",N124/Market_Price)</f>
         <v/>
       </c>
       <c r="O125" s="77" t="str">
-        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
+        <f t="shared" ref="O125" si="56">IF(O$4="","",O124/Market_Price)</f>
         <v/>
       </c>
       <c r="P125" s="77" t="str">
-        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
+        <f t="shared" ref="P125" si="57">IF(P$4="","",P124/Market_Price)</f>
         <v/>
       </c>
       <c r="Q125" s="77" t="str">
-        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
+        <f t="shared" ref="Q125" si="58">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
@@ -15096,7 +15167,7 @@
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="341">
+      <c r="C4" s="114">
         <f>Normalized_FCF!C19</f>
         <v>-540.75</v>
       </c>
@@ -15128,7 +15199,7 @@
       <c r="B6" s="149" t="s">
         <v>229</v>
       </c>
-      <c r="C6" s="342">
+      <c r="C6" s="338">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>-6759.375</v>
       </c>
@@ -15136,17 +15207,17 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="355" t="s">
+      <c r="E6" s="356" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="355"/>
+      <c r="F6" s="356"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="341">
+      <c r="C7" s="114">
         <f>BS!G31</f>
         <v>0</v>
       </c>
@@ -15154,15 +15225,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="355"/>
-      <c r="F7" s="355"/>
+      <c r="E7" s="356"/>
+      <c r="F7" s="356"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="341">
+      <c r="C8" s="114">
         <f>BS!D66</f>
         <v>0</v>
       </c>
@@ -15170,15 +15241,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="355"/>
-      <c r="F8" s="355"/>
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="343">
+      <c r="C9" s="339">
         <f>BS!H42</f>
         <v>0</v>
       </c>
@@ -15186,15 +15257,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="355"/>
-      <c r="F9" s="355"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="342">
+      <c r="C10" s="338">
         <f>C6-C7+C8+C9</f>
         <v>-6759.375</v>
       </c>
@@ -16599,7 +16670,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -16611,7 +16682,7 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
@@ -16624,9 +16695,9 @@
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>449</v>
-      </c>
-      <c r="C4" s="341">
+        <v>448</v>
+      </c>
+      <c r="C4" s="114">
         <f>Normalized_FCF!C91</f>
         <v>22020.769943020001</v>
       </c>
@@ -16656,9 +16727,9 @@
     </row>
     <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>450</v>
-      </c>
-      <c r="C6" s="342">
+        <v>449</v>
+      </c>
+      <c r="C6" s="338">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>275259.62428774999</v>
       </c>
@@ -16666,13 +16737,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="355"/>
-      <c r="F6" s="355"/>
+      <c r="E6" s="356"/>
+      <c r="F6" s="356"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -16745,7 +16816,7 @@
         <v>108</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D15" s="128" t="s">
         <v>119</v>
@@ -16754,7 +16825,7 @@
         <v>110</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -18124,7 +18195,7 @@
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="341">
+      <c r="C7" s="114">
         <f>Normalized_FCF!G8</f>
         <v>-721</v>
       </c>
@@ -18132,11 +18203,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="357" t="str">
+      <c r="E7" s="358" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 兴业银行(601166.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="357"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18149,7 +18220,7 @@
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="341">
+      <c r="C8" s="114">
         <f>Normalized_FCF!G19</f>
         <v>-206364</v>
       </c>
@@ -18157,8 +18228,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="357"/>
-      <c r="F8" s="357"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18171,7 +18242,7 @@
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="341">
+      <c r="C9" s="114">
         <f>Normalized_FCF!C19</f>
         <v>-540.75</v>
       </c>
@@ -18179,8 +18250,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="357"/>
-      <c r="F9" s="357"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18190,8 +18261,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="357"/>
-      <c r="F10" s="357"/>
+      <c r="E10" s="358"/>
+      <c r="F10" s="358"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18202,10 +18273,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>456</v>
-      </c>
-      <c r="E11" s="357"/>
-      <c r="F11" s="357"/>
+        <v>455</v>
+      </c>
+      <c r="E11" s="358"/>
+      <c r="F11" s="358"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18223,8 +18294,8 @@
         <v>#VALUE!</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="357"/>
-      <c r="F12" s="357"/>
+      <c r="E12" s="358"/>
+      <c r="F12" s="358"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18241,8 +18312,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E13" s="357"/>
-      <c r="F13" s="357"/>
+      <c r="E13" s="358"/>
+      <c r="F13" s="358"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18259,8 +18330,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E14" s="357"/>
-      <c r="F14" s="357"/>
+      <c r="E14" s="358"/>
+      <c r="F14" s="358"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -18286,21 +18357,21 @@
       <c r="C18" s="150">
         <v>30</v>
       </c>
-      <c r="E18" s="357" t="s">
+      <c r="E18" s="358" t="s">
         <v>333</v>
       </c>
-      <c r="F18" s="358"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="358"/>
-      <c r="F19" s="358"/>
+      <c r="E19" s="359"/>
+      <c r="F19" s="359"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>305</v>
       </c>
-      <c r="E20" s="358"/>
-      <c r="F20" s="358"/>
+      <c r="E20" s="359"/>
+      <c r="F20" s="359"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -18314,8 +18385,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="358"/>
-      <c r="F21" s="358"/>
+      <c r="E21" s="359"/>
+      <c r="F21" s="359"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -18329,8 +18400,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="358"/>
-      <c r="F22" s="358"/>
+      <c r="E22" s="359"/>
+      <c r="F22" s="359"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -18350,8 +18421,8 @@
         <v>30</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="356"/>
-      <c r="F25" s="356"/>
+      <c r="E25" s="357"/>
+      <c r="F25" s="357"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -18361,8 +18432,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="356"/>
-      <c r="F26" s="356"/>
+      <c r="E26" s="357"/>
+      <c r="F26" s="357"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -18376,8 +18447,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="356"/>
-      <c r="F27" s="356"/>
+      <c r="E27" s="357"/>
+      <c r="F27" s="357"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -18387,8 +18458,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="356"/>
-      <c r="F28" s="356"/>
+      <c r="E28" s="357"/>
+      <c r="F28" s="357"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -18408,8 +18479,8 @@
         <v>30</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="356"/>
-      <c r="F31" s="356"/>
+      <c r="E31" s="357"/>
+      <c r="F31" s="357"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -18419,8 +18490,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="356"/>
-      <c r="F32" s="356"/>
+      <c r="E32" s="357"/>
+      <c r="F32" s="357"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -18434,8 +18505,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="356"/>
-      <c r="F33" s="356"/>
+      <c r="E33" s="357"/>
+      <c r="F33" s="357"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -18445,8 +18516,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="356"/>
-      <c r="F34" s="356"/>
+      <c r="E34" s="357"/>
+      <c r="F34" s="357"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -18466,8 +18537,8 @@
         <v>30</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="356"/>
-      <c r="F37" s="356"/>
+      <c r="E37" s="357"/>
+      <c r="F37" s="357"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -18477,8 +18548,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="356"/>
-      <c r="F38" s="356"/>
+      <c r="E38" s="357"/>
+      <c r="F38" s="357"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -18492,8 +18563,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="356"/>
-      <c r="F39" s="356"/>
+      <c r="E39" s="357"/>
+      <c r="F39" s="357"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -18504,8 +18575,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="356"/>
-      <c r="F40" s="356"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -18567,8 +18638,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="356"/>
-      <c r="F49" s="356"/>
+      <c r="E49" s="357"/>
+      <c r="F49" s="357"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -18578,8 +18649,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="356"/>
-      <c r="F50" s="356"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -18593,8 +18664,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="356"/>
-      <c r="F51" s="356"/>
+      <c r="E51" s="357"/>
+      <c r="F51" s="357"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -18604,8 +18675,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="356"/>
-      <c r="F52" s="356"/>
+      <c r="E52" s="357"/>
+      <c r="F52" s="357"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -18625,8 +18696,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="356"/>
-      <c r="F55" s="356"/>
+      <c r="E55" s="357"/>
+      <c r="F55" s="357"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -18636,8 +18707,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="356"/>
-      <c r="F56" s="356"/>
+      <c r="E56" s="357"/>
+      <c r="F56" s="357"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -18651,8 +18722,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="356"/>
-      <c r="F57" s="356"/>
+      <c r="E57" s="357"/>
+      <c r="F57" s="357"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -18662,8 +18733,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="356"/>
-      <c r="F58" s="356"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -18927,12 +18998,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19047,12 +19118,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>

--- a/financial_models/templates/Valuation_v2.0.xlsx
+++ b/financial_models/templates/Valuation_v2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3515DA4-D1E2-4DBC-A1F9-BF27F66B0943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2F4B9A-16E0-40A7-8135-7BB5B9F8803D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="464">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -465,10 +466,6 @@
   <si>
     <t>PV of FCFE</t>
     <phoneticPr fontId="28" type="noConversion"/>
-  </si>
-  <si>
-    <t>Annual Dividend per share</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HGP</t>
@@ -1501,14 +1498,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Dividend/Market Cap =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dividend Yield</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2470,6 +2459,18 @@
   </si>
   <si>
     <t>LT AR and Prepayments</t>
+  </si>
+  <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
   </si>
 </sst>
 </file>
@@ -3143,7 +3144,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="368">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3888,6 +3889,10 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4232,18 +4237,18 @@
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4257,7 +4262,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4266,10 +4271,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4283,7 +4288,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4293,7 +4298,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4306,17 +4311,17 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D11" s="49"/>
       <c r="E11" s="34"/>
@@ -4333,17 +4338,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4357,7 +4362,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4384,34 +4389,34 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="356" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="B18" s="358" t="s">
+        <v>359</v>
+      </c>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4419,7 +4424,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4431,26 +4436,26 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4471,7 +4476,7 @@
         <v>14.723869312014129</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
@@ -4484,7 +4489,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4495,7 +4500,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4503,7 +4508,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
@@ -4514,7 +4519,7 @@
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="F29" s="302">
         <v>0.4</v>
@@ -4522,7 +4527,7 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
@@ -4533,7 +4538,7 @@
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F30" s="312">
         <v>0.22</v>
@@ -4541,7 +4546,7 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
@@ -4552,7 +4557,7 @@
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F31" s="312">
         <v>0.08</v>
@@ -4560,7 +4565,7 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
@@ -4571,7 +4576,7 @@
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F32" s="312">
         <v>0.12</v>
@@ -4583,7 +4588,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4592,26 +4597,26 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="356" t="s">
-        <v>363</v>
-      </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="B36" s="358" t="s">
+        <v>360</v>
+      </c>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="358" t="s">
-        <v>341</v>
-      </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="B37" s="360" t="s">
+        <v>338</v>
+      </c>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
@@ -4619,17 +4624,17 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="357" t="s">
-        <v>231</v>
-      </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="B40" s="359" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4645,17 +4650,17 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="357" t="s">
-        <v>233</v>
-      </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="B43" s="359" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4668,7 +4673,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4680,17 +4685,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
-        <v>236</v>
-      </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="B47" s="359" t="s">
+        <v>235</v>
+      </c>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4702,17 +4707,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
-        <v>240</v>
-      </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="B50" s="359" t="s">
+        <v>239</v>
+      </c>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4727,7 +4732,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4742,7 +4747,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4755,12 +4760,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4772,17 +4777,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
-        <v>241</v>
-      </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="B58" s="359" t="s">
+        <v>240</v>
+      </c>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4794,17 +4799,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
-        <v>340</v>
-      </c>
-      <c r="C61" s="360"/>
-      <c r="D61" s="360"/>
-      <c r="E61" s="360"/>
-      <c r="F61" s="360"/>
+      <c r="B61" s="359" t="s">
+        <v>337</v>
+      </c>
+      <c r="C61" s="362"/>
+      <c r="D61" s="362"/>
+      <c r="E61" s="362"/>
+      <c r="F61" s="362"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4816,26 +4821,26 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="356" t="s">
-        <v>345</v>
-      </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="B64" s="358" t="s">
+        <v>342</v>
+      </c>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="356" t="s">
-        <v>364</v>
-      </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="B65" s="358" t="s">
+        <v>361</v>
+      </c>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4848,7 +4853,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4861,24 +4866,24 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C69" s="92">
-        <f>Normalized_FCF!C125</f>
+        <f>Normalized_FCF!C126</f>
         <v>-1.1466847491076299E-3</v>
       </c>
       <c r="F69" s="314"/>
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>309</v>
+        <v>462</v>
       </c>
       <c r="C70" s="92">
-        <f>Normalized_FCF!C93</f>
+        <f>Normalized_FCF!C94</f>
         <v>4.6696035242290754E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -4887,73 +4892,73 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
+        <v>455</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>457</v>
+      </c>
+      <c r="D72" s="323" t="s">
         <v>458</v>
-      </c>
-      <c r="C72" s="323" t="s">
-        <v>460</v>
-      </c>
-      <c r="D72" s="323" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C73" s="92">
-        <f>Normalized_FCF!C120</f>
+        <f>Normalized_FCF!C121</f>
         <v>-240.33333333333334</v>
       </c>
       <c r="D73" s="92">
-        <f>Normalized_FCF!G120</f>
+        <f>Normalized_FCF!G121</f>
         <v>-65483</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
-        <f>Normalized_FCF!B117</f>
+        <f>Normalized_FCF!B118</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
       <c r="C74" s="322">
-        <f>Normalized_FCF!C117</f>
+        <f>Normalized_FCF!C118</f>
         <v>-1.1649701082565843E-2</v>
       </c>
       <c r="D74" s="322">
-        <f>Normalized_FCF!G117</f>
+        <f>Normalized_FCF!G118</f>
         <v>1.4678118322150659</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
-        <f>Normalized_FCF!B118</f>
+        <f>Normalized_FCF!B119</f>
         <v>Sales/Total Assets</v>
       </c>
       <c r="C75" s="324">
-        <f>Normalized_FCF!C118</f>
+        <f>Normalized_FCF!C119</f>
         <v>15472.5</v>
       </c>
       <c r="D75" s="324">
-        <f>Normalized_FCF!G118</f>
+        <f>Normalized_FCF!G119</f>
         <v>-33459.5</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
-        <f>Normalized_FCF!B119</f>
+        <f>Normalized_FCF!B120</f>
         <v>Total Assets/Equity</v>
       </c>
       <c r="C76" s="324">
-        <f>Normalized_FCF!C119</f>
+        <f>Normalized_FCF!C120</f>
         <v>1.3333333333333333</v>
       </c>
       <c r="D76" s="324">
-        <f>Normalized_FCF!G119</f>
+        <f>Normalized_FCF!G120</f>
         <v>1.3333333333333333</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -4966,31 +4971,31 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
-        <v>365</v>
-      </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="B80" s="358" t="s">
+        <v>362</v>
+      </c>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
-        <v>252</v>
-      </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="B81" s="360" t="s">
+        <v>251</v>
+      </c>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -4999,7 +5004,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5008,7 +5013,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5020,31 +5025,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="356" t="s">
-        <v>366</v>
-      </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="B89" s="358" t="s">
+        <v>363</v>
+      </c>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="356" t="s">
-        <v>367</v>
-      </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="B90" s="358" t="s">
+        <v>364</v>
+      </c>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5052,7 +5057,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5065,7 +5070,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5077,36 +5082,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
-        <v>368</v>
-      </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="B97" s="358" t="s">
+        <v>365</v>
+      </c>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="356" t="s">
-        <v>346</v>
-      </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="B101" s="358" t="s">
+        <v>343</v>
+      </c>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5119,7 +5124,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5132,7 +5137,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5141,7 +5146,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5150,12 +5155,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5168,7 +5173,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5181,7 +5186,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5194,12 +5199,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5212,7 +5217,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5224,17 +5229,17 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="356" t="s">
-        <v>369</v>
-      </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="B116" s="358" t="s">
+        <v>366</v>
+      </c>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5247,7 +5252,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5260,7 +5265,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5269,29 +5274,29 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="357" t="s">
-        <v>370</v>
-      </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="B123" s="359" t="s">
+        <v>367</v>
+      </c>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5406,7 +5411,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5418,17 +5423,17 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="361" t="s">
-        <v>373</v>
-      </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="B134" s="363" t="s">
+        <v>370</v>
+      </c>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5437,31 +5442,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
-        <v>371</v>
-      </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="B138" s="361" t="s">
+        <v>368</v>
+      </c>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="356" t="s">
-        <v>372</v>
-      </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="B139" s="358" t="s">
+        <v>369</v>
+      </c>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5470,7 +5475,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
@@ -5479,7 +5484,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
@@ -5492,7 +5497,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5505,7 +5510,7 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
@@ -5534,7 +5539,7 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
@@ -5547,7 +5552,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5560,7 +5565,7 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
@@ -5569,12 +5574,12 @@
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5603,7 +5608,7 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
@@ -5616,7 +5621,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5629,7 +5634,7 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
@@ -5638,12 +5643,12 @@
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5672,7 +5677,7 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
@@ -5685,7 +5690,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5698,7 +5703,7 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
@@ -5707,12 +5712,12 @@
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5741,7 +5746,7 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
@@ -5754,7 +5759,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5767,7 +5772,7 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
@@ -5776,7 +5781,7 @@
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5785,98 +5790,98 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
-        <v>379</v>
-      </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="B179" s="365" t="s">
+        <v>376</v>
+      </c>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="360" t="s">
-        <v>383</v>
-      </c>
-      <c r="C182" s="360"/>
-      <c r="D182" s="360"/>
-      <c r="E182" s="360"/>
-      <c r="F182" s="360"/>
+      <c r="B182" s="362" t="s">
+        <v>380</v>
+      </c>
+      <c r="C182" s="362"/>
+      <c r="D182" s="362"/>
+      <c r="E182" s="362"/>
+      <c r="F182" s="362"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
-        <v>384</v>
-      </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="B188" s="359" t="s">
+        <v>381</v>
+      </c>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="362" t="s">
-        <v>385</v>
-      </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="B191" s="364" t="s">
+        <v>382</v>
+      </c>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="362" t="s">
-        <v>386</v>
-      </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="B192" s="364" t="s">
+        <v>383</v>
+      </c>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -6111,7 +6116,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C9" s="351"/>
       <c r="D9" s="351"/>
@@ -6127,7 +6132,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6143,7 +6148,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6303,7 +6308,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C22" s="351">
         <v>-237258</v>
@@ -6321,7 +6326,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C23" s="351">
         <v>23438</v>
@@ -6339,7 +6344,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C24" s="351">
         <v>194894</v>
@@ -6380,7 +6385,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -6461,7 +6466,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -6844,7 +6849,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -6893,7 +6898,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7241,12 +7246,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7295,7 +7300,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7344,7 +7349,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7393,7 +7398,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7595,7 +7600,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7847,7 +7852,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C71" s="101" t="str">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8242,7 +8247,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8253,19 +8258,19 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H3" s="183" t="s">
         <v>35</v>
@@ -8325,7 +8330,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8346,7 +8351,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -8357,7 +8362,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8367,7 +8372,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8388,7 +8393,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8452,19 +8457,19 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D14" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H14" s="183" t="s">
         <v>35</v>
@@ -8472,7 +8477,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -8501,7 +8506,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8521,7 +8526,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -8532,7 +8537,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8541,7 +8546,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8561,7 +8566,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -8581,7 +8586,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -8601,7 +8606,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -8660,16 +8665,16 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H26" s="186" t="s">
         <v>35</v>
@@ -8702,7 +8707,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G28" s="12">
         <v>0</v>
@@ -8746,7 +8751,7 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
@@ -8796,10 +8801,10 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H34" s="198" t="s">
         <v>35</v>
@@ -8807,10 +8812,10 @@
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="199" t="s">
         <v>31</v>
@@ -8832,7 +8837,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -8848,7 +8853,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -8864,7 +8869,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -8893,14 +8898,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>0</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -8920,7 +8925,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -8939,7 +8944,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -8963,13 +8968,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="F45" s="256" t="s">
         <v>59</v>
@@ -8977,7 +8982,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9009,7 +9014,7 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C49" s="235" t="s">
         <v>57</v>
@@ -9036,7 +9041,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9050,7 +9055,7 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C53" s="235" t="s">
         <v>57</v>
@@ -9062,7 +9067,7 @@
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9076,7 +9081,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9093,7 +9098,7 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C57" s="235" t="s">
         <v>57</v>
@@ -9130,10 +9135,10 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D61" s="197" t="s">
         <v>95</v>
@@ -9142,7 +9147,7 @@
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9153,12 +9158,12 @@
         <v>0</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9169,13 +9174,13 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F65" s="256" t="s">
         <v>59</v>
@@ -9183,7 +9188,7 @@
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9194,12 +9199,12 @@
         <v>0</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9209,7 +9214,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9219,7 +9224,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9229,7 +9234,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9242,7 +9247,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C72" s="234" t="s">
         <v>95</v>
@@ -9254,7 +9259,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9265,12 +9270,12 @@
         <v>-7052.6474952516664</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9281,12 +9286,12 @@
         <v>2.8358144956862504E-4</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9294,12 +9299,12 @@
         <v>2</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9307,7 +9312,7 @@
         <v>2.8358144956862504E-4</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9315,10 +9320,10 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D78" s="183" t="s">
         <v>35</v>
@@ -9327,7 +9332,7 @@
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9341,7 +9346,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9355,7 +9360,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9369,7 +9374,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9383,7 +9388,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9394,15 +9399,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="D85" s="241" t="s">
         <v>290</v>
-      </c>
-      <c r="D85" s="241" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9419,7 +9424,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9436,7 +9441,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9453,7 +9458,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9481,7 +9486,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q808"/>
+  <dimension ref="A1:Q809"/>
   <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
@@ -9813,7 +9818,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -9980,7 +9985,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10092,7 +10097,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10202,7 +10207,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10259,7 +10264,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10324,7 +10329,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10349,7 +10354,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10443,7 +10448,7 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
@@ -10662,7 +10667,7 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E27" s="268"/>
     </row>
@@ -10677,7 +10682,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10737,7 +10742,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10854,14 +10859,14 @@
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C33" s="340">
         <f>AVERAGE(G33:J33)</f>
         <v>-62611</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -10919,7 +10924,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -11031,7 +11036,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11213,21 +11218,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11281,7 +11286,7 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
@@ -11366,7 +11371,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11421,7 +11426,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11537,11 +11542,11 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
@@ -11553,7 +11558,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11580,7 +11585,7 @@
         <v>0</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11659,17 +11664,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -11724,7 +11729,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -11779,7 +11784,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -11834,7 +11839,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -11889,13 +11894,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -11945,7 +11950,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12004,17 +12009,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12039,7 +12044,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12064,7 +12069,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12089,7 +12094,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12119,7 +12124,7 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
@@ -12142,7 +12147,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12334,7 +12339,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12456,7 +12461,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12507,7 +12512,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12621,7 +12626,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -12793,7 +12798,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -12900,7 +12905,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -12961,7 +12966,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13080,7 +13085,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13135,606 +13140,570 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C93" s="23">
-        <f>C90/Market_Price</f>
-        <v>4.6696035242290754E-2</v>
+        <v>461</v>
+      </c>
+      <c r="C93" s="356">
+        <v>0</v>
       </c>
       <c r="E93" s="268"/>
-      <c r="G93" s="23">
-        <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.6696035242290754E-2</v>
-      </c>
-      <c r="H93" s="23" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="I93" s="23" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="J93" s="23" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="K93" s="23" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="L93" s="23" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="M93" s="23" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="N93" s="23" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="O93" s="23" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="P93" s="23" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="Q93" s="23" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
+      <c r="G93" s="357"/>
+      <c r="H93" s="357"/>
+      <c r="I93" s="357"/>
+      <c r="J93" s="357"/>
+      <c r="K93" s="357"/>
+      <c r="L93" s="357"/>
+      <c r="M93" s="357"/>
+      <c r="N93" s="357"/>
+      <c r="O93" s="357"/>
+      <c r="P93" s="357"/>
+      <c r="Q93" s="357"/>
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
+      <c r="B94" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C94" s="23">
+        <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
+        <v>4.6696035242290754E-2</v>
+      </c>
       <c r="E94" s="268"/>
+      <c r="G94" s="23">
+        <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
+        <v>4.6696035242290754E-2</v>
+      </c>
+      <c r="H94" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="I94" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="J94" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K94" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="L94" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="M94" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="N94" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="O94" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P94" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="Q94" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
-      <c r="B95" s="157" t="s">
-        <v>84</v>
-      </c>
-      <c r="C95" s="62"/>
-      <c r="D95" s="27"/>
-      <c r="E95" s="265"/>
-      <c r="F95" s="27"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="12"/>
-      <c r="I95" s="12"/>
-      <c r="J95" s="12"/>
-      <c r="K95" s="12"/>
-      <c r="L95" s="12"/>
-      <c r="M95" s="12"/>
-      <c r="N95" s="12"/>
-      <c r="O95" s="12"/>
-      <c r="P95" s="12"/>
-      <c r="Q95" s="12"/>
+      <c r="E95" s="268"/>
     </row>
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
-      <c r="B96" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C96" s="77">
-        <f>C4/G4-1</f>
-        <v>0</v>
-      </c>
+      <c r="B96" s="157" t="s">
+        <v>84</v>
+      </c>
+      <c r="C96" s="62"/>
       <c r="D96" s="27"/>
       <c r="E96" s="265"/>
       <c r="F96" s="27"/>
-      <c r="G96" s="6" t="str">
-        <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
-        <v/>
-      </c>
-      <c r="H96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="I96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="J96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="K96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="L96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="M96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="N96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="O96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="P96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="Q96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
+      <c r="K96" s="12"/>
+      <c r="L96" s="12"/>
+      <c r="M96" s="12"/>
+      <c r="N96" s="12"/>
+      <c r="O96" s="12"/>
+      <c r="P96" s="12"/>
+      <c r="Q96" s="12"/>
     </row>
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
-      <c r="B97" s="70" t="s">
-        <v>164</v>
+      <c r="B97" s="27" t="s">
+        <v>143</v>
       </c>
       <c r="C97" s="77">
-        <f>C13/G13-1</f>
-        <v>-0.99632983624248528</v>
+        <f>C4/G4-1</f>
+        <v>0</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="265"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6" t="str">
-        <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
+        <f t="shared" ref="G97:Q97" si="40">IF(H4="","",G4/H4-1)</f>
         <v/>
       </c>
       <c r="H97" s="6" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="I97" s="6" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J97" s="6" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="K97" s="6" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="L97" s="6" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="M97" s="6" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="N97" s="6" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="O97" s="6" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="P97" s="6" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="Q97" s="6" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
+      <c r="B98" s="70" t="s">
+        <v>163</v>
+      </c>
+      <c r="C98" s="77">
+        <f>C13/G13-1</f>
+        <v>-0.99632983624248528</v>
+      </c>
+      <c r="D98" s="27"/>
+      <c r="E98" s="265"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="6" t="str">
+        <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
+        <v/>
+      </c>
+      <c r="H98" s="6" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="I98" s="6" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="J98" s="6" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="K98" s="6" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="L98" s="6" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="M98" s="6" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="N98" s="6" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="O98" s="6" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="P98" s="6" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="Q98" s="6" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
     </row>
     <row r="99" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A99" s="3"/>
-      <c r="B99" s="54" t="s">
-        <v>215</v>
-      </c>
-      <c r="C99" s="54"/>
-      <c r="D99" s="56"/>
-      <c r="E99" s="66" t="s">
+      <c r="A99" s="10"/>
+    </row>
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A100" s="3"/>
+      <c r="B100" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="C100" s="54"/>
+      <c r="D100" s="56"/>
+      <c r="E100" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="F99" s="56"/>
-      <c r="G99" s="37"/>
-      <c r="H99" s="37"/>
-      <c r="I99" s="37"/>
-      <c r="J99" s="37"/>
-      <c r="K99" s="37"/>
-      <c r="L99" s="37"/>
-      <c r="M99" s="37"/>
-      <c r="N99" s="37"/>
-      <c r="O99" s="37"/>
-      <c r="P99" s="37"/>
-      <c r="Q99" s="37"/>
-    </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A100" s="10"/>
-      <c r="B100" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="E100" s="268"/>
-      <c r="G100" s="97" t="s">
-        <v>219</v>
-      </c>
+      <c r="F100" s="56"/>
+      <c r="G100" s="37"/>
+      <c r="H100" s="37"/>
+      <c r="I100" s="37"/>
+      <c r="J100" s="37"/>
+      <c r="K100" s="37"/>
+      <c r="L100" s="37"/>
+      <c r="M100" s="37"/>
+      <c r="N100" s="37"/>
+      <c r="O100" s="37"/>
+      <c r="P100" s="37"/>
+      <c r="Q100" s="37"/>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
-      <c r="B101" s="26" t="s">
+      <c r="B101" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E101" s="268"/>
+      <c r="G101" s="97" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A102" s="10"/>
+      <c r="B102" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="344">
+      <c r="C102" s="344">
         <f>BS!G32</f>
         <v>4</v>
       </c>
-      <c r="D101" s="26"/>
-      <c r="E101" s="269"/>
-      <c r="F101" s="26"/>
-      <c r="G101" s="333">
-        <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
+      <c r="D102" s="26"/>
+      <c r="E102" s="269"/>
+      <c r="F102" s="26"/>
+      <c r="G102" s="333">
+        <f t="shared" ref="G102:Q102" si="42">IF(G$4="","",G106+G105)</f>
         <v>4</v>
       </c>
-      <c r="H101" s="333" t="str">
+      <c r="H102" s="333" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="I101" s="333" t="str">
+      <c r="I102" s="333" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="J101" s="333" t="str">
+      <c r="J102" s="333" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="K101" s="333" t="str">
+      <c r="K102" s="333" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="L101" s="333" t="str">
+      <c r="L102" s="333" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="M101" s="333" t="str">
+      <c r="M102" s="333" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="N101" s="333" t="str">
+      <c r="N102" s="333" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="O101" s="333" t="str">
+      <c r="O102" s="333" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="P101" s="333" t="str">
+      <c r="P102" s="333" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="Q101" s="333" t="str">
+      <c r="Q102" s="333" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A102" s="10"/>
-      <c r="B102" s="93" t="s">
-        <v>210</v>
-      </c>
-      <c r="C102" s="345">
-        <f>BS!C4</f>
-        <v>0</v>
-      </c>
-      <c r="D102" s="89"/>
-      <c r="E102" s="270"/>
-      <c r="F102" s="89"/>
-      <c r="G102" s="346" t="str">
-        <f>IF(G$4="","",Data!D77)</f>
-        <v/>
-      </c>
-      <c r="H102" s="346" t="str">
-        <f>IF(H$4="","",Data!E77)</f>
-        <v/>
-      </c>
-      <c r="I102" s="346" t="str">
-        <f>IF(I$4="","",Data!F77)</f>
-        <v/>
-      </c>
-      <c r="J102" s="346" t="str">
-        <f>IF(J$4="","",Data!G77)</f>
-        <v/>
-      </c>
-      <c r="K102" s="346" t="str">
-        <f>IF(K$4="","",Data!H77)</f>
-        <v/>
-      </c>
-      <c r="L102" s="346" t="str">
-        <f>IF(L$4="","",Data!I77)</f>
-        <v/>
-      </c>
-      <c r="M102" s="346" t="str">
-        <f>IF(M$4="","",Data!J77)</f>
-        <v/>
-      </c>
-      <c r="N102" s="346" t="str">
-        <f>IF(N$4="","",Data!K77)</f>
-        <v/>
-      </c>
-      <c r="O102" s="346" t="str">
-        <f>IF(O$4="","",Data!L77)</f>
-        <v/>
-      </c>
-      <c r="P102" s="346" t="str">
-        <f>IF(P$4="","",Data!M77)</f>
-        <v/>
-      </c>
-      <c r="Q102" s="346" t="str">
-        <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
     </row>
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C103" s="345">
-        <f>BS!C6+BS!C7</f>
+        <f>BS!C4</f>
         <v>0</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
       <c r="G103" s="346" t="str">
-        <f>IF(G$4="","",Data!D78)</f>
+        <f>IF(G$4="","",Data!D77)</f>
         <v/>
       </c>
       <c r="H103" s="346" t="str">
-        <f>IF(H$4="","",Data!E78)</f>
+        <f>IF(H$4="","",Data!E77)</f>
         <v/>
       </c>
       <c r="I103" s="346" t="str">
-        <f>IF(I$4="","",Data!F78)</f>
+        <f>IF(I$4="","",Data!F77)</f>
         <v/>
       </c>
       <c r="J103" s="346" t="str">
-        <f>IF(J$4="","",Data!G78)</f>
+        <f>IF(J$4="","",Data!G77)</f>
         <v/>
       </c>
       <c r="K103" s="346" t="str">
-        <f>IF(K$4="","",Data!H78)</f>
+        <f>IF(K$4="","",Data!H77)</f>
         <v/>
       </c>
       <c r="L103" s="346" t="str">
-        <f>IF(L$4="","",Data!I78)</f>
+        <f>IF(L$4="","",Data!I77)</f>
         <v/>
       </c>
       <c r="M103" s="346" t="str">
-        <f>IF(M$4="","",Data!J78)</f>
+        <f>IF(M$4="","",Data!J77)</f>
         <v/>
       </c>
       <c r="N103" s="346" t="str">
-        <f>IF(N$4="","",Data!K78)</f>
+        <f>IF(N$4="","",Data!K77)</f>
         <v/>
       </c>
       <c r="O103" s="346" t="str">
-        <f>IF(O$4="","",Data!L78)</f>
+        <f>IF(O$4="","",Data!L77)</f>
         <v/>
       </c>
       <c r="P103" s="346" t="str">
-        <f>IF(P$4="","",Data!M78)</f>
+        <f>IF(P$4="","",Data!M77)</f>
         <v/>
       </c>
       <c r="Q103" s="346" t="str">
-        <f>IF(Q$4="","",Data!N78)</f>
+        <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
     </row>
     <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
-      <c r="B104" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C104" s="344">
-        <f>BS!G30</f>
-        <v>1</v>
-      </c>
-      <c r="D104" s="26"/>
-      <c r="E104" s="269"/>
-      <c r="F104" s="26"/>
-      <c r="G104" s="333">
-        <f>Data!C79</f>
-        <v>1</v>
-      </c>
-      <c r="H104" s="333" t="str">
-        <f>Data!D79</f>
-        <v/>
-      </c>
-      <c r="I104" s="333" t="str">
-        <f>Data!E79</f>
-        <v/>
-      </c>
-      <c r="J104" s="333" t="str">
-        <f>Data!F79</f>
-        <v/>
-      </c>
-      <c r="K104" s="333" t="str">
-        <f>Data!G79</f>
-        <v/>
-      </c>
-      <c r="L104" s="333" t="str">
-        <f>Data!H79</f>
-        <v/>
-      </c>
-      <c r="M104" s="333" t="str">
-        <f>Data!I79</f>
-        <v/>
-      </c>
-      <c r="N104" s="333" t="str">
-        <f>Data!J79</f>
-        <v/>
-      </c>
-      <c r="O104" s="333" t="str">
-        <f>Data!K79</f>
-        <v/>
-      </c>
-      <c r="P104" s="333" t="str">
-        <f>Data!L79</f>
-        <v/>
-      </c>
-      <c r="Q104" s="333" t="str">
-        <f>Data!M79</f>
+      <c r="B104" s="93" t="s">
+        <v>210</v>
+      </c>
+      <c r="C104" s="345">
+        <f>BS!C6+BS!C7</f>
+        <v>0</v>
+      </c>
+      <c r="D104" s="89"/>
+      <c r="E104" s="270"/>
+      <c r="F104" s="89"/>
+      <c r="G104" s="346" t="str">
+        <f>IF(G$4="","",Data!D78)</f>
+        <v/>
+      </c>
+      <c r="H104" s="346" t="str">
+        <f>IF(H$4="","",Data!E78)</f>
+        <v/>
+      </c>
+      <c r="I104" s="346" t="str">
+        <f>IF(I$4="","",Data!F78)</f>
+        <v/>
+      </c>
+      <c r="J104" s="346" t="str">
+        <f>IF(J$4="","",Data!G78)</f>
+        <v/>
+      </c>
+      <c r="K104" s="346" t="str">
+        <f>IF(K$4="","",Data!H78)</f>
+        <v/>
+      </c>
+      <c r="L104" s="346" t="str">
+        <f>IF(L$4="","",Data!I78)</f>
+        <v/>
+      </c>
+      <c r="M104" s="346" t="str">
+        <f>IF(M$4="","",Data!J78)</f>
+        <v/>
+      </c>
+      <c r="N104" s="346" t="str">
+        <f>IF(N$4="","",Data!K78)</f>
+        <v/>
+      </c>
+      <c r="O104" s="346" t="str">
+        <f>IF(O$4="","",Data!L78)</f>
+        <v/>
+      </c>
+      <c r="P104" s="346" t="str">
+        <f>IF(P$4="","",Data!M78)</f>
+        <v/>
+      </c>
+      <c r="Q104" s="346" t="str">
+        <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
     </row>
     <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C105" s="344">
-        <f>BS!G27</f>
-        <v>3</v>
+        <f>BS!G30</f>
+        <v>1</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
       <c r="G105" s="333">
+        <f>Data!C79</f>
+        <v>1</v>
+      </c>
+      <c r="H105" s="333" t="str">
+        <f>Data!D79</f>
+        <v/>
+      </c>
+      <c r="I105" s="333" t="str">
+        <f>Data!E79</f>
+        <v/>
+      </c>
+      <c r="J105" s="333" t="str">
+        <f>Data!F79</f>
+        <v/>
+      </c>
+      <c r="K105" s="333" t="str">
+        <f>Data!G79</f>
+        <v/>
+      </c>
+      <c r="L105" s="333" t="str">
+        <f>Data!H79</f>
+        <v/>
+      </c>
+      <c r="M105" s="333" t="str">
+        <f>Data!I79</f>
+        <v/>
+      </c>
+      <c r="N105" s="333" t="str">
+        <f>Data!J79</f>
+        <v/>
+      </c>
+      <c r="O105" s="333" t="str">
+        <f>Data!K79</f>
+        <v/>
+      </c>
+      <c r="P105" s="333" t="str">
+        <f>Data!L79</f>
+        <v/>
+      </c>
+      <c r="Q105" s="333" t="str">
+        <f>Data!M79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A106" s="10"/>
+      <c r="B106" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106" s="344">
+        <f>BS!G27</f>
+        <v>3</v>
+      </c>
+      <c r="D106" s="26"/>
+      <c r="E106" s="269"/>
+      <c r="F106" s="26"/>
+      <c r="G106" s="333">
         <f>Data!C80</f>
         <v>3</v>
       </c>
-      <c r="H105" s="333" t="str">
+      <c r="H106" s="333" t="str">
         <f>Data!D80</f>
         <v/>
       </c>
-      <c r="I105" s="333" t="str">
+      <c r="I106" s="333" t="str">
         <f>Data!E80</f>
         <v/>
       </c>
-      <c r="J105" s="333" t="str">
+      <c r="J106" s="333" t="str">
         <f>Data!F80</f>
         <v/>
       </c>
-      <c r="K105" s="333" t="str">
+      <c r="K106" s="333" t="str">
         <f>Data!G80</f>
         <v/>
       </c>
-      <c r="L105" s="333" t="str">
+      <c r="L106" s="333" t="str">
         <f>Data!H80</f>
         <v/>
       </c>
-      <c r="M105" s="333" t="str">
+      <c r="M106" s="333" t="str">
         <f>Data!I80</f>
         <v/>
       </c>
-      <c r="N105" s="333" t="str">
+      <c r="N106" s="333" t="str">
         <f>Data!J80</f>
         <v/>
       </c>
-      <c r="O105" s="333" t="str">
+      <c r="O106" s="333" t="str">
         <f>Data!K80</f>
         <v/>
       </c>
-      <c r="P105" s="333" t="str">
+      <c r="P106" s="333" t="str">
         <f>Data!L80</f>
         <v/>
       </c>
-      <c r="Q105" s="333" t="str">
+      <c r="Q106" s="333" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
-    </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A106" s="10"/>
-      <c r="E106" s="268"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
-      <c r="B107" s="91" t="s">
-        <v>220</v>
-      </c>
-      <c r="C107" s="26"/>
-      <c r="D107" s="26"/>
-      <c r="E107" s="269"/>
-      <c r="F107" s="26"/>
-      <c r="G107" s="97" t="s">
-        <v>219</v>
-      </c>
-      <c r="H107" s="12"/>
-      <c r="I107" s="12"/>
-      <c r="J107" s="12"/>
-      <c r="K107" s="12"/>
-      <c r="L107" s="12"/>
-      <c r="M107" s="12"/>
-      <c r="N107" s="12"/>
-      <c r="O107" s="12"/>
-      <c r="P107" s="12"/>
-      <c r="Q107" s="12"/>
+      <c r="E107" s="268"/>
     </row>
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
-      <c r="B108" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="C108" s="94">
-        <f>C102/C$4</f>
-        <v>0</v>
-      </c>
+      <c r="B108" s="91" t="s">
+        <v>219</v>
+      </c>
+      <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
       <c r="F108" s="26"/>
-      <c r="G108" s="94" t="e">
-        <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="I108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="J108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="K108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="L108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="M108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="N108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="O108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="P108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="Q108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
+      <c r="G108" s="97" t="s">
+        <v>218</v>
+      </c>
+      <c r="H108" s="12"/>
+      <c r="I108" s="12"/>
+      <c r="J108" s="12"/>
+      <c r="K108" s="12"/>
+      <c r="L108" s="12"/>
+      <c r="M108" s="12"/>
+      <c r="N108" s="12"/>
+      <c r="O108" s="12"/>
+      <c r="P108" s="12"/>
+      <c r="Q108" s="12"/>
     </row>
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
@@ -13744,701 +13713,757 @@
       <c r="E109" s="269"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94" t="e">
-        <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
+        <f t="shared" ref="G109:Q109" si="43">IF(G$4="","",G103/G$4)</f>
         <v>#VALUE!</v>
       </c>
       <c r="H109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="I109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="J109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="L109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="M109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="N109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="O109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="P109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="Q109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
     <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>69</v>
+        <v>217</v>
       </c>
       <c r="C110" s="94">
-        <f>BS!$G$38/C$4</f>
+        <f>C104/C$4</f>
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
       <c r="E110" s="269"/>
       <c r="F110" s="26"/>
-      <c r="G110" s="94">
-        <f>BS!$G$38/G$4</f>
-        <v>0</v>
-      </c>
-      <c r="H110" s="204"/>
-      <c r="I110" s="204"/>
-      <c r="J110" s="204"/>
-      <c r="K110" s="204"/>
-      <c r="L110" s="204"/>
-      <c r="M110" s="204"/>
-      <c r="N110" s="204"/>
-      <c r="O110" s="204"/>
-      <c r="P110" s="204"/>
-      <c r="Q110" s="204"/>
+      <c r="G110" s="94" t="e">
+        <f t="shared" ref="G110:Q110" si="44">IF(G$4="","",G104/G$4)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="I110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="J110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="K110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="L110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="M110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="N110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="O110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="P110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="Q110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="268"/>
+      <c r="B111" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C111" s="94">
+        <f>BS!$G$38/C$4</f>
+        <v>0</v>
+      </c>
+      <c r="D111" s="26"/>
+      <c r="E111" s="269"/>
+      <c r="F111" s="26"/>
+      <c r="G111" s="94">
+        <f>BS!$G$38/G$4</f>
+        <v>0</v>
+      </c>
+      <c r="H111" s="204"/>
+      <c r="I111" s="204"/>
+      <c r="J111" s="204"/>
+      <c r="K111" s="204"/>
+      <c r="L111" s="204"/>
+      <c r="M111" s="204"/>
+      <c r="N111" s="204"/>
+      <c r="O111" s="204"/>
+      <c r="P111" s="204"/>
+      <c r="Q111" s="204"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
-      <c r="B112" s="64" t="s">
-        <v>51</v>
-      </c>
       <c r="E112" s="268"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
-      <c r="B113" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C113" s="169"/>
+      <c r="B113" s="64" t="s">
+        <v>51</v>
+      </c>
       <c r="E113" s="268"/>
-      <c r="G113" s="295">
-        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
-        <v>-3.0617491063478339</v>
-      </c>
-      <c r="H113" s="295" t="str">
-        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
-        <v/>
-      </c>
-      <c r="I113" s="295" t="str">
-        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
-        <v/>
-      </c>
-      <c r="J113" s="295" t="str">
-        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
-        <v/>
-      </c>
-      <c r="K113" s="295" t="str">
-        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
-        <v/>
-      </c>
-      <c r="L113" s="295" t="str">
-        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
-        <v/>
-      </c>
-      <c r="M113" s="295" t="str">
-        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
-        <v/>
-      </c>
-      <c r="N113" s="295" t="str">
-        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
-        <v/>
-      </c>
-      <c r="O113" s="295" t="str">
-        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
-        <v/>
-      </c>
-      <c r="P113" s="295" t="str">
-        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
-        <v/>
-      </c>
-      <c r="Q113" s="295" t="str">
-        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
-        <v/>
-      </c>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
       <c r="G114" s="295">
+        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
+        <v>-3.0617491063478339</v>
+      </c>
+      <c r="H114" s="295" t="str">
+        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
+        <v/>
+      </c>
+      <c r="I114" s="295" t="str">
+        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
+        <v/>
+      </c>
+      <c r="J114" s="295" t="str">
+        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
+        <v/>
+      </c>
+      <c r="K114" s="295" t="str">
+        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
+        <v/>
+      </c>
+      <c r="L114" s="295" t="str">
+        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
+        <v/>
+      </c>
+      <c r="M114" s="295" t="str">
+        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
+        <v/>
+      </c>
+      <c r="N114" s="295" t="str">
+        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
+        <v/>
+      </c>
+      <c r="O114" s="295" t="str">
+        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
+        <v/>
+      </c>
+      <c r="P114" s="295" t="str">
+        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
+        <v/>
+      </c>
+      <c r="Q114" s="295" t="str">
+        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A115" s="10"/>
+      <c r="B115" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C115" s="169"/>
+      <c r="E115" s="268"/>
+      <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.1497063441297901</v>
       </c>
-      <c r="H114" s="295" t="str">
+      <c r="H115" s="295" t="str">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v/>
       </c>
-      <c r="I114" s="295" t="str">
+      <c r="I115" s="295" t="str">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v/>
       </c>
-      <c r="J114" s="295" t="str">
+      <c r="J115" s="295" t="str">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v/>
       </c>
-      <c r="K114" s="295" t="str">
+      <c r="K115" s="295" t="str">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v/>
       </c>
-      <c r="L114" s="295" t="str">
+      <c r="L115" s="295" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v/>
       </c>
-      <c r="M114" s="295" t="str">
+      <c r="M115" s="295" t="str">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v/>
       </c>
-      <c r="N114" s="295" t="str">
+      <c r="N115" s="295" t="str">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v/>
       </c>
-      <c r="O114" s="295" t="str">
+      <c r="O115" s="295" t="str">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v/>
       </c>
-      <c r="P114" s="295" t="str">
+      <c r="P115" s="295" t="str">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v/>
       </c>
-      <c r="Q114" s="295" t="str">
+      <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
-    </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A115" s="10"/>
-      <c r="E115" s="268"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
-      <c r="B116" s="91" t="s">
-        <v>38</v>
-      </c>
-      <c r="C116" s="55"/>
-      <c r="D116" s="55"/>
-      <c r="E116" s="271"/>
-      <c r="F116" s="55"/>
-      <c r="G116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*H118*(1/#REF!)=H120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*I118*(1/#REF!)=I120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*J118*(1/#REF!)=J120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*K118*(1/#REF!)=K120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*L118*(1/#REF!)=L120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*M118*(1/#REF!)=M120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*N118*(1/#REF!)=N120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*O118*(1/#REF!)=O120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*P118*(1/#REF!)=P120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*Q118*(1/#REF!)=Q120,"","Error"),"")</f>
-        <v/>
-      </c>
+      <c r="E116" s="268"/>
     </row>
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
-      <c r="B117" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C117" s="23">
+      <c r="B117" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="C117" s="55"/>
+      <c r="D117" s="55"/>
+      <c r="E117" s="271"/>
+      <c r="F117" s="55"/>
+      <c r="G117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*G119*(1/#REF!)=G121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*H119*(1/#REF!)=H121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*I119*(1/#REF!)=I121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*J119*(1/#REF!)=J121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*K119*(1/#REF!)=K121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*L119*(1/#REF!)=L121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*M119*(1/#REF!)=M121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*N119*(1/#REF!)=N121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*O119*(1/#REF!)=O121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*P119*(1/#REF!)=P121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*Q119*(1/#REF!)=Q121,"","Error"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A118" s="10"/>
+      <c r="B118" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
         <v>-1.1649701082565843E-2</v>
       </c>
-      <c r="E117" s="268"/>
-      <c r="G117" s="23">
-        <f t="shared" ref="G117:Q117" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
+      <c r="E118" s="268"/>
+      <c r="G118" s="23">
+        <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
         <v>1.4678118322150659</v>
       </c>
-      <c r="H117" s="23" t="str">
+      <c r="H118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="I117" s="23" t="str">
+      <c r="I118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="J117" s="23" t="str">
+      <c r="J118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="K117" s="23" t="str">
+      <c r="K118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="L117" s="23" t="str">
+      <c r="L118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="M117" s="23" t="str">
+      <c r="M118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="N117" s="23" t="str">
+      <c r="N118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="O117" s="23" t="str">
+      <c r="O118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="P117" s="23" t="str">
+      <c r="P118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="Q117" s="23" t="str">
+      <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
-        <v/>
-      </c>
-    </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B118" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C118" s="42">
-        <f>IF(valuation_method="DDM",(C4+C12)/C101,C4/C101)</f>
-        <v>15472.5</v>
-      </c>
-      <c r="E118" s="268"/>
-      <c r="G118" s="42">
-        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G101,G4/G101))</f>
-        <v>-33459.5</v>
-      </c>
-      <c r="H118" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="I118" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="J118" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="K118" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="L118" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="M118" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="N118" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="O118" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="P118" s="42" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="Q118" s="42" t="str">
-        <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
     <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C119" s="42">
+        <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
+        <v>15472.5</v>
+      </c>
+      <c r="E119" s="268"/>
+      <c r="G119" s="42">
+        <f t="shared" ref="G119:Q119" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G102,G4/G102))</f>
+        <v>-33459.5</v>
+      </c>
+      <c r="H119" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="I119" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="J119" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="K119" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="L119" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="M119" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="N119" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="O119" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="P119" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="Q119" s="42" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+    </row>
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B120" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C119" s="15">
-        <f>C101/C105</f>
+      <c r="C120" s="15">
+        <f>C102/C106</f>
         <v>1.3333333333333333</v>
       </c>
-      <c r="D119" s="11"/>
-      <c r="E119" s="272"/>
-      <c r="F119" s="11"/>
-      <c r="G119" s="15">
-        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
+      <c r="D120" s="11"/>
+      <c r="E120" s="272"/>
+      <c r="F120" s="11"/>
+      <c r="G120" s="15">
+        <f t="shared" ref="G120:Q120" si="47">IF(G$4="","",G102/G106)</f>
         <v>1.3333333333333333</v>
       </c>
-      <c r="H119" s="15" t="str">
+      <c r="H120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="I119" s="15" t="str">
+      <c r="I120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="J119" s="15" t="str">
+      <c r="J120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="K119" s="15" t="str">
+      <c r="K120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="L119" s="15" t="str">
+      <c r="L120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="M119" s="15" t="str">
+      <c r="M120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="N119" s="15" t="str">
+      <c r="N120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="O119" s="15" t="str">
+      <c r="O120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="P119" s="15" t="str">
+      <c r="P120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="Q119" s="15" t="str">
+      <c r="Q120" s="15" t="str">
         <f t="shared" si="47"/>
-        <v/>
-      </c>
-    </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A120" s="10"/>
-      <c r="B120" s="70" t="s">
-        <v>222</v>
-      </c>
-      <c r="C120" s="102">
-        <f>C13/C105</f>
-        <v>-240.33333333333334</v>
-      </c>
-      <c r="D120" s="103"/>
-      <c r="E120" s="271"/>
-      <c r="F120" s="103"/>
-      <c r="G120" s="102">
-        <f>IF(G$4="","",G13/G105)</f>
-        <v>-65483</v>
-      </c>
-      <c r="H120" s="102" t="str">
-        <f t="shared" ref="H120:Q120" si="48">IF(H$4="","",H13/H105)</f>
-        <v/>
-      </c>
-      <c r="I120" s="102" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="J120" s="102" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="K120" s="102" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="L120" s="102" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="M120" s="102" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="N120" s="102" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="O120" s="102" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="P120" s="102" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="Q120" s="102" t="str">
-        <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
     <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
-      <c r="B121" s="27"/>
-      <c r="C121" s="62"/>
-      <c r="D121" s="27"/>
-      <c r="E121" s="67"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="12"/>
-      <c r="H121" s="12"/>
-      <c r="I121" s="12"/>
-      <c r="J121" s="12"/>
-      <c r="K121" s="12"/>
-      <c r="L121" s="12"/>
-      <c r="M121" s="12"/>
-      <c r="N121" s="12"/>
-      <c r="O121" s="12"/>
-      <c r="P121" s="12"/>
-      <c r="Q121" s="12"/>
+      <c r="B121" s="70" t="s">
+        <v>221</v>
+      </c>
+      <c r="C121" s="102">
+        <f>C13/C106</f>
+        <v>-240.33333333333334</v>
+      </c>
+      <c r="D121" s="103"/>
+      <c r="E121" s="271"/>
+      <c r="F121" s="103"/>
+      <c r="G121" s="102">
+        <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
+        <v>-65483</v>
+      </c>
+      <c r="H121" s="102" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="I121" s="102" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="J121" s="102" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="K121" s="102" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="L121" s="102" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="M121" s="102" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="N121" s="102" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="O121" s="102" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="P121" s="102" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="Q121" s="102" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
     </row>
     <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
-      <c r="B122" s="54" t="s">
-        <v>223</v>
-      </c>
-      <c r="C122" s="54"/>
-      <c r="D122" s="56"/>
-      <c r="E122" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="F122" s="56"/>
-      <c r="G122" s="37"/>
-      <c r="H122" s="37"/>
-      <c r="I122" s="37"/>
-      <c r="J122" s="37"/>
-      <c r="K122" s="37"/>
-      <c r="L122" s="37"/>
-      <c r="M122" s="37"/>
-      <c r="N122" s="37"/>
-      <c r="O122" s="37"/>
-      <c r="P122" s="37"/>
-      <c r="Q122" s="37"/>
+      <c r="B122" s="27"/>
+      <c r="C122" s="62"/>
+      <c r="D122" s="27"/>
+      <c r="E122" s="67"/>
+      <c r="F122" s="27"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+      <c r="I122" s="12"/>
+      <c r="J122" s="12"/>
+      <c r="K122" s="12"/>
+      <c r="L122" s="12"/>
+      <c r="M122" s="12"/>
+      <c r="N122" s="12"/>
+      <c r="O122" s="12"/>
+      <c r="P122" s="12"/>
+      <c r="Q122" s="12"/>
     </row>
     <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
-      <c r="B123" s="178" t="s">
-        <v>170</v>
-      </c>
-      <c r="C123" s="179"/>
-      <c r="D123" s="27"/>
-      <c r="E123" s="265"/>
-      <c r="F123" s="27"/>
-      <c r="G123" s="12"/>
-      <c r="H123" s="12"/>
-      <c r="I123" s="12"/>
-      <c r="J123" s="12"/>
-      <c r="K123" s="12"/>
-      <c r="L123" s="12"/>
-      <c r="M123" s="12"/>
-      <c r="N123" s="12"/>
-      <c r="O123" s="12"/>
-      <c r="P123" s="12"/>
-      <c r="Q123" s="12"/>
+      <c r="B123" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="C123" s="54"/>
+      <c r="D123" s="56"/>
+      <c r="E123" s="66" t="s">
+        <v>59</v>
+      </c>
+      <c r="F123" s="56"/>
+      <c r="G123" s="37"/>
+      <c r="H123" s="37"/>
+      <c r="I123" s="37"/>
+      <c r="J123" s="37"/>
+      <c r="K123" s="37"/>
+      <c r="L123" s="37"/>
+      <c r="M123" s="37"/>
+      <c r="N123" s="37"/>
+      <c r="O123" s="37"/>
+      <c r="P123" s="37"/>
+      <c r="Q123" s="37"/>
     </row>
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
-      <c r="B124" s="27" t="str">
-        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
-        <v>FCFE per share (CNY)</v>
-      </c>
-      <c r="C124" s="177">
-        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>-2.6029743804743193E-2</v>
-      </c>
+      <c r="B124" s="178" t="s">
+        <v>169</v>
+      </c>
+      <c r="C124" s="179"/>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
-      <c r="G124" s="177">
-        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>-9.9336145178400823</v>
-      </c>
-      <c r="H124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="I124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="J124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="K124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="L124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="M124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="N124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="O124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="P124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="Q124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
+      <c r="G124" s="12"/>
+      <c r="H124" s="12"/>
+      <c r="I124" s="12"/>
+      <c r="J124" s="12"/>
+      <c r="K124" s="12"/>
+      <c r="L124" s="12"/>
+      <c r="M124" s="12"/>
+      <c r="N124" s="12"/>
+      <c r="O124" s="12"/>
+      <c r="P124" s="12"/>
+      <c r="Q124" s="12"/>
     </row>
     <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
-      <c r="B125" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="C125" s="77">
-        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>-1.1466847491076299E-3</v>
+      <c r="B125" s="27" t="str">
+        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
+        <v>FCFE per share (CNY)</v>
+      </c>
+      <c r="C125" s="177">
+        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
+        <v>-2.6029743804743193E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
-      <c r="G125" s="77">
-        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
+      <c r="G125" s="177">
+        <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>-9.9336145178400823</v>
+      </c>
+      <c r="H125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="I125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="J125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="K125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="L125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="M125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="N125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="O125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="P125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="Q125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A126" s="10"/>
+      <c r="B126" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C126" s="77">
+        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
+        <v>-1.1466847491076299E-3</v>
+      </c>
+      <c r="D126" s="27"/>
+      <c r="E126" s="265"/>
+      <c r="F126" s="27"/>
+      <c r="G126" s="77">
+        <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
         <v>-0.43760416378150141</v>
       </c>
-      <c r="H125" s="77" t="str">
-        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="I125" s="77" t="str">
-        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="J125" s="77" t="str">
-        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="K125" s="77" t="str">
-        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="L125" s="77" t="str">
-        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="M125" s="77" t="str">
-        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="N125" s="77" t="str">
-        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="O125" s="77" t="str">
-        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="P125" s="77" t="str">
-        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="Q125" s="77" t="str">
-        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B126" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="C126" s="169"/>
-      <c r="G126" s="23">
+      <c r="H126" s="77" t="str">
+        <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="I126" s="77" t="str">
+        <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="J126" s="77" t="str">
+        <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="K126" s="77" t="str">
+        <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="L126" s="77" t="str">
+        <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="M126" s="77" t="str">
+        <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="N126" s="77" t="str">
+        <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="O126" s="77" t="str">
+        <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="P126" s="77" t="str">
+        <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="Q126" s="77" t="str">
+        <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B127" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C127" s="169"/>
+      <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.16432315837836217</v>
       </c>
-      <c r="H126" s="23" t="str">
+      <c r="H127" s="23" t="str">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
-      <c r="I126" s="23" t="str">
+      <c r="I127" s="23" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
-      <c r="J126" s="23" t="str">
+      <c r="J127" s="23" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
-      <c r="K126" s="23" t="str">
+      <c r="K127" s="23" t="str">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
-      <c r="L126" s="23" t="str">
+      <c r="L127" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
-      <c r="M126" s="23" t="str">
+      <c r="M127" s="23" t="str">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
-      <c r="N126" s="23" t="str">
+      <c r="N127" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
-      <c r="O126" s="23" t="str">
+      <c r="O127" s="23" t="str">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
-      <c r="P126" s="23" t="str">
+      <c r="P127" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
-      <c r="Q126" s="23" t="str">
+      <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="129" ht="15.75" customHeight="1"/>
     <row r="130" ht="15.75" customHeight="1"/>
@@ -15120,6 +15145,7 @@
     <row r="806" ht="15.75" customHeight="1"/>
     <row r="807" ht="15.75" customHeight="1"/>
     <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15164,20 +15190,20 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1000000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
@@ -15188,7 +15214,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Terminal_Growth</f>
@@ -15198,7 +15224,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -15209,7 +15235,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -15219,15 +15245,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="364" t="s">
-        <v>249</v>
-      </c>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366" t="s">
+        <v>248</v>
+      </c>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
@@ -15237,13 +15263,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="364"/>
-      <c r="F7" s="364"/>
+      <c r="E7" s="366"/>
+      <c r="F7" s="366"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
@@ -15253,13 +15279,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="364"/>
-      <c r="F8" s="364"/>
+      <c r="E8" s="366"/>
+      <c r="F8" s="366"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
@@ -15269,13 +15295,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="364"/>
-      <c r="F9" s="364"/>
+      <c r="E9" s="366"/>
+      <c r="F9" s="366"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
@@ -15289,7 +15315,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
@@ -15320,7 +15346,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15330,13 +15356,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H15" s="120"/>
     </row>
     <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
@@ -15346,7 +15372,7 @@
     </row>
     <row r="17" spans="2:17" ht="13.35" customHeight="1">
       <c r="B17" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
@@ -15379,7 +15405,7 @@
         <v>108</v>
       </c>
       <c r="D20" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E20" s="128" t="s">
         <v>109</v>
@@ -16151,7 +16177,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -16188,7 +16214,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C54" s="136"/>
       <c r="D54" s="136"/>
@@ -16409,7 +16435,7 @@
     </row>
     <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="114"/>
@@ -16638,19 +16664,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C73" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D73" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E73" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E73" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F73" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -16775,7 +16801,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C80" s="155" t="s">
         <v>105</v>
@@ -16912,7 +16938,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -16924,23 +16950,23 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1000000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C4" s="114">
-        <f>Normalized_FCF!C91</f>
+        <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
         <v>22020.769943020001</v>
       </c>
       <c r="D4" t="str">
@@ -16948,7 +16974,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
@@ -16958,7 +16984,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -16969,7 +16995,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -16979,13 +17005,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366"/>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -17002,7 +17028,7 @@
     </row>
     <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -17012,13 +17038,13 @@
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H10" s="120"/>
     </row>
     <row r="11" spans="2:8" ht="13.35" customHeight="1">
       <c r="B11" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
@@ -17028,7 +17054,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.35" customHeight="1">
       <c r="B12" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
@@ -17058,16 +17084,16 @@
         <v>107</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E15" s="128" t="s">
         <v>109</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -17733,7 +17759,7 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
@@ -17770,7 +17796,7 @@
     </row>
     <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C49" s="136"/>
       <c r="D49" s="136"/>
@@ -17941,7 +17967,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C58" s="114"/>
       <c r="D58" s="114"/>
@@ -18160,19 +18186,19 @@
     </row>
     <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C68" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D68" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E68" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E68" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F68" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -18297,7 +18323,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C75" s="155" t="s">
         <v>105</v>
@@ -18361,20 +18387,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I2" s="249"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H3" s="247">
         <v>0</v>
@@ -18386,14 +18412,14 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C4" s="120">
         <v>3</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F4" s="155"/>
       <c r="H4" s="247">
@@ -18422,7 +18448,7 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="247">
@@ -18435,7 +18461,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C7" s="338">
         <f>Normalized_FCF!G8</f>
@@ -18445,11 +18471,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="366" t="str">
+      <c r="E7" s="368" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 兴业银行(601166.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="366"/>
+      <c r="F7" s="368"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18470,8 +18496,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="368"/>
+      <c r="F8" s="368"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18492,8 +18518,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="368"/>
+      <c r="F9" s="368"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18503,8 +18529,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="366"/>
-      <c r="F10" s="366"/>
+      <c r="E10" s="368"/>
+      <c r="F10" s="368"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18515,10 +18541,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>454</v>
-      </c>
-      <c r="E11" s="366"/>
-      <c r="F11" s="366"/>
+        <v>451</v>
+      </c>
+      <c r="E11" s="368"/>
+      <c r="F11" s="368"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18529,15 +18555,15 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" s="158" t="e">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="366"/>
-      <c r="F12" s="366"/>
+      <c r="E12" s="368"/>
+      <c r="F12" s="368"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18548,14 +18574,14 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C13" s="158" t="e">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E13" s="366"/>
-      <c r="F13" s="366"/>
+      <c r="E13" s="368"/>
+      <c r="F13" s="368"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18572,12 +18598,12 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E14" s="366"/>
-      <c r="F14" s="366"/>
+      <c r="E14" s="368"/>
+      <c r="F14" s="368"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -18586,38 +18612,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="366" t="s">
-        <v>332</v>
-      </c>
-      <c r="F18" s="367"/>
+      <c r="E18" s="368" t="s">
+        <v>329</v>
+      </c>
+      <c r="F18" s="369"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="367"/>
-      <c r="F19" s="367"/>
+      <c r="E19" s="369"/>
+      <c r="F19" s="369"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>304</v>
-      </c>
-      <c r="E20" s="367"/>
-      <c r="F20" s="367"/>
+        <v>303</v>
+      </c>
+      <c r="E20" s="369"/>
+      <c r="F20" s="369"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
@@ -18627,12 +18653,12 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="367"/>
-      <c r="F21" s="367"/>
+      <c r="E21" s="369"/>
+      <c r="F21" s="369"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -18642,44 +18668,44 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="367"/>
-      <c r="F22" s="367"/>
+      <c r="E22" s="369"/>
+      <c r="F22" s="369"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F24" s="159"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C25" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="365"/>
-      <c r="F25" s="365"/>
+      <c r="E25" s="367"/>
+      <c r="F25" s="367"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" s="164">
         <v>0.02</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="365"/>
-      <c r="F26" s="365"/>
+      <c r="E26" s="367"/>
+      <c r="F26" s="367"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
@@ -18689,55 +18715,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="365"/>
-      <c r="F27" s="365"/>
+      <c r="E27" s="367"/>
+      <c r="F27" s="367"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" s="165">
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="365"/>
-      <c r="F28" s="365"/>
+      <c r="E28" s="367"/>
+      <c r="F28" s="367"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E30" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F30" s="159"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C31" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="365"/>
-      <c r="F31" s="365"/>
+      <c r="E31" s="367"/>
+      <c r="F31" s="367"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C32" s="164">
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="365"/>
-      <c r="F32" s="365"/>
+      <c r="E32" s="367"/>
+      <c r="F32" s="367"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
@@ -18747,55 +18773,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="365"/>
-      <c r="F33" s="365"/>
+      <c r="E33" s="367"/>
+      <c r="F33" s="367"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C34" s="165">
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="365"/>
-      <c r="F34" s="365"/>
+      <c r="E34" s="367"/>
+      <c r="F34" s="367"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E36" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F36" s="159"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C37" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="365"/>
-      <c r="F37" s="365"/>
+      <c r="E37" s="367"/>
+      <c r="F37" s="367"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" s="164">
         <v>0.03</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="365"/>
-      <c r="F38" s="365"/>
+      <c r="E38" s="367"/>
+      <c r="F38" s="367"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
@@ -18805,24 +18831,24 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="365"/>
-      <c r="F39" s="365"/>
+      <c r="E39" s="367"/>
+      <c r="F39" s="367"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C40" s="167">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="365"/>
-      <c r="F40" s="365"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -18835,7 +18861,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -18844,12 +18870,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C46" s="150">
         <v>10</v>
@@ -18864,39 +18890,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E48" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F48" s="159"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C49" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="365"/>
-      <c r="F49" s="365"/>
+      <c r="E49" s="367"/>
+      <c r="F49" s="367"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C50" s="164">
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="365"/>
-      <c r="F50" s="365"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
@@ -18906,55 +18932,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="365"/>
-      <c r="F51" s="365"/>
+      <c r="E51" s="367"/>
+      <c r="F51" s="367"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C52" s="165">
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="365"/>
-      <c r="F52" s="365"/>
+      <c r="E52" s="367"/>
+      <c r="F52" s="367"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E54" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F54" s="159"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C55" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="365"/>
-      <c r="F55" s="365"/>
+      <c r="E55" s="367"/>
+      <c r="F55" s="367"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C56" s="164">
         <v>0.04</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="365"/>
-      <c r="F56" s="365"/>
+      <c r="E56" s="367"/>
+      <c r="F56" s="367"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
@@ -18964,23 +18990,23 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="365"/>
-      <c r="F57" s="365"/>
+      <c r="E57" s="367"/>
+      <c r="F57" s="367"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C58" s="165">
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="365"/>
-      <c r="F58" s="365"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -18991,7 +19017,7 @@
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19000,7 +19026,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19009,15 +19035,15 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E63" s="252" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C64" s="166">
         <f>C18</f>
@@ -19025,19 +19051,19 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C65" s="151">
         <v>2.3752619295331442E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -19053,20 +19079,20 @@
         <v>CNY</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19076,19 +19102,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19098,14 +19124,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19114,7 +19140,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -19123,12 +19149,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19138,10 +19164,10 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>111</v>
+        <v>463</v>
       </c>
       <c r="C77" s="173">
-        <f>Normalized_FCF!C90</f>
+        <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
         <v>1.06</v>
       </c>
       <c r="D77" t="str">
@@ -19151,12 +19177,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
@@ -19165,7 +19191,7 @@
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -19177,7 +19203,7 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
@@ -19198,7 +19224,7 @@
         <v>CNY</v>
       </c>
       <c r="E83" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
@@ -19210,12 +19236,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19228,7 +19254,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -19240,12 +19266,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19254,7 +19280,7 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
@@ -19266,7 +19292,7 @@
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
@@ -19287,7 +19313,7 @@
         <v>CNY</v>
       </c>
       <c r="E93" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
@@ -19296,14 +19322,14 @@
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19314,7 +19340,7 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
@@ -19326,7 +19352,7 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
@@ -19338,17 +19364,17 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
         <v>14.420004978927032</v>
       </c>
       <c r="D99" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E99" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
@@ -19360,12 +19386,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19374,7 +19400,7 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
@@ -19384,7 +19410,7 @@
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
@@ -19394,17 +19420,17 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
         <v>13.026100491992562</v>
       </c>
       <c r="D105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E105" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
@@ -19416,32 +19442,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
+        <v>324</v>
+      </c>
+      <c r="F110" s="284" t="s">
         <v>327</v>
-      </c>
-      <c r="F110" s="284" t="s">
-        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/templates/Valuation_v2.0.xlsx
+++ b/financial_models/templates/Valuation_v2.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2F4B9A-16E0-40A7-8135-7BB5B9F8803D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD72D39-C188-4510-A765-E015799D97EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
+    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="465">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2471,6 +2472,9 @@
   </si>
   <si>
     <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
   </si>
 </sst>
 </file>
@@ -3893,29 +3897,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4389,13 +4393,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4597,22 +4601,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>338</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4628,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4654,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4689,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4711,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4781,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4803,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>337</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4825,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>342</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4971,22 +4975,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5034,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5086,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5105,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>343</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5233,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5278,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5427,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5446,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5794,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5837,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5851,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,17 +5890,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5913,6 +5906,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -19484,4 +19488,27 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+  <dimension ref="B2:E2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>464</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/financial_models/templates/Valuation_v2.0.xlsx
+++ b/financial_models/templates/Valuation_v2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD72D39-C188-4510-A765-E015799D97EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43400BA7-FF71-480F-B9C0-8F842B1CDA97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,6 +21,7 @@
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
     <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
+    <sheet name="投资主题" sheetId="12" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
@@ -42,20 +43,14 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="465">
-  <si>
-    <t>Number of Shares:</t>
-  </si>
-  <si>
-    <t>Exchange Rate:</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="559">
   <si>
     <t>Sales</t>
   </si>
@@ -398,10 +393,6 @@
   </si>
   <si>
     <t>Debt/EBIT</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Price:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1335,10 +1326,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Update Required After:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>FCFE/Market Cap</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1495,10 +1482,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1516,10 +1499,6 @@
   </si>
   <si>
     <t>Note on the logic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Company Name</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1759,71 +1738,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 2: The No-Growth Baseline (Calculating Stable Income Value)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Step 3: Adjusting for Financial Structure (Calculating No Growth Equity Value)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 4: Incorporating Future Potential &amp; Risk (Scenario Analysis)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">Guidance Note: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>This model determines a target buy price consistent with defined investment criteria. It follows a logical progression: establishing current sustainable earnings, adjusting for financial structure, incorporating growth scenarios, and finally applying the investor’s required return.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates for its equity owners, stripping away temporary fluctuations or accounting choices.The FCFE/Market Cap yield gives a direct measure of this cash generation relative to the current market price.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1863,32 +1782,6 @@
         <family val="2"/>
         <scheme val="major"/>
       </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To determine the intrinsic value of the company’s equity if the Normalized FCFE (calculated in Step 1) were to remain constant perpetually, with zero future growth. This establishes a baseline value derived solely from the current sustainable earnings power.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
       <t>Cost of Equity:</t>
     </r>
     <r>
@@ -1986,30 +1879,6 @@
     <r>
       <rPr>
         <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To estimate the company’s intrinsic value by considering plausible future scenarios beyond the static no-growth assumption. Based on fundamental research, each scenario defines high growth periods (HGP), high growth rates (HGR), and its probability.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
         <i/>
         <sz val="9"/>
         <color rgb="FF000000"/>
@@ -2033,58 +1902,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Calculation Logic:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Insight:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CFO</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2102,23 +1919,6 @@
   </si>
   <si>
     <t>Key Risk Factors</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Goal: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>To identify and assess the key risk factors inherent in this valuation model, focusing on those with the greatest potential impact on the final result.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2161,10 +1961,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation, prioritizing consistency and long-term decision-making over market-derived metrics.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium to account for ownership risks.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>- The Expected Equity Value is heavily dependent on the specific growth rates (HGR), durations (HGP), and probabilities assigned to each scenario. These are inherently forecasts about an uncertain future.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2283,10 +2079,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -2333,148 +2125,1163 @@
     <t>Market Currency</t>
   </si>
   <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>兴业银行</t>
+  </si>
+  <si>
+    <t>601166.SS</t>
+  </si>
+  <si>
+    <t>FIN_01</t>
+  </si>
+  <si>
+    <t>DDM</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>DuPont Analysis</t>
+  </si>
+  <si>
+    <t>ROE =</t>
+  </si>
+  <si>
+    <t>Normalized</t>
+  </si>
+  <si>
+    <t>Latest</t>
+  </si>
+  <si>
+    <t>LT AR and Prepayments</t>
+  </si>
+  <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
+  </si>
+  <si>
+    <t>模型最后更新日期:</t>
+  </si>
+  <si>
+    <t>执行摘要</t>
+  </si>
+  <si>
+    <t>公司信息</t>
+  </si>
+  <si>
+    <t>上市信息</t>
+  </si>
+  <si>
+    <t>增长分类:</t>
+  </si>
+  <si>
+    <t>对比板块:</t>
+  </si>
+  <si>
+    <t>商业模式风险溢价:</t>
+  </si>
+  <si>
+    <t>管理风险溢价:</t>
+  </si>
+  <si>
+    <t>报告货币:</t>
+  </si>
+  <si>
+    <t>市场隐含年回报率:</t>
+  </si>
+  <si>
+    <t>估值方法</t>
+  </si>
+  <si>
+    <t>估值输出</t>
+  </si>
+  <si>
+    <t>目标价格</t>
+  </si>
+  <si>
+    <t>入场价格</t>
+  </si>
+  <si>
+    <t>卖出价格</t>
+  </si>
+  <si>
+    <t>退出价格</t>
+  </si>
+  <si>
+    <t>持有期</t>
+  </si>
+  <si>
+    <t>入场收益率</t>
+  </si>
+  <si>
+    <t>目标回报率</t>
+  </si>
+  <si>
+    <t>基准收益率</t>
+  </si>
+  <si>
+    <t>步骤1：确定公司可持续盈利能力（计算标准化FCFE）</t>
+  </si>
+  <si>
+    <t>Company Name:</t>
+  </si>
+  <si>
+    <t>Number of Shares:</t>
+  </si>
+  <si>
+    <t>Report Interval:</t>
+  </si>
+  <si>
+    <t>Update Required After:</t>
+  </si>
+  <si>
     <t>Symbol:</t>
   </si>
   <si>
-    <t>Listing Information</t>
+    <t>Market Price:</t>
+  </si>
+  <si>
+    <t>Market Currency:</t>
+  </si>
+  <si>
+    <t>Market Capitalization:</t>
   </si>
   <si>
     <t>Forex Symbol:</t>
   </si>
   <si>
-    <t>Capitalization:</t>
-  </si>
-  <si>
-    <t>@Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Exit Price Output</t>
-  </si>
-  <si>
-    <t>Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Target return</t>
-  </si>
-  <si>
-    <t>Target Price</t>
-  </si>
-  <si>
-    <t>Entry Price</t>
-  </si>
-  <si>
-    <t>Sell Price</t>
-  </si>
-  <si>
-    <t>Exit Price</t>
-  </si>
-  <si>
-    <t>Holding Period</t>
-  </si>
-  <si>
-    <t>Risk Premium</t>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-  </si>
-  <si>
-    <t>Result (Exit)</t>
-  </si>
-  <si>
-    <t>Valuation Outputs</t>
-  </si>
-  <si>
-    <t>Business Model Risk Premium:</t>
-  </si>
-  <si>
-    <t>Management Risk Premium:</t>
-  </si>
-  <si>
-    <t>Base equity cost</t>
-  </si>
-  <si>
-    <t>Entry yield</t>
-  </si>
-  <si>
-    <t>Benchmark yield</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>兴业银行</t>
-  </si>
-  <si>
-    <t>601166.SS</t>
-  </si>
-  <si>
-    <t>FIN_01</t>
-  </si>
-  <si>
-    <t>DDM</t>
-  </si>
-  <si>
-    <t>Dividend</t>
-  </si>
-  <si>
-    <t>Dividend Value</t>
-  </si>
-  <si>
-    <t>No-Growth DDM</t>
-  </si>
-  <si>
-    <t>No-Growth DDM Valuation</t>
-  </si>
-  <si>
-    <t>Dividend Value per share</t>
-  </si>
-  <si>
-    <t>PV of Dividends</t>
-  </si>
-  <si>
-    <t>Dividends</t>
-  </si>
-  <si>
-    <t>YoY CAGR</t>
-  </si>
-  <si>
-    <t>Payout Ratio:</t>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
-  </si>
-  <si>
-    <t>INT</t>
-  </si>
-  <si>
-    <t>DuPont Analysis</t>
-  </si>
-  <si>
-    <t>ROE =</t>
-  </si>
-  <si>
-    <t>Normalized</t>
-  </si>
-  <si>
-    <t>Latest</t>
-  </si>
-  <si>
-    <t>LT AR and Prepayments</t>
-  </si>
-  <si>
-    <t>Dividend after tax Yield</t>
-  </si>
-  <si>
-    <t>Dividend tax rate</t>
-  </si>
-  <si>
-    <t>After tax Dividend/Market Cap =</t>
-  </si>
-  <si>
-    <t>After-tax Dividend per share</t>
-  </si>
-  <si>
-    <t>Divisional Analysis (Optional)</t>
+    <t>Exchange Rate:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Guidance Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>This model evaluates the company using a structured investment process to determine its intrinsic value and target prices. It focuses on sustainable FCF capacity, adjusts for financial structure, incorporates growth scenarios, and calculates expected returns based on the derived intrinsic value.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates, stripping away temporary fluctuations or accounting choices.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 2: Calculating the No-Growth Baseline (Calculating Stable Income Value)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Determine the intrinsic value assuming the current Normalized FCFE remains constant with no growth, providing a conservative baseline.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 4: Incorporating Future Potential (Scenario Analysis)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Estimate intrinsic value by modeling plausible FCFE/Dividend, high growth periods (HGP), and high growth rates (HGR) scenarios, weighted by probability.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Insight:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 5: Determining Investment Decisions</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Calculation Logic:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Discount future dividends and the expected equity value at the target return rates.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Highlight risks impacting the valuation, focusing on factors affecting FCFE/dividend sustainability.</t>
+    </r>
+  </si>
+  <si>
+    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF/DDM analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium.</t>
+  </si>
+  <si>
+    <t>公司名称：</t>
+  </si>
+  <si>
+    <t>股份数量：</t>
+  </si>
+  <si>
+    <t>报告间隔：</t>
+  </si>
+  <si>
+    <t>下次更新日期：</t>
+  </si>
+  <si>
+    <t>股票代码：</t>
+  </si>
+  <si>
+    <t>市场价格：</t>
+  </si>
+  <si>
+    <t>市价货币：</t>
+  </si>
+  <si>
+    <t>市值：</t>
+  </si>
+  <si>
+    <t>外汇符号：</t>
+  </si>
+  <si>
+    <t>汇率：</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>指导说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>该模型使用结构化的投资流程来评估公司，确定其内在价值和目标价格。它关注可持续的自由现金流（FCF）能力，调整财务结构，纳入增长情景，并根据得出的内在价值计算预期回报。</t>
+    </r>
+  </si>
+  <si>
+    <t>估值概述</t>
+  </si>
+  <si>
+    <t>基础Equity Cost</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>量化业务持续生成的潜在自由现金流（FCFE），去除临时波动或会计选择的影响。</t>
+    </r>
+  </si>
+  <si>
+    <t>关键组成部分</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Normalized Operating EBIT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>：核心业务运营的税前息前利润，调整以剔除一次性或非经常性项目，形成可持续盈利基础。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Depreciation &amp; Amortization (D&amp;A):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 非现金费用，加入以反映运营产生的现金。
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Capital Expenditures (Capex)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>: 维持或扩展运营资产所需的现金流出。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Stable Non-Operating EBIT: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>来自非核心资产的持续收益，如固定收益投资、支付股息的股票或租赁物业。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Net Interest Income:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 利息收入减去利息支出</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>• NCI’s Share of Profits:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> NCI代表子公司中母公司未拥有的股权部分。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Working Capital Investment (WCInv):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> WCInv仅在显著扭曲FCFE时纳入。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关于净借款的说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>理论上，本金偿还通过净借款核算。然而，该模型旨在避免明确预测债务发行或偿还。相反，本金偿还通过有息债务在股权价值调整中反映。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>这一步骤通过纳入运营和稳定的非运营来源，同时考虑税金和再投资需求，确保现金流的全面衡量。</t>
+    </r>
+  </si>
+  <si>
+    <t>最新FCFE =</t>
+  </si>
+  <si>
+    <t>派息比率:</t>
+  </si>
+  <si>
+    <t>最新</t>
+  </si>
+  <si>
+    <t>步骤2：计算无增长基线（计算稳定收入价值）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>确定内在价值，假设当前的标准化FCFE保持不变且无增长，提供保守的基线。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 反映公司的风险概况，代表投资者为承担拥有此类业务一般风险所需的最低回报，而目标年回报率作为投资者要求的回报率。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Terminal Growth Rate:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 将g设为0%是一个保守假设，仅基于公司当前表现的盈利能力估值，不依赖潜在乐观的未来增长预测。</t>
+    </r>
+  </si>
+  <si>
+    <t>步骤3：调整财务结构（计算无增长股权价值）</t>
+  </si>
+  <si>
+    <t>目标：通过纳入公司的资产负债表结构，细化稳定收入价值（SIV）。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关于债务的说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>总有息债务包括本金偿还。理想情况下，应根据偿还时间表贴现。但为简单和保守起见，该模型使用总有息债务的账面价值。</t>
+    </r>
+  </si>
+  <si>
+    <t>说明：</t>
+  </si>
+  <si>
+    <t>杜邦分析</t>
+  </si>
+  <si>
+    <t>• Non-Operating Cash: 运营不需要的超额现金</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Other Non-Operating Assets:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 不贡献FCFE的资产（如非收益性投资或物业）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>无增长股权价值每股代表公司在考虑未来增长潜力前，基于当前可持续运营和净财务状况的内在价值估计，作为基本锚定的估值基线。</t>
+    </r>
+  </si>
+  <si>
+    <t>无增长股权价值每股 =</t>
+  </si>
+  <si>
+    <t>步骤4：纳入未来潜力（情景分析）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>通过建模合理的FCFE/股息、高增长期（HGP）和高增长率（HGR）情景，并按概率加权，估计内在价值。</t>
+    </r>
+  </si>
+  <si>
+    <t>情景</t>
+  </si>
+  <si>
+    <t>HGR</t>
+  </si>
+  <si>
+    <t>每股EV</t>
+  </si>
+  <si>
+    <t>概率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>分析市场大幅波动作为市场感知结果范围的指标，包括定义“雪球”或“魔鬼代言人”等情景边界的极端情况。情景分析使用基本推理评估这些情景的可能性。</t>
+    </r>
+  </si>
+  <si>
+    <t>步骤5：确定投资决策</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>将公司内在价值估计（来自步骤4）转化为满足特定投资要求的具体买入价格。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>计算逻辑：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">预期持有期 = </t>
+  </si>
+  <si>
+    <t>目标年回报率 =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每股年度股息 = </t>
+  </si>
+  <si>
+    <t>结果 (Target)</t>
+  </si>
+  <si>
+    <t>市场货币</t>
+  </si>
+  <si>
+    <t>@ 安全边际</t>
+  </si>
+  <si>
+    <r>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关注影响FCFE/股息可持续性的估值风险因素。</t>
+    </r>
+  </si>
+  <si>
+    <t>关键风险因素</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>标准化FCFE的准确性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>, 受不确定性影响，包括：</t>
+    </r>
+  </si>
+  <si>
+    <t>- 可持续收入和利润率</t>
+  </si>
+  <si>
+    <t>- 资本支出</t>
+  </si>
+  <si>
+    <t>- 营运资金</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity的适当性</t>
+    </r>
+  </si>
+  <si>
+    <t>作为资本配置的机会成本门槛。该模型在DCF/DDM分析中使用标准化的贴现率，计算内在价值。此利率作为最低可接受的长期回报门槛，反映长期无风险利率加上股权风险溢价。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>增长情景的可靠性</t>
+    </r>
+  </si>
+  <si>
+    <t>- 预期股权价值高度依赖各情景的特定增长率（HGR）、持续时间（HGP）和概率，这些是对不确定未来的预测。</t>
+  </si>
+  <si>
+    <t>- 极端情景（“雪球”、“魔鬼代言人”）概率较低；若市场条件剧变，可能变得比预期更相关。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>外部和公司特定风险</t>
+    </r>
+  </si>
+  <si>
+    <t>- 宏观经济敏感性</t>
+  </si>
+  <si>
+    <t>- 投入成本波动</t>
+  </si>
+  <si>
+    <t>- 激烈竞争等</t>
+  </si>
+  <si>
+    <t>Est. (Net Asset) Realizable Value</t>
+  </si>
+  <si>
+    <t>估计(净资产)可变现价值</t>
   </si>
 </sst>
 </file>
@@ -3148,7 +3955,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="370">
+  <cellXfs count="379">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3897,16 +4704,49 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="175" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3914,12 +4754,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4235,24 +5069,24 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C1" s="44">
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4266,7 +5100,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4275,15 +5109,15 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>313</v>
+        <v>466</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>440</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="C6" s="51">
         <v>20774311267</v>
@@ -4292,7 +5126,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>307</v>
+        <v>468</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4302,7 +5136,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>267</v>
+        <v>469</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4315,24 +5149,24 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>417</v>
+        <v>470</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="D11" s="49"/>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
-        <v>94</v>
+        <v>471</v>
       </c>
       <c r="C12" s="50">
         <v>22.7</v>
@@ -4342,17 +5176,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>416</v>
+        <v>472</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>420</v>
+        <v>473</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4366,7 +5200,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>419</v>
+        <v>474</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4380,7 +5214,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
-        <v>1</v>
+        <v>475</v>
       </c>
       <c r="C16" s="50">
         <v>1</v>
@@ -4393,46 +5227,46 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
-        <v>359</v>
-      </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="B18" s="371" t="s">
+        <v>476</v>
+      </c>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="D22" s="1" t="str">
-        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
-        <v>DDM Terminal Value</v>
+        <f>IF(valuation_method="DDM","Terminal Value Discount Rate","")</f>
+        <v>Terminal Value Discount Rate</v>
       </c>
       <c r="E22" s="313">
         <v>0.02</v>
@@ -4440,26 +5274,26 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4480,7 +5314,7 @@
         <v>14.723869312014129</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
@@ -4493,7 +5327,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4504,7 +5338,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4512,7 +5346,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
@@ -4523,7 +5357,7 @@
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="F29" s="302">
         <v>0.4</v>
@@ -4531,7 +5365,7 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
@@ -4542,7 +5376,7 @@
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="F30" s="312">
         <v>0.22</v>
@@ -4550,7 +5384,7 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
@@ -4561,7 +5395,7 @@
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="F31" s="312">
         <v>0.08</v>
@@ -4569,7 +5403,7 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
@@ -4580,7 +5414,7 @@
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="F32" s="312">
         <v>0.12</v>
@@ -4592,7 +5426,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4600,27 +5434,27 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
-        <v>360</v>
-      </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+    <row r="36" spans="1:6">
+      <c r="B36" s="371" t="s">
+        <v>477</v>
+      </c>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
-        <v>338</v>
-      </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="B37" s="374" t="s">
+        <v>332</v>
+      </c>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
@@ -4628,17 +5462,17 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
-        <v>230</v>
-      </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="B40" s="367" t="s">
+        <v>227</v>
+      </c>
+      <c r="C40" s="367"/>
+      <c r="D40" s="367"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4654,17 +5488,17 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
-        <v>232</v>
-      </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="B43" s="367" t="s">
+        <v>229</v>
+      </c>
+      <c r="C43" s="367"/>
+      <c r="D43" s="367"/>
+      <c r="E43" s="367"/>
+      <c r="F43" s="367"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4677,7 +5511,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4689,17 +5523,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
-        <v>235</v>
-      </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="B47" s="367" t="s">
+        <v>232</v>
+      </c>
+      <c r="C47" s="367"/>
+      <c r="D47" s="367"/>
+      <c r="E47" s="367"/>
+      <c r="F47" s="367"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4711,17 +5545,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
-        <v>239</v>
-      </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="B50" s="367" t="s">
+        <v>236</v>
+      </c>
+      <c r="C50" s="367"/>
+      <c r="D50" s="367"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4736,7 +5570,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4751,7 +5585,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4764,12 +5598,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4781,17 +5615,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
-        <v>240</v>
-      </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="B58" s="367" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="367"/>
+      <c r="D58" s="367"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4803,17 +5637,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
-        <v>337</v>
-      </c>
-      <c r="C61" s="362"/>
-      <c r="D61" s="362"/>
-      <c r="E61" s="362"/>
-      <c r="F61" s="362"/>
+      <c r="B61" s="367" t="s">
+        <v>331</v>
+      </c>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4825,26 +5659,26 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
-        <v>342</v>
-      </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="B64" s="371" t="s">
+        <v>336</v>
+      </c>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
-        <v>361</v>
-      </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="B65" s="371" t="s">
+        <v>351</v>
+      </c>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4857,7 +5691,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4870,7 +5704,7 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
@@ -4880,14 +5714,14 @@
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>462</v>
+        <v>442</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
         <v>4.6696035242290754E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -4896,18 +5730,18 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="C72" s="323" t="s">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="D72" s="323" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
@@ -4962,7 +5796,7 @@
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>355</v>
+        <v>478</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -4973,33 +5807,33 @@
     <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
-        <v>362</v>
-      </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="B80" s="371" t="s">
+        <v>479</v>
+      </c>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
-        <v>251</v>
-      </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="B81" s="374" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -5008,7 +5842,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5017,7 +5851,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5029,31 +5863,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
-        <v>363</v>
-      </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="B89" s="371" t="s">
+        <v>352</v>
+      </c>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
-        <v>364</v>
-      </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="B90" s="371" t="s">
+        <v>353</v>
+      </c>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5061,7 +5895,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5074,7 +5908,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5086,36 +5920,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
-        <v>365</v>
-      </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="B97" s="371" t="s">
+        <v>354</v>
+      </c>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
-        <v>343</v>
-      </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="B101" s="371" t="s">
+        <v>337</v>
+      </c>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5128,7 +5962,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5141,7 +5975,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5150,7 +5984,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5159,12 +5993,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5177,7 +6011,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5190,7 +6024,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5203,12 +6037,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5221,7 +6055,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5233,17 +6067,17 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
-        <v>366</v>
-      </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="B116" s="371" t="s">
+        <v>355</v>
+      </c>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>453</v>
+        <v>433</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5256,7 +6090,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>405</v>
+        <v>557</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5269,7 +6103,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>358</v>
+        <v>480</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5277,30 +6111,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
-        <v>367</v>
-      </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+    <row r="123" spans="1:6">
+      <c r="B123" s="367" t="s">
+        <v>481</v>
+      </c>
+      <c r="C123" s="367"/>
+      <c r="D123" s="367"/>
+      <c r="E123" s="367"/>
+      <c r="F123" s="367"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5415,7 +6249,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5427,17 +6261,17 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
-        <v>370</v>
-      </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="B134" s="369" t="s">
+        <v>482</v>
+      </c>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>402</v>
+        <v>483</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5446,31 +6280,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
-        <v>368</v>
-      </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
-        <v>369</v>
-      </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="B138" s="370" t="s">
+        <v>356</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="B139" s="371" t="s">
+        <v>484</v>
+      </c>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5479,7 +6313,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
@@ -5488,7 +6322,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
@@ -5501,7 +6335,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5514,7 +6348,7 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
@@ -5543,7 +6377,7 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
@@ -5556,7 +6390,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5569,7 +6403,7 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
@@ -5578,12 +6412,12 @@
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5612,7 +6446,7 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
@@ -5625,7 +6459,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5638,7 +6472,7 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
@@ -5647,12 +6481,12 @@
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>400</v>
+        <v>384</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5681,7 +6515,7 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>401</v>
+        <v>385</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
@@ -5694,7 +6528,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5707,7 +6541,7 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
@@ -5716,12 +6550,12 @@
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5750,7 +6584,7 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>401</v>
+        <v>385</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
@@ -5763,7 +6597,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5776,7 +6610,7 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
@@ -5785,7 +6619,7 @@
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5794,98 +6628,98 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
-        <v>376</v>
-      </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="B179" s="372" t="s">
+        <v>485</v>
+      </c>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="362" t="s">
-        <v>380</v>
-      </c>
-      <c r="C182" s="362"/>
-      <c r="D182" s="362"/>
-      <c r="E182" s="362"/>
-      <c r="F182" s="362"/>
+      <c r="B182" s="373" t="s">
+        <v>365</v>
+      </c>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
-        <v>381</v>
-      </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+        <v>368</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="34.35" customHeight="1">
+      <c r="B188" s="367" t="s">
+        <v>486</v>
+      </c>
+      <c r="C188" s="367"/>
+      <c r="D188" s="367"/>
+      <c r="E188" s="367"/>
+      <c r="F188" s="367"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
-        <v>382</v>
-      </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="B191" s="368" t="s">
+        <v>366</v>
+      </c>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
-        <v>383</v>
-      </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="B192" s="368" t="s">
+        <v>367</v>
+      </c>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -6006,7 +6840,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -6022,7 +6856,7 @@
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3" s="106">
         <v>1000000</v>
@@ -6030,7 +6864,7 @@
     </row>
     <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" s="351">
         <v>61890</v>
@@ -6048,7 +6882,7 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C5" s="351">
         <v>0</v>
@@ -6066,7 +6900,7 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C6" s="351">
         <v>62611</v>
@@ -6084,7 +6918,7 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7" s="352">
         <v>0</v>
@@ -6102,7 +6936,7 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C8" s="351">
         <v>0</v>
@@ -6120,7 +6954,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C9" s="351"/>
       <c r="D9" s="351"/>
@@ -6136,7 +6970,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6152,7 +6986,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6168,7 +7002,7 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" s="351">
         <v>195728</v>
@@ -6186,7 +7020,7 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" s="351">
         <v>343835</v>
@@ -6204,7 +7038,7 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C14" s="351">
         <v>9629</v>
@@ -6222,7 +7056,7 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" s="353">
         <v>77491</v>
@@ -6240,7 +7074,7 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" s="351">
         <v>286</v>
@@ -6258,13 +7092,13 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C19" s="351"/>
       <c r="D19" s="351"/>
@@ -6280,7 +7114,7 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C20" s="351"/>
       <c r="D20" s="351"/>
@@ -6296,7 +7130,7 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" s="351"/>
       <c r="D21" s="351"/>
@@ -6312,7 +7146,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="C22" s="351">
         <v>-237258</v>
@@ -6330,7 +7164,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="C23" s="351">
         <v>23438</v>
@@ -6348,7 +7182,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="C24" s="351">
         <v>194894</v>
@@ -6386,15 +7220,15 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C28" s="333">
         <f>BS!C4</f>
@@ -6413,7 +7247,7 @@
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C29" s="333">
         <f>BS!C6</f>
@@ -6432,7 +7266,7 @@
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C30" s="334">
         <f>BS!C33+BS!C42</f>
@@ -6451,7 +7285,7 @@
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C31" s="334">
         <f>BS!G27</f>
@@ -6470,7 +7304,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -6489,7 +7323,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -6505,12 +7339,12 @@
     </row>
     <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C36" s="333">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
@@ -6559,7 +7393,7 @@
     </row>
     <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C37" s="333">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -6608,7 +7442,7 @@
     </row>
     <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C38" s="329">
         <f>IF(C36="","",C36+C37)</f>
@@ -6657,7 +7491,7 @@
     </row>
     <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C39" s="333">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -6706,7 +7540,7 @@
     </row>
     <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C40" s="346">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -6755,7 +7589,7 @@
     </row>
     <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C41" s="346">
         <f>IF(C$4="","",C39-C40)</f>
@@ -6804,7 +7638,7 @@
     </row>
     <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C42" s="333">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -6853,7 +7687,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -6902,7 +7736,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -6951,7 +7785,7 @@
     </row>
     <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C45" s="349">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -7000,7 +7834,7 @@
     </row>
     <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C46" s="333">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -7049,7 +7883,7 @@
     </row>
     <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C47" s="334">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -7098,7 +7932,7 @@
     </row>
     <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C48" s="333">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -7147,12 +7981,12 @@
     </row>
     <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C51" s="333">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -7201,7 +8035,7 @@
     </row>
     <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C52" s="333">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -7250,12 +8084,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7304,7 +8138,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7353,7 +8187,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7402,7 +8236,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7451,13 +8285,13 @@
     </row>
     <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C61" s="333">
         <f>IF(C$4="","",-C19)</f>
@@ -7506,7 +8340,7 @@
     </row>
     <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C62" s="333">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
@@ -7555,7 +8389,7 @@
     </row>
     <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C63" s="333">
         <f>IF(C$4="","",-C21)</f>
@@ -7604,7 +8438,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7653,7 +8487,7 @@
     </row>
     <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
@@ -7702,7 +8536,7 @@
     </row>
     <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -7757,7 +8591,7 @@
     </row>
     <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C69" s="92" t="str">
         <f>IF(D$36="","",C38/D38-1)</f>
@@ -7856,7 +8690,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C71" s="101" t="str">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -7955,7 +8789,7 @@
     </row>
     <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -7971,13 +8805,13 @@
     </row>
     <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
     <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C76" s="76">
         <f>IF(C$4="","",C79+C80)</f>
@@ -8026,7 +8860,7 @@
     </row>
     <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C77" s="318">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
@@ -8060,7 +8894,7 @@
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C78" s="318">
         <f t="shared" si="40"/>
@@ -8094,7 +8928,7 @@
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C79" s="317">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
@@ -8143,7 +8977,7 @@
     </row>
     <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C80" s="317">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
@@ -8235,7 +9069,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C1" s="99">
         <v>45657</v>
@@ -8251,7 +9085,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8262,27 +9096,27 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D3" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H3" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="19">
         <v>0</v>
@@ -8292,7 +9126,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G4" s="19">
         <v>1</v>
@@ -8303,7 +9137,7 @@
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" s="19">
         <v>0</v>
@@ -8313,7 +9147,7 @@
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G5" s="19">
         <v>0</v>
@@ -8324,7 +9158,7 @@
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="19">
         <v>0</v>
@@ -8334,7 +9168,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8345,7 +9179,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C7" s="19">
         <v>0</v>
@@ -8355,7 +9189,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -8366,7 +9200,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8376,7 +9210,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8387,7 +9221,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" s="19">
         <v>1</v>
@@ -8397,7 +9231,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8408,7 +9242,7 @@
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" s="19">
         <v>0</v>
@@ -8420,7 +9254,7 @@
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C11" s="19">
         <v>0</v>
@@ -8432,7 +9266,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C12" s="81">
         <f>SUM(C4:C11)</f>
@@ -8443,7 +9277,7 @@
         <v>0.1</v>
       </c>
       <c r="F12" s="80" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G12" s="81">
         <f>SUM(G4:G9)</f>
@@ -8461,27 +9295,27 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="182" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" s="183" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="182" t="s">
-        <v>135</v>
-      </c>
-      <c r="D14" s="183" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>185</v>
-      </c>
       <c r="G14" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H14" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -8490,7 +9324,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G15" s="19">
         <v>1</v>
@@ -8501,7 +9335,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" s="19">
         <v>0</v>
@@ -8510,7 +9344,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8521,7 +9355,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C17" s="19">
         <v>0</v>
@@ -8530,7 +9364,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -8541,7 +9375,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8550,7 +9384,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8561,7 +9395,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="19">
         <v>1</v>
@@ -8570,7 +9404,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -8581,7 +9415,7 @@
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C20" s="19">
         <v>0</v>
@@ -8590,7 +9424,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -8601,7 +9435,7 @@
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" s="19">
         <v>0</v>
@@ -8610,7 +9444,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -8621,7 +9455,7 @@
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C22" s="19">
         <v>0</v>
@@ -8633,7 +9467,7 @@
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C23" s="19">
         <v>0</v>
@@ -8645,7 +9479,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C24" s="81">
         <f>SUM(C15:C23)</f>
@@ -8656,7 +9490,7 @@
         <v>0.1</v>
       </c>
       <c r="F24" s="80" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G24" s="81">
         <f>SUM(G15:G21)</f>
@@ -8669,30 +9503,30 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H26" s="186" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C27" s="19">
         <v>0</v>
       </c>
       <c r="F27" s="187" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G27" s="85">
         <f>G32-G30</f>
@@ -8705,13 +9539,13 @@
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C28" s="19">
         <v>0</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G28" s="12">
         <v>0</v>
@@ -8720,13 +9554,13 @@
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C29" s="19">
         <v>0</v>
       </c>
       <c r="F29" s="190" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -8739,13 +9573,13 @@
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C30" s="19">
         <v>0</v>
       </c>
       <c r="F30" s="187" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G30" s="85">
         <f>C33+C42</f>
@@ -8755,14 +9589,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
         <v>0</v>
       </c>
       <c r="F31" s="190" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G31" s="191">
         <f>C31+C40</f>
@@ -8772,14 +9606,14 @@
     </row>
     <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
         <v>1</v>
       </c>
       <c r="F32" s="192" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G32" s="193">
         <f>G35+G40</f>
@@ -8792,7 +9626,7 @@
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33" s="84">
         <v>1</v>
@@ -8805,24 +9639,24 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H34" s="198" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F35" s="199" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G35" s="193">
         <f>C12+C24</f>
@@ -8835,13 +9669,13 @@
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C36" s="19">
         <v>0</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -8851,13 +9685,13 @@
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C37" s="19">
         <v>0</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -8867,13 +9701,13 @@
     </row>
     <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C38" s="19">
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -8883,13 +9717,13 @@
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C39" s="19">
         <v>0</v>
       </c>
       <c r="F39" s="190" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G39" s="191">
         <f>C7+C17+C19+C20</f>
@@ -8902,14 +9736,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>0</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -8922,14 +9756,14 @@
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C41" s="21">
         <f>C42-C40</f>
         <v>0</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -8942,13 +9776,13 @@
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C42" s="84">
         <v>0</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -8961,7 +9795,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -8972,21 +9806,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="F45" s="256" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9018,20 +9852,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C49" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D49" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C50" s="95">
         <f>G31/Normalized_FCF!C8</f>
@@ -9045,7 +9879,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9059,19 +9893,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C53" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D53" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F53" s="253"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9085,7 +9919,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9102,19 +9936,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C57" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D57" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F57" s="253"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C58" s="98"/>
       <c r="D58" s="23">
@@ -9125,7 +9959,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C59" s="98"/>
       <c r="D59" s="92">
@@ -9139,19 +9973,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D61" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F61" s="253"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9162,12 +9996,12 @@
         <v>0</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9178,21 +10012,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F65" s="256" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9203,12 +10037,12 @@
         <v>0</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9218,7 +10052,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9228,7 +10062,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9238,7 +10072,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9251,19 +10085,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C72" s="234" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D72" s="182" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F72" s="253"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9274,12 +10108,12 @@
         <v>-7052.6474952516664</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9290,12 +10124,12 @@
         <v>2.8358144956862504E-4</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9303,12 +10137,12 @@
         <v>2</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9316,7 +10150,7 @@
         <v>2.8358144956862504E-4</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9324,19 +10158,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D78" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F78" s="253"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9350,7 +10184,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9364,7 +10198,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9378,7 +10212,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9392,7 +10226,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9403,15 +10237,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D85" s="241" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9428,7 +10262,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9445,7 +10279,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9462,7 +10296,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9510,7 +10344,7 @@
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -9563,12 +10397,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -9586,7 +10420,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
@@ -9600,7 +10434,7 @@
     <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" s="327">
         <f>AVERAGE(G4:J4)</f>
@@ -9657,7 +10491,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C5" s="328">
         <f>C25</f>
@@ -9712,7 +10546,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C6" s="329">
         <f>C4+C5</f>
@@ -9767,7 +10601,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C7" s="328">
         <f>C35</f>
@@ -9822,7 +10656,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -9879,7 +10713,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C9" s="328">
         <f>BS!$G$39*BS!D58</f>
@@ -9934,7 +10768,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C10" s="328">
         <f>-C4*C78</f>
@@ -9989,7 +10823,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10046,7 +10880,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C12" s="328">
         <f>C50</f>
@@ -10101,7 +10935,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10156,7 +10990,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -10211,7 +11045,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10268,7 +11102,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10325,7 +11159,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C17" s="328">
         <f>-C4*C85</f>
@@ -10333,7 +11167,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10351,14 +11185,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C18" s="328">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10376,7 +11210,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
@@ -10452,12 +11286,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -10475,7 +11309,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
@@ -10496,7 +11330,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C23" s="337">
         <f>-C4*C28</f>
@@ -10553,7 +11387,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C24" s="328">
         <f>-C4*C29</f>
@@ -10610,7 +11444,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C25" s="329">
         <f>C23+C24</f>
@@ -10671,14 +11505,14 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E27" s="268"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C28" s="63">
         <f>AVERAGE(G28:J28)</f>
@@ -10686,7 +11520,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10746,7 +11580,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10797,7 +11631,7 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C30" s="71">
         <f>ABS(C25/$C$4)</f>
@@ -10856,21 +11690,21 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E32" s="268"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C33" s="340">
         <f>AVERAGE(G33:J33)</f>
         <v>-62611</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -10920,7 +11754,7 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C34" s="340">
         <f>AVERAGE(G34:J34)</f>
@@ -10928,7 +11762,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -10979,7 +11813,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C35" s="329">
         <f>C33+C34</f>
@@ -11040,7 +11874,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11163,7 +11997,7 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C40" s="71">
         <f>ABS(C35/$C$4)</f>
@@ -11222,21 +12056,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11290,12 +12124,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -11313,14 +12147,14 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E46" s="268"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C47" s="328">
         <f>-BS!G31*Normalized_FCF!C54</f>
@@ -11375,7 +12209,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11430,7 +12264,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11487,7 +12321,7 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
@@ -11546,23 +12380,23 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C53" s="87">
         <v>0</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11582,14 +12416,14 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C54" s="82">
         <f>G54</f>
         <v>0</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11609,7 +12443,7 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C55" s="42" t="e">
         <f>-C8/C47</f>
@@ -11668,17 +12502,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -11733,7 +12567,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -11788,7 +12622,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -11843,7 +12677,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -11898,13 +12732,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -11954,7 +12788,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12013,17 +12847,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12048,7 +12882,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12073,7 +12907,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12098,7 +12932,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12128,12 +12962,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12151,7 +12985,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12172,7 +13006,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C73" s="77">
         <f>ABS(C5/C$4)</f>
@@ -12229,7 +13063,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C74" s="78">
         <f>ABS(C6/C$4)</f>
@@ -12286,7 +13120,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C75" s="77">
         <f>ABS(C7/C$4)</f>
@@ -12343,7 +13177,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12400,7 +13234,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C77" s="77">
         <f>ABS(C9/C$4)</f>
@@ -12457,7 +13291,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C78" s="88">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
@@ -12465,7 +13299,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12516,7 +13350,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12573,7 +13407,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
@@ -12630,7 +13464,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -12687,7 +13521,7 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
@@ -12802,7 +13636,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -12859,7 +13693,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C85" s="264">
         <v>0</v>
@@ -12885,7 +13719,7 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C86" s="77">
         <v>0</v>
@@ -12909,7 +13743,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -12970,7 +13804,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13089,7 +13923,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13144,7 +13978,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>461</v>
+        <v>441</v>
       </c>
       <c r="C93" s="356">
         <v>0</v>
@@ -13165,7 +13999,7 @@
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="2" t="s">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
@@ -13224,7 +14058,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="157" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C96" s="62"/>
       <c r="D96" s="27"/>
@@ -13245,7 +14079,7 @@
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="27" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C97" s="77">
         <f>C4/G4-1</f>
@@ -13302,7 +14136,7 @@
     <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
       <c r="B98" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
@@ -13362,12 +14196,12 @@
     <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="3"/>
       <c r="B100" s="54" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C100" s="54"/>
       <c r="D100" s="56"/>
       <c r="E100" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F100" s="56"/>
       <c r="G100" s="37"/>
@@ -13385,17 +14219,17 @@
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="64" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E101" s="268"/>
       <c r="G101" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="26" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C102" s="344">
         <f>BS!G32</f>
@@ -13452,7 +14286,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C103" s="345">
         <f>BS!C4</f>
@@ -13509,7 +14343,7 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="93" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C104" s="345">
         <f>BS!C6+BS!C7</f>
@@ -13566,7 +14400,7 @@
     <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C105" s="344">
         <f>BS!G30</f>
@@ -13623,7 +14457,7 @@
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C106" s="344">
         <f>BS!G27</f>
@@ -13684,14 +14518,14 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="91" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H108" s="12"/>
       <c r="I108" s="12"/>
@@ -13707,7 +14541,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
@@ -13764,7 +14598,7 @@
     <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C110" s="94">
         <f>C104/C$4</f>
@@ -13821,7 +14655,7 @@
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C111" s="94">
         <f>BS!$G$38/C$4</f>
@@ -13852,14 +14686,14 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="64" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E113" s="268"/>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
@@ -13911,7 +14745,7 @@
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="2" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="C115" s="169"/>
       <c r="E115" s="268"/>
@@ -13967,7 +14801,7 @@
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="91" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C117" s="55"/>
       <c r="D117" s="55"/>
@@ -14021,7 +14855,7 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="A118" s="10"/>
       <c r="B118" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
@@ -14075,7 +14909,7 @@
     </row>
     <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C119" s="42">
         <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
@@ -14129,7 +14963,7 @@
     </row>
     <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="B120" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C120" s="15">
         <f>C102/C106</f>
@@ -14186,7 +15020,7 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="70" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
@@ -14262,12 +15096,12 @@
     <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="54" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C123" s="54"/>
       <c r="D123" s="56"/>
       <c r="E123" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F123" s="56"/>
       <c r="G123" s="37"/>
@@ -14285,7 +15119,7 @@
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="178" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C124" s="179"/>
       <c r="D124" s="27"/>
@@ -14364,7 +15198,7 @@
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="A126" s="10"/>
       <c r="B126" s="27" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -14420,7 +15254,7 @@
     </row>
     <row r="127" spans="1:17" ht="15.75" customHeight="1">
       <c r="B127" s="2" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="C127" s="169"/>
       <c r="G127" s="23">
@@ -15182,32 +16016,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="130" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1000000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
@@ -15218,7 +16052,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F4" s="134">
         <f>Terminal_Growth</f>
@@ -15228,7 +16062,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -15239,7 +16073,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -15249,15 +16083,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="366" t="s">
-        <v>248</v>
-      </c>
-      <c r="F6" s="366"/>
+      <c r="E6" s="375" t="s">
+        <v>245</v>
+      </c>
+      <c r="F6" s="375"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
@@ -15267,13 +16101,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="366"/>
-      <c r="F7" s="366"/>
+      <c r="E7" s="375"/>
+      <c r="F7" s="375"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
@@ -15283,13 +16117,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="375"/>
+      <c r="F8" s="375"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
@@ -15299,13 +16133,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="375"/>
+      <c r="F9" s="375"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
@@ -15319,7 +16153,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
@@ -15333,7 +16167,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -15350,7 +16184,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15360,13 +16194,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H15" s="120"/>
     </row>
     <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
@@ -15376,7 +16210,7 @@
     </row>
     <row r="17" spans="2:17" ht="13.35" customHeight="1">
       <c r="B17" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
@@ -15386,7 +16220,7 @@
     </row>
     <row r="18" spans="2:17" ht="13.35" customHeight="1">
       <c r="B18" s="153" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
@@ -15403,19 +16237,19 @@
     </row>
     <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="128" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="128" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="128" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="129" t="s">
         <v>107</v>
-      </c>
-      <c r="C20" s="128" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" s="128" t="s">
-        <v>117</v>
-      </c>
-      <c r="E20" s="128" t="s">
-        <v>109</v>
-      </c>
-      <c r="F20" s="129" t="s">
-        <v>110</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -16181,7 +17015,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -16204,7 +17038,7 @@
     <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
@@ -16218,7 +17052,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C54" s="136"/>
       <c r="D54" s="136"/>
@@ -16439,7 +17273,7 @@
     </row>
     <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="114"/>
@@ -16668,19 +17502,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C73" s="171" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D73" s="171" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E73" s="172" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F73" s="172" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -16805,20 +17639,20 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C80" s="155" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="155" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" s="155" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="3:3">
@@ -16942,32 +17776,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="130" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1000000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
@@ -16978,7 +17812,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
@@ -16988,7 +17822,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -16999,7 +17833,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -17009,13 +17843,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="366"/>
-      <c r="F6" s="366"/>
+      <c r="E6" s="375"/>
+      <c r="F6" s="375"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -17032,7 +17866,7 @@
     </row>
     <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -17042,13 +17876,13 @@
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H10" s="120"/>
     </row>
     <row r="11" spans="2:8" ht="13.35" customHeight="1">
       <c r="B11" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
@@ -17058,7 +17892,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.35" customHeight="1">
       <c r="B12" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
@@ -17068,7 +17902,7 @@
     </row>
     <row r="13" spans="2:8" ht="13.35" customHeight="1">
       <c r="B13" s="153" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
@@ -17085,19 +17919,19 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="128" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E15" s="128" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -17763,7 +18597,7 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
@@ -17786,7 +18620,7 @@
     <row r="47" spans="2:8">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
@@ -17800,7 +18634,7 @@
     </row>
     <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C49" s="136"/>
       <c r="D49" s="136"/>
@@ -17971,7 +18805,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C58" s="114"/>
       <c r="D58" s="114"/>
@@ -18190,19 +19024,19 @@
     </row>
     <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C68" s="171" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D68" s="171" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E68" s="172" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F68" s="172" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -18327,20 +19161,20 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C75" s="155" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="C76" s="155" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="C77" s="155" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87" spans="3:3">
@@ -18391,20 +19225,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="I2" s="249"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H3" s="247">
         <v>0</v>
@@ -18416,14 +19250,14 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C4" s="120">
         <v>3</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="155" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F4" s="155"/>
       <c r="H4" s="247">
@@ -18445,14 +19279,14 @@
     </row>
     <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="159" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C6" s="107">
         <f>DCF!C3</f>
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="247">
@@ -18465,7 +19299,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C7" s="338">
         <f>Normalized_FCF!G8</f>
@@ -18475,11 +19309,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="368" t="str">
+      <c r="E7" s="377" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 兴业银行(601166.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="368"/>
+      <c r="F7" s="377"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18490,7 +19324,7 @@
     </row>
     <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
@@ -18500,8 +19334,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="368"/>
-      <c r="F8" s="368"/>
+      <c r="E8" s="377"/>
+      <c r="F8" s="377"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18512,7 +19346,7 @@
     </row>
     <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
@@ -18522,8 +19356,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="368"/>
-      <c r="F9" s="368"/>
+      <c r="E9" s="377"/>
+      <c r="F9" s="377"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18533,8 +19367,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="368"/>
-      <c r="F10" s="368"/>
+      <c r="E10" s="377"/>
+      <c r="F10" s="377"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18545,10 +19379,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>451</v>
-      </c>
-      <c r="E11" s="368"/>
-      <c r="F11" s="368"/>
+        <v>431</v>
+      </c>
+      <c r="E11" s="377"/>
+      <c r="F11" s="377"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18559,15 +19393,15 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C12" s="158" t="e">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="368"/>
-      <c r="F12" s="368"/>
+      <c r="E12" s="377"/>
+      <c r="F12" s="377"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18578,14 +19412,14 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C13" s="158" t="e">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E13" s="368"/>
-      <c r="F13" s="368"/>
+      <c r="E13" s="377"/>
+      <c r="F13" s="377"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18596,18 +19430,18 @@
     </row>
     <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="158" t="e">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E14" s="368"/>
-      <c r="F14" s="368"/>
+      <c r="E14" s="377"/>
+      <c r="F14" s="377"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -18616,38 +19450,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="368" t="s">
-        <v>329</v>
-      </c>
-      <c r="F18" s="369"/>
+      <c r="E18" s="377" t="s">
+        <v>323</v>
+      </c>
+      <c r="F18" s="378"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="369"/>
-      <c r="F19" s="369"/>
+      <c r="E19" s="378"/>
+      <c r="F19" s="378"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>303</v>
-      </c>
-      <c r="E20" s="369"/>
-      <c r="F20" s="369"/>
+        <v>299</v>
+      </c>
+      <c r="E20" s="378"/>
+      <c r="F20" s="378"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
@@ -18657,12 +19491,12 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="369"/>
-      <c r="F21" s="369"/>
+      <c r="E21" s="378"/>
+      <c r="F21" s="378"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -18672,44 +19506,44 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="369"/>
-      <c r="F22" s="369"/>
+      <c r="E22" s="378"/>
+      <c r="F22" s="378"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F24" s="159"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C25" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="367"/>
-      <c r="F25" s="367"/>
+      <c r="E25" s="376"/>
+      <c r="F25" s="376"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C26" s="164">
         <v>0.02</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="367"/>
-      <c r="F26" s="367"/>
+      <c r="E26" s="376"/>
+      <c r="F26" s="376"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
@@ -18719,55 +19553,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="367"/>
-      <c r="F27" s="367"/>
+      <c r="E27" s="376"/>
+      <c r="F27" s="376"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C28" s="165">
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="367"/>
-      <c r="F28" s="367"/>
+      <c r="E28" s="376"/>
+      <c r="F28" s="376"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E30" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F30" s="159"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C31" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="367"/>
-      <c r="F31" s="367"/>
+      <c r="E31" s="376"/>
+      <c r="F31" s="376"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C32" s="164">
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="367"/>
-      <c r="F32" s="367"/>
+      <c r="E32" s="376"/>
+      <c r="F32" s="376"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
@@ -18777,55 +19611,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="367"/>
-      <c r="F33" s="367"/>
+      <c r="E33" s="376"/>
+      <c r="F33" s="376"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C34" s="165">
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="367"/>
-      <c r="F34" s="367"/>
+      <c r="E34" s="376"/>
+      <c r="F34" s="376"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E36" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F36" s="159"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C37" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="367"/>
-      <c r="F37" s="367"/>
+      <c r="E37" s="376"/>
+      <c r="F37" s="376"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C38" s="164">
         <v>0.03</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="367"/>
-      <c r="F38" s="367"/>
+      <c r="E38" s="376"/>
+      <c r="F38" s="376"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
@@ -18835,24 +19669,24 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="367"/>
-      <c r="F39" s="367"/>
+      <c r="E39" s="376"/>
+      <c r="F39" s="376"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C40" s="167">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="E40" s="376"/>
+      <c r="F40" s="376"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -18865,7 +19699,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -18874,12 +19708,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C46" s="150">
         <v>10</v>
@@ -18894,39 +19728,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E48" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F48" s="159"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C49" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="367"/>
-      <c r="F49" s="367"/>
+      <c r="E49" s="376"/>
+      <c r="F49" s="376"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C50" s="164">
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="E50" s="376"/>
+      <c r="F50" s="376"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
@@ -18936,55 +19770,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="367"/>
-      <c r="F51" s="367"/>
+      <c r="E51" s="376"/>
+      <c r="F51" s="376"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C52" s="165">
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="367"/>
-      <c r="F52" s="367"/>
+      <c r="E52" s="376"/>
+      <c r="F52" s="376"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="E54" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F54" s="159"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C55" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="367"/>
-      <c r="F55" s="367"/>
+      <c r="E55" s="376"/>
+      <c r="F55" s="376"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C56" s="164">
         <v>0.04</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="367"/>
-      <c r="F56" s="367"/>
+      <c r="E56" s="376"/>
+      <c r="F56" s="376"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
@@ -18994,23 +19828,23 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="367"/>
-      <c r="F57" s="367"/>
+      <c r="E57" s="376"/>
+      <c r="F57" s="376"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C58" s="165">
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="E58" s="376"/>
+      <c r="F58" s="376"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -19021,7 +19855,7 @@
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19030,7 +19864,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19039,15 +19873,15 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
+        <v>300</v>
+      </c>
+      <c r="E63" s="252" t="s">
         <v>304</v>
-      </c>
-      <c r="E63" s="252" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C64" s="166">
         <f>C18</f>
@@ -19055,24 +19889,24 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C65" s="151">
         <v>2.3752619295331442E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
@@ -19083,20 +19917,20 @@
         <v>CNY</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19106,19 +19940,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19128,14 +19962,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19144,7 +19978,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -19153,12 +19987,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19168,7 +20002,7 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>463</v>
+        <v>443</v>
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
@@ -19181,12 +20015,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
@@ -19195,7 +20029,7 @@
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -19207,7 +20041,7 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
@@ -19217,7 +20051,7 @@
     </row>
     <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="110" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
@@ -19228,7 +20062,7 @@
         <v>CNY</v>
       </c>
       <c r="E83" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
@@ -19240,12 +20074,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19258,7 +20092,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -19270,12 +20104,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19284,7 +20118,7 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
@@ -19296,7 +20130,7 @@
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
@@ -19306,7 +20140,7 @@
     </row>
     <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="110" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
@@ -19317,7 +20151,7 @@
         <v>CNY</v>
       </c>
       <c r="E93" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
@@ -19326,14 +20160,14 @@
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19344,7 +20178,7 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
@@ -19356,7 +20190,7 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
@@ -19368,17 +20202,17 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
         <v>14.420004978927032</v>
       </c>
       <c r="D99" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="E99" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
@@ -19390,12 +20224,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19404,7 +20238,7 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
@@ -19414,7 +20248,7 @@
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
@@ -19424,17 +20258,17 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
         <v>13.026100491992562</v>
       </c>
       <c r="D105" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="E105" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
@@ -19446,32 +20280,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="F110" s="284" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -19502,7 +20336,7 @@
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -19511,4 +20345,1747 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA287911-AF8F-41DE-9E8E-72556F041FFB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J197"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <cols>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="B1" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C1" s="33">
+        <f>Thesis!C1</f>
+        <v>45797</v>
+      </c>
+      <c r="D1" s="358" t="str">
+        <f>Thesis!D1</f>
+        <v>INT</v>
+      </c>
+      <c r="E1" s="292" t="s">
+        <v>346</v>
+      </c>
+      <c r="F1" s="307" t="str">
+        <f>Thesis!F1</f>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.9">
+      <c r="A2" s="222" t="s">
+        <v>446</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" s="45" t="s">
+        <v>447</v>
+      </c>
+      <c r="C4" s="46"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="12.4">
+      <c r="B5" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C5" s="359" t="str">
+        <f>Thesis!C5</f>
+        <v>兴业银行</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C6" s="34">
+        <f>Common_Shares</f>
+        <v>20774311267</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C7" s="360">
+        <f>Thesis!C7</f>
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>448</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C11" s="365" t="str">
+        <f>Thesis!C11</f>
+        <v>601166.SS</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="C12" s="366">
+        <f>Market_Price</f>
+        <v>22.7</v>
+      </c>
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C13" s="32" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="C14" s="35">
+        <f>投资主题!C12*Common_Shares/1000000</f>
+        <v>471576.86576089996</v>
+      </c>
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
+        <v>CNY</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="C16" s="366">
+        <f>Exchange_Rate</f>
+        <v>1</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="371" t="s">
+        <v>497</v>
+      </c>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="45" t="s">
+        <v>498</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C21" s="32" t="str">
+        <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
+        <v xml:space="preserve">Low Growth </v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E21" s="363" t="str">
+        <f>valuation_method</f>
+        <v>DDM</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C22" s="32" t="str">
+        <f>Thesis!C22</f>
+        <v>FIN_01</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","终值贴现率","")</f>
+        <v>终值贴现率</v>
+      </c>
+      <c r="E22" s="364">
+        <f>Thesis!E22</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C23" s="253" t="str">
+        <f>Thesis!C23</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C24" s="253" t="str">
+        <f>Thesis!C24</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="C25" s="32" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D25" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E25" s="299" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"预期股权价值 ("&amp;C13&amp;") :"</f>
+        <v>预期股权价值 (CNY) :</v>
+      </c>
+      <c r="C26" s="304">
+        <f>C132</f>
+        <v>14.723869312014129</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="E26" s="301">
+        <f ca="1">Scenarios!C87</f>
+        <v>-8.0365599930497522E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>456</v>
+      </c>
+      <c r="C28" s="309" t="str">
+        <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>601166.SS (CNY)</v>
+      </c>
+      <c r="D28" s="309" t="str">
+        <f>IF(D11="","",D145&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="305" t="s">
+        <v>461</v>
+      </c>
+      <c r="F28" s="361">
+        <f>Thesis!F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C29" s="310">
+        <f>C149</f>
+        <v>7.0500981457777456</v>
+      </c>
+      <c r="D29" s="310" t="str">
+        <f>D149</f>
+        <v/>
+      </c>
+      <c r="E29" s="306" t="s">
+        <v>463</v>
+      </c>
+      <c r="F29" s="362">
+        <f>Thesis!F29</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C30" s="311">
+        <f>C157</f>
+        <v>10.273312145077192</v>
+      </c>
+      <c r="D30" s="311" t="str">
+        <f>D157</f>
+        <v/>
+      </c>
+      <c r="E30" s="307" t="s">
+        <v>462</v>
+      </c>
+      <c r="F30" s="224">
+        <f>Thesis!F30</f>
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C31" s="311">
+        <f>C165</f>
+        <v>14.420004978927032</v>
+      </c>
+      <c r="D31" s="311" t="str">
+        <f>D165</f>
+        <v/>
+      </c>
+      <c r="E31" s="307" t="s">
+        <v>499</v>
+      </c>
+      <c r="F31" s="224">
+        <f>Thesis!F31</f>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C32" s="311">
+        <f>C173</f>
+        <v>13.026100491992562</v>
+      </c>
+      <c r="D32" s="311" t="str">
+        <f>D173</f>
+        <v/>
+      </c>
+      <c r="E32" s="307" t="s">
+        <v>464</v>
+      </c>
+      <c r="F32" s="224">
+        <f>Thesis!F32</f>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="222" t="s">
+        <v>465</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="371" t="s">
+        <v>500</v>
+      </c>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="374" t="s">
+        <v>332</v>
+      </c>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="210" t="s">
+        <v>501</v>
+      </c>
+      <c r="C39" s="108">
+        <f>scaling_factor</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="B40" s="367" t="s">
+        <v>502</v>
+      </c>
+      <c r="C40" s="367"/>
+      <c r="D40" s="367"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" s="349">
+        <f>Normalized_FCF!C8</f>
+        <v>-721</v>
+      </c>
+      <c r="D41" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="367" t="s">
+        <v>503</v>
+      </c>
+      <c r="C43" s="367"/>
+      <c r="D43" s="367"/>
+      <c r="E43" s="367"/>
+      <c r="F43" s="367"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="C44" s="349">
+        <f>Normalized_FCF!C9</f>
+        <v>0</v>
+      </c>
+      <c r="D44" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="C45" s="349">
+        <f>Normalized_FCF!C10</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="367" t="s">
+        <v>504</v>
+      </c>
+      <c r="C47" s="367"/>
+      <c r="D47" s="367"/>
+      <c r="E47" s="367"/>
+      <c r="F47" s="367"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="C48" s="349">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="367" t="s">
+        <v>505</v>
+      </c>
+      <c r="C50" s="367"/>
+      <c r="D50" s="367"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>333</v>
+      </c>
+      <c r="C51" s="350">
+        <f>Normalized_FCF!C48</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E51" s="286"/>
+      <c r="F51" s="286"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>334</v>
+      </c>
+      <c r="C52" s="350">
+        <f>Normalized_FCF!C47</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E52" s="286"/>
+      <c r="F52" s="286"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53" s="349">
+        <f>Normalized_FCF!C12</f>
+        <v>0</v>
+      </c>
+      <c r="D53" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56" s="349">
+        <f>Normalized_FCF!C15</f>
+        <v>0</v>
+      </c>
+      <c r="D56" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="367" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="367"/>
+      <c r="D58" s="367"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="C59" s="349">
+        <f>Normalized_FCF!C14</f>
+        <v>180.25</v>
+      </c>
+      <c r="D59" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="367" t="s">
+        <v>507</v>
+      </c>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C62" s="349">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
+      <c r="B64" s="371" t="s">
+        <v>508</v>
+      </c>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="B65" s="371" t="s">
+        <v>509</v>
+      </c>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>510</v>
+      </c>
+      <c r="C67" s="349">
+        <f>Normalized_FCF!G19</f>
+        <v>-206364</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="C68" s="349">
+        <f>Normalized_FCF!C19</f>
+        <v>-540.75</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="227" t="s">
+        <v>374</v>
+      </c>
+      <c r="C69" s="92">
+        <f>Normalized_FCF!C126</f>
+        <v>-1.1466847491076299E-3</v>
+      </c>
+      <c r="F69" s="314"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="B70" s="227" t="s">
+        <v>442</v>
+      </c>
+      <c r="C70" s="92">
+        <f>Normalized_FCF!C94</f>
+        <v>4.6696035242290754E-2</v>
+      </c>
+      <c r="E70" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="F70" s="315">
+        <f>Normalized_FCF!C92</f>
+        <v>-40.722644369893672</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="B72" s="210" t="s">
+        <v>521</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>437</v>
+      </c>
+      <c r="D72" s="323" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73" s="47" t="s">
+        <v>436</v>
+      </c>
+      <c r="C73" s="92">
+        <f>Normalized_FCF!C121</f>
+        <v>-240.33333333333334</v>
+      </c>
+      <c r="D73" s="92">
+        <f>Normalized_FCF!G121</f>
+        <v>-65483</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="259" t="str">
+        <f>Normalized_FCF!B118</f>
+        <v>Pre-tax Profit/Sales</v>
+      </c>
+      <c r="C74" s="322">
+        <f>Normalized_FCF!C118</f>
+        <v>-1.1649701082565843E-2</v>
+      </c>
+      <c r="D74" s="322">
+        <f>Normalized_FCF!G118</f>
+        <v>1.4678118322150659</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="259" t="str">
+        <f>Normalized_FCF!B119</f>
+        <v>Sales/Total Assets</v>
+      </c>
+      <c r="C75" s="324">
+        <f>Normalized_FCF!C119</f>
+        <v>15472.5</v>
+      </c>
+      <c r="D75" s="324">
+        <f>Normalized_FCF!G119</f>
+        <v>-33459.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="B76" s="259" t="str">
+        <f>Normalized_FCF!B120</f>
+        <v>Total Assets/Equity</v>
+      </c>
+      <c r="C76" s="324">
+        <f>Normalized_FCF!C120</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="D76" s="324">
+        <f>Normalized_FCF!G120</f>
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="13.9">
+      <c r="A78" s="222" t="s">
+        <v>513</v>
+      </c>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="209"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="17"/>
+      <c r="B80" s="371" t="s">
+        <v>514</v>
+      </c>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="374" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="B83" s="210" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="B84" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C84" s="92">
+        <f>F31</f>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="B85" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C85" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="80" t="s">
+        <v>243</v>
+      </c>
+      <c r="C86" s="236">
+        <f>F31+C85</f>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="C87" s="121"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="B88" s="293" t="s">
+        <v>520</v>
+      </c>
+      <c r="C88" s="121"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="B89" s="371" t="s">
+        <v>515</v>
+      </c>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="B90" s="371" t="s">
+        <v>516</v>
+      </c>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="C92" s="236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="B93" s="47" t="s">
+        <v>275</v>
+      </c>
+      <c r="C93" s="223">
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>-0.32537179755928991</v>
+      </c>
+      <c r="D93" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="13.9">
+      <c r="A95" s="222" t="s">
+        <v>517</v>
+      </c>
+      <c r="B95" s="36"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="36"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="209"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="371" t="s">
+        <v>518</v>
+      </c>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6">
+      <c r="B100" s="210" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6">
+      <c r="B101" s="371" t="s">
+        <v>519</v>
+      </c>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
+    </row>
+    <row r="102" spans="2:6">
+      <c r="B102" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="C102" s="349">
+        <f>DCF!C7</f>
+        <v>0</v>
+      </c>
+      <c r="D102" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
+        <v>276</v>
+      </c>
+      <c r="C103" s="223">
+        <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0</v>
+      </c>
+      <c r="D103" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6">
+      <c r="B104" s="296" t="s">
+        <v>387</v>
+      </c>
+      <c r="C104" s="325">
+        <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="296" t="s">
+        <v>389</v>
+      </c>
+      <c r="C105" s="326">
+        <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="C108" s="349">
+        <f>BS!C66</f>
+        <v>2</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="C109" s="349">
+        <f>DCF!C8</f>
+        <v>0</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6">
+      <c r="B110" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="C110" s="223">
+        <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0</v>
+      </c>
+      <c r="D110" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6">
+      <c r="B112" s="1" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" s="349">
+        <f>DCF!C9</f>
+        <v>0</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="C114" s="223">
+        <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="B116" s="371" t="s">
+        <v>524</v>
+      </c>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="B118" s="47" t="s">
+        <v>525</v>
+      </c>
+      <c r="C118" s="223">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
+        <v>13.25</v>
+      </c>
+      <c r="D118" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="B119" s="296" t="s">
+        <v>558</v>
+      </c>
+      <c r="C119" s="223">
+        <f>BS!D47</f>
+        <v>4.3322735874745961E-5</v>
+      </c>
+      <c r="D119" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
+      <c r="A121" s="222" t="s">
+        <v>526</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="B123" s="367" t="s">
+        <v>527</v>
+      </c>
+      <c r="C123" s="367"/>
+      <c r="D123" s="367"/>
+      <c r="E123" s="367"/>
+      <c r="F123" s="367"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
+      <c r="B125" s="233" t="s">
+        <v>528</v>
+      </c>
+      <c r="C125" s="233" t="s">
+        <v>529</v>
+      </c>
+      <c r="D125" s="233" t="s">
+        <v>108</v>
+      </c>
+      <c r="E125" s="233" t="s">
+        <v>530</v>
+      </c>
+      <c r="F125" s="233" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="B126" s="228" t="str">
+        <f>DCF!B74</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C126" s="229">
+        <f>DCF!C74</f>
+        <v>0.04</v>
+      </c>
+      <c r="D126" s="230">
+        <f>DCF!D74</f>
+        <v>10</v>
+      </c>
+      <c r="E126" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
+        <v>16.44 CNY</v>
+      </c>
+      <c r="F126" s="232">
+        <f>DCF!F74</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="B127" s="218" t="str">
+        <f>DCF!B75</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C127" s="219">
+        <f>DCF!C75</f>
+        <v>0.03</v>
+      </c>
+      <c r="D127" s="220">
+        <f>DCF!D75</f>
+        <v>5</v>
+      </c>
+      <c r="E127" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
+        <v>14.86 CNY</v>
+      </c>
+      <c r="F127" s="221">
+        <f>DCF!F75</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="218" t="str">
+        <f>DCF!B76</f>
+        <v>Base</v>
+      </c>
+      <c r="C128" s="219">
+        <f>DCF!C76</f>
+        <v>0.02</v>
+      </c>
+      <c r="D128" s="220">
+        <f>DCF!D76</f>
+        <v>5</v>
+      </c>
+      <c r="E128" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
+        <v>14.63 CNY</v>
+      </c>
+      <c r="F128" s="221">
+        <f>DCF!F76</f>
+        <v>0.53999999999999992</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="B129" s="218" t="str">
+        <f>DCF!B77</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C129" s="219">
+        <f>DCF!C77</f>
+        <v>0.01</v>
+      </c>
+      <c r="D129" s="220">
+        <f>DCF!D77</f>
+        <v>5</v>
+      </c>
+      <c r="E129" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
+        <v>14.41 CNY</v>
+      </c>
+      <c r="F129" s="221">
+        <f>DCF!F77</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="B130" s="218" t="str">
+        <f>DCF!B78</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C130" s="219">
+        <f>DCF!C78</f>
+        <v>0</v>
+      </c>
+      <c r="D130" s="220">
+        <f>DCF!D78</f>
+        <v>10</v>
+      </c>
+      <c r="E130" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
+        <v>14.59 CNY</v>
+      </c>
+      <c r="F130" s="221">
+        <f>DCF!F78</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="211" t="s">
+        <v>254</v>
+      </c>
+      <c r="C132" s="217">
+        <f>Scenarios!C60</f>
+        <v>14.723869312014129</v>
+      </c>
+      <c r="D132" s="212" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="B134" s="369" t="s">
+        <v>532</v>
+      </c>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
+      <c r="A136" s="222" t="s">
+        <v>533</v>
+      </c>
+      <c r="B136" s="36"/>
+      <c r="C136" s="36"/>
+      <c r="D136" s="36"/>
+      <c r="E136" s="36"/>
+      <c r="F136" s="36"/>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="B138" s="370" t="s">
+        <v>534</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="371" t="s">
+        <v>535</v>
+      </c>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="B140" s="210" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C141" s="225">
+        <f>F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="B142" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C142" s="224">
+        <f>F29</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="B143" s="212" t="s">
+        <v>538</v>
+      </c>
+      <c r="C143" s="213">
+        <f>Scenarios!C77</f>
+        <v>1.06</v>
+      </c>
+      <c r="D143" s="212" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="210" t="s">
+        <v>539</v>
+      </c>
+      <c r="C145" s="241" t="str">
+        <f>C11</f>
+        <v>601166.SS</v>
+      </c>
+      <c r="D145" s="241" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C146" s="297">
+        <f>F29</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="B147" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C147" s="216">
+        <f>Scenarios!C81</f>
+        <v>1.6842565597667636</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="B148" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C148" s="216">
+        <f>Scenarios!C82</f>
+        <v>5.3658415860109816</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C149" s="215">
+        <f>Scenarios!C83</f>
+        <v>7.0500981457777456</v>
+      </c>
+      <c r="D149" s="300" t="str">
+        <f>IF($D$11="","",C149*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" s="259" t="s">
+        <v>540</v>
+      </c>
+      <c r="C150" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D150" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="B151" s="214" t="s">
+        <v>541</v>
+      </c>
+      <c r="C151" s="92">
+        <f>Scenarios!F83</f>
+        <v>0.52117897840718208</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="210" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C154" s="297">
+        <f>Scenarios!C90</f>
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C155" s="216">
+        <f>Scenarios!C91</f>
+        <v>2.1647759063533951</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C156" s="216">
+        <f>Scenarios!C92</f>
+        <v>8.1085362387237971</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C157" s="215">
+        <f>Scenarios!C93</f>
+        <v>10.273312145077192</v>
+      </c>
+      <c r="D157" s="300" t="str">
+        <f>IF($D$11="","",C157*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" s="259" t="s">
+        <v>540</v>
+      </c>
+      <c r="C158" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D158" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="214" t="s">
+        <v>541</v>
+      </c>
+      <c r="C159" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.30226817914673065</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" s="210" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="B162" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C162" s="92">
+        <f>Scenarios!C96</f>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C163" s="216">
+        <f>Scenarios!C97</f>
+        <v>2.731722806482753</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="B164" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C164" s="216">
+        <f>Scenarios!C98</f>
+        <v>11.688282172444278</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165" s="80" t="s">
+        <v>385</v>
+      </c>
+      <c r="C165" s="215">
+        <f>Scenarios!C99</f>
+        <v>14.420004978927032</v>
+      </c>
+      <c r="D165" s="300" t="str">
+        <f>IF($D$11="","",C165*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" s="259" t="s">
+        <v>540</v>
+      </c>
+      <c r="C166" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D166" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" s="214" t="s">
+        <v>541</v>
+      </c>
+      <c r="C167" s="92">
+        <f>Scenarios!F99</f>
+        <v>2.0637532611020526E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169" s="210" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C170" s="92">
+        <f>F32</f>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="B171" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C171" s="216">
+        <f>Scenarios!C103</f>
+        <v>2.5459411443148712</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="B172" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C172" s="216">
+        <f>Scenarios!C104</f>
+        <v>10.480159347677692</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" s="80" t="s">
+        <v>385</v>
+      </c>
+      <c r="C173" s="215">
+        <f>Scenarios!C105</f>
+        <v>13.026100491992562</v>
+      </c>
+      <c r="D173" s="300" t="str">
+        <f>IF($D$11="","",C173*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="B174" s="259" t="s">
+        <v>540</v>
+      </c>
+      <c r="C174" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D174" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" s="214" t="s">
+        <v>541</v>
+      </c>
+      <c r="C175" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.11507499641644758</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="13.9">
+      <c r="A177" s="222" t="s">
+        <v>360</v>
+      </c>
+      <c r="B177" s="36"/>
+      <c r="C177" s="36"/>
+      <c r="D177" s="36"/>
+      <c r="E177" s="36"/>
+      <c r="F177" s="36"/>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="B179" s="372" t="s">
+        <v>542</v>
+      </c>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="B181" s="210" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="B182" s="373" t="s">
+        <v>544</v>
+      </c>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="B183" s="214" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="B184" s="214" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="B185" s="214" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="B187" s="1" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B188" s="367" t="s">
+        <v>549</v>
+      </c>
+      <c r="C188" s="367"/>
+      <c r="D188" s="367"/>
+      <c r="E188" s="367"/>
+      <c r="F188" s="367"/>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="B190" s="1" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="B191" s="368" t="s">
+        <v>551</v>
+      </c>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="B192" s="368" t="s">
+        <v>552</v>
+      </c>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" s="214" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" s="214" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="214" t="s">
+        <v>556</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B116:F116"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
+      <formula1>"INT,CN"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{0BE1D34E-D50B-41CB-99F3-E9F8694C38CA}">
+      <formula1>"DCF,DDM"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{4F076B80-6574-480B-B48C-99BFFF6B4B13}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{B605A743-B0FC-4D89-AD54-945707F01FA1}">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{CF966412-2762-45A3-9589-2A9D9DD6B905}">
+      <formula1>"Y, N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
+</worksheet>
 </file>